--- a/InOrders_latest.xlsx
+++ b/InOrders_latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
   <si>
     <t>Status</t>
   </si>
@@ -85,12 +85,48 @@
     <t>Updated</t>
   </si>
   <si>
-    <t>Arrival space</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
+    <t>0101857485</t>
+  </si>
+  <si>
+    <t>Truck 58</t>
+  </si>
+  <si>
+    <t>0101851677</t>
+  </si>
+  <si>
+    <t>Truck 55</t>
+  </si>
+  <si>
+    <t>0101865821</t>
+  </si>
+  <si>
+    <t>Truck 61</t>
+  </si>
+  <si>
+    <t>Notified</t>
+  </si>
+  <si>
+    <t>0101878091</t>
+  </si>
+  <si>
+    <t>Truck 68</t>
+  </si>
+  <si>
+    <t>0101878078</t>
+  </si>
+  <si>
+    <t>Truck 67</t>
+  </si>
+  <si>
+    <t>0101878070</t>
+  </si>
+  <si>
+    <t>Truck 66</t>
+  </si>
+  <si>
     <t>0101873444</t>
   </si>
   <si>
@@ -109,67 +145,35 @@
     <t>Truck 64</t>
   </si>
   <si>
-    <t>0101865821</t>
-  </si>
-  <si>
-    <t>Truck 61</t>
-  </si>
-  <si>
-    <t>0101857485</t>
-  </si>
-  <si>
-    <t>Truck 58</t>
-  </si>
-  <si>
-    <t>0101851677</t>
-  </si>
-  <si>
-    <t>Truck 55</t>
-  </si>
-  <si>
-    <t>Notified</t>
-  </si>
-  <si>
-    <t>0101878091</t>
-  </si>
-  <si>
-    <t>Truck 68</t>
-  </si>
-  <si>
-    <t>0101850638</t>
-  </si>
-  <si>
-    <t>Truck 54</t>
-  </si>
-  <si>
-    <t>JohannesUPSStockUP</t>
-  </si>
-  <si>
-    <t>Johannes_Prod_Test_UPS_StockUP</t>
+    <t>0101847437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truck 53
+</t>
+  </si>
+  <si>
+    <t>0101861223</t>
+  </si>
+  <si>
+    <t>Truck 60</t>
+  </si>
+  <si>
+    <t>0101857514</t>
+  </si>
+  <si>
+    <t>Truck 59</t>
+  </si>
+  <si>
+    <t>0101867048</t>
+  </si>
+  <si>
+    <t>Truck 63</t>
   </si>
   <si>
     <t>0101865832</t>
   </si>
   <si>
     <t>Truck 62</t>
-  </si>
-  <si>
-    <t>0101867048</t>
-  </si>
-  <si>
-    <t>Truck 63</t>
-  </si>
-  <si>
-    <t>0101861223</t>
-  </si>
-  <si>
-    <t>Truck 60</t>
-  </si>
-  <si>
-    <t>0101857514</t>
-  </si>
-  <si>
-    <t>Truck 59</t>
   </si>
   <si>
     <t>0101856191</t>
@@ -179,87 +183,6 @@
 </t>
   </si>
   <si>
-    <t>520063571300100</t>
-  </si>
-  <si>
-    <t>2026-05-22 | Gelişim Tekstil | ASN-GTK-001</t>
-  </si>
-  <si>
-    <t>520063571200100</t>
-  </si>
-  <si>
-    <t>520063571600100</t>
-  </si>
-  <si>
-    <t>520063571100100</t>
-  </si>
-  <si>
-    <t>520064225200100</t>
-  </si>
-  <si>
-    <t>520064227400100</t>
-  </si>
-  <si>
-    <t>520064225500100</t>
-  </si>
-  <si>
-    <t>520064226900100</t>
-  </si>
-  <si>
-    <t>520064227000100</t>
-  </si>
-  <si>
-    <t>520064226800100</t>
-  </si>
-  <si>
-    <t>520064226600100</t>
-  </si>
-  <si>
-    <t>520063570500100</t>
-  </si>
-  <si>
-    <t>520064225900100</t>
-  </si>
-  <si>
-    <t>520064224800100</t>
-  </si>
-  <si>
-    <t>520064225000100</t>
-  </si>
-  <si>
-    <t>520064224900100</t>
-  </si>
-  <si>
-    <t>520064227300100</t>
-  </si>
-  <si>
-    <t>520064227100100</t>
-  </si>
-  <si>
-    <t>520064226700100</t>
-  </si>
-  <si>
-    <t>520064225800100</t>
-  </si>
-  <si>
-    <t>520063571000100</t>
-  </si>
-  <si>
-    <t>520064226500100</t>
-  </si>
-  <si>
-    <t>520063570300100</t>
-  </si>
-  <si>
-    <t>520064225300100</t>
-  </si>
-  <si>
-    <t>520063570600100</t>
-  </si>
-  <si>
-    <t>520064225100100</t>
-  </si>
-  <si>
     <t>0101856108</t>
   </si>
   <si>
@@ -267,53 +190,95 @@
 </t>
   </si>
   <si>
-    <t>0101847437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truck 53
+    <t>0101850638</t>
+  </si>
+  <si>
+    <t>Truck 54</t>
+  </si>
+  <si>
+    <t>0101843290</t>
+  </si>
+  <si>
+    <t>Truck 52</t>
+  </si>
+  <si>
+    <t>0101843289</t>
+  </si>
+  <si>
+    <t>Truck 51</t>
+  </si>
+  <si>
+    <t>0101819595</t>
+  </si>
+  <si>
+    <t>Truck 45_2</t>
+  </si>
+  <si>
+    <t>0101819592</t>
+  </si>
+  <si>
+    <t>Truck 45_1</t>
+  </si>
+  <si>
+    <t>0101807477</t>
+  </si>
+  <si>
+    <t>Truck 41</t>
+  </si>
+  <si>
+    <t>0101811225</t>
+  </si>
+  <si>
+    <t>Truck 42</t>
+  </si>
+  <si>
+    <t>0101803752</t>
+  </si>
+  <si>
+    <t>Truck 38</t>
+  </si>
+  <si>
+    <t>0101835438</t>
+  </si>
+  <si>
+    <t>Truck 50_1</t>
+  </si>
+  <si>
+    <t>0101833617</t>
+  </si>
+  <si>
+    <t>Truck50_2</t>
+  </si>
+  <si>
+    <t>0101828861</t>
+  </si>
+  <si>
+    <t>Truck 47</t>
+  </si>
+  <si>
+    <t>0101833616</t>
+  </si>
+  <si>
+    <t>Truck 49</t>
+  </si>
+  <si>
+    <t>0101803882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truck 40
 </t>
   </si>
   <si>
-    <t>0101843290</t>
-  </si>
-  <si>
-    <t>Truck 52</t>
-  </si>
-  <si>
-    <t>0101843289</t>
-  </si>
-  <si>
-    <t>Truck 51</t>
-  </si>
-  <si>
-    <t>0101835438</t>
-  </si>
-  <si>
-    <t>Truck 50_1</t>
-  </si>
-  <si>
-    <t>0101833617</t>
-  </si>
-  <si>
-    <t>Truck50_2</t>
-  </si>
-  <si>
-    <t>0101833616</t>
-  </si>
-  <si>
-    <t>Truck 49</t>
-  </si>
-  <si>
-    <t>0101829631</t>
-  </si>
-  <si>
-    <t>Truck 48</t>
-  </si>
-  <si>
-    <t>0101828861</t>
-  </si>
-  <si>
-    <t>Truck 47</t>
+    <t>0101787704</t>
+  </si>
+  <si>
+    <t>Truck 35</t>
+  </si>
+  <si>
+    <t>0101786095</t>
+  </si>
+  <si>
+    <t>truck31</t>
   </si>
   <si>
     <t>0101822294</t>
@@ -326,12 +291,6 @@
   </si>
   <si>
     <t>Truck46_2</t>
-  </si>
-  <si>
-    <t>0101814762</t>
-  </si>
-  <si>
-    <t>Truck 44</t>
   </si>
   <si>
     <t>0101811564</t>
@@ -341,35 +300,40 @@
 </t>
   </si>
   <si>
-    <t>0101819592</t>
-  </si>
-  <si>
-    <t>Truck 45_1</t>
-  </si>
-  <si>
-    <t>0101819595</t>
-  </si>
-  <si>
-    <t>Truck 45_2</t>
-  </si>
-  <si>
-    <t>0101807477</t>
-  </si>
-  <si>
-    <t>Truck 41</t>
-  </si>
-  <si>
-    <t>0101811225</t>
-  </si>
-  <si>
-    <t>Truck 42</t>
-  </si>
-  <si>
-    <t>0101803882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truck 40
-</t>
+    <t>0101829631</t>
+  </si>
+  <si>
+    <t>Truck 48</t>
+  </si>
+  <si>
+    <t>0101814762</t>
+  </si>
+  <si>
+    <t>Truck 44</t>
+  </si>
+  <si>
+    <t>0101791647</t>
+  </si>
+  <si>
+    <t>Truck 37</t>
+  </si>
+  <si>
+    <t>0101783775</t>
+  </si>
+  <si>
+    <t>truck29_1</t>
+  </si>
+  <si>
+    <t>0101781187</t>
+  </si>
+  <si>
+    <t>truck28</t>
+  </si>
+  <si>
+    <t>0101780369</t>
+  </si>
+  <si>
+    <t>truck 25_1</t>
   </si>
   <si>
     <t>0101803799</t>
@@ -378,88 +342,52 @@
     <t>Truck 39</t>
   </si>
   <si>
-    <t>0101791647</t>
-  </si>
-  <si>
-    <t>Truck 37</t>
-  </si>
-  <si>
-    <t>0101803752</t>
-  </si>
-  <si>
-    <t>Truck 38</t>
-  </si>
-  <si>
     <t>0101791598</t>
   </si>
   <si>
     <t>Truck 36</t>
   </si>
   <si>
+    <t>0101787699</t>
+  </si>
+  <si>
+    <t>Truck 33</t>
+  </si>
+  <si>
+    <t>0101783855</t>
+  </si>
+  <si>
+    <t>truck32_1</t>
+  </si>
+  <si>
+    <t>0101783934</t>
+  </si>
+  <si>
+    <t>truck32_2</t>
+  </si>
+  <si>
     <t>0101788940</t>
   </si>
   <si>
     <t>Truck 34</t>
   </si>
   <si>
-    <t>0101787699</t>
-  </si>
-  <si>
-    <t>Truck 33</t>
-  </si>
-  <si>
-    <t>0101787704</t>
-  </si>
-  <si>
-    <t>Truck 35</t>
-  </si>
-  <si>
-    <t>0101783934</t>
-  </si>
-  <si>
-    <t>truck32_2</t>
-  </si>
-  <si>
-    <t>0101783855</t>
-  </si>
-  <si>
-    <t>truck32_1</t>
-  </si>
-  <si>
     <t>0101784196</t>
   </si>
   <si>
     <t>truck30</t>
   </si>
   <si>
-    <t>0101786095</t>
-  </si>
-  <si>
-    <t>truck31</t>
-  </si>
-  <si>
     <t>0101783776</t>
   </si>
   <si>
     <t>truck29_2</t>
   </si>
   <si>
-    <t>0101783775</t>
-  </si>
-  <si>
-    <t>truck29_1</t>
-  </si>
-  <si>
-    <t>Shopify Cutover Inbound</t>
-  </si>
-  <si>
-    <t>Shopify Cutover Virtual Inbound Stockupf for Cutover Outbound</t>
-  </si>
-  <si>
-    <t>0101781187</t>
-  </si>
-  <si>
-    <t>truck28</t>
+    <t>0101768495</t>
+  </si>
+  <si>
+    <t>truck20</t>
   </si>
   <si>
     <t>0101772410</t>
@@ -480,12 +408,6 @@
     <t>truck25_2</t>
   </si>
   <si>
-    <t>0101780369</t>
-  </si>
-  <si>
-    <t>truck 25_1</t>
-  </si>
-  <si>
     <t>0101771085</t>
   </si>
   <si>
@@ -504,6 +426,12 @@
     <t>truck22_2</t>
   </si>
   <si>
+    <t>0101737929</t>
+  </si>
+  <si>
+    <t>Truck6</t>
+  </si>
+  <si>
     <t>0101768624</t>
   </si>
   <si>
@@ -516,28 +444,28 @@
     <t>truck21</t>
   </si>
   <si>
-    <t>0101768495</t>
-  </si>
-  <si>
-    <t>truck20</t>
+    <t>0101765025</t>
+  </si>
+  <si>
+    <t>truck18</t>
+  </si>
+  <si>
+    <t>0101765180</t>
+  </si>
+  <si>
+    <t>truck17</t>
+  </si>
+  <si>
+    <t>0101744972</t>
+  </si>
+  <si>
+    <t>truck8</t>
   </si>
   <si>
     <t>0101767215</t>
   </si>
   <si>
     <t>truck19</t>
-  </si>
-  <si>
-    <t>0101765025</t>
-  </si>
-  <si>
-    <t>truck18</t>
-  </si>
-  <si>
-    <t>0101765180</t>
-  </si>
-  <si>
-    <t>truck17</t>
   </si>
   <si>
     <t>0101762744</t>
@@ -565,18 +493,24 @@
 </t>
   </si>
   <si>
+    <t>0101754210</t>
+  </si>
+  <si>
+    <t>truck 12_2</t>
+  </si>
+  <si>
+    <t>0101743044</t>
+  </si>
+  <si>
+    <t>truck7</t>
+  </si>
+  <si>
     <t>0101759115</t>
   </si>
   <si>
     <t>truck13</t>
   </si>
   <si>
-    <t>0101754210</t>
-  </si>
-  <si>
-    <t>truck 12_2</t>
-  </si>
-  <si>
     <t>0101754187</t>
   </si>
   <si>
@@ -601,24 +535,6 @@
     <t>truck9</t>
   </si>
   <si>
-    <t>0101744972</t>
-  </si>
-  <si>
-    <t>truck8</t>
-  </si>
-  <si>
-    <t>0101743044</t>
-  </si>
-  <si>
-    <t>truck7</t>
-  </si>
-  <si>
-    <t>0101737929</t>
-  </si>
-  <si>
-    <t>Truck6</t>
-  </si>
-  <si>
     <t>0101738755</t>
   </si>
   <si>
@@ -650,21 +566,6 @@
   </si>
   <si>
     <t>Truck1</t>
-  </si>
-  <si>
-    <t>Container 1</t>
-  </si>
-  <si>
-    <t>Inboundtest1</t>
-  </si>
-  <si>
-    <t>SUP_111</t>
-  </si>
-  <si>
-    <t>TestSUP</t>
-  </si>
-  <si>
-    <t>Germany</t>
   </si>
 </sst>
 </file>
@@ -1031,21 +932,21 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W108"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="13.421875" customWidth="1"/>
+    <col min="1" max="1" width="10.28125" customWidth="1"/>
     <col min="2" max="2" width="16.00390625" customWidth="1"/>
     <col min="3" max="3" width="29.8515625" customWidth="1"/>
-    <col min="4" max="4" width="12.28125" customWidth="1"/>
+    <col min="4" max="4" width="10.8515625" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" customWidth="1"/>
+    <col min="6" max="6" width="22.8515625" customWidth="1"/>
     <col min="7" max="7" width="18.7109375" customWidth="1"/>
     <col min="8" max="8" width="22.28125" customWidth="1"/>
     <col min="9" max="9" width="12.8515625" customWidth="1"/>
     <col min="10" max="10" width="15.00390625" customWidth="1"/>
     <col min="11" max="11" width="16.7109375" customWidth="1"/>
-    <col min="13" max="13" width="58.57421875" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" customWidth="1"/>
     <col min="14" max="14" width="14.00390625" customWidth="1" style="1"/>
     <col min="15" max="15" width="16.8515625" customWidth="1"/>
     <col min="16" max="16" width="11.57421875" customWidth="1" style="1"/>
@@ -1130,43 +1031,43 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2">
+        <v>7355667</v>
+      </c>
+      <c r="F2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2">
-        <v>7369152</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>26</v>
-      </c>
       <c r="P2" s="1">
-        <v>46196.459848344908</v>
+        <v>46191.4713122338</v>
       </c>
       <c r="R2" s="4">
-        <v>46197.493816087961</v>
+        <v>46198.319310104169</v>
       </c>
       <c r="S2">
-        <v>300.000</v>
+        <v>15383.000</v>
       </c>
       <c r="T2">
-        <v>300.000</v>
+        <v>15383.000</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -1175,98 +1076,98 @@
         <v>0</v>
       </c>
       <c r="W2" s="4">
-        <v>46197.462741932868</v>
+        <v>46198.319958796295</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>7369151</v>
+        <v>7352722</v>
       </c>
       <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" t="s">
-        <v>28</v>
-      </c>
       <c r="P3" s="1">
-        <v>46196.459830243053</v>
+        <v>46190.517798842593</v>
       </c>
       <c r="R3" s="4">
-        <v>46197.505754942133</v>
+        <v>46198.316219409724</v>
       </c>
       <c r="S3">
-        <v>3638.000</v>
+        <v>13727.000</v>
       </c>
       <c r="T3">
-        <v>1350.000</v>
+        <v>13727.000</v>
       </c>
       <c r="U3">
-        <v>2288.000</v>
+        <v>0</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
       <c r="W3" s="4">
-        <v>46197.470179942131</v>
+        <v>46198.317383530091</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>7368806</v>
+        <v>7362235</v>
       </c>
       <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" t="s">
-        <v>30</v>
-      </c>
       <c r="P4" s="1">
-        <v>46196.377559722219</v>
+        <v>46195.402748692133</v>
       </c>
       <c r="R4" s="4">
-        <v>46197.497936342595</v>
+        <v>46198.313491319444</v>
       </c>
       <c r="S4">
-        <v>5755.000</v>
+        <v>10614.000</v>
       </c>
       <c r="T4">
-        <v>5755.000</v>
+        <v>10614.000</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -1275,204 +1176,198 @@
         <v>0</v>
       </c>
       <c r="W4" s="4">
-        <v>46197.328573645835</v>
+        <v>46198.314641435187</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>7362235</v>
+        <v>7373968</v>
       </c>
       <c r="F5" t="s">
         <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M5" t="s">
         <v>32</v>
       </c>
       <c r="P5" s="1">
-        <v>46195.402748692133</v>
-      </c>
-      <c r="R5" s="4">
-        <v>46197.397536493052</v>
+        <v>46197.485422534723</v>
       </c>
       <c r="S5">
-        <v>10614.000</v>
+        <v>18575.000</v>
       </c>
       <c r="T5">
-        <v>9645.000</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>969.000</v>
+        <v>18575.000</v>
       </c>
       <c r="V5">
         <v>0</v>
       </c>
       <c r="W5" s="4">
-        <v>46196.386357604169</v>
+        <v>46197.668712349536</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>7355667</v>
+        <v>7374444</v>
       </c>
       <c r="F6" t="s">
         <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M6" t="s">
         <v>34</v>
       </c>
       <c r="P6" s="1">
-        <v>46191.4713122338</v>
-      </c>
-      <c r="R6" s="4">
-        <v>46197.480876006943</v>
+        <v>46197.553791817132</v>
       </c>
       <c r="S6">
-        <v>15383.000</v>
+        <v>10410.000</v>
       </c>
       <c r="T6">
-        <v>15108.000</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>275.000</v>
+        <v>10410.000</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6" s="4">
-        <v>46195.405326423614</v>
+        <v>46197.554211886571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>7352722</v>
+        <v>7374441</v>
       </c>
       <c r="F7" t="s">
         <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M7" t="s">
         <v>36</v>
       </c>
       <c r="P7" s="1">
-        <v>46190.517798842593</v>
-      </c>
-      <c r="R7" s="4">
-        <v>46197.338562233796</v>
+        <v>46197.552075150466</v>
       </c>
       <c r="S7">
-        <v>13727.000</v>
+        <v>10194.000</v>
       </c>
       <c r="T7">
-        <v>13671.000</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>56.000</v>
+        <v>10194.000</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7" s="4">
-        <v>46191.406867129626</v>
+        <v>46197.552593900466</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8">
+        <v>7369152</v>
+      </c>
+      <c r="F8" t="s">
         <v>37</v>
       </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8">
-        <v>7373968</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" t="s">
         <v>38</v>
       </c>
-      <c r="G8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8" t="s">
-        <v>39</v>
-      </c>
       <c r="P8" s="1">
-        <v>46197.485422534723</v>
+        <v>46196.459848344908</v>
+      </c>
+      <c r="R8" s="4">
+        <v>46197.493816087961</v>
       </c>
       <c r="S8">
-        <v>18490.000</v>
+        <v>300.000</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>300.000</v>
       </c>
       <c r="U8">
-        <v>18490.000</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8" s="4">
-        <v>46197.485947650464</v>
+        <v>46197.550397141204</v>
       </c>
     </row>
     <row r="9">
@@ -1480,46 +1375,40 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9">
-        <v>7349603</v>
+        <v>7369151</v>
       </c>
       <c r="F9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" t="s">
         <v>40</v>
       </c>
-      <c r="G9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" s="1">
-        <v>46190</v>
-      </c>
       <c r="P9" s="1">
-        <v>46189.643392094906</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>46190.996527777781</v>
+        <v>46196.459830243053</v>
       </c>
       <c r="R9" s="4">
-        <v>46190.579668171296</v>
+        <v>46197.531721678242</v>
       </c>
       <c r="S9">
-        <v>5965.000</v>
+        <v>3638.000</v>
       </c>
       <c r="T9">
-        <v>5965.000</v>
+        <v>3638.000</v>
       </c>
       <c r="U9">
         <v>0</v>
@@ -1528,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="4">
-        <v>46191.313541932868</v>
+        <v>46197.550396956016</v>
       </c>
     </row>
     <row r="10">
@@ -1536,55 +1425,49 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10">
-        <v>7166305</v>
+        <v>7368806</v>
       </c>
       <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" t="s">
         <v>42</v>
       </c>
-      <c r="G10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" t="s">
-        <v>43</v>
-      </c>
-      <c r="N10" s="1">
-        <v>46152</v>
-      </c>
       <c r="P10" s="1">
-        <v>46154.508897418978</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>46162.29583333333</v>
+        <v>46196.377559722219</v>
       </c>
       <c r="R10" s="4">
-        <v>46154.512428125003</v>
+        <v>46197.497936342595</v>
       </c>
       <c r="S10">
-        <v>100.000</v>
+        <v>5755.000</v>
       </c>
       <c r="T10">
-        <v>98.000</v>
+        <v>5755.000</v>
       </c>
       <c r="U10">
-        <v>2.000</v>
+        <v>0</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10" s="4">
-        <v>46190.318931481481</v>
+        <v>46197.550396064813</v>
       </c>
     </row>
     <row r="11">
@@ -1592,40 +1475,40 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11">
-        <v>7362625</v>
+        <v>7352670</v>
       </c>
       <c r="F11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" t="s">
-        <v>45</v>
-      </c>
       <c r="P11" s="1">
-        <v>46195.438085185182</v>
+        <v>46190.508466550928</v>
       </c>
       <c r="R11" s="4">
-        <v>46196.523870486111</v>
+        <v>46197.408573148146</v>
       </c>
       <c r="S11">
-        <v>6200.000</v>
+        <v>10751.000</v>
       </c>
       <c r="T11">
-        <v>6200.000</v>
+        <v>10751.000</v>
       </c>
       <c r="U11">
         <v>0</v>
@@ -1634,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="W11" s="4">
-        <v>46197.278575775461</v>
+        <v>46197.438478206015</v>
       </c>
     </row>
     <row r="12">
@@ -1642,40 +1525,40 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12">
-        <v>7362236</v>
+        <v>7358767</v>
       </c>
       <c r="F12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" t="s">
         <v>46</v>
       </c>
-      <c r="G12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" t="s">
-        <v>47</v>
-      </c>
       <c r="P12" s="1">
-        <v>46195.402819178242</v>
+        <v>46192.659844444446</v>
       </c>
       <c r="R12" s="4">
-        <v>46196.601059108798</v>
+        <v>46197.3828096875</v>
       </c>
       <c r="S12">
-        <v>6305.000</v>
+        <v>10207.000</v>
       </c>
       <c r="T12">
-        <v>6305.000</v>
+        <v>10207.000</v>
       </c>
       <c r="U12">
         <v>0</v>
@@ -1684,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="4">
-        <v>46197.278671446758</v>
+        <v>46197.391247916668</v>
       </c>
     </row>
     <row r="13">
@@ -1692,40 +1575,40 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13">
-        <v>7358767</v>
+        <v>7358766</v>
       </c>
       <c r="F13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" t="s">
         <v>48</v>
       </c>
-      <c r="G13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" t="s">
-        <v>24</v>
-      </c>
-      <c r="M13" t="s">
-        <v>49</v>
-      </c>
       <c r="P13" s="1">
-        <v>46192.659844444446</v>
+        <v>46192.659814814811</v>
       </c>
       <c r="R13" s="4">
-        <v>46197.3828096875</v>
+        <v>46197.366926122682</v>
       </c>
       <c r="S13">
-        <v>10207.000</v>
+        <v>8661.000</v>
       </c>
       <c r="T13">
-        <v>10207.000</v>
+        <v>8661.000</v>
       </c>
       <c r="U13">
         <v>0</v>
@@ -1734,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="W13" s="4">
-        <v>46197.391247916668</v>
+        <v>46197.391093518519</v>
       </c>
     </row>
     <row r="14">
@@ -1742,40 +1625,40 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E14">
-        <v>7358766</v>
+        <v>7362236</v>
       </c>
       <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" t="s">
         <v>50</v>
       </c>
-      <c r="G14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" t="s">
-        <v>24</v>
-      </c>
-      <c r="M14" t="s">
-        <v>51</v>
-      </c>
       <c r="P14" s="1">
-        <v>46192.659814814811</v>
+        <v>46195.402819178242</v>
       </c>
       <c r="R14" s="4">
-        <v>46197.366926122682</v>
+        <v>46196.601059108798</v>
       </c>
       <c r="S14">
-        <v>8661.000</v>
+        <v>6305.000</v>
       </c>
       <c r="T14">
-        <v>8661.000</v>
+        <v>6305.000</v>
       </c>
       <c r="U14">
         <v>0</v>
@@ -1784,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="W14" s="4">
-        <v>46197.391093518519</v>
+        <v>46197.278671446758</v>
       </c>
     </row>
     <row r="15">
@@ -1792,40 +1675,40 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15">
-        <v>7355924</v>
+        <v>7362625</v>
       </c>
       <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" t="s">
         <v>52</v>
       </c>
-      <c r="G15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" t="s">
-        <v>24</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="P15" s="1">
-        <v>46191.548452546296</v>
+        <v>46195.438085185182</v>
       </c>
       <c r="R15" s="4">
-        <v>46195.391070254627</v>
+        <v>46196.523870486111</v>
       </c>
       <c r="S15">
-        <v>8044.000</v>
+        <v>6200.000</v>
       </c>
       <c r="T15">
-        <v>8044.000</v>
+        <v>6200.000</v>
       </c>
       <c r="U15">
         <v>0</v>
@@ -1834,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="W15" s="4">
-        <v>46196.389409641204</v>
+        <v>46197.278575775461</v>
       </c>
     </row>
     <row r="16">
@@ -1842,40 +1725,40 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16">
-        <v>7353363</v>
+        <v>7355924</v>
       </c>
       <c r="F16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" t="s">
-        <v>55</v>
-      </c>
       <c r="P16" s="1">
-        <v>46190.666969988422</v>
+        <v>46191.548452546296</v>
       </c>
       <c r="R16" s="4">
-        <v>46195.511062997684</v>
+        <v>46195.391070254627</v>
       </c>
       <c r="S16">
-        <v>472.000</v>
+        <v>8044.000</v>
       </c>
       <c r="T16">
-        <v>472.000</v>
+        <v>8044.000</v>
       </c>
       <c r="U16">
         <v>0</v>
@@ -1892,40 +1775,40 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17">
-        <v>7353362</v>
+        <v>7353112</v>
       </c>
       <c r="F17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" t="s">
+        <v>23</v>
+      </c>
+      <c r="M17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" t="s">
-        <v>24</v>
-      </c>
-      <c r="M17" t="s">
-        <v>55</v>
-      </c>
       <c r="P17" s="1">
-        <v>46190.666969444443</v>
+        <v>46190.633443321756</v>
       </c>
       <c r="R17" s="4">
-        <v>46195.521521527779</v>
+        <v>46195.593899918982</v>
       </c>
       <c r="S17">
-        <v>612.000</v>
+        <v>15034.000</v>
       </c>
       <c r="T17">
-        <v>612.000</v>
+        <v>15034.000</v>
       </c>
       <c r="U17">
         <v>0</v>
@@ -1934,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="W17" s="4">
-        <v>46196.389409641204</v>
+        <v>46196.389407835646</v>
       </c>
     </row>
     <row r="18">
@@ -1942,40 +1825,46 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E18">
-        <v>7353361</v>
+        <v>7349603</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M18" t="s">
-        <v>55</v>
+        <v>58</v>
+      </c>
+      <c r="N18" s="1">
+        <v>46190</v>
       </c>
       <c r="P18" s="1">
-        <v>46190.666967094905</v>
+        <v>46189.643392094906</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>46190.996527777781</v>
       </c>
       <c r="R18" s="4">
-        <v>46195.535836192132</v>
+        <v>46190.579668171296</v>
       </c>
       <c r="S18">
-        <v>2383.000</v>
+        <v>5965.000</v>
       </c>
       <c r="T18">
-        <v>2383.000</v>
+        <v>5965.000</v>
       </c>
       <c r="U18">
         <v>0</v>
@@ -1984,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="W18" s="4">
-        <v>46196.389409641204</v>
+        <v>46191.313541932868</v>
       </c>
     </row>
     <row r="19">
@@ -1992,40 +1881,40 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19">
-        <v>7353360</v>
+        <v>7344984</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M19" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="P19" s="1">
-        <v>46190.666964201388</v>
+        <v>46188.6820028125</v>
       </c>
       <c r="R19" s="4">
-        <v>46195.523977164354</v>
+        <v>46189.581174189814</v>
       </c>
       <c r="S19">
-        <v>2262.000</v>
+        <v>14515.000</v>
       </c>
       <c r="T19">
-        <v>2262.000</v>
+        <v>14515.000</v>
       </c>
       <c r="U19">
         <v>0</v>
@@ -2034,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="W19" s="4">
-        <v>46196.389409641204</v>
+        <v>46190.318753738429</v>
       </c>
     </row>
     <row r="20">
@@ -2042,40 +1931,43 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E20">
-        <v>7353359</v>
+        <v>7343721</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M20" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="P20" s="1">
-        <v>46190.66696145833</v>
+        <v>46188.52897230324</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>46189.270138888889</v>
       </c>
       <c r="R20" s="4">
-        <v>46195.537172372686</v>
+        <v>46189.525954201388</v>
       </c>
       <c r="S20">
-        <v>3982.000</v>
+        <v>9210.000</v>
       </c>
       <c r="T20">
-        <v>3982.000</v>
+        <v>9210.000</v>
       </c>
       <c r="U20">
         <v>0</v>
@@ -2084,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="W20" s="4">
-        <v>46196.389409456016</v>
+        <v>46189.538887268522</v>
       </c>
     </row>
     <row r="21">
@@ -2092,40 +1984,43 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E21">
-        <v>7353358</v>
+        <v>7312333</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M21" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="P21" s="1">
-        <v>46190.666954432869</v>
+        <v>46181.394416122683</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>46182.458333333336</v>
       </c>
       <c r="R21" s="4">
-        <v>46195.532108368054</v>
+        <v>46188.402503240737</v>
       </c>
       <c r="S21">
-        <v>1113.000</v>
+        <v>8272.000</v>
       </c>
       <c r="T21">
-        <v>1113.000</v>
+        <v>8272.000</v>
       </c>
       <c r="U21">
         <v>0</v>
@@ -2134,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="W21" s="4">
-        <v>46196.389409456016</v>
+        <v>46188.404413310185</v>
       </c>
     </row>
     <row r="22">
@@ -2142,40 +2037,43 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E22">
-        <v>7353357</v>
+        <v>7312334</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M22" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="P22" s="1">
-        <v>46190.666949340281</v>
+        <v>46181.394481597221</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>46182.458333333336</v>
       </c>
       <c r="R22" s="4">
-        <v>46195.517305439818</v>
+        <v>46188.363727511576</v>
       </c>
       <c r="S22">
-        <v>447.000</v>
+        <v>5617.000</v>
       </c>
       <c r="T22">
-        <v>447.000</v>
+        <v>5617.000</v>
       </c>
       <c r="U22">
         <v>0</v>
@@ -2184,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="W22" s="4">
-        <v>46196.389409456016</v>
+        <v>46188.368130752315</v>
       </c>
     </row>
     <row r="23">
@@ -2192,40 +2090,43 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23">
-        <v>7353356</v>
+        <v>7306694</v>
       </c>
       <c r="F23" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M23" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="P23" s="1">
-        <v>46190.66694664352</v>
+        <v>46178.650135613425</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>46181.3125</v>
       </c>
       <c r="R23" s="4">
-        <v>46195.528761724534</v>
+        <v>46188.351883217591</v>
       </c>
       <c r="S23">
-        <v>284.000</v>
+        <v>7291.000</v>
       </c>
       <c r="T23">
-        <v>284.000</v>
+        <v>7291.000</v>
       </c>
       <c r="U23">
         <v>0</v>
@@ -2234,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="4">
-        <v>46196.389409456016</v>
+        <v>46188.368130405092</v>
       </c>
     </row>
     <row r="24">
@@ -2242,40 +2143,43 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E24">
-        <v>7353355</v>
+        <v>7306693</v>
       </c>
       <c r="F24" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M24" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="P24" s="1">
-        <v>46190.666944293982</v>
+        <v>46178.650101388892</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>46181.395833333336</v>
       </c>
       <c r="R24" s="4">
-        <v>46195.528790659722</v>
+        <v>46188.361928472223</v>
       </c>
       <c r="S24">
-        <v>304.000</v>
+        <v>5272.000</v>
       </c>
       <c r="T24">
-        <v>304.000</v>
+        <v>5272.000</v>
       </c>
       <c r="U24">
         <v>0</v>
@@ -2284,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="W24" s="4">
-        <v>46196.389409456016</v>
+        <v>46188.368129826391</v>
       </c>
     </row>
     <row r="25">
@@ -2292,40 +2196,40 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E25">
-        <v>7353354</v>
+        <v>7296112</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M25" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="P25" s="1">
-        <v>46190.666940659721</v>
+        <v>46176.490794872683</v>
       </c>
       <c r="R25" s="4">
-        <v>46195.536209409722</v>
+        <v>46188.357570370368</v>
       </c>
       <c r="S25">
-        <v>1251.000</v>
+        <v>7146.000</v>
       </c>
       <c r="T25">
-        <v>1251.000</v>
+        <v>7146.000</v>
       </c>
       <c r="U25">
         <v>0</v>
@@ -2334,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="W25" s="4">
-        <v>46196.389409456016</v>
+        <v>46188.368129664355</v>
       </c>
     </row>
     <row r="26">
@@ -2342,40 +2246,43 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26">
-        <v>7353353</v>
+        <v>7331780</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M26" t="s">
-        <v>55</v>
+        <v>74</v>
+      </c>
+      <c r="O26" s="4">
+        <v>46185.364583333336</v>
       </c>
       <c r="P26" s="1">
-        <v>46190.666939583331</v>
+        <v>46184.420189351855</v>
       </c>
       <c r="R26" s="4">
-        <v>46195.537300034724</v>
+        <v>46188.330705902779</v>
       </c>
       <c r="S26">
-        <v>1257.000</v>
+        <v>2185.000</v>
       </c>
       <c r="T26">
-        <v>1257.000</v>
+        <v>2185.000</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -2384,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="W26" s="4">
-        <v>46196.389409456016</v>
+        <v>46188.33742491898</v>
       </c>
     </row>
     <row r="27">
@@ -2392,40 +2299,46 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E27">
-        <v>7353352</v>
+        <v>7331779</v>
       </c>
       <c r="F27" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M27" t="s">
-        <v>55</v>
+        <v>76</v>
+      </c>
+      <c r="O27" s="4">
+        <v>46185</v>
       </c>
       <c r="P27" s="1">
-        <v>46190.66693417824</v>
+        <v>46184.420142511575</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>46181</v>
       </c>
       <c r="R27" s="4">
-        <v>46195.537318483795</v>
+        <v>46188.332772222224</v>
       </c>
       <c r="S27">
-        <v>7113.000</v>
+        <v>16497.000</v>
       </c>
       <c r="T27">
-        <v>7113.000</v>
+        <v>16497.000</v>
       </c>
       <c r="U27">
         <v>0</v>
@@ -2434,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="W27" s="4">
-        <v>46196.388202118054</v>
+        <v>46188.337424189813</v>
       </c>
     </row>
     <row r="28">
@@ -2442,40 +2355,43 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E28">
-        <v>7353351</v>
+        <v>7327419</v>
       </c>
       <c r="F28" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M28" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="P28" s="1">
-        <v>46190.666933101849</v>
+        <v>46183.517797372682</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>46184.3125</v>
       </c>
       <c r="R28" s="4">
-        <v>46195.523942245367</v>
+        <v>46188.329073842593</v>
       </c>
       <c r="S28">
-        <v>1295.000</v>
+        <v>10574.000</v>
       </c>
       <c r="T28">
-        <v>1295.000</v>
+        <v>10574.000</v>
       </c>
       <c r="U28">
         <v>0</v>
@@ -2484,7 +2400,7 @@
         <v>0</v>
       </c>
       <c r="W28" s="4">
-        <v>46196.389409293981</v>
+        <v>46188.337423263889</v>
       </c>
     </row>
     <row r="29">
@@ -2492,40 +2408,40 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E29">
-        <v>7353350</v>
+        <v>7331318</v>
       </c>
       <c r="F29" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M29" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="P29" s="1">
-        <v>46190.666932719905</v>
+        <v>46184.369259340281</v>
       </c>
       <c r="R29" s="4">
-        <v>46195.536177581016</v>
+        <v>46185.506102002313</v>
       </c>
       <c r="S29">
-        <v>72.000</v>
+        <v>10749.000</v>
       </c>
       <c r="T29">
-        <v>72.000</v>
+        <v>10749.000</v>
       </c>
       <c r="U29">
         <v>0</v>
@@ -2534,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="W29" s="4">
-        <v>46196.389409293981</v>
+        <v>46188.329308333334</v>
       </c>
     </row>
     <row r="30">
@@ -2542,40 +2458,43 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E30">
-        <v>7353349</v>
+        <v>7306692</v>
       </c>
       <c r="F30" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H30" t="s">
-        <v>24</v>
-      </c>
-      <c r="M30" t="s">
-        <v>55</v>
+        <v>23</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="O30" s="4">
+        <v>46181.34375</v>
       </c>
       <c r="P30" s="1">
-        <v>46190.666930555555</v>
+        <v>46178.650014085651</v>
       </c>
       <c r="R30" s="4">
-        <v>46195.536192395833</v>
+        <v>46188.321652777777</v>
       </c>
       <c r="S30">
-        <v>101.000</v>
+        <v>10749.000</v>
       </c>
       <c r="T30">
-        <v>101.000</v>
+        <v>10749.000</v>
       </c>
       <c r="U30">
         <v>0</v>
@@ -2584,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="W30" s="4">
-        <v>46196.389409293981</v>
+        <v>46188.329306516207</v>
       </c>
     </row>
     <row r="31">
@@ -2592,40 +2511,43 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E31">
-        <v>7353348</v>
+        <v>7290512</v>
       </c>
       <c r="F31" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M31" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="P31" s="1">
-        <v>46190.666919525465</v>
+        <v>46175.705376817132</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>46176.5</v>
       </c>
       <c r="R31" s="4">
-        <v>46195.534000462962</v>
+        <v>46188.325696840278</v>
       </c>
       <c r="S31">
-        <v>1620.000</v>
+        <v>14234.000</v>
       </c>
       <c r="T31">
-        <v>1620.000</v>
+        <v>14234.000</v>
       </c>
       <c r="U31">
         <v>0</v>
@@ -2634,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="W31" s="4">
-        <v>46196.389409293981</v>
+        <v>46188.329304166669</v>
       </c>
     </row>
     <row r="32">
@@ -2642,40 +2564,43 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E32">
-        <v>7353347</v>
+        <v>7277742</v>
       </c>
       <c r="F32" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="G32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M32" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="P32" s="1">
-        <v>46190.666916979164</v>
+        <v>46174.491930821758</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>46174.416666666664</v>
       </c>
       <c r="R32" s="4">
-        <v>46195.527235069443</v>
+        <v>46188.313768368054</v>
       </c>
       <c r="S32">
-        <v>600.000</v>
+        <v>18914.000</v>
       </c>
       <c r="T32">
-        <v>600.000</v>
+        <v>18914.000</v>
       </c>
       <c r="U32">
         <v>0</v>
@@ -2684,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="W32" s="4">
-        <v>46196.389409293981</v>
+        <v>46188.329302546299</v>
       </c>
     </row>
     <row r="33">
@@ -2692,40 +2617,43 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E33">
-        <v>7353346</v>
+        <v>7321304</v>
       </c>
       <c r="F33" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="G33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M33" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="P33" s="1">
-        <v>46190.66691284722</v>
+        <v>46182.379826539349</v>
+      </c>
+      <c r="Q33" s="4">
+        <v>46183.458333333336</v>
       </c>
       <c r="R33" s="4">
-        <v>46195.522001273152</v>
+        <v>46184.566309837966</v>
       </c>
       <c r="S33">
-        <v>1338.000</v>
+        <v>1784.000</v>
       </c>
       <c r="T33">
-        <v>1338.000</v>
+        <v>1784.000</v>
       </c>
       <c r="U33">
         <v>0</v>
@@ -2734,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="W33" s="4">
-        <v>46196.389409293981</v>
+        <v>46188.318567708331</v>
       </c>
     </row>
     <row r="34">
@@ -2742,40 +2670,43 @@
         <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E34">
-        <v>7353345</v>
+        <v>7321303</v>
       </c>
       <c r="F34" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M34" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="P34" s="1">
-        <v>46190.666911921297</v>
+        <v>46182.379728553242</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>46183.458333333336</v>
       </c>
       <c r="R34" s="4">
-        <v>46195.532152511572</v>
+        <v>46185.474632175923</v>
       </c>
       <c r="S34">
-        <v>968.000</v>
+        <v>15852.000</v>
       </c>
       <c r="T34">
-        <v>968.000</v>
+        <v>15852.000</v>
       </c>
       <c r="U34">
         <v>0</v>
@@ -2784,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="W34" s="4">
-        <v>46196.389409293981</v>
+        <v>46188.318567164351</v>
       </c>
     </row>
     <row r="35">
@@ -2792,40 +2723,43 @@
         <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E35">
-        <v>7353344</v>
+        <v>7312335</v>
       </c>
       <c r="F35" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="G35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H35" t="s">
-        <v>24</v>
-      </c>
-      <c r="M35" t="s">
-        <v>55</v>
+        <v>23</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="P35" s="1">
-        <v>46190.666910844906</v>
+        <v>46181.394497488429</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>46182.388888888891</v>
       </c>
       <c r="R35" s="4">
-        <v>46195.537341087962</v>
+        <v>46185.475467280092</v>
       </c>
       <c r="S35">
-        <v>917.000</v>
+        <v>16641.000</v>
       </c>
       <c r="T35">
-        <v>917.000</v>
+        <v>16641.000</v>
       </c>
       <c r="U35">
         <v>0</v>
@@ -2834,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="W35" s="4">
-        <v>46196.389409293981</v>
+        <v>46188.318566284725</v>
       </c>
     </row>
     <row r="36">
@@ -2842,40 +2776,40 @@
         <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E36">
-        <v>7353343</v>
+        <v>7329559</v>
       </c>
       <c r="F36" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M36" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="P36" s="1">
-        <v>46190.666907604165</v>
+        <v>46183.835381215278</v>
       </c>
       <c r="R36" s="4">
-        <v>46195.526307291664</v>
+        <v>46185.394576122686</v>
       </c>
       <c r="S36">
-        <v>3514.000</v>
+        <v>18992.000</v>
       </c>
       <c r="T36">
-        <v>3514.000</v>
+        <v>18992.000</v>
       </c>
       <c r="U36">
         <v>0</v>
@@ -2884,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="W36" s="4">
-        <v>46196.389409108793</v>
+        <v>46188.318260497683</v>
       </c>
     </row>
     <row r="37">
@@ -2892,40 +2826,43 @@
         <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37">
-        <v>7353342</v>
+        <v>7312336</v>
       </c>
       <c r="F37" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="G37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M37" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="P37" s="1">
-        <v>46190.666906134262</v>
+        <v>46181.394619016202</v>
+      </c>
+      <c r="Q37" s="4">
+        <v>46182.416666666664</v>
       </c>
       <c r="R37" s="4">
-        <v>46195.518147222225</v>
+        <v>46182.563263425924</v>
       </c>
       <c r="S37">
-        <v>646.000</v>
+        <v>8559.000</v>
       </c>
       <c r="T37">
-        <v>646.000</v>
+        <v>8559.000</v>
       </c>
       <c r="U37">
         <v>0</v>
@@ -2934,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="W37" s="4">
-        <v>46196.389409108793</v>
+        <v>46183.499163692133</v>
       </c>
     </row>
     <row r="38">
@@ -2942,40 +2879,46 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38">
-        <v>7353341</v>
+        <v>7297491</v>
       </c>
       <c r="F38" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M38" t="s">
-        <v>55</v>
+        <v>98</v>
+      </c>
+      <c r="O38" s="4">
+        <v>46178.416666666664</v>
       </c>
       <c r="P38" s="1">
-        <v>46190.666903969905</v>
+        <v>46176.651283530089</v>
+      </c>
+      <c r="Q38" s="4">
+        <v>46178.260416666664</v>
       </c>
       <c r="R38" s="4">
-        <v>46195.535854247682</v>
+        <v>46182.304580173608</v>
       </c>
       <c r="S38">
-        <v>2209.000</v>
+        <v>19653.000</v>
       </c>
       <c r="T38">
-        <v>2209.000</v>
+        <v>19653.000</v>
       </c>
       <c r="U38">
         <v>0</v>
@@ -2984,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="W38" s="4">
-        <v>46196.389409108793</v>
+        <v>46182.394867361108</v>
       </c>
     </row>
     <row r="39">
@@ -2992,40 +2935,43 @@
         <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39">
-        <v>7353340</v>
+        <v>7276670</v>
       </c>
       <c r="F39" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M39" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="P39" s="1">
-        <v>46190.666894560185</v>
+        <v>46174.386795023151</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>46174.3125</v>
       </c>
       <c r="R39" s="4">
-        <v>46195.524072835651</v>
+        <v>46181.602299189813</v>
       </c>
       <c r="S39">
-        <v>4385.000</v>
+        <v>7766.000</v>
       </c>
       <c r="T39">
-        <v>4385.000</v>
+        <v>7766.000</v>
       </c>
       <c r="U39">
         <v>0</v>
@@ -3034,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="W39" s="4">
-        <v>46196.389409108793</v>
+        <v>46181.607877893519</v>
       </c>
     </row>
     <row r="40">
@@ -3042,40 +2988,43 @@
         <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E40">
-        <v>7353339</v>
+        <v>7256959</v>
       </c>
       <c r="F40" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M40" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="P40" s="1">
-        <v>46190.666882442129</v>
+        <v>46169.73840185185</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>46171.520833333336</v>
       </c>
       <c r="R40" s="4">
-        <v>46195.535098726854</v>
+        <v>46181.602367395833</v>
       </c>
       <c r="S40">
-        <v>2886.000</v>
+        <v>11921.000</v>
       </c>
       <c r="T40">
-        <v>2886.000</v>
+        <v>11921.000</v>
       </c>
       <c r="U40">
         <v>0</v>
@@ -3084,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="W40" s="4">
-        <v>46196.389408912037</v>
+        <v>46181.607877002316</v>
       </c>
     </row>
     <row r="41">
@@ -3092,40 +3041,46 @@
         <v>19</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E41">
-        <v>7353338</v>
+        <v>7256837</v>
       </c>
       <c r="F41" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="G41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M41" t="s">
-        <v>55</v>
+        <v>104</v>
+      </c>
+      <c r="O41" s="4">
+        <v>46170.541666666664</v>
       </c>
       <c r="P41" s="1">
-        <v>46190.666870520836</v>
+        <v>46169.717724456015</v>
+      </c>
+      <c r="Q41" s="4">
+        <v>46171.375</v>
       </c>
       <c r="R41" s="4">
-        <v>46195.537258252312</v>
+        <v>46181.601758877317</v>
       </c>
       <c r="S41">
-        <v>2648.000</v>
+        <v>10645.000</v>
       </c>
       <c r="T41">
-        <v>2648.000</v>
+        <v>10645.000</v>
       </c>
       <c r="U41">
         <v>0</v>
@@ -3134,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="W41" s="4">
-        <v>46196.389408912037</v>
+        <v>46181.607876122682</v>
       </c>
     </row>
     <row r="42">
@@ -3142,40 +3097,43 @@
         <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E42">
-        <v>7353112</v>
+        <v>7297492</v>
       </c>
       <c r="F42" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="G42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H42" t="s">
-        <v>24</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>82</v>
+        <v>23</v>
+      </c>
+      <c r="M42" t="s">
+        <v>106</v>
+      </c>
+      <c r="O42" s="4">
+        <v>46178.427083333336</v>
       </c>
       <c r="P42" s="1">
-        <v>46190.633443321756</v>
+        <v>46176.651338159725</v>
       </c>
       <c r="R42" s="4">
-        <v>46195.593899918982</v>
+        <v>46178.483032060183</v>
       </c>
       <c r="S42">
-        <v>15034.000</v>
+        <v>6802.000</v>
       </c>
       <c r="T42">
-        <v>15034.000</v>
+        <v>6802.000</v>
       </c>
       <c r="U42">
         <v>0</v>
@@ -3184,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="W42" s="4">
-        <v>46196.389407835646</v>
+        <v>46181.304573692127</v>
       </c>
     </row>
     <row r="43">
@@ -3192,40 +3150,43 @@
         <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E43">
-        <v>7352670</v>
+        <v>7290516</v>
       </c>
       <c r="F43" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H43" t="s">
-        <v>24</v>
-      </c>
-      <c r="M43" s="5" t="s">
-        <v>84</v>
+        <v>23</v>
+      </c>
+      <c r="M43" t="s">
+        <v>108</v>
       </c>
       <c r="P43" s="1">
-        <v>46190.508466550928</v>
+        <v>46175.705564502314</v>
+      </c>
+      <c r="Q43" s="4">
+        <v>46176.59375</v>
       </c>
       <c r="R43" s="4">
-        <v>46197.408573148146</v>
+        <v>46178.37381646991</v>
       </c>
       <c r="S43">
-        <v>10751.000</v>
+        <v>6600.000</v>
       </c>
       <c r="T43">
-        <v>10751.000</v>
+        <v>6600.000</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -3234,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="W43" s="4">
-        <v>46197.438478206015</v>
+        <v>46181.304297951392</v>
       </c>
     </row>
     <row r="44">
@@ -3242,40 +3203,43 @@
         <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E44">
-        <v>7344984</v>
+        <v>7290513</v>
       </c>
       <c r="F44" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="G44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M44" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="P44" s="1">
-        <v>46188.6820028125</v>
+        <v>46175.705472835645</v>
+      </c>
+      <c r="Q44" s="4">
+        <v>46175.541666666664</v>
       </c>
       <c r="R44" s="4">
-        <v>46189.581174189814</v>
+        <v>46176.390187384262</v>
       </c>
       <c r="S44">
-        <v>14515.000</v>
+        <v>10634.000</v>
       </c>
       <c r="T44">
-        <v>14515.000</v>
+        <v>10634.000</v>
       </c>
       <c r="U44">
         <v>0</v>
@@ -3284,7 +3248,7 @@
         <v>0</v>
       </c>
       <c r="W44" s="4">
-        <v>46190.318753738429</v>
+        <v>46176.479922453706</v>
       </c>
     </row>
     <row r="45">
@@ -3292,43 +3256,43 @@
         <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E45">
-        <v>7343721</v>
+        <v>7277745</v>
       </c>
       <c r="F45" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="G45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M45" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="P45" s="1">
-        <v>46188.52897230324</v>
+        <v>46174.492115972222</v>
       </c>
       <c r="Q45" s="4">
-        <v>46189.270138888889</v>
+        <v>46175.291666666664</v>
       </c>
       <c r="R45" s="4">
-        <v>46189.525954201388</v>
+        <v>46176.394080127313</v>
       </c>
       <c r="S45">
-        <v>9210.000</v>
+        <v>8925.000</v>
       </c>
       <c r="T45">
-        <v>9210.000</v>
+        <v>8925.000</v>
       </c>
       <c r="U45">
         <v>0</v>
@@ -3337,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="W45" s="4">
-        <v>46189.538887268522</v>
+        <v>46176.479621759259</v>
       </c>
     </row>
     <row r="46">
@@ -3345,43 +3309,43 @@
         <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E46">
-        <v>7331780</v>
+        <v>7277755</v>
       </c>
       <c r="F46" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="G46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M46" t="s">
-        <v>90</v>
-      </c>
-      <c r="O46" s="4">
-        <v>46185.364583333336</v>
+        <v>114</v>
       </c>
       <c r="P46" s="1">
-        <v>46184.420189351855</v>
+        <v>46174.492233680554</v>
+      </c>
+      <c r="Q46" s="4">
+        <v>46175.291666666664</v>
       </c>
       <c r="R46" s="4">
-        <v>46188.330705902779</v>
+        <v>46175.460509027776</v>
       </c>
       <c r="S46">
-        <v>2185.000</v>
+        <v>1502.000</v>
       </c>
       <c r="T46">
-        <v>2185.000</v>
+        <v>1502.000</v>
       </c>
       <c r="U46">
         <v>0</v>
@@ -3390,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="W46" s="4">
-        <v>46188.33742491898</v>
+        <v>46176.367452777777</v>
       </c>
     </row>
     <row r="47">
@@ -3398,46 +3362,43 @@
         <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E47">
-        <v>7331779</v>
+        <v>7290515</v>
       </c>
       <c r="F47" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="G47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M47" t="s">
-        <v>92</v>
-      </c>
-      <c r="O47" s="4">
-        <v>46185</v>
+        <v>116</v>
       </c>
       <c r="P47" s="1">
-        <v>46184.420142511575</v>
+        <v>46175.705520370371</v>
       </c>
       <c r="Q47" s="4">
-        <v>46181</v>
+        <v>46175.604166666664</v>
       </c>
       <c r="R47" s="4">
-        <v>46188.332772222224</v>
+        <v>46176.32743784722</v>
       </c>
       <c r="S47">
-        <v>16497.000</v>
+        <v>9893.000</v>
       </c>
       <c r="T47">
-        <v>16497.000</v>
+        <v>9893.000</v>
       </c>
       <c r="U47">
         <v>0</v>
@@ -3446,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="W47" s="4">
-        <v>46188.337424189813</v>
+        <v>46176.36704571759</v>
       </c>
     </row>
     <row r="48">
@@ -3454,40 +3415,43 @@
         <v>19</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E48">
-        <v>7331318</v>
+        <v>7277744</v>
       </c>
       <c r="F48" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="G48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M48" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="P48" s="1">
-        <v>46184.369259340281</v>
+        <v>46174.49203425926</v>
+      </c>
+      <c r="Q48" s="4">
+        <v>46174.5</v>
       </c>
       <c r="R48" s="4">
-        <v>46185.506102002313</v>
+        <v>46175.401104085649</v>
       </c>
       <c r="S48">
-        <v>10749.000</v>
+        <v>14377.000</v>
       </c>
       <c r="T48">
-        <v>10749.000</v>
+        <v>14377.000</v>
       </c>
       <c r="U48">
         <v>0</v>
@@ -3496,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="W48" s="4">
-        <v>46188.329308333334</v>
+        <v>46175.446175925928</v>
       </c>
     </row>
     <row r="49">
@@ -3504,40 +3468,43 @@
         <v>19</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E49">
-        <v>7329559</v>
+        <v>7276672</v>
       </c>
       <c r="F49" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="G49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M49" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="P49" s="1">
-        <v>46183.835381215278</v>
+        <v>46174.386965358797</v>
+      </c>
+      <c r="Q49" s="4">
+        <v>46174.3125</v>
       </c>
       <c r="R49" s="4">
-        <v>46185.394576122686</v>
+        <v>46175.277797997682</v>
       </c>
       <c r="S49">
-        <v>18992.000</v>
+        <v>445.000</v>
       </c>
       <c r="T49">
-        <v>18992.000</v>
+        <v>445.000</v>
       </c>
       <c r="U49">
         <v>0</v>
@@ -3546,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="W49" s="4">
-        <v>46188.318260497683</v>
+        <v>46175.446175925928</v>
       </c>
     </row>
     <row r="50">
@@ -3554,43 +3521,43 @@
         <v>19</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E50">
-        <v>7327419</v>
+        <v>7243664</v>
       </c>
       <c r="F50" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="G50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M50" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="P50" s="1">
-        <v>46183.517797372682</v>
+        <v>46167.397293715279</v>
       </c>
       <c r="Q50" s="4">
-        <v>46184.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="R50" s="4">
-        <v>46188.329073842593</v>
+        <v>46170.486638159724</v>
       </c>
       <c r="S50">
-        <v>10574.000</v>
+        <v>5002.000</v>
       </c>
       <c r="T50">
-        <v>10574.000</v>
+        <v>5002.000</v>
       </c>
       <c r="U50">
         <v>0</v>
@@ -3599,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="W50" s="4">
-        <v>46188.337423263889</v>
+        <v>46171.52288329861</v>
       </c>
     </row>
     <row r="51">
@@ -3607,43 +3574,43 @@
         <v>19</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E51">
-        <v>7321304</v>
+        <v>7256954</v>
       </c>
       <c r="F51" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="G51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M51" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="P51" s="1">
-        <v>46182.379826539349</v>
+        <v>46169.737280092595</v>
       </c>
       <c r="Q51" s="4">
-        <v>46183.458333333336</v>
+        <v>46171.416666666664</v>
       </c>
       <c r="R51" s="4">
-        <v>46184.566309837966</v>
+        <v>46171.471500266205</v>
       </c>
       <c r="S51">
-        <v>1784.000</v>
+        <v>11226.000</v>
       </c>
       <c r="T51">
-        <v>1784.000</v>
+        <v>11226.000</v>
       </c>
       <c r="U51">
         <v>0</v>
@@ -3652,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="W51" s="4">
-        <v>46188.318567708331</v>
+        <v>46171.521807557867</v>
       </c>
     </row>
     <row r="52">
@@ -3660,43 +3627,43 @@
         <v>19</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E52">
-        <v>7321303</v>
+        <v>7256935</v>
       </c>
       <c r="F52" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="G52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M52" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="P52" s="1">
-        <v>46182.379728553242</v>
+        <v>46169.735800810187</v>
       </c>
       <c r="Q52" s="4">
-        <v>46183.458333333336</v>
+        <v>46171.25</v>
       </c>
       <c r="R52" s="4">
-        <v>46185.474632175923</v>
+        <v>46171.474860069444</v>
       </c>
       <c r="S52">
-        <v>15852.000</v>
+        <v>12909.000</v>
       </c>
       <c r="T52">
-        <v>15852.000</v>
+        <v>12909.000</v>
       </c>
       <c r="U52">
         <v>0</v>
@@ -3705,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="W52" s="4">
-        <v>46188.318567164351</v>
+        <v>46171.521807025463</v>
       </c>
     </row>
     <row r="53">
@@ -3713,43 +3680,46 @@
         <v>19</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E53">
-        <v>7312336</v>
+        <v>7256927</v>
       </c>
       <c r="F53" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="G53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M53" t="s">
-        <v>104</v>
+        <v>128</v>
+      </c>
+      <c r="O53" s="4">
+        <v>46170.541666666664</v>
       </c>
       <c r="P53" s="1">
-        <v>46181.394619016202</v>
+        <v>46169.733974768518</v>
       </c>
       <c r="Q53" s="4">
-        <v>46182.416666666664</v>
+        <v>46171.375</v>
       </c>
       <c r="R53" s="4">
-        <v>46182.563263425924</v>
+        <v>46171.384800081018</v>
       </c>
       <c r="S53">
-        <v>8559.000</v>
+        <v>470.000</v>
       </c>
       <c r="T53">
-        <v>8559.000</v>
+        <v>470.000</v>
       </c>
       <c r="U53">
         <v>0</v>
@@ -3758,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="W53" s="4">
-        <v>46183.499163692133</v>
+        <v>46171.521806828707</v>
       </c>
     </row>
     <row r="54">
@@ -3766,43 +3736,46 @@
         <v>19</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E54">
-        <v>7312335</v>
+        <v>7256698</v>
       </c>
       <c r="F54" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="G54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H54" t="s">
-        <v>24</v>
-      </c>
-      <c r="M54" s="5" t="s">
-        <v>106</v>
+        <v>23</v>
+      </c>
+      <c r="M54" t="s">
+        <v>130</v>
+      </c>
+      <c r="O54" s="4">
+        <v>46170.416666666664</v>
       </c>
       <c r="P54" s="1">
-        <v>46181.394497488429</v>
+        <v>46169.704318553238</v>
       </c>
       <c r="Q54" s="4">
-        <v>46182.388888888891</v>
+        <v>46170.4375</v>
       </c>
       <c r="R54" s="4">
-        <v>46185.475467280092</v>
+        <v>46170.55747615741</v>
       </c>
       <c r="S54">
-        <v>16641.000</v>
+        <v>15811.000</v>
       </c>
       <c r="T54">
-        <v>16641.000</v>
+        <v>15811.000</v>
       </c>
       <c r="U54">
         <v>0</v>
@@ -3811,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="W54" s="4">
-        <v>46188.318566284725</v>
+        <v>46171.52180628472</v>
       </c>
     </row>
     <row r="55">
@@ -3819,43 +3792,46 @@
         <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E55">
-        <v>7312334</v>
+        <v>7256674</v>
       </c>
       <c r="F55" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="G55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M55" t="s">
-        <v>108</v>
+        <v>132</v>
+      </c>
+      <c r="O55" s="4">
+        <v>46170.291666666664</v>
       </c>
       <c r="P55" s="1">
-        <v>46181.394481597221</v>
+        <v>46169.697586805552</v>
       </c>
       <c r="Q55" s="4">
-        <v>46182.458333333336</v>
+        <v>46171.291666666664</v>
       </c>
       <c r="R55" s="4">
-        <v>46188.363727511576</v>
+        <v>46171.366929745367</v>
       </c>
       <c r="S55">
-        <v>5617.000</v>
+        <v>6703.000</v>
       </c>
       <c r="T55">
-        <v>5617.000</v>
+        <v>6703.000</v>
       </c>
       <c r="U55">
         <v>0</v>
@@ -3864,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="W55" s="4">
-        <v>46188.368130752315</v>
+        <v>46171.521805937497</v>
       </c>
     </row>
     <row r="56">
@@ -3872,43 +3848,43 @@
         <v>19</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E56">
-        <v>7312333</v>
+        <v>7243671</v>
       </c>
       <c r="F56" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="G56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M56" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="P56" s="1">
-        <v>46181.394416122683</v>
+        <v>46167.398480636577</v>
       </c>
       <c r="Q56" s="4">
-        <v>46182.458333333336</v>
+        <v>46170.25</v>
       </c>
       <c r="R56" s="4">
-        <v>46188.402503240737</v>
+        <v>46170.38833533565</v>
       </c>
       <c r="S56">
-        <v>8272.000</v>
+        <v>767.000</v>
       </c>
       <c r="T56">
-        <v>8272.000</v>
+        <v>767.000</v>
       </c>
       <c r="U56">
         <v>0</v>
@@ -3917,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="W56" s="4">
-        <v>46188.404413310185</v>
+        <v>46171.521805752316</v>
       </c>
     </row>
     <row r="57">
@@ -3925,43 +3901,43 @@
         <v>19</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E57">
-        <v>7306694</v>
+        <v>7186225</v>
       </c>
       <c r="F57" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="G57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M57" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="P57" s="1">
-        <v>46178.650135613425</v>
+        <v>46157.585703935183</v>
       </c>
       <c r="Q57" s="4">
-        <v>46181.3125</v>
+        <v>46160.493105243055</v>
       </c>
       <c r="R57" s="4">
-        <v>46188.351883217591</v>
+        <v>46170.487253356485</v>
       </c>
       <c r="S57">
-        <v>7291.000</v>
+        <v>13685.000</v>
       </c>
       <c r="T57">
-        <v>7291.000</v>
+        <v>13685.000</v>
       </c>
       <c r="U57">
         <v>0</v>
@@ -3970,7 +3946,7 @@
         <v>0</v>
       </c>
       <c r="W57" s="4">
-        <v>46188.368130405092</v>
+        <v>46171.521805011573</v>
       </c>
     </row>
     <row r="58">
@@ -3978,43 +3954,43 @@
         <v>19</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E58">
-        <v>7306693</v>
+        <v>7243667</v>
       </c>
       <c r="F58" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="G58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M58" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="P58" s="1">
-        <v>46178.650101388892</v>
+        <v>46167.398084108798</v>
       </c>
       <c r="Q58" s="4">
-        <v>46181.395833333336</v>
+        <v>46170.25</v>
       </c>
       <c r="R58" s="4">
-        <v>46188.361928472223</v>
+        <v>46170.366140659724</v>
       </c>
       <c r="S58">
-        <v>5272.000</v>
+        <v>7345.000</v>
       </c>
       <c r="T58">
-        <v>5272.000</v>
+        <v>7345.000</v>
       </c>
       <c r="U58">
         <v>0</v>
@@ -4023,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="W58" s="4">
-        <v>46188.368129826391</v>
+        <v>46170.37235636574</v>
       </c>
     </row>
     <row r="59">
@@ -4031,43 +4007,43 @@
         <v>19</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E59">
-        <v>7306692</v>
+        <v>7243666</v>
       </c>
       <c r="F59" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="G59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H59" t="s">
-        <v>24</v>
-      </c>
-      <c r="M59" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="O59" s="4">
-        <v>46181.34375</v>
+        <v>23</v>
+      </c>
+      <c r="M59" t="s">
+        <v>140</v>
       </c>
       <c r="P59" s="1">
-        <v>46178.650014085651</v>
+        <v>46167.397709988429</v>
+      </c>
+      <c r="Q59" s="4">
+        <v>46169.444444444445</v>
       </c>
       <c r="R59" s="4">
-        <v>46188.321652777777</v>
+        <v>46169.627317511571</v>
       </c>
       <c r="S59">
-        <v>10749.000</v>
+        <v>5379.000</v>
       </c>
       <c r="T59">
-        <v>10749.000</v>
+        <v>5379.000</v>
       </c>
       <c r="U59">
         <v>0</v>
@@ -4076,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="W59" s="4">
-        <v>46188.329306516207</v>
+        <v>46170.372355636573</v>
       </c>
     </row>
     <row r="60">
@@ -4084,43 +4060,43 @@
         <v>19</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E60">
-        <v>7297492</v>
+        <v>7243660</v>
       </c>
       <c r="F60" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="G60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M60" t="s">
-        <v>118</v>
-      </c>
-      <c r="O60" s="4">
-        <v>46178.427083333336</v>
+        <v>142</v>
       </c>
       <c r="P60" s="1">
-        <v>46176.651338159725</v>
+        <v>46167.396469907406</v>
+      </c>
+      <c r="Q60" s="4">
+        <v>46168.375</v>
       </c>
       <c r="R60" s="4">
-        <v>46178.483032060183</v>
+        <v>46168.522693749997</v>
       </c>
       <c r="S60">
-        <v>6802.000</v>
+        <v>15726.000</v>
       </c>
       <c r="T60">
-        <v>6802.000</v>
+        <v>15726.000</v>
       </c>
       <c r="U60">
         <v>0</v>
@@ -4129,7 +4105,7 @@
         <v>0</v>
       </c>
       <c r="W60" s="4">
-        <v>46181.304573692127</v>
+        <v>46168.603323611111</v>
       </c>
     </row>
     <row r="61">
@@ -4137,46 +4113,43 @@
         <v>19</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E61">
-        <v>7297491</v>
+        <v>7243658</v>
       </c>
       <c r="F61" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="G61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M61" t="s">
-        <v>120</v>
-      </c>
-      <c r="O61" s="4">
-        <v>46178.416666666664</v>
+        <v>144</v>
       </c>
       <c r="P61" s="1">
-        <v>46176.651283530089</v>
+        <v>46167.396019097221</v>
       </c>
       <c r="Q61" s="4">
-        <v>46178.260416666664</v>
+        <v>46168.479166666664</v>
       </c>
       <c r="R61" s="4">
-        <v>46182.304580173608</v>
+        <v>46168.596083993056</v>
       </c>
       <c r="S61">
-        <v>19653.000</v>
+        <v>18164.000</v>
       </c>
       <c r="T61">
-        <v>19653.000</v>
+        <v>18164.000</v>
       </c>
       <c r="U61">
         <v>0</v>
@@ -4185,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="W61" s="4">
-        <v>46182.394867361108</v>
+        <v>46168.603323067131</v>
       </c>
     </row>
     <row r="62">
@@ -4193,40 +4166,40 @@
         <v>19</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E62">
-        <v>7296112</v>
+        <v>7209851</v>
       </c>
       <c r="F62" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="G62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M62" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="P62" s="1">
-        <v>46176.490794872683</v>
+        <v>46161.374809525463</v>
       </c>
       <c r="R62" s="4">
-        <v>46188.357570370368</v>
+        <v>46168.442082719906</v>
       </c>
       <c r="S62">
-        <v>7146.000</v>
+        <v>10564.000</v>
       </c>
       <c r="T62">
-        <v>7146.000</v>
+        <v>10564.000</v>
       </c>
       <c r="U62">
         <v>0</v>
@@ -4235,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="W62" s="4">
-        <v>46188.368129664355</v>
+        <v>46168.603322337964</v>
       </c>
     </row>
     <row r="63">
@@ -4243,43 +4216,43 @@
         <v>19</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E63">
-        <v>7290516</v>
+        <v>7243663</v>
       </c>
       <c r="F63" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="G63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M63" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="P63" s="1">
-        <v>46175.705564502314</v>
+        <v>46167.396879664353</v>
       </c>
       <c r="Q63" s="4">
-        <v>46176.59375</v>
+        <v>46168.3125</v>
       </c>
       <c r="R63" s="4">
-        <v>46178.37381646991</v>
+        <v>46168.372719247687</v>
       </c>
       <c r="S63">
-        <v>6600.000</v>
+        <v>7178.000</v>
       </c>
       <c r="T63">
-        <v>6600.000</v>
+        <v>7178.000</v>
       </c>
       <c r="U63">
         <v>0</v>
@@ -4288,7 +4261,7 @@
         <v>0</v>
       </c>
       <c r="W63" s="4">
-        <v>46181.304297951392</v>
+        <v>46168.383504201389</v>
       </c>
     </row>
     <row r="64">
@@ -4296,43 +4269,43 @@
         <v>19</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E64">
-        <v>7290515</v>
+        <v>7243656</v>
       </c>
       <c r="F64" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M64" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="P64" s="1">
-        <v>46175.705520370371</v>
+        <v>46167.395494872682</v>
       </c>
       <c r="Q64" s="4">
-        <v>46175.604166666664</v>
+        <v>46168.25</v>
       </c>
       <c r="R64" s="4">
-        <v>46176.32743784722</v>
+        <v>46168.325715162035</v>
       </c>
       <c r="S64">
-        <v>9893.000</v>
+        <v>8924.000</v>
       </c>
       <c r="T64">
-        <v>9893.000</v>
+        <v>8924.000</v>
       </c>
       <c r="U64">
         <v>0</v>
@@ -4341,7 +4314,7 @@
         <v>0</v>
       </c>
       <c r="W64" s="4">
-        <v>46176.36704571759</v>
+        <v>46168.383503321762</v>
       </c>
     </row>
     <row r="65">
@@ -4349,43 +4322,40 @@
         <v>19</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E65">
-        <v>7290513</v>
+        <v>7234523</v>
       </c>
       <c r="F65" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="G65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M65" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="P65" s="1">
-        <v>46175.705472835645</v>
-      </c>
-      <c r="Q65" s="4">
-        <v>46175.541666666664</v>
+        <v>46164.418446909724</v>
       </c>
       <c r="R65" s="4">
-        <v>46176.390187384262</v>
+        <v>46164.542648229166</v>
       </c>
       <c r="S65">
-        <v>10634.000</v>
+        <v>3573.000</v>
       </c>
       <c r="T65">
-        <v>10634.000</v>
+        <v>3573.000</v>
       </c>
       <c r="U65">
         <v>0</v>
@@ -4394,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="W65" s="4">
-        <v>46176.479922453706</v>
+        <v>46164.552599270835</v>
       </c>
     </row>
     <row r="66">
@@ -4402,43 +4372,43 @@
         <v>19</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E66">
-        <v>7290512</v>
+        <v>7222955</v>
       </c>
       <c r="F66" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="G66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M66" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="P66" s="1">
-        <v>46175.705376817132</v>
+        <v>46162.757414780091</v>
       </c>
       <c r="Q66" s="4">
-        <v>46176.5</v>
+        <v>46164.260416666664</v>
       </c>
       <c r="R66" s="4">
-        <v>46188.325696840278</v>
+        <v>46164.550929016201</v>
       </c>
       <c r="S66">
-        <v>14234.000</v>
+        <v>10360.000</v>
       </c>
       <c r="T66">
-        <v>14234.000</v>
+        <v>10360.000</v>
       </c>
       <c r="U66">
         <v>0</v>
@@ -4447,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="W66" s="4">
-        <v>46188.329304166669</v>
+        <v>46164.552598877315</v>
       </c>
     </row>
     <row r="67">
@@ -4455,43 +4425,43 @@
         <v>19</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E67">
-        <v>7277755</v>
+        <v>7222913</v>
       </c>
       <c r="F67" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="G67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H67" t="s">
-        <v>24</v>
-      </c>
-      <c r="M67" t="s">
-        <v>132</v>
+        <v>23</v>
+      </c>
+      <c r="M67" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="P67" s="1">
-        <v>46174.492233680554</v>
+        <v>46162.756352662036</v>
       </c>
       <c r="Q67" s="4">
-        <v>46175.291666666664</v>
+        <v>46164.333333333336</v>
       </c>
       <c r="R67" s="4">
-        <v>46175.460509027776</v>
+        <v>46164.404302395837</v>
       </c>
       <c r="S67">
-        <v>1502.000</v>
+        <v>7657.000</v>
       </c>
       <c r="T67">
-        <v>1502.000</v>
+        <v>7657.000</v>
       </c>
       <c r="U67">
         <v>0</v>
@@ -4500,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="W67" s="4">
-        <v>46176.367452777777</v>
+        <v>46164.453907951392</v>
       </c>
     </row>
     <row r="68">
@@ -4508,43 +4478,43 @@
         <v>19</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E68">
-        <v>7277745</v>
+        <v>7217995</v>
       </c>
       <c r="F68" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="G68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M68" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="P68" s="1">
-        <v>46174.492115972222</v>
+        <v>46162.28924351852</v>
       </c>
       <c r="Q68" s="4">
-        <v>46175.291666666664</v>
+        <v>46163.291666666664</v>
       </c>
       <c r="R68" s="4">
-        <v>46176.394080127313</v>
+        <v>46163.616474340277</v>
       </c>
       <c r="S68">
-        <v>8925.000</v>
+        <v>5708.000</v>
       </c>
       <c r="T68">
-        <v>8925.000</v>
+        <v>5708.000</v>
       </c>
       <c r="U68">
         <v>0</v>
@@ -4553,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="W68" s="4">
-        <v>46176.479621759259</v>
+        <v>46164.389474687501</v>
       </c>
     </row>
     <row r="69">
@@ -4561,43 +4531,46 @@
         <v>19</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C69" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D69" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E69">
-        <v>7277744</v>
+        <v>7209848</v>
       </c>
       <c r="F69" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="G69" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H69" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M69" t="s">
-        <v>136</v>
+        <v>160</v>
+      </c>
+      <c r="O69" s="4">
+        <v>46161.291666666664</v>
       </c>
       <c r="P69" s="1">
-        <v>46174.49203425926</v>
+        <v>46161.373708449071</v>
       </c>
       <c r="Q69" s="4">
-        <v>46174.5</v>
+        <v>46161.586805555555</v>
       </c>
       <c r="R69" s="4">
-        <v>46175.401104085649</v>
+        <v>46163.626690358797</v>
       </c>
       <c r="S69">
-        <v>14377.000</v>
+        <v>16674.000</v>
       </c>
       <c r="T69">
-        <v>14377.000</v>
+        <v>16674.000</v>
       </c>
       <c r="U69">
         <v>0</v>
@@ -4606,7 +4579,7 @@
         <v>0</v>
       </c>
       <c r="W69" s="4">
-        <v>46175.446175925928</v>
+        <v>46164.389386608796</v>
       </c>
     </row>
     <row r="70">
@@ -4614,43 +4587,43 @@
         <v>19</v>
       </c>
       <c r="B70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E70">
-        <v>7277742</v>
+        <v>7222907</v>
       </c>
       <c r="F70" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="G70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M70" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="P70" s="1">
-        <v>46174.491930821758</v>
+        <v>46162.75522561343</v>
       </c>
       <c r="Q70" s="4">
-        <v>46174.416666666664</v>
+        <v>46163.368055555555</v>
       </c>
       <c r="R70" s="4">
-        <v>46188.313768368054</v>
+        <v>46163.519357025463</v>
       </c>
       <c r="S70">
-        <v>18914.000</v>
+        <v>10357.000</v>
       </c>
       <c r="T70">
-        <v>18914.000</v>
+        <v>10357.000</v>
       </c>
       <c r="U70">
         <v>0</v>
@@ -4659,7 +4632,7 @@
         <v>0</v>
       </c>
       <c r="W70" s="4">
-        <v>46188.329302546299</v>
+        <v>46163.541440972222</v>
       </c>
     </row>
     <row r="71">
@@ -4667,43 +4640,43 @@
         <v>19</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E71">
-        <v>7276672</v>
+        <v>7217994</v>
       </c>
       <c r="F71" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="G71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M71" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="P71" s="1">
-        <v>46174.386965358797</v>
+        <v>46162.288815127315</v>
       </c>
       <c r="Q71" s="4">
-        <v>46174.3125</v>
+        <v>46163.291666666664</v>
       </c>
       <c r="R71" s="4">
-        <v>46175.277797997682</v>
+        <v>46163.35348445602</v>
       </c>
       <c r="S71">
-        <v>445.000</v>
+        <v>3946.000</v>
       </c>
       <c r="T71">
-        <v>445.000</v>
+        <v>3946.000</v>
       </c>
       <c r="U71">
         <v>0</v>
@@ -4712,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="W71" s="4">
-        <v>46175.446175925928</v>
+        <v>46163.541440775465</v>
       </c>
     </row>
     <row r="72">
@@ -4720,43 +4693,46 @@
         <v>19</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E72">
-        <v>7276670</v>
+        <v>7217993</v>
       </c>
       <c r="F72" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="G72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M72" t="s">
-        <v>142</v>
+        <v>166</v>
+      </c>
+      <c r="O72" s="4">
+        <v>46162.416666666664</v>
       </c>
       <c r="P72" s="1">
-        <v>46174.386795023151</v>
+        <v>46162.287909756946</v>
       </c>
       <c r="Q72" s="4">
-        <v>46174.3125</v>
+        <v>46162.416666666664</v>
       </c>
       <c r="R72" s="4">
-        <v>46181.602299189813</v>
+        <v>46163.518015046298</v>
       </c>
       <c r="S72">
-        <v>7766.000</v>
+        <v>12356.000</v>
       </c>
       <c r="T72">
-        <v>7766.000</v>
+        <v>12356.000</v>
       </c>
       <c r="U72">
         <v>0</v>
@@ -4765,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="W72" s="4">
-        <v>46181.607877893519</v>
+        <v>46163.541439895831</v>
       </c>
     </row>
     <row r="73">
@@ -4773,40 +4749,46 @@
         <v>19</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E73">
-        <v>7261067</v>
+        <v>7217991</v>
       </c>
       <c r="F73" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="G73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M73" t="s">
-        <v>144</v>
+        <v>168</v>
+      </c>
+      <c r="O73" s="4">
+        <v>46162.291666666664</v>
       </c>
       <c r="P73" s="1">
-        <v>46171.450339317133</v>
+        <v>46162.28736678241</v>
+      </c>
+      <c r="Q73" s="4">
+        <v>46162.513220173612</v>
       </c>
       <c r="R73" s="4">
-        <v>46171.468652743053</v>
+        <v>46163.531940428242</v>
       </c>
       <c r="S73">
-        <v>13827.000</v>
+        <v>12360.000</v>
       </c>
       <c r="T73">
-        <v>13827.000</v>
+        <v>12360.000</v>
       </c>
       <c r="U73">
         <v>0</v>
@@ -4815,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="W73" s="4">
-        <v>46171.521808101854</v>
+        <v>46163.541439351851</v>
       </c>
     </row>
     <row r="74">
@@ -4823,43 +4805,40 @@
         <v>19</v>
       </c>
       <c r="B74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E74">
-        <v>7256959</v>
+        <v>7209853</v>
       </c>
       <c r="F74" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="G74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M74" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="P74" s="1">
-        <v>46169.73840185185</v>
-      </c>
-      <c r="Q74" s="4">
-        <v>46171.520833333336</v>
+        <v>46161.375624884262</v>
       </c>
       <c r="R74" s="4">
-        <v>46181.602367395833</v>
+        <v>46162.474544826386</v>
       </c>
       <c r="S74">
-        <v>11921.000</v>
+        <v>10350.000</v>
       </c>
       <c r="T74">
-        <v>11921.000</v>
+        <v>10350.000</v>
       </c>
       <c r="U74">
         <v>0</v>
@@ -4868,7 +4847,7 @@
         <v>0</v>
       </c>
       <c r="W74" s="4">
-        <v>46181.607877002316</v>
+        <v>46163.484965937503</v>
       </c>
     </row>
     <row r="75">
@@ -4876,43 +4855,43 @@
         <v>19</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E75">
-        <v>7256954</v>
+        <v>7186224</v>
       </c>
       <c r="F75" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="G75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M75" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="P75" s="1">
-        <v>46169.737280092595</v>
+        <v>46157.585680983793</v>
       </c>
       <c r="Q75" s="4">
-        <v>46171.416666666664</v>
+        <v>46160.493105243055</v>
       </c>
       <c r="R75" s="4">
-        <v>46171.471500266205</v>
+        <v>46160.607764236112</v>
       </c>
       <c r="S75">
-        <v>11226.000</v>
+        <v>8153.000</v>
       </c>
       <c r="T75">
-        <v>11226.000</v>
+        <v>8153.000</v>
       </c>
       <c r="U75">
         <v>0</v>
@@ -4921,7 +4900,7 @@
         <v>0</v>
       </c>
       <c r="W75" s="4">
-        <v>46171.521807557867</v>
+        <v>46161.606680011573</v>
       </c>
     </row>
     <row r="76">
@@ -4929,43 +4908,43 @@
         <v>19</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E76">
-        <v>7256935</v>
+        <v>7186209</v>
       </c>
       <c r="F76" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="G76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M76" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="P76" s="1">
-        <v>46169.735800810187</v>
+        <v>46157.580364664354</v>
       </c>
       <c r="Q76" s="4">
-        <v>46171.25</v>
+        <v>46160.367256516205</v>
       </c>
       <c r="R76" s="4">
-        <v>46171.474860069444</v>
+        <v>46160.444021875002</v>
       </c>
       <c r="S76">
-        <v>12909.000</v>
+        <v>19189.000</v>
       </c>
       <c r="T76">
-        <v>12909.000</v>
+        <v>19189.000</v>
       </c>
       <c r="U76">
         <v>0</v>
@@ -4974,7 +4953,7 @@
         <v>0</v>
       </c>
       <c r="W76" s="4">
-        <v>46171.521807025463</v>
+        <v>46161.605472025461</v>
       </c>
     </row>
     <row r="77">
@@ -4982,46 +4961,43 @@
         <v>19</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E77">
-        <v>7256927</v>
+        <v>7185903</v>
       </c>
       <c r="F77" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="G77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M77" t="s">
-        <v>152</v>
-      </c>
-      <c r="O77" s="4">
-        <v>46170.541666666664</v>
+        <v>175</v>
       </c>
       <c r="P77" s="1">
-        <v>46169.733974768518</v>
+        <v>46157.55131412037</v>
       </c>
       <c r="Q77" s="4">
-        <v>46171.375</v>
+        <v>46160.493105243055</v>
       </c>
       <c r="R77" s="4">
-        <v>46171.384800081018</v>
+        <v>46160.545683645832</v>
       </c>
       <c r="S77">
-        <v>470.000</v>
+        <v>39356.000</v>
       </c>
       <c r="T77">
-        <v>470.000</v>
+        <v>39356.000</v>
       </c>
       <c r="U77">
         <v>0</v>
@@ -5030,7 +5006,7 @@
         <v>0</v>
       </c>
       <c r="W77" s="4">
-        <v>46171.521806828707</v>
+        <v>46161.604525312498</v>
       </c>
     </row>
     <row r="78">
@@ -5038,46 +5014,46 @@
         <v>19</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E78">
-        <v>7256837</v>
+        <v>7177836</v>
       </c>
       <c r="F78" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="G78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M78" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="O78" s="4">
-        <v>46170.541666666664</v>
+        <v>46157.416666666664</v>
       </c>
       <c r="P78" s="1">
-        <v>46169.717724456015</v>
+        <v>46155.705813773151</v>
       </c>
       <c r="Q78" s="4">
-        <v>46171.375</v>
+        <v>46157.466666666667</v>
       </c>
       <c r="R78" s="4">
-        <v>46181.601758877317</v>
+        <v>46160.360912615739</v>
       </c>
       <c r="S78">
-        <v>10645.000</v>
+        <v>17794.000</v>
       </c>
       <c r="T78">
-        <v>10645.000</v>
+        <v>17794.000</v>
       </c>
       <c r="U78">
         <v>0</v>
@@ -5086,7 +5062,7 @@
         <v>0</v>
       </c>
       <c r="W78" s="4">
-        <v>46181.607876122682</v>
+        <v>46160.503910451385</v>
       </c>
     </row>
     <row r="79">
@@ -5094,46 +5070,46 @@
         <v>19</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E79">
-        <v>7256698</v>
+        <v>7175007</v>
       </c>
       <c r="F79" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M79" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="O79" s="4">
-        <v>46170.416666666664</v>
+        <v>46157.291666666664</v>
       </c>
       <c r="P79" s="1">
-        <v>46169.704318553238</v>
+        <v>46155.454049652777</v>
       </c>
       <c r="Q79" s="4">
-        <v>46170.4375</v>
+        <v>46157.35833333333</v>
       </c>
       <c r="R79" s="4">
-        <v>46170.55747615741</v>
+        <v>46157.601774965275</v>
       </c>
       <c r="S79">
-        <v>15811.000</v>
+        <v>21375.000</v>
       </c>
       <c r="T79">
-        <v>15811.000</v>
+        <v>21375.000</v>
       </c>
       <c r="U79">
         <v>0</v>
@@ -5142,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="W79" s="4">
-        <v>46171.52180628472</v>
+        <v>46157.688587037039</v>
       </c>
     </row>
     <row r="80">
@@ -5150,46 +5126,40 @@
         <v>19</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E80">
-        <v>7256674</v>
+        <v>7167099</v>
       </c>
       <c r="F80" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="G80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M80" t="s">
-        <v>158</v>
-      </c>
-      <c r="O80" s="4">
-        <v>46170.291666666664</v>
+        <v>181</v>
       </c>
       <c r="P80" s="1">
-        <v>46169.697586805552</v>
-      </c>
-      <c r="Q80" s="4">
-        <v>46171.291666666664</v>
+        <v>46154.541764120368</v>
       </c>
       <c r="R80" s="4">
-        <v>46171.366929745367</v>
+        <v>46155.643980821762</v>
       </c>
       <c r="S80">
-        <v>6703.000</v>
+        <v>11855.000</v>
       </c>
       <c r="T80">
-        <v>6703.000</v>
+        <v>11855.000</v>
       </c>
       <c r="U80">
         <v>0</v>
@@ -5198,1464 +5168,24 @@
         <v>0</v>
       </c>
       <c r="W80" s="4">
-        <v>46171.521805937497</v>
+        <v>46157.304165428242</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="s">
-        <v>19</v>
-      </c>
-      <c r="B81" t="s">
-        <v>24</v>
-      </c>
-      <c r="C81" t="s">
-        <v>24</v>
-      </c>
-      <c r="D81" t="s">
-        <v>24</v>
-      </c>
-      <c r="E81">
-        <v>7243671</v>
-      </c>
-      <c r="F81" t="s">
-        <v>159</v>
-      </c>
-      <c r="G81" t="s">
-        <v>24</v>
-      </c>
-      <c r="H81" t="s">
-        <v>24</v>
-      </c>
-      <c r="M81" t="s">
-        <v>160</v>
-      </c>
-      <c r="P81" s="1">
-        <v>46167.398480636577</v>
-      </c>
-      <c r="Q81" s="4">
-        <v>46170.25</v>
-      </c>
-      <c r="R81" s="4">
-        <v>46170.38833533565</v>
-      </c>
-      <c r="S81">
-        <v>767.000</v>
-      </c>
-      <c r="T81">
-        <v>767.000</v>
-      </c>
-      <c r="U81">
-        <v>0</v>
-      </c>
-      <c r="V81">
-        <v>0</v>
-      </c>
-      <c r="W81" s="4">
-        <v>46171.521805752316</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>19</v>
-      </c>
-      <c r="B82" t="s">
-        <v>24</v>
-      </c>
-      <c r="C82" t="s">
-        <v>24</v>
-      </c>
-      <c r="D82" t="s">
-        <v>24</v>
-      </c>
-      <c r="E82">
-        <v>7243667</v>
-      </c>
-      <c r="F82" t="s">
-        <v>161</v>
-      </c>
-      <c r="G82" t="s">
-        <v>24</v>
-      </c>
-      <c r="H82" t="s">
-        <v>24</v>
-      </c>
-      <c r="M82" t="s">
-        <v>162</v>
-      </c>
-      <c r="P82" s="1">
-        <v>46167.398084108798</v>
-      </c>
-      <c r="Q82" s="4">
-        <v>46170.25</v>
-      </c>
-      <c r="R82" s="4">
-        <v>46170.366140659724</v>
-      </c>
-      <c r="S82">
-        <v>7345.000</v>
-      </c>
-      <c r="T82">
-        <v>7345.000</v>
-      </c>
-      <c r="U82">
-        <v>0</v>
-      </c>
-      <c r="V82">
-        <v>0</v>
-      </c>
-      <c r="W82" s="4">
-        <v>46170.37235636574</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>19</v>
-      </c>
-      <c r="B83" t="s">
-        <v>24</v>
-      </c>
-      <c r="C83" t="s">
-        <v>24</v>
-      </c>
-      <c r="D83" t="s">
-        <v>24</v>
-      </c>
-      <c r="E83">
-        <v>7243666</v>
-      </c>
-      <c r="F83" t="s">
-        <v>163</v>
-      </c>
-      <c r="G83" t="s">
-        <v>24</v>
-      </c>
-      <c r="H83" t="s">
-        <v>24</v>
-      </c>
-      <c r="M83" t="s">
-        <v>164</v>
-      </c>
-      <c r="P83" s="1">
-        <v>46167.397709988429</v>
-      </c>
-      <c r="Q83" s="4">
-        <v>46169.444444444445</v>
-      </c>
-      <c r="R83" s="4">
-        <v>46169.627317511571</v>
-      </c>
-      <c r="S83">
-        <v>5379.000</v>
-      </c>
-      <c r="T83">
-        <v>5379.000</v>
-      </c>
-      <c r="U83">
-        <v>0</v>
-      </c>
-      <c r="V83">
-        <v>0</v>
-      </c>
-      <c r="W83" s="4">
-        <v>46170.372355636573</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>19</v>
-      </c>
-      <c r="B84" t="s">
-        <v>24</v>
-      </c>
-      <c r="C84" t="s">
-        <v>24</v>
-      </c>
-      <c r="D84" t="s">
-        <v>24</v>
-      </c>
-      <c r="E84">
-        <v>7243664</v>
-      </c>
-      <c r="F84" t="s">
-        <v>165</v>
-      </c>
-      <c r="G84" t="s">
-        <v>24</v>
-      </c>
-      <c r="H84" t="s">
-        <v>24</v>
-      </c>
-      <c r="M84" t="s">
-        <v>166</v>
-      </c>
-      <c r="P84" s="1">
-        <v>46167.397293715279</v>
-      </c>
-      <c r="Q84" s="4">
-        <v>46169.3125</v>
-      </c>
-      <c r="R84" s="4">
-        <v>46170.486638159724</v>
-      </c>
-      <c r="S84">
-        <v>5002.000</v>
-      </c>
-      <c r="T84">
-        <v>5002.000</v>
-      </c>
-      <c r="U84">
-        <v>0</v>
-      </c>
-      <c r="V84">
-        <v>0</v>
-      </c>
-      <c r="W84" s="4">
-        <v>46171.52288329861</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>19</v>
-      </c>
-      <c r="B85" t="s">
-        <v>24</v>
-      </c>
-      <c r="C85" t="s">
-        <v>24</v>
-      </c>
-      <c r="D85" t="s">
-        <v>24</v>
-      </c>
-      <c r="E85">
-        <v>7243663</v>
-      </c>
-      <c r="F85" t="s">
-        <v>167</v>
-      </c>
-      <c r="G85" t="s">
-        <v>24</v>
-      </c>
-      <c r="H85" t="s">
-        <v>24</v>
-      </c>
-      <c r="M85" t="s">
-        <v>168</v>
-      </c>
-      <c r="P85" s="1">
-        <v>46167.396879664353</v>
-      </c>
-      <c r="Q85" s="4">
-        <v>46168.3125</v>
-      </c>
-      <c r="R85" s="4">
-        <v>46168.372719247687</v>
-      </c>
-      <c r="S85">
-        <v>7178.000</v>
-      </c>
-      <c r="T85">
-        <v>7178.000</v>
-      </c>
-      <c r="U85">
-        <v>0</v>
-      </c>
-      <c r="V85">
-        <v>0</v>
-      </c>
-      <c r="W85" s="4">
-        <v>46168.383504201389</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>19</v>
-      </c>
-      <c r="B86" t="s">
-        <v>24</v>
-      </c>
-      <c r="C86" t="s">
-        <v>24</v>
-      </c>
-      <c r="D86" t="s">
-        <v>24</v>
-      </c>
-      <c r="E86">
-        <v>7243660</v>
-      </c>
-      <c r="F86" t="s">
-        <v>169</v>
-      </c>
-      <c r="G86" t="s">
-        <v>24</v>
-      </c>
-      <c r="H86" t="s">
-        <v>24</v>
-      </c>
-      <c r="M86" t="s">
-        <v>170</v>
-      </c>
-      <c r="P86" s="1">
-        <v>46167.396469907406</v>
-      </c>
-      <c r="Q86" s="4">
-        <v>46168.375</v>
-      </c>
-      <c r="R86" s="4">
-        <v>46168.522693749997</v>
-      </c>
-      <c r="S86">
-        <v>15726.000</v>
-      </c>
-      <c r="T86">
-        <v>15726.000</v>
-      </c>
-      <c r="U86">
-        <v>0</v>
-      </c>
-      <c r="V86">
-        <v>0</v>
-      </c>
-      <c r="W86" s="4">
-        <v>46168.603323611111</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>19</v>
-      </c>
-      <c r="B87" t="s">
-        <v>24</v>
-      </c>
-      <c r="C87" t="s">
-        <v>24</v>
-      </c>
-      <c r="D87" t="s">
-        <v>24</v>
-      </c>
-      <c r="E87">
-        <v>7243658</v>
-      </c>
-      <c r="F87" t="s">
-        <v>171</v>
-      </c>
-      <c r="G87" t="s">
-        <v>24</v>
-      </c>
-      <c r="H87" t="s">
-        <v>24</v>
-      </c>
-      <c r="M87" t="s">
-        <v>172</v>
-      </c>
-      <c r="P87" s="1">
-        <v>46167.396019097221</v>
-      </c>
-      <c r="Q87" s="4">
-        <v>46168.479166666664</v>
-      </c>
-      <c r="R87" s="4">
-        <v>46168.596083993056</v>
-      </c>
-      <c r="S87">
-        <v>18164.000</v>
-      </c>
-      <c r="T87">
-        <v>18164.000</v>
-      </c>
-      <c r="U87">
-        <v>0</v>
-      </c>
-      <c r="V87">
-        <v>0</v>
-      </c>
-      <c r="W87" s="4">
-        <v>46168.603323067131</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>19</v>
-      </c>
-      <c r="B88" t="s">
-        <v>24</v>
-      </c>
-      <c r="C88" t="s">
-        <v>24</v>
-      </c>
-      <c r="D88" t="s">
-        <v>24</v>
-      </c>
-      <c r="E88">
-        <v>7243656</v>
-      </c>
-      <c r="F88" t="s">
-        <v>173</v>
-      </c>
-      <c r="G88" t="s">
-        <v>24</v>
-      </c>
-      <c r="H88" t="s">
-        <v>24</v>
-      </c>
-      <c r="M88" t="s">
-        <v>174</v>
-      </c>
-      <c r="P88" s="1">
-        <v>46167.395494872682</v>
-      </c>
-      <c r="Q88" s="4">
-        <v>46168.25</v>
-      </c>
-      <c r="R88" s="4">
-        <v>46168.325715162035</v>
-      </c>
-      <c r="S88">
-        <v>8924.000</v>
-      </c>
-      <c r="T88">
-        <v>8924.000</v>
-      </c>
-      <c r="U88">
-        <v>0</v>
-      </c>
-      <c r="V88">
-        <v>0</v>
-      </c>
-      <c r="W88" s="4">
-        <v>46168.383503321762</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>19</v>
-      </c>
-      <c r="B89" t="s">
-        <v>24</v>
-      </c>
-      <c r="C89" t="s">
-        <v>24</v>
-      </c>
-      <c r="D89" t="s">
-        <v>24</v>
-      </c>
-      <c r="E89">
-        <v>7234523</v>
-      </c>
-      <c r="F89" t="s">
-        <v>175</v>
-      </c>
-      <c r="G89" t="s">
-        <v>24</v>
-      </c>
-      <c r="H89" t="s">
-        <v>24</v>
-      </c>
-      <c r="M89" t="s">
-        <v>176</v>
-      </c>
-      <c r="P89" s="1">
-        <v>46164.418446909724</v>
-      </c>
-      <c r="R89" s="4">
-        <v>46164.542648229166</v>
-      </c>
-      <c r="S89">
-        <v>3573.000</v>
-      </c>
-      <c r="T89">
-        <v>3573.000</v>
-      </c>
-      <c r="U89">
-        <v>0</v>
-      </c>
-      <c r="V89">
-        <v>0</v>
-      </c>
-      <c r="W89" s="4">
-        <v>46164.552599270835</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>19</v>
-      </c>
-      <c r="B90" t="s">
-        <v>24</v>
-      </c>
-      <c r="C90" t="s">
-        <v>24</v>
-      </c>
-      <c r="D90" t="s">
-        <v>24</v>
-      </c>
-      <c r="E90">
-        <v>7222955</v>
-      </c>
-      <c r="F90" t="s">
-        <v>177</v>
-      </c>
-      <c r="G90" t="s">
-        <v>24</v>
-      </c>
-      <c r="H90" t="s">
-        <v>24</v>
-      </c>
-      <c r="M90" t="s">
-        <v>178</v>
-      </c>
-      <c r="P90" s="1">
-        <v>46162.757414780091</v>
-      </c>
-      <c r="Q90" s="4">
-        <v>46164.260416666664</v>
-      </c>
-      <c r="R90" s="4">
-        <v>46164.550929016201</v>
-      </c>
-      <c r="S90">
-        <v>10360.000</v>
-      </c>
-      <c r="T90">
-        <v>10360.000</v>
-      </c>
-      <c r="U90">
-        <v>0</v>
-      </c>
-      <c r="V90">
-        <v>0</v>
-      </c>
-      <c r="W90" s="4">
-        <v>46164.552598877315</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>19</v>
-      </c>
-      <c r="B91" t="s">
-        <v>24</v>
-      </c>
-      <c r="C91" t="s">
-        <v>24</v>
-      </c>
-      <c r="D91" t="s">
-        <v>24</v>
-      </c>
-      <c r="E91">
-        <v>7222913</v>
-      </c>
-      <c r="F91" t="s">
-        <v>179</v>
-      </c>
-      <c r="G91" t="s">
-        <v>24</v>
-      </c>
-      <c r="H91" t="s">
-        <v>24</v>
-      </c>
-      <c r="M91" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="P91" s="1">
-        <v>46162.756352662036</v>
-      </c>
-      <c r="Q91" s="4">
-        <v>46164.333333333336</v>
-      </c>
-      <c r="R91" s="4">
-        <v>46164.404302395837</v>
-      </c>
-      <c r="S91">
-        <v>7657.000</v>
-      </c>
-      <c r="T91">
-        <v>7657.000</v>
-      </c>
-      <c r="U91">
-        <v>0</v>
-      </c>
-      <c r="V91">
-        <v>0</v>
-      </c>
-      <c r="W91" s="4">
-        <v>46164.453907951392</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>19</v>
-      </c>
-      <c r="B92" t="s">
-        <v>24</v>
-      </c>
-      <c r="C92" t="s">
-        <v>24</v>
-      </c>
-      <c r="D92" t="s">
-        <v>24</v>
-      </c>
-      <c r="E92">
-        <v>7222907</v>
-      </c>
-      <c r="F92" t="s">
-        <v>181</v>
-      </c>
-      <c r="G92" t="s">
-        <v>24</v>
-      </c>
-      <c r="H92" t="s">
-        <v>24</v>
-      </c>
-      <c r="M92" t="s">
-        <v>182</v>
-      </c>
-      <c r="P92" s="1">
-        <v>46162.75522561343</v>
-      </c>
-      <c r="Q92" s="4">
-        <v>46163.368055555555</v>
-      </c>
-      <c r="R92" s="4">
-        <v>46163.519357025463</v>
-      </c>
-      <c r="S92">
-        <v>10357.000</v>
-      </c>
-      <c r="T92">
-        <v>10357.000</v>
-      </c>
-      <c r="U92">
-        <v>0</v>
-      </c>
-      <c r="V92">
-        <v>0</v>
-      </c>
-      <c r="W92" s="4">
-        <v>46163.541440972222</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>19</v>
-      </c>
-      <c r="B93" t="s">
-        <v>24</v>
-      </c>
-      <c r="C93" t="s">
-        <v>24</v>
-      </c>
-      <c r="D93" t="s">
-        <v>24</v>
-      </c>
-      <c r="E93">
-        <v>7217995</v>
-      </c>
-      <c r="F93" t="s">
-        <v>183</v>
-      </c>
-      <c r="G93" t="s">
-        <v>24</v>
-      </c>
-      <c r="H93" t="s">
-        <v>24</v>
-      </c>
-      <c r="M93" t="s">
-        <v>184</v>
-      </c>
-      <c r="P93" s="1">
-        <v>46162.28924351852</v>
-      </c>
-      <c r="Q93" s="4">
-        <v>46163.291666666664</v>
-      </c>
-      <c r="R93" s="4">
-        <v>46163.616474340277</v>
-      </c>
-      <c r="S93">
-        <v>5708.000</v>
-      </c>
-      <c r="T93">
-        <v>5708.000</v>
-      </c>
-      <c r="U93">
-        <v>0</v>
-      </c>
-      <c r="V93">
-        <v>0</v>
-      </c>
-      <c r="W93" s="4">
-        <v>46164.389474687501</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B94" t="s">
-        <v>24</v>
-      </c>
-      <c r="C94" t="s">
-        <v>24</v>
-      </c>
-      <c r="D94" t="s">
-        <v>24</v>
-      </c>
-      <c r="E94">
-        <v>7217994</v>
-      </c>
-      <c r="F94" t="s">
-        <v>185</v>
-      </c>
-      <c r="G94" t="s">
-        <v>24</v>
-      </c>
-      <c r="H94" t="s">
-        <v>24</v>
-      </c>
-      <c r="M94" t="s">
-        <v>186</v>
-      </c>
-      <c r="P94" s="1">
-        <v>46162.288815127315</v>
-      </c>
-      <c r="Q94" s="4">
-        <v>46163.291666666664</v>
-      </c>
-      <c r="R94" s="4">
-        <v>46163.35348445602</v>
-      </c>
-      <c r="S94">
-        <v>3946.000</v>
-      </c>
-      <c r="T94">
-        <v>3946.000</v>
-      </c>
-      <c r="U94">
-        <v>0</v>
-      </c>
-      <c r="V94">
-        <v>0</v>
-      </c>
-      <c r="W94" s="4">
-        <v>46163.541440775465</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>19</v>
-      </c>
-      <c r="B95" t="s">
-        <v>24</v>
-      </c>
-      <c r="C95" t="s">
-        <v>24</v>
-      </c>
-      <c r="D95" t="s">
-        <v>24</v>
-      </c>
-      <c r="E95">
-        <v>7217993</v>
-      </c>
-      <c r="F95" t="s">
-        <v>187</v>
-      </c>
-      <c r="G95" t="s">
-        <v>24</v>
-      </c>
-      <c r="H95" t="s">
-        <v>24</v>
-      </c>
-      <c r="M95" t="s">
-        <v>188</v>
-      </c>
-      <c r="O95" s="4">
-        <v>46162.416666666664</v>
-      </c>
-      <c r="P95" s="1">
-        <v>46162.287909756946</v>
-      </c>
-      <c r="Q95" s="4">
-        <v>46162.416666666664</v>
-      </c>
-      <c r="R95" s="4">
-        <v>46163.518015046298</v>
-      </c>
-      <c r="S95">
-        <v>12356.000</v>
-      </c>
-      <c r="T95">
-        <v>12356.000</v>
-      </c>
-      <c r="U95">
-        <v>0</v>
-      </c>
-      <c r="V95">
-        <v>0</v>
-      </c>
-      <c r="W95" s="4">
-        <v>46163.541439895831</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>19</v>
-      </c>
-      <c r="B96" t="s">
-        <v>24</v>
-      </c>
-      <c r="C96" t="s">
-        <v>24</v>
-      </c>
-      <c r="D96" t="s">
-        <v>24</v>
-      </c>
-      <c r="E96">
-        <v>7217991</v>
-      </c>
-      <c r="F96" t="s">
-        <v>189</v>
-      </c>
-      <c r="G96" t="s">
-        <v>24</v>
-      </c>
-      <c r="H96" t="s">
-        <v>24</v>
-      </c>
-      <c r="M96" t="s">
-        <v>190</v>
-      </c>
-      <c r="O96" s="4">
-        <v>46162.291666666664</v>
-      </c>
-      <c r="P96" s="1">
-        <v>46162.28736678241</v>
-      </c>
-      <c r="Q96" s="4">
-        <v>46162.513220173612</v>
-      </c>
-      <c r="R96" s="4">
-        <v>46163.531940428242</v>
-      </c>
-      <c r="S96">
-        <v>12360.000</v>
-      </c>
-      <c r="T96">
-        <v>12360.000</v>
-      </c>
-      <c r="U96">
-        <v>0</v>
-      </c>
-      <c r="V96">
-        <v>0</v>
-      </c>
-      <c r="W96" s="4">
-        <v>46163.541439351851</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>19</v>
-      </c>
-      <c r="B97" t="s">
-        <v>24</v>
-      </c>
-      <c r="C97" t="s">
-        <v>24</v>
-      </c>
-      <c r="D97" t="s">
-        <v>24</v>
-      </c>
-      <c r="E97">
-        <v>7209853</v>
-      </c>
-      <c r="F97" t="s">
-        <v>191</v>
-      </c>
-      <c r="G97" t="s">
-        <v>24</v>
-      </c>
-      <c r="H97" t="s">
-        <v>24</v>
-      </c>
-      <c r="M97" t="s">
-        <v>192</v>
-      </c>
-      <c r="P97" s="1">
-        <v>46161.375624884262</v>
-      </c>
-      <c r="R97" s="4">
-        <v>46162.474544826386</v>
-      </c>
-      <c r="S97">
-        <v>10350.000</v>
-      </c>
-      <c r="T97">
-        <v>10350.000</v>
-      </c>
-      <c r="U97">
-        <v>0</v>
-      </c>
-      <c r="V97">
-        <v>0</v>
-      </c>
-      <c r="W97" s="4">
-        <v>46163.484965937503</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>19</v>
-      </c>
-      <c r="B98" t="s">
-        <v>24</v>
-      </c>
-      <c r="C98" t="s">
-        <v>24</v>
-      </c>
-      <c r="D98" t="s">
-        <v>24</v>
-      </c>
-      <c r="E98">
-        <v>7209851</v>
-      </c>
-      <c r="F98" t="s">
-        <v>193</v>
-      </c>
-      <c r="G98" t="s">
-        <v>24</v>
-      </c>
-      <c r="H98" t="s">
-        <v>24</v>
-      </c>
-      <c r="M98" t="s">
-        <v>194</v>
-      </c>
-      <c r="P98" s="1">
-        <v>46161.374809525463</v>
-      </c>
-      <c r="R98" s="4">
-        <v>46168.442082719906</v>
-      </c>
-      <c r="S98">
-        <v>10564.000</v>
-      </c>
-      <c r="T98">
-        <v>10564.000</v>
-      </c>
-      <c r="U98">
-        <v>0</v>
-      </c>
-      <c r="V98">
-        <v>0</v>
-      </c>
-      <c r="W98" s="4">
-        <v>46168.603322337964</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>19</v>
-      </c>
-      <c r="B99" t="s">
-        <v>24</v>
-      </c>
-      <c r="C99" t="s">
-        <v>24</v>
-      </c>
-      <c r="D99" t="s">
-        <v>24</v>
-      </c>
-      <c r="E99">
-        <v>7209848</v>
-      </c>
-      <c r="F99" t="s">
-        <v>195</v>
-      </c>
-      <c r="G99" t="s">
-        <v>24</v>
-      </c>
-      <c r="H99" t="s">
-        <v>24</v>
-      </c>
-      <c r="M99" t="s">
-        <v>196</v>
-      </c>
-      <c r="O99" s="4">
-        <v>46161.291666666664</v>
-      </c>
-      <c r="P99" s="1">
-        <v>46161.373708449071</v>
-      </c>
-      <c r="Q99" s="4">
-        <v>46161.586805555555</v>
-      </c>
-      <c r="R99" s="4">
-        <v>46163.626690358797</v>
-      </c>
-      <c r="S99">
-        <v>16674.000</v>
-      </c>
-      <c r="T99">
-        <v>16674.000</v>
-      </c>
-      <c r="U99">
-        <v>0</v>
-      </c>
-      <c r="V99">
-        <v>0</v>
-      </c>
-      <c r="W99" s="4">
-        <v>46164.389386608796</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>19</v>
-      </c>
-      <c r="B100" t="s">
-        <v>24</v>
-      </c>
-      <c r="C100" t="s">
-        <v>24</v>
-      </c>
-      <c r="D100" t="s">
-        <v>24</v>
-      </c>
-      <c r="E100">
-        <v>7186225</v>
-      </c>
-      <c r="F100" t="s">
-        <v>197</v>
-      </c>
-      <c r="G100" t="s">
-        <v>24</v>
-      </c>
-      <c r="H100" t="s">
-        <v>24</v>
-      </c>
-      <c r="M100" t="s">
-        <v>198</v>
-      </c>
-      <c r="P100" s="1">
-        <v>46157.585703935183</v>
-      </c>
-      <c r="Q100" s="4">
-        <v>46160.493105243055</v>
-      </c>
-      <c r="R100" s="4">
-        <v>46170.487253356485</v>
-      </c>
-      <c r="S100">
-        <v>13685.000</v>
-      </c>
-      <c r="T100">
-        <v>13685.000</v>
-      </c>
-      <c r="U100">
-        <v>0</v>
-      </c>
-      <c r="V100">
-        <v>0</v>
-      </c>
-      <c r="W100" s="4">
-        <v>46171.521805011573</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>19</v>
-      </c>
-      <c r="B101" t="s">
-        <v>24</v>
-      </c>
-      <c r="C101" t="s">
-        <v>24</v>
-      </c>
-      <c r="D101" t="s">
-        <v>24</v>
-      </c>
-      <c r="E101">
-        <v>7186224</v>
-      </c>
-      <c r="F101" t="s">
-        <v>199</v>
-      </c>
-      <c r="G101" t="s">
-        <v>24</v>
-      </c>
-      <c r="H101" t="s">
-        <v>24</v>
-      </c>
-      <c r="M101" t="s">
-        <v>198</v>
-      </c>
-      <c r="P101" s="1">
-        <v>46157.585680983793</v>
-      </c>
-      <c r="Q101" s="4">
-        <v>46160.493105243055</v>
-      </c>
-      <c r="R101" s="4">
-        <v>46160.607764236112</v>
-      </c>
-      <c r="S101">
-        <v>8153.000</v>
-      </c>
-      <c r="T101">
-        <v>8153.000</v>
-      </c>
-      <c r="U101">
-        <v>0</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101" s="4">
-        <v>46161.606680011573</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>19</v>
-      </c>
-      <c r="B102" t="s">
-        <v>24</v>
-      </c>
-      <c r="C102" t="s">
-        <v>24</v>
-      </c>
-      <c r="D102" t="s">
-        <v>24</v>
-      </c>
-      <c r="E102">
-        <v>7186209</v>
-      </c>
-      <c r="F102" t="s">
-        <v>200</v>
-      </c>
-      <c r="G102" t="s">
-        <v>24</v>
-      </c>
-      <c r="H102" t="s">
-        <v>24</v>
-      </c>
-      <c r="M102" t="s">
-        <v>201</v>
-      </c>
-      <c r="P102" s="1">
-        <v>46157.580364664354</v>
-      </c>
-      <c r="Q102" s="4">
-        <v>46160.367256516205</v>
-      </c>
-      <c r="R102" s="4">
-        <v>46160.444021875002</v>
-      </c>
-      <c r="S102">
-        <v>19189.000</v>
-      </c>
-      <c r="T102">
-        <v>19189.000</v>
-      </c>
-      <c r="U102">
-        <v>0</v>
-      </c>
-      <c r="V102">
-        <v>0</v>
-      </c>
-      <c r="W102" s="4">
-        <v>46161.605472025461</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>19</v>
-      </c>
-      <c r="B103" t="s">
-        <v>24</v>
-      </c>
-      <c r="C103" t="s">
-        <v>24</v>
-      </c>
-      <c r="D103" t="s">
-        <v>24</v>
-      </c>
-      <c r="E103">
-        <v>7185903</v>
-      </c>
-      <c r="F103" t="s">
-        <v>202</v>
-      </c>
-      <c r="G103" t="s">
-        <v>24</v>
-      </c>
-      <c r="H103" t="s">
-        <v>24</v>
-      </c>
-      <c r="M103" t="s">
-        <v>203</v>
-      </c>
-      <c r="P103" s="1">
-        <v>46157.55131412037</v>
-      </c>
-      <c r="Q103" s="4">
-        <v>46160.493105243055</v>
-      </c>
-      <c r="R103" s="4">
-        <v>46160.545683645832</v>
-      </c>
-      <c r="S103">
-        <v>39356.000</v>
-      </c>
-      <c r="T103">
-        <v>39356.000</v>
-      </c>
-      <c r="U103">
-        <v>0</v>
-      </c>
-      <c r="V103">
-        <v>0</v>
-      </c>
-      <c r="W103" s="4">
-        <v>46161.604525312498</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>19</v>
-      </c>
-      <c r="B104" t="s">
-        <v>24</v>
-      </c>
-      <c r="C104" t="s">
-        <v>24</v>
-      </c>
-      <c r="D104" t="s">
-        <v>24</v>
-      </c>
-      <c r="E104">
-        <v>7177836</v>
-      </c>
-      <c r="F104" t="s">
-        <v>204</v>
-      </c>
-      <c r="G104" t="s">
-        <v>24</v>
-      </c>
-      <c r="H104" t="s">
-        <v>24</v>
-      </c>
-      <c r="M104" t="s">
-        <v>205</v>
-      </c>
-      <c r="O104" s="4">
-        <v>46157.416666666664</v>
-      </c>
-      <c r="P104" s="1">
-        <v>46155.705813773151</v>
-      </c>
-      <c r="Q104" s="4">
-        <v>46157.466666666667</v>
-      </c>
-      <c r="R104" s="4">
-        <v>46160.360912615739</v>
-      </c>
-      <c r="S104">
-        <v>17794.000</v>
-      </c>
-      <c r="T104">
-        <v>17794.000</v>
-      </c>
-      <c r="U104">
-        <v>0</v>
-      </c>
-      <c r="V104">
-        <v>0</v>
-      </c>
-      <c r="W104" s="4">
-        <v>46160.503910451385</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>19</v>
-      </c>
-      <c r="B105" t="s">
-        <v>24</v>
-      </c>
-      <c r="C105" t="s">
-        <v>24</v>
-      </c>
-      <c r="D105" t="s">
-        <v>24</v>
-      </c>
-      <c r="E105">
-        <v>7175007</v>
-      </c>
-      <c r="F105" t="s">
-        <v>206</v>
-      </c>
-      <c r="G105" t="s">
-        <v>24</v>
-      </c>
-      <c r="H105" t="s">
-        <v>24</v>
-      </c>
-      <c r="M105" t="s">
-        <v>207</v>
-      </c>
-      <c r="O105" s="4">
-        <v>46157.291666666664</v>
-      </c>
-      <c r="P105" s="1">
-        <v>46155.454049652777</v>
-      </c>
-      <c r="Q105" s="4">
-        <v>46157.35833333333</v>
-      </c>
-      <c r="R105" s="4">
-        <v>46157.601774965275</v>
-      </c>
-      <c r="S105">
-        <v>21375.000</v>
-      </c>
-      <c r="T105">
-        <v>21375.000</v>
-      </c>
-      <c r="U105">
-        <v>0</v>
-      </c>
-      <c r="V105">
-        <v>0</v>
-      </c>
-      <c r="W105" s="4">
-        <v>46157.688587037039</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>19</v>
-      </c>
-      <c r="B106" t="s">
-        <v>24</v>
-      </c>
-      <c r="C106" t="s">
-        <v>24</v>
-      </c>
-      <c r="D106" t="s">
-        <v>24</v>
-      </c>
-      <c r="E106">
-        <v>7167099</v>
-      </c>
-      <c r="F106" t="s">
-        <v>208</v>
-      </c>
-      <c r="G106" t="s">
-        <v>24</v>
-      </c>
-      <c r="H106" t="s">
-        <v>24</v>
-      </c>
-      <c r="M106" t="s">
-        <v>209</v>
-      </c>
-      <c r="P106" s="1">
-        <v>46154.541764120368</v>
-      </c>
-      <c r="R106" s="4">
-        <v>46155.643980821762</v>
-      </c>
-      <c r="S106">
-        <v>11855.000</v>
-      </c>
-      <c r="T106">
-        <v>11855.000</v>
-      </c>
-      <c r="U106">
-        <v>0</v>
-      </c>
-      <c r="V106">
-        <v>0</v>
-      </c>
-      <c r="W106" s="4">
-        <v>46157.304165428242</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>19</v>
-      </c>
-      <c r="B107" t="s">
-        <v>24</v>
-      </c>
-      <c r="C107" t="s">
-        <v>24</v>
-      </c>
-      <c r="D107" t="s">
-        <v>210</v>
-      </c>
-      <c r="E107">
-        <v>7108660</v>
-      </c>
-      <c r="F107" t="s">
-        <v>211</v>
-      </c>
-      <c r="G107" t="s">
-        <v>24</v>
-      </c>
-      <c r="H107" t="s">
-        <v>212</v>
-      </c>
-      <c r="I107" t="s">
-        <v>212</v>
-      </c>
-      <c r="J107" t="s">
-        <v>213</v>
-      </c>
-      <c r="K107" t="s">
-        <v>214</v>
-      </c>
-      <c r="M107" t="s">
-        <v>24</v>
-      </c>
-      <c r="P107" s="1">
-        <v>46142.678548877317</v>
-      </c>
-      <c r="R107" s="4">
-        <v>46142.683541168983</v>
-      </c>
-      <c r="S107">
-        <v>100.000</v>
-      </c>
-      <c r="T107">
-        <v>100.000</v>
-      </c>
-      <c r="U107">
-        <v>0</v>
-      </c>
-      <c r="V107">
-        <v>0</v>
-      </c>
-      <c r="W107" s="4">
-        <v>46142.68461369213</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="S108" s="2">
-        <f ca="1">SUM(S2:S107)</f>
-        <v>0</v>
-      </c>
-      <c r="T108" s="2">
-        <f ca="1">SUM(T2:T107)</f>
-        <v>0</v>
-      </c>
-      <c r="U108" s="2">
-        <f ca="1">SUM(U2:U107)</f>
-        <v>0</v>
-      </c>
-      <c r="V108" s="2">
-        <f ca="1">SUM(V2:V107)</f>
+      <c r="S81" s="2">
+        <f ca="1">SUM(S2:S80)</f>
+        <v>0</v>
+      </c>
+      <c r="T81" s="2">
+        <f ca="1">SUM(T2:T80)</f>
+        <v>0</v>
+      </c>
+      <c r="U81" s="2">
+        <f ca="1">SUM(U2:U80)</f>
+        <v>0</v>
+      </c>
+      <c r="V81" s="2">
+        <f ca="1">SUM(V2:V80)</f>
         <v>0</v>
       </c>
     </row>

--- a/InOrders_latest.xlsx
+++ b/InOrders_latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
   <si>
     <t>Status</t>
   </si>
@@ -176,6 +176,21 @@
     <t>Truck 62</t>
   </si>
   <si>
+    <t>520063571300100</t>
+  </si>
+  <si>
+    <t>2026-05-22 | Gelişim Tekstil | ASN-GTK-001</t>
+  </si>
+  <si>
+    <t>520063571200100</t>
+  </si>
+  <si>
+    <t>520063571600100</t>
+  </si>
+  <si>
+    <t>520063571100100</t>
+  </si>
+  <si>
     <t>0101856191</t>
   </si>
   <si>
@@ -183,6 +198,69 @@
 </t>
   </si>
   <si>
+    <t>520064225200100</t>
+  </si>
+  <si>
+    <t>520064227400100</t>
+  </si>
+  <si>
+    <t>520064225500100</t>
+  </si>
+  <si>
+    <t>520064226900100</t>
+  </si>
+  <si>
+    <t>520064227000100</t>
+  </si>
+  <si>
+    <t>520064226800100</t>
+  </si>
+  <si>
+    <t>520064226600100</t>
+  </si>
+  <si>
+    <t>520064225900100</t>
+  </si>
+  <si>
+    <t>520064224800100</t>
+  </si>
+  <si>
+    <t>520064225000100</t>
+  </si>
+  <si>
+    <t>520064224900100</t>
+  </si>
+  <si>
+    <t>520064227300100</t>
+  </si>
+  <si>
+    <t>520064227100100</t>
+  </si>
+  <si>
+    <t>520064226700100</t>
+  </si>
+  <si>
+    <t>520064225800100</t>
+  </si>
+  <si>
+    <t>520063571000100</t>
+  </si>
+  <si>
+    <t>520064226500100</t>
+  </si>
+  <si>
+    <t>520063570300100</t>
+  </si>
+  <si>
+    <t>520064225300100</t>
+  </si>
+  <si>
+    <t>520063570600100</t>
+  </si>
+  <si>
+    <t>520064225100100</t>
+  </si>
+  <si>
     <t>0101856108</t>
   </si>
   <si>
@@ -190,10 +268,19 @@
 </t>
   </si>
   <si>
+    <t>520063570500100</t>
+  </si>
+  <si>
     <t>0101850638</t>
   </si>
   <si>
     <t>Truck 54</t>
+  </si>
+  <si>
+    <t>JohannesUPSStockUP</t>
+  </si>
+  <si>
+    <t>Johannes_Prod_Test_UPS_StockUP</t>
   </si>
   <si>
     <t>0101843290</t>
@@ -390,6 +477,12 @@
     <t>truck20</t>
   </si>
   <si>
+    <t>Shopify Cutover Inbound</t>
+  </si>
+  <si>
+    <t>Shopify Cutover Virtual Inbound Stockupf for Cutover Outbound</t>
+  </si>
+  <si>
     <t>0101772410</t>
   </si>
   <si>
@@ -566,6 +659,21 @@
   </si>
   <si>
     <t>Truck1</t>
+  </si>
+  <si>
+    <t>Container 1</t>
+  </si>
+  <si>
+    <t>Inboundtest1</t>
+  </si>
+  <si>
+    <t>SUP_111</t>
+  </si>
+  <si>
+    <t>TestSUP</t>
+  </si>
+  <si>
+    <t>Germany</t>
   </si>
 </sst>
 </file>
@@ -932,21 +1040,21 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W81"/>
+  <dimension ref="A1:W110"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10.28125" customWidth="1"/>
     <col min="2" max="2" width="16.00390625" customWidth="1"/>
     <col min="3" max="3" width="29.8515625" customWidth="1"/>
-    <col min="4" max="4" width="10.8515625" customWidth="1"/>
+    <col min="4" max="4" width="12.28125" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.8515625" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" customWidth="1"/>
     <col min="7" max="7" width="18.7109375" customWidth="1"/>
     <col min="8" max="8" width="22.28125" customWidth="1"/>
     <col min="9" max="9" width="12.8515625" customWidth="1"/>
     <col min="10" max="10" width="15.00390625" customWidth="1"/>
     <col min="11" max="11" width="16.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" customWidth="1"/>
+    <col min="13" max="13" width="58.57421875" customWidth="1"/>
     <col min="14" max="14" width="14.00390625" customWidth="1" style="1"/>
     <col min="15" max="15" width="16.8515625" customWidth="1"/>
     <col min="16" max="16" width="11.57421875" customWidth="1" style="1"/>
@@ -1734,7 +1842,7 @@
         <v>23</v>
       </c>
       <c r="E16">
-        <v>7355924</v>
+        <v>7353363</v>
       </c>
       <c r="F16" t="s">
         <v>53</v>
@@ -1745,20 +1853,20 @@
       <c r="H16" t="s">
         <v>23</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="M16" t="s">
         <v>54</v>
       </c>
       <c r="P16" s="1">
-        <v>46191.548452546296</v>
+        <v>46190.666969988422</v>
       </c>
       <c r="R16" s="4">
-        <v>46195.391070254627</v>
+        <v>46195.511062997684</v>
       </c>
       <c r="S16">
-        <v>8044.000</v>
+        <v>472.000</v>
       </c>
       <c r="T16">
-        <v>8044.000</v>
+        <v>472.000</v>
       </c>
       <c r="U16">
         <v>0</v>
@@ -1784,7 +1892,7 @@
         <v>23</v>
       </c>
       <c r="E17">
-        <v>7353112</v>
+        <v>7353362</v>
       </c>
       <c r="F17" t="s">
         <v>55</v>
@@ -1795,20 +1903,20 @@
       <c r="H17" t="s">
         <v>23</v>
       </c>
-      <c r="M17" s="5" t="s">
-        <v>56</v>
+      <c r="M17" t="s">
+        <v>54</v>
       </c>
       <c r="P17" s="1">
-        <v>46190.633443321756</v>
+        <v>46190.666969444443</v>
       </c>
       <c r="R17" s="4">
-        <v>46195.593899918982</v>
+        <v>46195.521521527779</v>
       </c>
       <c r="S17">
-        <v>15034.000</v>
+        <v>612.000</v>
       </c>
       <c r="T17">
-        <v>15034.000</v>
+        <v>612.000</v>
       </c>
       <c r="U17">
         <v>0</v>
@@ -1817,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="W17" s="4">
-        <v>46196.389407835646</v>
+        <v>46196.389409641204</v>
       </c>
     </row>
     <row r="18">
@@ -1834,10 +1942,10 @@
         <v>23</v>
       </c>
       <c r="E18">
-        <v>7349603</v>
+        <v>7353361</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G18" t="s">
         <v>23</v>
@@ -1846,25 +1954,19 @@
         <v>23</v>
       </c>
       <c r="M18" t="s">
-        <v>58</v>
-      </c>
-      <c r="N18" s="1">
-        <v>46190</v>
+        <v>54</v>
       </c>
       <c r="P18" s="1">
-        <v>46189.643392094906</v>
-      </c>
-      <c r="Q18" s="4">
-        <v>46190.996527777781</v>
+        <v>46190.666967094905</v>
       </c>
       <c r="R18" s="4">
-        <v>46190.579668171296</v>
+        <v>46195.535836192132</v>
       </c>
       <c r="S18">
-        <v>5965.000</v>
+        <v>2383.000</v>
       </c>
       <c r="T18">
-        <v>5965.000</v>
+        <v>2383.000</v>
       </c>
       <c r="U18">
         <v>0</v>
@@ -1873,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="W18" s="4">
-        <v>46191.313541932868</v>
+        <v>46196.389409641204</v>
       </c>
     </row>
     <row r="19">
@@ -1890,10 +1992,10 @@
         <v>23</v>
       </c>
       <c r="E19">
-        <v>7344984</v>
+        <v>7353360</v>
       </c>
       <c r="F19" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
         <v>23</v>
@@ -1902,19 +2004,19 @@
         <v>23</v>
       </c>
       <c r="M19" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="P19" s="1">
-        <v>46188.6820028125</v>
+        <v>46190.666964201388</v>
       </c>
       <c r="R19" s="4">
-        <v>46189.581174189814</v>
+        <v>46195.523977164354</v>
       </c>
       <c r="S19">
-        <v>14515.000</v>
+        <v>2262.000</v>
       </c>
       <c r="T19">
-        <v>14515.000</v>
+        <v>2262.000</v>
       </c>
       <c r="U19">
         <v>0</v>
@@ -1923,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="W19" s="4">
-        <v>46190.318753738429</v>
+        <v>46196.389409641204</v>
       </c>
     </row>
     <row r="20">
@@ -1940,10 +2042,10 @@
         <v>23</v>
       </c>
       <c r="E20">
-        <v>7343721</v>
+        <v>7355924</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G20" t="s">
         <v>23</v>
@@ -1951,23 +2053,20 @@
       <c r="H20" t="s">
         <v>23</v>
       </c>
-      <c r="M20" t="s">
-        <v>62</v>
+      <c r="M20" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="P20" s="1">
-        <v>46188.52897230324</v>
-      </c>
-      <c r="Q20" s="4">
-        <v>46189.270138888889</v>
+        <v>46191.548452546296</v>
       </c>
       <c r="R20" s="4">
-        <v>46189.525954201388</v>
+        <v>46195.391070254627</v>
       </c>
       <c r="S20">
-        <v>9210.000</v>
+        <v>8044.000</v>
       </c>
       <c r="T20">
-        <v>9210.000</v>
+        <v>8044.000</v>
       </c>
       <c r="U20">
         <v>0</v>
@@ -1976,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="W20" s="4">
-        <v>46189.538887268522</v>
+        <v>46196.389409641204</v>
       </c>
     </row>
     <row r="21">
@@ -1993,10 +2092,10 @@
         <v>23</v>
       </c>
       <c r="E21">
-        <v>7312333</v>
+        <v>7353359</v>
       </c>
       <c r="F21" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G21" t="s">
         <v>23</v>
@@ -2005,22 +2104,19 @@
         <v>23</v>
       </c>
       <c r="M21" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="P21" s="1">
-        <v>46181.394416122683</v>
-      </c>
-      <c r="Q21" s="4">
-        <v>46182.458333333336</v>
+        <v>46190.66696145833</v>
       </c>
       <c r="R21" s="4">
-        <v>46188.402503240737</v>
+        <v>46195.537172372686</v>
       </c>
       <c r="S21">
-        <v>8272.000</v>
+        <v>3982.000</v>
       </c>
       <c r="T21">
-        <v>8272.000</v>
+        <v>3982.000</v>
       </c>
       <c r="U21">
         <v>0</v>
@@ -2029,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="W21" s="4">
-        <v>46188.404413310185</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="22">
@@ -2046,10 +2142,10 @@
         <v>23</v>
       </c>
       <c r="E22">
-        <v>7312334</v>
+        <v>7353358</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G22" t="s">
         <v>23</v>
@@ -2058,22 +2154,19 @@
         <v>23</v>
       </c>
       <c r="M22" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="P22" s="1">
-        <v>46181.394481597221</v>
-      </c>
-      <c r="Q22" s="4">
-        <v>46182.458333333336</v>
+        <v>46190.666954432869</v>
       </c>
       <c r="R22" s="4">
-        <v>46188.363727511576</v>
+        <v>46195.532108368054</v>
       </c>
       <c r="S22">
-        <v>5617.000</v>
+        <v>1113.000</v>
       </c>
       <c r="T22">
-        <v>5617.000</v>
+        <v>1113.000</v>
       </c>
       <c r="U22">
         <v>0</v>
@@ -2082,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="W22" s="4">
-        <v>46188.368130752315</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="23">
@@ -2099,10 +2192,10 @@
         <v>23</v>
       </c>
       <c r="E23">
-        <v>7306694</v>
+        <v>7353357</v>
       </c>
       <c r="F23" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G23" t="s">
         <v>23</v>
@@ -2111,22 +2204,19 @@
         <v>23</v>
       </c>
       <c r="M23" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="P23" s="1">
-        <v>46178.650135613425</v>
-      </c>
-      <c r="Q23" s="4">
-        <v>46181.3125</v>
+        <v>46190.666949340281</v>
       </c>
       <c r="R23" s="4">
-        <v>46188.351883217591</v>
+        <v>46195.517305439818</v>
       </c>
       <c r="S23">
-        <v>7291.000</v>
+        <v>447.000</v>
       </c>
       <c r="T23">
-        <v>7291.000</v>
+        <v>447.000</v>
       </c>
       <c r="U23">
         <v>0</v>
@@ -2135,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="4">
-        <v>46188.368130405092</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="24">
@@ -2152,10 +2242,10 @@
         <v>23</v>
       </c>
       <c r="E24">
-        <v>7306693</v>
+        <v>7353356</v>
       </c>
       <c r="F24" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G24" t="s">
         <v>23</v>
@@ -2164,22 +2254,19 @@
         <v>23</v>
       </c>
       <c r="M24" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="P24" s="1">
-        <v>46178.650101388892</v>
-      </c>
-      <c r="Q24" s="4">
-        <v>46181.395833333336</v>
+        <v>46190.66694664352</v>
       </c>
       <c r="R24" s="4">
-        <v>46188.361928472223</v>
+        <v>46195.528761724534</v>
       </c>
       <c r="S24">
-        <v>5272.000</v>
+        <v>284.000</v>
       </c>
       <c r="T24">
-        <v>5272.000</v>
+        <v>284.000</v>
       </c>
       <c r="U24">
         <v>0</v>
@@ -2188,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="W24" s="4">
-        <v>46188.368129826391</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="25">
@@ -2205,10 +2292,10 @@
         <v>23</v>
       </c>
       <c r="E25">
-        <v>7296112</v>
+        <v>7353355</v>
       </c>
       <c r="F25" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G25" t="s">
         <v>23</v>
@@ -2217,19 +2304,19 @@
         <v>23</v>
       </c>
       <c r="M25" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="P25" s="1">
-        <v>46176.490794872683</v>
+        <v>46190.666944293982</v>
       </c>
       <c r="R25" s="4">
-        <v>46188.357570370368</v>
+        <v>46195.528790659722</v>
       </c>
       <c r="S25">
-        <v>7146.000</v>
+        <v>304.000</v>
       </c>
       <c r="T25">
-        <v>7146.000</v>
+        <v>304.000</v>
       </c>
       <c r="U25">
         <v>0</v>
@@ -2238,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="W25" s="4">
-        <v>46188.368129664355</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="26">
@@ -2255,10 +2342,10 @@
         <v>23</v>
       </c>
       <c r="E26">
-        <v>7331780</v>
+        <v>7353354</v>
       </c>
       <c r="F26" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G26" t="s">
         <v>23</v>
@@ -2267,22 +2354,19 @@
         <v>23</v>
       </c>
       <c r="M26" t="s">
-        <v>74</v>
-      </c>
-      <c r="O26" s="4">
-        <v>46185.364583333336</v>
+        <v>54</v>
       </c>
       <c r="P26" s="1">
-        <v>46184.420189351855</v>
+        <v>46190.666940659721</v>
       </c>
       <c r="R26" s="4">
-        <v>46188.330705902779</v>
+        <v>46195.536209409722</v>
       </c>
       <c r="S26">
-        <v>2185.000</v>
+        <v>1251.000</v>
       </c>
       <c r="T26">
-        <v>2185.000</v>
+        <v>1251.000</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -2291,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="W26" s="4">
-        <v>46188.33742491898</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="27">
@@ -2308,10 +2392,10 @@
         <v>23</v>
       </c>
       <c r="E27">
-        <v>7331779</v>
+        <v>7353353</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G27" t="s">
         <v>23</v>
@@ -2320,25 +2404,19 @@
         <v>23</v>
       </c>
       <c r="M27" t="s">
-        <v>76</v>
-      </c>
-      <c r="O27" s="4">
-        <v>46185</v>
+        <v>54</v>
       </c>
       <c r="P27" s="1">
-        <v>46184.420142511575</v>
-      </c>
-      <c r="Q27" s="4">
-        <v>46181</v>
+        <v>46190.666939583331</v>
       </c>
       <c r="R27" s="4">
-        <v>46188.332772222224</v>
+        <v>46195.537300034724</v>
       </c>
       <c r="S27">
-        <v>16497.000</v>
+        <v>1257.000</v>
       </c>
       <c r="T27">
-        <v>16497.000</v>
+        <v>1257.000</v>
       </c>
       <c r="U27">
         <v>0</v>
@@ -2347,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="W27" s="4">
-        <v>46188.337424189813</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="28">
@@ -2364,10 +2442,10 @@
         <v>23</v>
       </c>
       <c r="E28">
-        <v>7327419</v>
+        <v>7353351</v>
       </c>
       <c r="F28" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="G28" t="s">
         <v>23</v>
@@ -2376,22 +2454,19 @@
         <v>23</v>
       </c>
       <c r="M28" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="P28" s="1">
-        <v>46183.517797372682</v>
-      </c>
-      <c r="Q28" s="4">
-        <v>46184.3125</v>
+        <v>46190.666933101849</v>
       </c>
       <c r="R28" s="4">
-        <v>46188.329073842593</v>
+        <v>46195.523942245367</v>
       </c>
       <c r="S28">
-        <v>10574.000</v>
+        <v>1295.000</v>
       </c>
       <c r="T28">
-        <v>10574.000</v>
+        <v>1295.000</v>
       </c>
       <c r="U28">
         <v>0</v>
@@ -2400,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="W28" s="4">
-        <v>46188.337423263889</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="29">
@@ -2417,10 +2492,10 @@
         <v>23</v>
       </c>
       <c r="E29">
-        <v>7331318</v>
+        <v>7353350</v>
       </c>
       <c r="F29" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="G29" t="s">
         <v>23</v>
@@ -2429,19 +2504,19 @@
         <v>23</v>
       </c>
       <c r="M29" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="P29" s="1">
-        <v>46184.369259340281</v>
+        <v>46190.666932719905</v>
       </c>
       <c r="R29" s="4">
-        <v>46185.506102002313</v>
+        <v>46195.536177581016</v>
       </c>
       <c r="S29">
-        <v>10749.000</v>
+        <v>72.000</v>
       </c>
       <c r="T29">
-        <v>10749.000</v>
+        <v>72.000</v>
       </c>
       <c r="U29">
         <v>0</v>
@@ -2450,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="W29" s="4">
-        <v>46188.329308333334</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="30">
@@ -2467,10 +2542,10 @@
         <v>23</v>
       </c>
       <c r="E30">
-        <v>7306692</v>
+        <v>7353349</v>
       </c>
       <c r="F30" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="G30" t="s">
         <v>23</v>
@@ -2478,23 +2553,20 @@
       <c r="H30" t="s">
         <v>23</v>
       </c>
-      <c r="M30" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="O30" s="4">
-        <v>46181.34375</v>
+      <c r="M30" t="s">
+        <v>54</v>
       </c>
       <c r="P30" s="1">
-        <v>46178.650014085651</v>
+        <v>46190.666930555555</v>
       </c>
       <c r="R30" s="4">
-        <v>46188.321652777777</v>
+        <v>46195.536192395833</v>
       </c>
       <c r="S30">
-        <v>10749.000</v>
+        <v>101.000</v>
       </c>
       <c r="T30">
-        <v>10749.000</v>
+        <v>101.000</v>
       </c>
       <c r="U30">
         <v>0</v>
@@ -2503,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="W30" s="4">
-        <v>46188.329306516207</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="31">
@@ -2520,10 +2592,10 @@
         <v>23</v>
       </c>
       <c r="E31">
-        <v>7290512</v>
+        <v>7353348</v>
       </c>
       <c r="F31" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="G31" t="s">
         <v>23</v>
@@ -2532,22 +2604,19 @@
         <v>23</v>
       </c>
       <c r="M31" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="P31" s="1">
-        <v>46175.705376817132</v>
-      </c>
-      <c r="Q31" s="4">
-        <v>46176.5</v>
+        <v>46190.666919525465</v>
       </c>
       <c r="R31" s="4">
-        <v>46188.325696840278</v>
+        <v>46195.534000462962</v>
       </c>
       <c r="S31">
-        <v>14234.000</v>
+        <v>1620.000</v>
       </c>
       <c r="T31">
-        <v>14234.000</v>
+        <v>1620.000</v>
       </c>
       <c r="U31">
         <v>0</v>
@@ -2556,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="W31" s="4">
-        <v>46188.329304166669</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="32">
@@ -2573,10 +2642,10 @@
         <v>23</v>
       </c>
       <c r="E32">
-        <v>7277742</v>
+        <v>7353347</v>
       </c>
       <c r="F32" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G32" t="s">
         <v>23</v>
@@ -2585,22 +2654,19 @@
         <v>23</v>
       </c>
       <c r="M32" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="P32" s="1">
-        <v>46174.491930821758</v>
-      </c>
-      <c r="Q32" s="4">
-        <v>46174.416666666664</v>
+        <v>46190.666916979164</v>
       </c>
       <c r="R32" s="4">
-        <v>46188.313768368054</v>
+        <v>46195.527235069443</v>
       </c>
       <c r="S32">
-        <v>18914.000</v>
+        <v>600.000</v>
       </c>
       <c r="T32">
-        <v>18914.000</v>
+        <v>600.000</v>
       </c>
       <c r="U32">
         <v>0</v>
@@ -2609,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="W32" s="4">
-        <v>46188.329302546299</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="33">
@@ -2626,10 +2692,10 @@
         <v>23</v>
       </c>
       <c r="E33">
-        <v>7321304</v>
+        <v>7353346</v>
       </c>
       <c r="F33" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="G33" t="s">
         <v>23</v>
@@ -2638,22 +2704,19 @@
         <v>23</v>
       </c>
       <c r="M33" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="P33" s="1">
-        <v>46182.379826539349</v>
-      </c>
-      <c r="Q33" s="4">
-        <v>46183.458333333336</v>
+        <v>46190.66691284722</v>
       </c>
       <c r="R33" s="4">
-        <v>46184.566309837966</v>
+        <v>46195.522001273152</v>
       </c>
       <c r="S33">
-        <v>1784.000</v>
+        <v>1338.000</v>
       </c>
       <c r="T33">
-        <v>1784.000</v>
+        <v>1338.000</v>
       </c>
       <c r="U33">
         <v>0</v>
@@ -2662,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="W33" s="4">
-        <v>46188.318567708331</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="34">
@@ -2679,10 +2742,10 @@
         <v>23</v>
       </c>
       <c r="E34">
-        <v>7321303</v>
+        <v>7353345</v>
       </c>
       <c r="F34" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="G34" t="s">
         <v>23</v>
@@ -2691,22 +2754,19 @@
         <v>23</v>
       </c>
       <c r="M34" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="P34" s="1">
-        <v>46182.379728553242</v>
-      </c>
-      <c r="Q34" s="4">
-        <v>46183.458333333336</v>
+        <v>46190.666911921297</v>
       </c>
       <c r="R34" s="4">
-        <v>46185.474632175923</v>
+        <v>46195.532152511572</v>
       </c>
       <c r="S34">
-        <v>15852.000</v>
+        <v>968.000</v>
       </c>
       <c r="T34">
-        <v>15852.000</v>
+        <v>968.000</v>
       </c>
       <c r="U34">
         <v>0</v>
@@ -2715,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="W34" s="4">
-        <v>46188.318567164351</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="35">
@@ -2732,10 +2792,10 @@
         <v>23</v>
       </c>
       <c r="E35">
-        <v>7312335</v>
+        <v>7353344</v>
       </c>
       <c r="F35" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s">
         <v>23</v>
@@ -2743,23 +2803,20 @@
       <c r="H35" t="s">
         <v>23</v>
       </c>
-      <c r="M35" s="5" t="s">
-        <v>92</v>
+      <c r="M35" t="s">
+        <v>54</v>
       </c>
       <c r="P35" s="1">
-        <v>46181.394497488429</v>
-      </c>
-      <c r="Q35" s="4">
-        <v>46182.388888888891</v>
+        <v>46190.666910844906</v>
       </c>
       <c r="R35" s="4">
-        <v>46185.475467280092</v>
+        <v>46195.537341087962</v>
       </c>
       <c r="S35">
-        <v>16641.000</v>
+        <v>917.000</v>
       </c>
       <c r="T35">
-        <v>16641.000</v>
+        <v>917.000</v>
       </c>
       <c r="U35">
         <v>0</v>
@@ -2768,7 +2825,7 @@
         <v>0</v>
       </c>
       <c r="W35" s="4">
-        <v>46188.318566284725</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="36">
@@ -2785,10 +2842,10 @@
         <v>23</v>
       </c>
       <c r="E36">
-        <v>7329559</v>
+        <v>7353343</v>
       </c>
       <c r="F36" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s">
         <v>23</v>
@@ -2797,19 +2854,19 @@
         <v>23</v>
       </c>
       <c r="M36" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="P36" s="1">
-        <v>46183.835381215278</v>
+        <v>46190.666907604165</v>
       </c>
       <c r="R36" s="4">
-        <v>46185.394576122686</v>
+        <v>46195.526307291664</v>
       </c>
       <c r="S36">
-        <v>18992.000</v>
+        <v>3514.000</v>
       </c>
       <c r="T36">
-        <v>18992.000</v>
+        <v>3514.000</v>
       </c>
       <c r="U36">
         <v>0</v>
@@ -2818,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="W36" s="4">
-        <v>46188.318260497683</v>
+        <v>46196.389409108793</v>
       </c>
     </row>
     <row r="37">
@@ -2835,10 +2892,10 @@
         <v>23</v>
       </c>
       <c r="E37">
-        <v>7312336</v>
+        <v>7353342</v>
       </c>
       <c r="F37" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="G37" t="s">
         <v>23</v>
@@ -2847,22 +2904,19 @@
         <v>23</v>
       </c>
       <c r="M37" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="P37" s="1">
-        <v>46181.394619016202</v>
-      </c>
-      <c r="Q37" s="4">
-        <v>46182.416666666664</v>
+        <v>46190.666906134262</v>
       </c>
       <c r="R37" s="4">
-        <v>46182.563263425924</v>
+        <v>46195.518147222225</v>
       </c>
       <c r="S37">
-        <v>8559.000</v>
+        <v>646.000</v>
       </c>
       <c r="T37">
-        <v>8559.000</v>
+        <v>646.000</v>
       </c>
       <c r="U37">
         <v>0</v>
@@ -2871,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="W37" s="4">
-        <v>46183.499163692133</v>
+        <v>46196.389409108793</v>
       </c>
     </row>
     <row r="38">
@@ -2888,10 +2942,10 @@
         <v>23</v>
       </c>
       <c r="E38">
-        <v>7297491</v>
+        <v>7353341</v>
       </c>
       <c r="F38" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s">
         <v>23</v>
@@ -2900,25 +2954,19 @@
         <v>23</v>
       </c>
       <c r="M38" t="s">
-        <v>98</v>
-      </c>
-      <c r="O38" s="4">
-        <v>46178.416666666664</v>
+        <v>54</v>
       </c>
       <c r="P38" s="1">
-        <v>46176.651283530089</v>
-      </c>
-      <c r="Q38" s="4">
-        <v>46178.260416666664</v>
+        <v>46190.666903969905</v>
       </c>
       <c r="R38" s="4">
-        <v>46182.304580173608</v>
+        <v>46195.535854247682</v>
       </c>
       <c r="S38">
-        <v>19653.000</v>
+        <v>2209.000</v>
       </c>
       <c r="T38">
-        <v>19653.000</v>
+        <v>2209.000</v>
       </c>
       <c r="U38">
         <v>0</v>
@@ -2927,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="W38" s="4">
-        <v>46182.394867361108</v>
+        <v>46196.389409108793</v>
       </c>
     </row>
     <row r="39">
@@ -2944,10 +2992,10 @@
         <v>23</v>
       </c>
       <c r="E39">
-        <v>7276670</v>
+        <v>7353340</v>
       </c>
       <c r="F39" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="G39" t="s">
         <v>23</v>
@@ -2956,22 +3004,19 @@
         <v>23</v>
       </c>
       <c r="M39" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="P39" s="1">
-        <v>46174.386795023151</v>
-      </c>
-      <c r="Q39" s="4">
-        <v>46174.3125</v>
+        <v>46190.666894560185</v>
       </c>
       <c r="R39" s="4">
-        <v>46181.602299189813</v>
+        <v>46195.524072835651</v>
       </c>
       <c r="S39">
-        <v>7766.000</v>
+        <v>4385.000</v>
       </c>
       <c r="T39">
-        <v>7766.000</v>
+        <v>4385.000</v>
       </c>
       <c r="U39">
         <v>0</v>
@@ -2980,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="W39" s="4">
-        <v>46181.607877893519</v>
+        <v>46196.389409108793</v>
       </c>
     </row>
     <row r="40">
@@ -2997,10 +3042,10 @@
         <v>23</v>
       </c>
       <c r="E40">
-        <v>7256959</v>
+        <v>7353339</v>
       </c>
       <c r="F40" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s">
         <v>23</v>
@@ -3009,22 +3054,19 @@
         <v>23</v>
       </c>
       <c r="M40" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="P40" s="1">
-        <v>46169.73840185185</v>
-      </c>
-      <c r="Q40" s="4">
-        <v>46171.520833333336</v>
+        <v>46190.666882442129</v>
       </c>
       <c r="R40" s="4">
-        <v>46181.602367395833</v>
+        <v>46195.535098726854</v>
       </c>
       <c r="S40">
-        <v>11921.000</v>
+        <v>2886.000</v>
       </c>
       <c r="T40">
-        <v>11921.000</v>
+        <v>2886.000</v>
       </c>
       <c r="U40">
         <v>0</v>
@@ -3033,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="W40" s="4">
-        <v>46181.607877002316</v>
+        <v>46196.389408912037</v>
       </c>
     </row>
     <row r="41">
@@ -3050,10 +3092,10 @@
         <v>23</v>
       </c>
       <c r="E41">
-        <v>7256837</v>
+        <v>7353338</v>
       </c>
       <c r="F41" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s">
         <v>23</v>
@@ -3062,25 +3104,19 @@
         <v>23</v>
       </c>
       <c r="M41" t="s">
-        <v>104</v>
-      </c>
-      <c r="O41" s="4">
-        <v>46170.541666666664</v>
+        <v>54</v>
       </c>
       <c r="P41" s="1">
-        <v>46169.717724456015</v>
-      </c>
-      <c r="Q41" s="4">
-        <v>46171.375</v>
+        <v>46190.666870520836</v>
       </c>
       <c r="R41" s="4">
-        <v>46181.601758877317</v>
+        <v>46195.537258252312</v>
       </c>
       <c r="S41">
-        <v>10645.000</v>
+        <v>2648.000</v>
       </c>
       <c r="T41">
-        <v>10645.000</v>
+        <v>2648.000</v>
       </c>
       <c r="U41">
         <v>0</v>
@@ -3089,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="W41" s="4">
-        <v>46181.607876122682</v>
+        <v>46196.389408912037</v>
       </c>
     </row>
     <row r="42">
@@ -3106,10 +3142,10 @@
         <v>23</v>
       </c>
       <c r="E42">
-        <v>7297492</v>
+        <v>7353112</v>
       </c>
       <c r="F42" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s">
         <v>23</v>
@@ -3117,23 +3153,20 @@
       <c r="H42" t="s">
         <v>23</v>
       </c>
-      <c r="M42" t="s">
-        <v>106</v>
-      </c>
-      <c r="O42" s="4">
-        <v>46178.427083333336</v>
+      <c r="M42" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="P42" s="1">
-        <v>46176.651338159725</v>
+        <v>46190.633443321756</v>
       </c>
       <c r="R42" s="4">
-        <v>46178.483032060183</v>
+        <v>46195.593899918982</v>
       </c>
       <c r="S42">
-        <v>6802.000</v>
+        <v>15034.000</v>
       </c>
       <c r="T42">
-        <v>6802.000</v>
+        <v>15034.000</v>
       </c>
       <c r="U42">
         <v>0</v>
@@ -3142,7 +3175,7 @@
         <v>0</v>
       </c>
       <c r="W42" s="4">
-        <v>46181.304573692127</v>
+        <v>46196.389407835646</v>
       </c>
     </row>
     <row r="43">
@@ -3159,10 +3192,10 @@
         <v>23</v>
       </c>
       <c r="E43">
-        <v>7290516</v>
+        <v>7353352</v>
       </c>
       <c r="F43" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G43" t="s">
         <v>23</v>
@@ -3171,22 +3204,19 @@
         <v>23</v>
       </c>
       <c r="M43" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="P43" s="1">
-        <v>46175.705564502314</v>
-      </c>
-      <c r="Q43" s="4">
-        <v>46176.59375</v>
+        <v>46190.66693417824</v>
       </c>
       <c r="R43" s="4">
-        <v>46178.37381646991</v>
+        <v>46195.537318483795</v>
       </c>
       <c r="S43">
-        <v>6600.000</v>
+        <v>7113.000</v>
       </c>
       <c r="T43">
-        <v>6600.000</v>
+        <v>7113.000</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -3195,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="W43" s="4">
-        <v>46181.304297951392</v>
+        <v>46196.388202118054</v>
       </c>
     </row>
     <row r="44">
@@ -3212,10 +3242,10 @@
         <v>23</v>
       </c>
       <c r="E44">
-        <v>7290513</v>
+        <v>7349603</v>
       </c>
       <c r="F44" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="G44" t="s">
         <v>23</v>
@@ -3224,22 +3254,25 @@
         <v>23</v>
       </c>
       <c r="M44" t="s">
-        <v>110</v>
+        <v>85</v>
+      </c>
+      <c r="N44" s="1">
+        <v>46190</v>
       </c>
       <c r="P44" s="1">
-        <v>46175.705472835645</v>
+        <v>46189.643392094906</v>
       </c>
       <c r="Q44" s="4">
-        <v>46175.541666666664</v>
+        <v>46190.996527777781</v>
       </c>
       <c r="R44" s="4">
-        <v>46176.390187384262</v>
+        <v>46190.579668171296</v>
       </c>
       <c r="S44">
-        <v>10634.000</v>
+        <v>5965.000</v>
       </c>
       <c r="T44">
-        <v>10634.000</v>
+        <v>5965.000</v>
       </c>
       <c r="U44">
         <v>0</v>
@@ -3248,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="W44" s="4">
-        <v>46176.479922453706</v>
+        <v>46191.313541932868</v>
       </c>
     </row>
     <row r="45">
@@ -3265,10 +3298,10 @@
         <v>23</v>
       </c>
       <c r="E45">
-        <v>7277745</v>
+        <v>7166305</v>
       </c>
       <c r="F45" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="G45" t="s">
         <v>23</v>
@@ -3277,31 +3310,34 @@
         <v>23</v>
       </c>
       <c r="M45" t="s">
-        <v>112</v>
+        <v>87</v>
+      </c>
+      <c r="N45" s="1">
+        <v>46152</v>
       </c>
       <c r="P45" s="1">
-        <v>46174.492115972222</v>
+        <v>46154.508897418978</v>
       </c>
       <c r="Q45" s="4">
-        <v>46175.291666666664</v>
+        <v>46162.29583333333</v>
       </c>
       <c r="R45" s="4">
-        <v>46176.394080127313</v>
+        <v>46154.512428125003</v>
       </c>
       <c r="S45">
-        <v>8925.000</v>
+        <v>100.000</v>
       </c>
       <c r="T45">
-        <v>8925.000</v>
+        <v>98.000</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.000</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45" s="4">
-        <v>46176.479621759259</v>
+        <v>46190.318931481481</v>
       </c>
     </row>
     <row r="46">
@@ -3318,10 +3354,10 @@
         <v>23</v>
       </c>
       <c r="E46">
-        <v>7277755</v>
+        <v>7344984</v>
       </c>
       <c r="F46" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s">
         <v>23</v>
@@ -3330,22 +3366,19 @@
         <v>23</v>
       </c>
       <c r="M46" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="P46" s="1">
-        <v>46174.492233680554</v>
-      </c>
-      <c r="Q46" s="4">
-        <v>46175.291666666664</v>
+        <v>46188.6820028125</v>
       </c>
       <c r="R46" s="4">
-        <v>46175.460509027776</v>
+        <v>46189.581174189814</v>
       </c>
       <c r="S46">
-        <v>1502.000</v>
+        <v>14515.000</v>
       </c>
       <c r="T46">
-        <v>1502.000</v>
+        <v>14515.000</v>
       </c>
       <c r="U46">
         <v>0</v>
@@ -3354,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="W46" s="4">
-        <v>46176.367452777777</v>
+        <v>46190.318753738429</v>
       </c>
     </row>
     <row r="47">
@@ -3371,10 +3404,10 @@
         <v>23</v>
       </c>
       <c r="E47">
-        <v>7290515</v>
+        <v>7343721</v>
       </c>
       <c r="F47" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="G47" t="s">
         <v>23</v>
@@ -3383,22 +3416,22 @@
         <v>23</v>
       </c>
       <c r="M47" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="P47" s="1">
-        <v>46175.705520370371</v>
+        <v>46188.52897230324</v>
       </c>
       <c r="Q47" s="4">
-        <v>46175.604166666664</v>
+        <v>46189.270138888889</v>
       </c>
       <c r="R47" s="4">
-        <v>46176.32743784722</v>
+        <v>46189.525954201388</v>
       </c>
       <c r="S47">
-        <v>9893.000</v>
+        <v>9210.000</v>
       </c>
       <c r="T47">
-        <v>9893.000</v>
+        <v>9210.000</v>
       </c>
       <c r="U47">
         <v>0</v>
@@ -3407,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="W47" s="4">
-        <v>46176.36704571759</v>
+        <v>46189.538887268522</v>
       </c>
     </row>
     <row r="48">
@@ -3424,10 +3457,10 @@
         <v>23</v>
       </c>
       <c r="E48">
-        <v>7277744</v>
+        <v>7312333</v>
       </c>
       <c r="F48" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="G48" t="s">
         <v>23</v>
@@ -3436,22 +3469,22 @@
         <v>23</v>
       </c>
       <c r="M48" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="P48" s="1">
-        <v>46174.49203425926</v>
+        <v>46181.394416122683</v>
       </c>
       <c r="Q48" s="4">
-        <v>46174.5</v>
+        <v>46182.458333333336</v>
       </c>
       <c r="R48" s="4">
-        <v>46175.401104085649</v>
+        <v>46188.402503240737</v>
       </c>
       <c r="S48">
-        <v>14377.000</v>
+        <v>8272.000</v>
       </c>
       <c r="T48">
-        <v>14377.000</v>
+        <v>8272.000</v>
       </c>
       <c r="U48">
         <v>0</v>
@@ -3460,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="W48" s="4">
-        <v>46175.446175925928</v>
+        <v>46188.404413310185</v>
       </c>
     </row>
     <row r="49">
@@ -3477,10 +3510,10 @@
         <v>23</v>
       </c>
       <c r="E49">
-        <v>7276672</v>
+        <v>7312334</v>
       </c>
       <c r="F49" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="G49" t="s">
         <v>23</v>
@@ -3489,22 +3522,22 @@
         <v>23</v>
       </c>
       <c r="M49" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="P49" s="1">
-        <v>46174.386965358797</v>
+        <v>46181.394481597221</v>
       </c>
       <c r="Q49" s="4">
-        <v>46174.3125</v>
+        <v>46182.458333333336</v>
       </c>
       <c r="R49" s="4">
-        <v>46175.277797997682</v>
+        <v>46188.363727511576</v>
       </c>
       <c r="S49">
-        <v>445.000</v>
+        <v>5617.000</v>
       </c>
       <c r="T49">
-        <v>445.000</v>
+        <v>5617.000</v>
       </c>
       <c r="U49">
         <v>0</v>
@@ -3513,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="W49" s="4">
-        <v>46175.446175925928</v>
+        <v>46188.368130752315</v>
       </c>
     </row>
     <row r="50">
@@ -3530,10 +3563,10 @@
         <v>23</v>
       </c>
       <c r="E50">
-        <v>7243664</v>
+        <v>7306694</v>
       </c>
       <c r="F50" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="G50" t="s">
         <v>23</v>
@@ -3542,22 +3575,22 @@
         <v>23</v>
       </c>
       <c r="M50" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="P50" s="1">
-        <v>46167.397293715279</v>
+        <v>46178.650135613425</v>
       </c>
       <c r="Q50" s="4">
-        <v>46169.3125</v>
+        <v>46181.3125</v>
       </c>
       <c r="R50" s="4">
-        <v>46170.486638159724</v>
+        <v>46188.351883217591</v>
       </c>
       <c r="S50">
-        <v>5002.000</v>
+        <v>7291.000</v>
       </c>
       <c r="T50">
-        <v>5002.000</v>
+        <v>7291.000</v>
       </c>
       <c r="U50">
         <v>0</v>
@@ -3566,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="W50" s="4">
-        <v>46171.52288329861</v>
+        <v>46188.368130405092</v>
       </c>
     </row>
     <row r="51">
@@ -3583,10 +3616,10 @@
         <v>23</v>
       </c>
       <c r="E51">
-        <v>7256954</v>
+        <v>7306693</v>
       </c>
       <c r="F51" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="G51" t="s">
         <v>23</v>
@@ -3595,22 +3628,22 @@
         <v>23</v>
       </c>
       <c r="M51" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="P51" s="1">
-        <v>46169.737280092595</v>
+        <v>46178.650101388892</v>
       </c>
       <c r="Q51" s="4">
-        <v>46171.416666666664</v>
+        <v>46181.395833333336</v>
       </c>
       <c r="R51" s="4">
-        <v>46171.471500266205</v>
+        <v>46188.361928472223</v>
       </c>
       <c r="S51">
-        <v>11226.000</v>
+        <v>5272.000</v>
       </c>
       <c r="T51">
-        <v>11226.000</v>
+        <v>5272.000</v>
       </c>
       <c r="U51">
         <v>0</v>
@@ -3619,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="W51" s="4">
-        <v>46171.521807557867</v>
+        <v>46188.368129826391</v>
       </c>
     </row>
     <row r="52">
@@ -3636,10 +3669,10 @@
         <v>23</v>
       </c>
       <c r="E52">
-        <v>7256935</v>
+        <v>7296112</v>
       </c>
       <c r="F52" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="G52" t="s">
         <v>23</v>
@@ -3648,22 +3681,19 @@
         <v>23</v>
       </c>
       <c r="M52" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="P52" s="1">
-        <v>46169.735800810187</v>
-      </c>
-      <c r="Q52" s="4">
-        <v>46171.25</v>
+        <v>46176.490794872683</v>
       </c>
       <c r="R52" s="4">
-        <v>46171.474860069444</v>
+        <v>46188.357570370368</v>
       </c>
       <c r="S52">
-        <v>12909.000</v>
+        <v>7146.000</v>
       </c>
       <c r="T52">
-        <v>12909.000</v>
+        <v>7146.000</v>
       </c>
       <c r="U52">
         <v>0</v>
@@ -3672,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="W52" s="4">
-        <v>46171.521807025463</v>
+        <v>46188.368129664355</v>
       </c>
     </row>
     <row r="53">
@@ -3689,10 +3719,10 @@
         <v>23</v>
       </c>
       <c r="E53">
-        <v>7256927</v>
+        <v>7331780</v>
       </c>
       <c r="F53" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="G53" t="s">
         <v>23</v>
@@ -3701,25 +3731,22 @@
         <v>23</v>
       </c>
       <c r="M53" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="O53" s="4">
-        <v>46170.541666666664</v>
+        <v>46185.364583333336</v>
       </c>
       <c r="P53" s="1">
-        <v>46169.733974768518</v>
-      </c>
-      <c r="Q53" s="4">
-        <v>46171.375</v>
+        <v>46184.420189351855</v>
       </c>
       <c r="R53" s="4">
-        <v>46171.384800081018</v>
+        <v>46188.330705902779</v>
       </c>
       <c r="S53">
-        <v>470.000</v>
+        <v>2185.000</v>
       </c>
       <c r="T53">
-        <v>470.000</v>
+        <v>2185.000</v>
       </c>
       <c r="U53">
         <v>0</v>
@@ -3728,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="W53" s="4">
-        <v>46171.521806828707</v>
+        <v>46188.33742491898</v>
       </c>
     </row>
     <row r="54">
@@ -3745,10 +3772,10 @@
         <v>23</v>
       </c>
       <c r="E54">
-        <v>7256698</v>
+        <v>7331779</v>
       </c>
       <c r="F54" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="G54" t="s">
         <v>23</v>
@@ -3757,25 +3784,25 @@
         <v>23</v>
       </c>
       <c r="M54" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="O54" s="4">
-        <v>46170.416666666664</v>
+        <v>46185</v>
       </c>
       <c r="P54" s="1">
-        <v>46169.704318553238</v>
+        <v>46184.420142511575</v>
       </c>
       <c r="Q54" s="4">
-        <v>46170.4375</v>
+        <v>46181</v>
       </c>
       <c r="R54" s="4">
-        <v>46170.55747615741</v>
+        <v>46188.332772222224</v>
       </c>
       <c r="S54">
-        <v>15811.000</v>
+        <v>16497.000</v>
       </c>
       <c r="T54">
-        <v>15811.000</v>
+        <v>16497.000</v>
       </c>
       <c r="U54">
         <v>0</v>
@@ -3784,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="W54" s="4">
-        <v>46171.52180628472</v>
+        <v>46188.337424189813</v>
       </c>
     </row>
     <row r="55">
@@ -3801,10 +3828,10 @@
         <v>23</v>
       </c>
       <c r="E55">
-        <v>7256674</v>
+        <v>7327419</v>
       </c>
       <c r="F55" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="G55" t="s">
         <v>23</v>
@@ -3813,25 +3840,22 @@
         <v>23</v>
       </c>
       <c r="M55" t="s">
-        <v>132</v>
-      </c>
-      <c r="O55" s="4">
-        <v>46170.291666666664</v>
+        <v>107</v>
       </c>
       <c r="P55" s="1">
-        <v>46169.697586805552</v>
+        <v>46183.517797372682</v>
       </c>
       <c r="Q55" s="4">
-        <v>46171.291666666664</v>
+        <v>46184.3125</v>
       </c>
       <c r="R55" s="4">
-        <v>46171.366929745367</v>
+        <v>46188.329073842593</v>
       </c>
       <c r="S55">
-        <v>6703.000</v>
+        <v>10574.000</v>
       </c>
       <c r="T55">
-        <v>6703.000</v>
+        <v>10574.000</v>
       </c>
       <c r="U55">
         <v>0</v>
@@ -3840,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="W55" s="4">
-        <v>46171.521805937497</v>
+        <v>46188.337423263889</v>
       </c>
     </row>
     <row r="56">
@@ -3857,10 +3881,10 @@
         <v>23</v>
       </c>
       <c r="E56">
-        <v>7243671</v>
+        <v>7331318</v>
       </c>
       <c r="F56" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="G56" t="s">
         <v>23</v>
@@ -3869,22 +3893,19 @@
         <v>23</v>
       </c>
       <c r="M56" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="P56" s="1">
-        <v>46167.398480636577</v>
-      </c>
-      <c r="Q56" s="4">
-        <v>46170.25</v>
+        <v>46184.369259340281</v>
       </c>
       <c r="R56" s="4">
-        <v>46170.38833533565</v>
+        <v>46185.506102002313</v>
       </c>
       <c r="S56">
-        <v>767.000</v>
+        <v>10749.000</v>
       </c>
       <c r="T56">
-        <v>767.000</v>
+        <v>10749.000</v>
       </c>
       <c r="U56">
         <v>0</v>
@@ -3893,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="W56" s="4">
-        <v>46171.521805752316</v>
+        <v>46188.329308333334</v>
       </c>
     </row>
     <row r="57">
@@ -3910,10 +3931,10 @@
         <v>23</v>
       </c>
       <c r="E57">
-        <v>7186225</v>
+        <v>7306692</v>
       </c>
       <c r="F57" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="G57" t="s">
         <v>23</v>
@@ -3921,23 +3942,23 @@
       <c r="H57" t="s">
         <v>23</v>
       </c>
-      <c r="M57" t="s">
-        <v>136</v>
+      <c r="M57" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="O57" s="4">
+        <v>46181.34375</v>
       </c>
       <c r="P57" s="1">
-        <v>46157.585703935183</v>
-      </c>
-      <c r="Q57" s="4">
-        <v>46160.493105243055</v>
+        <v>46178.650014085651</v>
       </c>
       <c r="R57" s="4">
-        <v>46170.487253356485</v>
+        <v>46188.321652777777</v>
       </c>
       <c r="S57">
-        <v>13685.000</v>
+        <v>10749.000</v>
       </c>
       <c r="T57">
-        <v>13685.000</v>
+        <v>10749.000</v>
       </c>
       <c r="U57">
         <v>0</v>
@@ -3946,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="W57" s="4">
-        <v>46171.521805011573</v>
+        <v>46188.329306516207</v>
       </c>
     </row>
     <row r="58">
@@ -3963,10 +3984,10 @@
         <v>23</v>
       </c>
       <c r="E58">
-        <v>7243667</v>
+        <v>7290512</v>
       </c>
       <c r="F58" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="G58" t="s">
         <v>23</v>
@@ -3975,22 +3996,22 @@
         <v>23</v>
       </c>
       <c r="M58" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="P58" s="1">
-        <v>46167.398084108798</v>
+        <v>46175.705376817132</v>
       </c>
       <c r="Q58" s="4">
-        <v>46170.25</v>
+        <v>46176.5</v>
       </c>
       <c r="R58" s="4">
-        <v>46170.366140659724</v>
+        <v>46188.325696840278</v>
       </c>
       <c r="S58">
-        <v>7345.000</v>
+        <v>14234.000</v>
       </c>
       <c r="T58">
-        <v>7345.000</v>
+        <v>14234.000</v>
       </c>
       <c r="U58">
         <v>0</v>
@@ -3999,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="W58" s="4">
-        <v>46170.37235636574</v>
+        <v>46188.329304166669</v>
       </c>
     </row>
     <row r="59">
@@ -4016,10 +4037,10 @@
         <v>23</v>
       </c>
       <c r="E59">
-        <v>7243666</v>
+        <v>7277742</v>
       </c>
       <c r="F59" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="G59" t="s">
         <v>23</v>
@@ -4028,22 +4049,22 @@
         <v>23</v>
       </c>
       <c r="M59" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="P59" s="1">
-        <v>46167.397709988429</v>
+        <v>46174.491930821758</v>
       </c>
       <c r="Q59" s="4">
-        <v>46169.444444444445</v>
+        <v>46174.416666666664</v>
       </c>
       <c r="R59" s="4">
-        <v>46169.627317511571</v>
+        <v>46188.313768368054</v>
       </c>
       <c r="S59">
-        <v>5379.000</v>
+        <v>18914.000</v>
       </c>
       <c r="T59">
-        <v>5379.000</v>
+        <v>18914.000</v>
       </c>
       <c r="U59">
         <v>0</v>
@@ -4052,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="W59" s="4">
-        <v>46170.372355636573</v>
+        <v>46188.329302546299</v>
       </c>
     </row>
     <row r="60">
@@ -4069,10 +4090,10 @@
         <v>23</v>
       </c>
       <c r="E60">
-        <v>7243660</v>
+        <v>7321304</v>
       </c>
       <c r="F60" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="G60" t="s">
         <v>23</v>
@@ -4081,22 +4102,22 @@
         <v>23</v>
       </c>
       <c r="M60" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="P60" s="1">
-        <v>46167.396469907406</v>
+        <v>46182.379826539349</v>
       </c>
       <c r="Q60" s="4">
-        <v>46168.375</v>
+        <v>46183.458333333336</v>
       </c>
       <c r="R60" s="4">
-        <v>46168.522693749997</v>
+        <v>46184.566309837966</v>
       </c>
       <c r="S60">
-        <v>15726.000</v>
+        <v>1784.000</v>
       </c>
       <c r="T60">
-        <v>15726.000</v>
+        <v>1784.000</v>
       </c>
       <c r="U60">
         <v>0</v>
@@ -4105,7 +4126,7 @@
         <v>0</v>
       </c>
       <c r="W60" s="4">
-        <v>46168.603323611111</v>
+        <v>46188.318567708331</v>
       </c>
     </row>
     <row r="61">
@@ -4122,10 +4143,10 @@
         <v>23</v>
       </c>
       <c r="E61">
-        <v>7243658</v>
+        <v>7321303</v>
       </c>
       <c r="F61" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="G61" t="s">
         <v>23</v>
@@ -4134,22 +4155,22 @@
         <v>23</v>
       </c>
       <c r="M61" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="P61" s="1">
-        <v>46167.396019097221</v>
+        <v>46182.379728553242</v>
       </c>
       <c r="Q61" s="4">
-        <v>46168.479166666664</v>
+        <v>46183.458333333336</v>
       </c>
       <c r="R61" s="4">
-        <v>46168.596083993056</v>
+        <v>46185.474632175923</v>
       </c>
       <c r="S61">
-        <v>18164.000</v>
+        <v>15852.000</v>
       </c>
       <c r="T61">
-        <v>18164.000</v>
+        <v>15852.000</v>
       </c>
       <c r="U61">
         <v>0</v>
@@ -4158,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="W61" s="4">
-        <v>46168.603323067131</v>
+        <v>46188.318567164351</v>
       </c>
     </row>
     <row r="62">
@@ -4175,10 +4196,10 @@
         <v>23</v>
       </c>
       <c r="E62">
-        <v>7209851</v>
+        <v>7312335</v>
       </c>
       <c r="F62" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="G62" t="s">
         <v>23</v>
@@ -4186,20 +4207,23 @@
       <c r="H62" t="s">
         <v>23</v>
       </c>
-      <c r="M62" t="s">
-        <v>146</v>
+      <c r="M62" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="P62" s="1">
-        <v>46161.374809525463</v>
+        <v>46181.394497488429</v>
+      </c>
+      <c r="Q62" s="4">
+        <v>46182.388888888891</v>
       </c>
       <c r="R62" s="4">
-        <v>46168.442082719906</v>
+        <v>46185.475467280092</v>
       </c>
       <c r="S62">
-        <v>10564.000</v>
+        <v>16641.000</v>
       </c>
       <c r="T62">
-        <v>10564.000</v>
+        <v>16641.000</v>
       </c>
       <c r="U62">
         <v>0</v>
@@ -4208,7 +4232,7 @@
         <v>0</v>
       </c>
       <c r="W62" s="4">
-        <v>46168.603322337964</v>
+        <v>46188.318566284725</v>
       </c>
     </row>
     <row r="63">
@@ -4225,10 +4249,10 @@
         <v>23</v>
       </c>
       <c r="E63">
-        <v>7243663</v>
+        <v>7329559</v>
       </c>
       <c r="F63" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="G63" t="s">
         <v>23</v>
@@ -4237,22 +4261,19 @@
         <v>23</v>
       </c>
       <c r="M63" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="P63" s="1">
-        <v>46167.396879664353</v>
-      </c>
-      <c r="Q63" s="4">
-        <v>46168.3125</v>
+        <v>46183.835381215278</v>
       </c>
       <c r="R63" s="4">
-        <v>46168.372719247687</v>
+        <v>46185.394576122686</v>
       </c>
       <c r="S63">
-        <v>7178.000</v>
+        <v>18992.000</v>
       </c>
       <c r="T63">
-        <v>7178.000</v>
+        <v>18992.000</v>
       </c>
       <c r="U63">
         <v>0</v>
@@ -4261,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="W63" s="4">
-        <v>46168.383504201389</v>
+        <v>46188.318260497683</v>
       </c>
     </row>
     <row r="64">
@@ -4278,10 +4299,10 @@
         <v>23</v>
       </c>
       <c r="E64">
-        <v>7243656</v>
+        <v>7312336</v>
       </c>
       <c r="F64" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="G64" t="s">
         <v>23</v>
@@ -4290,22 +4311,22 @@
         <v>23</v>
       </c>
       <c r="M64" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="P64" s="1">
-        <v>46167.395494872682</v>
+        <v>46181.394619016202</v>
       </c>
       <c r="Q64" s="4">
-        <v>46168.25</v>
+        <v>46182.416666666664</v>
       </c>
       <c r="R64" s="4">
-        <v>46168.325715162035</v>
+        <v>46182.563263425924</v>
       </c>
       <c r="S64">
-        <v>8924.000</v>
+        <v>8559.000</v>
       </c>
       <c r="T64">
-        <v>8924.000</v>
+        <v>8559.000</v>
       </c>
       <c r="U64">
         <v>0</v>
@@ -4314,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="W64" s="4">
-        <v>46168.383503321762</v>
+        <v>46183.499163692133</v>
       </c>
     </row>
     <row r="65">
@@ -4331,10 +4352,10 @@
         <v>23</v>
       </c>
       <c r="E65">
-        <v>7234523</v>
+        <v>7297491</v>
       </c>
       <c r="F65" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="G65" t="s">
         <v>23</v>
@@ -4343,19 +4364,25 @@
         <v>23</v>
       </c>
       <c r="M65" t="s">
-        <v>152</v>
+        <v>127</v>
+      </c>
+      <c r="O65" s="4">
+        <v>46178.416666666664</v>
       </c>
       <c r="P65" s="1">
-        <v>46164.418446909724</v>
+        <v>46176.651283530089</v>
+      </c>
+      <c r="Q65" s="4">
+        <v>46178.260416666664</v>
       </c>
       <c r="R65" s="4">
-        <v>46164.542648229166</v>
+        <v>46182.304580173608</v>
       </c>
       <c r="S65">
-        <v>3573.000</v>
+        <v>19653.000</v>
       </c>
       <c r="T65">
-        <v>3573.000</v>
+        <v>19653.000</v>
       </c>
       <c r="U65">
         <v>0</v>
@@ -4364,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="W65" s="4">
-        <v>46164.552599270835</v>
+        <v>46182.394867361108</v>
       </c>
     </row>
     <row r="66">
@@ -4381,10 +4408,10 @@
         <v>23</v>
       </c>
       <c r="E66">
-        <v>7222955</v>
+        <v>7276670</v>
       </c>
       <c r="F66" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="G66" t="s">
         <v>23</v>
@@ -4393,22 +4420,22 @@
         <v>23</v>
       </c>
       <c r="M66" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="P66" s="1">
-        <v>46162.757414780091</v>
+        <v>46174.386795023151</v>
       </c>
       <c r="Q66" s="4">
-        <v>46164.260416666664</v>
+        <v>46174.3125</v>
       </c>
       <c r="R66" s="4">
-        <v>46164.550929016201</v>
+        <v>46181.602299189813</v>
       </c>
       <c r="S66">
-        <v>10360.000</v>
+        <v>7766.000</v>
       </c>
       <c r="T66">
-        <v>10360.000</v>
+        <v>7766.000</v>
       </c>
       <c r="U66">
         <v>0</v>
@@ -4417,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="W66" s="4">
-        <v>46164.552598877315</v>
+        <v>46181.607877893519</v>
       </c>
     </row>
     <row r="67">
@@ -4434,10 +4461,10 @@
         <v>23</v>
       </c>
       <c r="E67">
-        <v>7222913</v>
+        <v>7256959</v>
       </c>
       <c r="F67" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G67" t="s">
         <v>23</v>
@@ -4445,23 +4472,23 @@
       <c r="H67" t="s">
         <v>23</v>
       </c>
-      <c r="M67" s="5" t="s">
-        <v>156</v>
+      <c r="M67" t="s">
+        <v>131</v>
       </c>
       <c r="P67" s="1">
-        <v>46162.756352662036</v>
+        <v>46169.73840185185</v>
       </c>
       <c r="Q67" s="4">
-        <v>46164.333333333336</v>
+        <v>46171.520833333336</v>
       </c>
       <c r="R67" s="4">
-        <v>46164.404302395837</v>
+        <v>46181.602367395833</v>
       </c>
       <c r="S67">
-        <v>7657.000</v>
+        <v>11921.000</v>
       </c>
       <c r="T67">
-        <v>7657.000</v>
+        <v>11921.000</v>
       </c>
       <c r="U67">
         <v>0</v>
@@ -4470,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="W67" s="4">
-        <v>46164.453907951392</v>
+        <v>46181.607877002316</v>
       </c>
     </row>
     <row r="68">
@@ -4487,10 +4514,10 @@
         <v>23</v>
       </c>
       <c r="E68">
-        <v>7217995</v>
+        <v>7256837</v>
       </c>
       <c r="F68" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="G68" t="s">
         <v>23</v>
@@ -4499,22 +4526,25 @@
         <v>23</v>
       </c>
       <c r="M68" t="s">
-        <v>158</v>
+        <v>133</v>
+      </c>
+      <c r="O68" s="4">
+        <v>46170.541666666664</v>
       </c>
       <c r="P68" s="1">
-        <v>46162.28924351852</v>
+        <v>46169.717724456015</v>
       </c>
       <c r="Q68" s="4">
-        <v>46163.291666666664</v>
+        <v>46171.375</v>
       </c>
       <c r="R68" s="4">
-        <v>46163.616474340277</v>
+        <v>46181.601758877317</v>
       </c>
       <c r="S68">
-        <v>5708.000</v>
+        <v>10645.000</v>
       </c>
       <c r="T68">
-        <v>5708.000</v>
+        <v>10645.000</v>
       </c>
       <c r="U68">
         <v>0</v>
@@ -4523,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="W68" s="4">
-        <v>46164.389474687501</v>
+        <v>46181.607876122682</v>
       </c>
     </row>
     <row r="69">
@@ -4540,10 +4570,10 @@
         <v>23</v>
       </c>
       <c r="E69">
-        <v>7209848</v>
+        <v>7297492</v>
       </c>
       <c r="F69" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="G69" t="s">
         <v>23</v>
@@ -4552,25 +4582,22 @@
         <v>23</v>
       </c>
       <c r="M69" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="O69" s="4">
-        <v>46161.291666666664</v>
+        <v>46178.427083333336</v>
       </c>
       <c r="P69" s="1">
-        <v>46161.373708449071</v>
-      </c>
-      <c r="Q69" s="4">
-        <v>46161.586805555555</v>
+        <v>46176.651338159725</v>
       </c>
       <c r="R69" s="4">
-        <v>46163.626690358797</v>
+        <v>46178.483032060183</v>
       </c>
       <c r="S69">
-        <v>16674.000</v>
+        <v>6802.000</v>
       </c>
       <c r="T69">
-        <v>16674.000</v>
+        <v>6802.000</v>
       </c>
       <c r="U69">
         <v>0</v>
@@ -4579,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="W69" s="4">
-        <v>46164.389386608796</v>
+        <v>46181.304573692127</v>
       </c>
     </row>
     <row r="70">
@@ -4596,10 +4623,10 @@
         <v>23</v>
       </c>
       <c r="E70">
-        <v>7222907</v>
+        <v>7290516</v>
       </c>
       <c r="F70" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="G70" t="s">
         <v>23</v>
@@ -4608,22 +4635,22 @@
         <v>23</v>
       </c>
       <c r="M70" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="P70" s="1">
-        <v>46162.75522561343</v>
+        <v>46175.705564502314</v>
       </c>
       <c r="Q70" s="4">
-        <v>46163.368055555555</v>
+        <v>46176.59375</v>
       </c>
       <c r="R70" s="4">
-        <v>46163.519357025463</v>
+        <v>46178.37381646991</v>
       </c>
       <c r="S70">
-        <v>10357.000</v>
+        <v>6600.000</v>
       </c>
       <c r="T70">
-        <v>10357.000</v>
+        <v>6600.000</v>
       </c>
       <c r="U70">
         <v>0</v>
@@ -4632,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="W70" s="4">
-        <v>46163.541440972222</v>
+        <v>46181.304297951392</v>
       </c>
     </row>
     <row r="71">
@@ -4649,10 +4676,10 @@
         <v>23</v>
       </c>
       <c r="E71">
-        <v>7217994</v>
+        <v>7290513</v>
       </c>
       <c r="F71" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="G71" t="s">
         <v>23</v>
@@ -4661,22 +4688,22 @@
         <v>23</v>
       </c>
       <c r="M71" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="P71" s="1">
-        <v>46162.288815127315</v>
+        <v>46175.705472835645</v>
       </c>
       <c r="Q71" s="4">
-        <v>46163.291666666664</v>
+        <v>46175.541666666664</v>
       </c>
       <c r="R71" s="4">
-        <v>46163.35348445602</v>
+        <v>46176.390187384262</v>
       </c>
       <c r="S71">
-        <v>3946.000</v>
+        <v>10634.000</v>
       </c>
       <c r="T71">
-        <v>3946.000</v>
+        <v>10634.000</v>
       </c>
       <c r="U71">
         <v>0</v>
@@ -4685,7 +4712,7 @@
         <v>0</v>
       </c>
       <c r="W71" s="4">
-        <v>46163.541440775465</v>
+        <v>46176.479922453706</v>
       </c>
     </row>
     <row r="72">
@@ -4702,10 +4729,10 @@
         <v>23</v>
       </c>
       <c r="E72">
-        <v>7217993</v>
+        <v>7277745</v>
       </c>
       <c r="F72" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="G72" t="s">
         <v>23</v>
@@ -4714,25 +4741,22 @@
         <v>23</v>
       </c>
       <c r="M72" t="s">
-        <v>166</v>
-      </c>
-      <c r="O72" s="4">
-        <v>46162.416666666664</v>
+        <v>141</v>
       </c>
       <c r="P72" s="1">
-        <v>46162.287909756946</v>
+        <v>46174.492115972222</v>
       </c>
       <c r="Q72" s="4">
-        <v>46162.416666666664</v>
+        <v>46175.291666666664</v>
       </c>
       <c r="R72" s="4">
-        <v>46163.518015046298</v>
+        <v>46176.394080127313</v>
       </c>
       <c r="S72">
-        <v>12356.000</v>
+        <v>8925.000</v>
       </c>
       <c r="T72">
-        <v>12356.000</v>
+        <v>8925.000</v>
       </c>
       <c r="U72">
         <v>0</v>
@@ -4741,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="W72" s="4">
-        <v>46163.541439895831</v>
+        <v>46176.479621759259</v>
       </c>
     </row>
     <row r="73">
@@ -4758,10 +4782,10 @@
         <v>23</v>
       </c>
       <c r="E73">
-        <v>7217991</v>
+        <v>7277755</v>
       </c>
       <c r="F73" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G73" t="s">
         <v>23</v>
@@ -4770,25 +4794,22 @@
         <v>23</v>
       </c>
       <c r="M73" t="s">
-        <v>168</v>
-      </c>
-      <c r="O73" s="4">
-        <v>46162.291666666664</v>
+        <v>143</v>
       </c>
       <c r="P73" s="1">
-        <v>46162.28736678241</v>
+        <v>46174.492233680554</v>
       </c>
       <c r="Q73" s="4">
-        <v>46162.513220173612</v>
+        <v>46175.291666666664</v>
       </c>
       <c r="R73" s="4">
-        <v>46163.531940428242</v>
+        <v>46175.460509027776</v>
       </c>
       <c r="S73">
-        <v>12360.000</v>
+        <v>1502.000</v>
       </c>
       <c r="T73">
-        <v>12360.000</v>
+        <v>1502.000</v>
       </c>
       <c r="U73">
         <v>0</v>
@@ -4797,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="W73" s="4">
-        <v>46163.541439351851</v>
+        <v>46176.367452777777</v>
       </c>
     </row>
     <row r="74">
@@ -4814,10 +4835,10 @@
         <v>23</v>
       </c>
       <c r="E74">
-        <v>7209853</v>
+        <v>7290515</v>
       </c>
       <c r="F74" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="G74" t="s">
         <v>23</v>
@@ -4826,19 +4847,22 @@
         <v>23</v>
       </c>
       <c r="M74" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="P74" s="1">
-        <v>46161.375624884262</v>
+        <v>46175.705520370371</v>
+      </c>
+      <c r="Q74" s="4">
+        <v>46175.604166666664</v>
       </c>
       <c r="R74" s="4">
-        <v>46162.474544826386</v>
+        <v>46176.32743784722</v>
       </c>
       <c r="S74">
-        <v>10350.000</v>
+        <v>9893.000</v>
       </c>
       <c r="T74">
-        <v>10350.000</v>
+        <v>9893.000</v>
       </c>
       <c r="U74">
         <v>0</v>
@@ -4847,7 +4871,7 @@
         <v>0</v>
       </c>
       <c r="W74" s="4">
-        <v>46163.484965937503</v>
+        <v>46176.36704571759</v>
       </c>
     </row>
     <row r="75">
@@ -4864,10 +4888,10 @@
         <v>23</v>
       </c>
       <c r="E75">
-        <v>7186224</v>
+        <v>7277744</v>
       </c>
       <c r="F75" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="G75" t="s">
         <v>23</v>
@@ -4876,22 +4900,22 @@
         <v>23</v>
       </c>
       <c r="M75" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="P75" s="1">
-        <v>46157.585680983793</v>
+        <v>46174.49203425926</v>
       </c>
       <c r="Q75" s="4">
-        <v>46160.493105243055</v>
+        <v>46174.5</v>
       </c>
       <c r="R75" s="4">
-        <v>46160.607764236112</v>
+        <v>46175.401104085649</v>
       </c>
       <c r="S75">
-        <v>8153.000</v>
+        <v>14377.000</v>
       </c>
       <c r="T75">
-        <v>8153.000</v>
+        <v>14377.000</v>
       </c>
       <c r="U75">
         <v>0</v>
@@ -4900,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="W75" s="4">
-        <v>46161.606680011573</v>
+        <v>46175.446175925928</v>
       </c>
     </row>
     <row r="76">
@@ -4917,10 +4941,10 @@
         <v>23</v>
       </c>
       <c r="E76">
-        <v>7186209</v>
+        <v>7276672</v>
       </c>
       <c r="F76" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="G76" t="s">
         <v>23</v>
@@ -4929,22 +4953,22 @@
         <v>23</v>
       </c>
       <c r="M76" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="P76" s="1">
-        <v>46157.580364664354</v>
+        <v>46174.386965358797</v>
       </c>
       <c r="Q76" s="4">
-        <v>46160.367256516205</v>
+        <v>46174.3125</v>
       </c>
       <c r="R76" s="4">
-        <v>46160.444021875002</v>
+        <v>46175.277797997682</v>
       </c>
       <c r="S76">
-        <v>19189.000</v>
+        <v>445.000</v>
       </c>
       <c r="T76">
-        <v>19189.000</v>
+        <v>445.000</v>
       </c>
       <c r="U76">
         <v>0</v>
@@ -4953,7 +4977,7 @@
         <v>0</v>
       </c>
       <c r="W76" s="4">
-        <v>46161.605472025461</v>
+        <v>46175.446175925928</v>
       </c>
     </row>
     <row r="77">
@@ -4970,10 +4994,10 @@
         <v>23</v>
       </c>
       <c r="E77">
-        <v>7185903</v>
+        <v>7243664</v>
       </c>
       <c r="F77" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="G77" t="s">
         <v>23</v>
@@ -4982,22 +5006,22 @@
         <v>23</v>
       </c>
       <c r="M77" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="P77" s="1">
-        <v>46157.55131412037</v>
+        <v>46167.397293715279</v>
       </c>
       <c r="Q77" s="4">
-        <v>46160.493105243055</v>
+        <v>46169.3125</v>
       </c>
       <c r="R77" s="4">
-        <v>46160.545683645832</v>
+        <v>46170.486638159724</v>
       </c>
       <c r="S77">
-        <v>39356.000</v>
+        <v>5002.000</v>
       </c>
       <c r="T77">
-        <v>39356.000</v>
+        <v>5002.000</v>
       </c>
       <c r="U77">
         <v>0</v>
@@ -5006,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="W77" s="4">
-        <v>46161.604525312498</v>
+        <v>46171.52288329861</v>
       </c>
     </row>
     <row r="78">
@@ -5023,10 +5047,10 @@
         <v>23</v>
       </c>
       <c r="E78">
-        <v>7177836</v>
+        <v>7261067</v>
       </c>
       <c r="F78" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="G78" t="s">
         <v>23</v>
@@ -5035,25 +5059,19 @@
         <v>23</v>
       </c>
       <c r="M78" t="s">
-        <v>177</v>
-      </c>
-      <c r="O78" s="4">
-        <v>46157.416666666664</v>
+        <v>153</v>
       </c>
       <c r="P78" s="1">
-        <v>46155.705813773151</v>
-      </c>
-      <c r="Q78" s="4">
-        <v>46157.466666666667</v>
+        <v>46171.450339317133</v>
       </c>
       <c r="R78" s="4">
-        <v>46160.360912615739</v>
+        <v>46171.468652743053</v>
       </c>
       <c r="S78">
-        <v>17794.000</v>
+        <v>13827.000</v>
       </c>
       <c r="T78">
-        <v>17794.000</v>
+        <v>13827.000</v>
       </c>
       <c r="U78">
         <v>0</v>
@@ -5062,7 +5080,7 @@
         <v>0</v>
       </c>
       <c r="W78" s="4">
-        <v>46160.503910451385</v>
+        <v>46171.521808101854</v>
       </c>
     </row>
     <row r="79">
@@ -5079,10 +5097,10 @@
         <v>23</v>
       </c>
       <c r="E79">
-        <v>7175007</v>
+        <v>7256954</v>
       </c>
       <c r="F79" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="G79" t="s">
         <v>23</v>
@@ -5091,25 +5109,22 @@
         <v>23</v>
       </c>
       <c r="M79" t="s">
-        <v>179</v>
-      </c>
-      <c r="O79" s="4">
-        <v>46157.291666666664</v>
+        <v>155</v>
       </c>
       <c r="P79" s="1">
-        <v>46155.454049652777</v>
+        <v>46169.737280092595</v>
       </c>
       <c r="Q79" s="4">
-        <v>46157.35833333333</v>
+        <v>46171.416666666664</v>
       </c>
       <c r="R79" s="4">
-        <v>46157.601774965275</v>
+        <v>46171.471500266205</v>
       </c>
       <c r="S79">
-        <v>21375.000</v>
+        <v>11226.000</v>
       </c>
       <c r="T79">
-        <v>21375.000</v>
+        <v>11226.000</v>
       </c>
       <c r="U79">
         <v>0</v>
@@ -5118,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="W79" s="4">
-        <v>46157.688587037039</v>
+        <v>46171.521807557867</v>
       </c>
     </row>
     <row r="80">
@@ -5135,57 +5150,1615 @@
         <v>23</v>
       </c>
       <c r="E80">
+        <v>7256935</v>
+      </c>
+      <c r="F80" t="s">
+        <v>156</v>
+      </c>
+      <c r="G80" t="s">
+        <v>23</v>
+      </c>
+      <c r="H80" t="s">
+        <v>23</v>
+      </c>
+      <c r="M80" t="s">
+        <v>157</v>
+      </c>
+      <c r="P80" s="1">
+        <v>46169.735800810187</v>
+      </c>
+      <c r="Q80" s="4">
+        <v>46171.25</v>
+      </c>
+      <c r="R80" s="4">
+        <v>46171.474860069444</v>
+      </c>
+      <c r="S80">
+        <v>12909.000</v>
+      </c>
+      <c r="T80">
+        <v>12909.000</v>
+      </c>
+      <c r="U80">
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80" s="4">
+        <v>46171.521807025463</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" t="s">
+        <v>23</v>
+      </c>
+      <c r="E81">
+        <v>7256927</v>
+      </c>
+      <c r="F81" t="s">
+        <v>158</v>
+      </c>
+      <c r="G81" t="s">
+        <v>23</v>
+      </c>
+      <c r="H81" t="s">
+        <v>23</v>
+      </c>
+      <c r="M81" t="s">
+        <v>159</v>
+      </c>
+      <c r="O81" s="4">
+        <v>46170.541666666664</v>
+      </c>
+      <c r="P81" s="1">
+        <v>46169.733974768518</v>
+      </c>
+      <c r="Q81" s="4">
+        <v>46171.375</v>
+      </c>
+      <c r="R81" s="4">
+        <v>46171.384800081018</v>
+      </c>
+      <c r="S81">
+        <v>470.000</v>
+      </c>
+      <c r="T81">
+        <v>470.000</v>
+      </c>
+      <c r="U81">
+        <v>0</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81" s="4">
+        <v>46171.521806828707</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>19</v>
+      </c>
+      <c r="B82" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" t="s">
+        <v>23</v>
+      </c>
+      <c r="D82" t="s">
+        <v>23</v>
+      </c>
+      <c r="E82">
+        <v>7256698</v>
+      </c>
+      <c r="F82" t="s">
+        <v>160</v>
+      </c>
+      <c r="G82" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" t="s">
+        <v>23</v>
+      </c>
+      <c r="M82" t="s">
+        <v>161</v>
+      </c>
+      <c r="O82" s="4">
+        <v>46170.416666666664</v>
+      </c>
+      <c r="P82" s="1">
+        <v>46169.704318553238</v>
+      </c>
+      <c r="Q82" s="4">
+        <v>46170.4375</v>
+      </c>
+      <c r="R82" s="4">
+        <v>46170.55747615741</v>
+      </c>
+      <c r="S82">
+        <v>15811.000</v>
+      </c>
+      <c r="T82">
+        <v>15811.000</v>
+      </c>
+      <c r="U82">
+        <v>0</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82" s="4">
+        <v>46171.52180628472</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" t="s">
+        <v>23</v>
+      </c>
+      <c r="D83" t="s">
+        <v>23</v>
+      </c>
+      <c r="E83">
+        <v>7256674</v>
+      </c>
+      <c r="F83" t="s">
+        <v>162</v>
+      </c>
+      <c r="G83" t="s">
+        <v>23</v>
+      </c>
+      <c r="H83" t="s">
+        <v>23</v>
+      </c>
+      <c r="M83" t="s">
+        <v>163</v>
+      </c>
+      <c r="O83" s="4">
+        <v>46170.291666666664</v>
+      </c>
+      <c r="P83" s="1">
+        <v>46169.697586805552</v>
+      </c>
+      <c r="Q83" s="4">
+        <v>46171.291666666664</v>
+      </c>
+      <c r="R83" s="4">
+        <v>46171.366929745367</v>
+      </c>
+      <c r="S83">
+        <v>6703.000</v>
+      </c>
+      <c r="T83">
+        <v>6703.000</v>
+      </c>
+      <c r="U83">
+        <v>0</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83" s="4">
+        <v>46171.521805937497</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>19</v>
+      </c>
+      <c r="B84" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D84" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84">
+        <v>7243671</v>
+      </c>
+      <c r="F84" t="s">
+        <v>164</v>
+      </c>
+      <c r="G84" t="s">
+        <v>23</v>
+      </c>
+      <c r="H84" t="s">
+        <v>23</v>
+      </c>
+      <c r="M84" t="s">
+        <v>165</v>
+      </c>
+      <c r="P84" s="1">
+        <v>46167.398480636577</v>
+      </c>
+      <c r="Q84" s="4">
+        <v>46170.25</v>
+      </c>
+      <c r="R84" s="4">
+        <v>46170.38833533565</v>
+      </c>
+      <c r="S84">
+        <v>767.000</v>
+      </c>
+      <c r="T84">
+        <v>767.000</v>
+      </c>
+      <c r="U84">
+        <v>0</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84" s="4">
+        <v>46171.521805752316</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>19</v>
+      </c>
+      <c r="B85" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" t="s">
+        <v>23</v>
+      </c>
+      <c r="E85">
+        <v>7186225</v>
+      </c>
+      <c r="F85" t="s">
+        <v>166</v>
+      </c>
+      <c r="G85" t="s">
+        <v>23</v>
+      </c>
+      <c r="H85" t="s">
+        <v>23</v>
+      </c>
+      <c r="M85" t="s">
+        <v>167</v>
+      </c>
+      <c r="P85" s="1">
+        <v>46157.585703935183</v>
+      </c>
+      <c r="Q85" s="4">
+        <v>46160.493105243055</v>
+      </c>
+      <c r="R85" s="4">
+        <v>46170.487253356485</v>
+      </c>
+      <c r="S85">
+        <v>13685.000</v>
+      </c>
+      <c r="T85">
+        <v>13685.000</v>
+      </c>
+      <c r="U85">
+        <v>0</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85" s="4">
+        <v>46171.521805011573</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>19</v>
+      </c>
+      <c r="B86" t="s">
+        <v>23</v>
+      </c>
+      <c r="C86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D86" t="s">
+        <v>23</v>
+      </c>
+      <c r="E86">
+        <v>7243667</v>
+      </c>
+      <c r="F86" t="s">
+        <v>168</v>
+      </c>
+      <c r="G86" t="s">
+        <v>23</v>
+      </c>
+      <c r="H86" t="s">
+        <v>23</v>
+      </c>
+      <c r="M86" t="s">
+        <v>169</v>
+      </c>
+      <c r="P86" s="1">
+        <v>46167.398084108798</v>
+      </c>
+      <c r="Q86" s="4">
+        <v>46170.25</v>
+      </c>
+      <c r="R86" s="4">
+        <v>46170.366140659724</v>
+      </c>
+      <c r="S86">
+        <v>7345.000</v>
+      </c>
+      <c r="T86">
+        <v>7345.000</v>
+      </c>
+      <c r="U86">
+        <v>0</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86" s="4">
+        <v>46170.37235636574</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" t="s">
+        <v>23</v>
+      </c>
+      <c r="E87">
+        <v>7243666</v>
+      </c>
+      <c r="F87" t="s">
+        <v>170</v>
+      </c>
+      <c r="G87" t="s">
+        <v>23</v>
+      </c>
+      <c r="H87" t="s">
+        <v>23</v>
+      </c>
+      <c r="M87" t="s">
+        <v>171</v>
+      </c>
+      <c r="P87" s="1">
+        <v>46167.397709988429</v>
+      </c>
+      <c r="Q87" s="4">
+        <v>46169.444444444445</v>
+      </c>
+      <c r="R87" s="4">
+        <v>46169.627317511571</v>
+      </c>
+      <c r="S87">
+        <v>5379.000</v>
+      </c>
+      <c r="T87">
+        <v>5379.000</v>
+      </c>
+      <c r="U87">
+        <v>0</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87" s="4">
+        <v>46170.372355636573</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>19</v>
+      </c>
+      <c r="B88" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88" t="s">
+        <v>23</v>
+      </c>
+      <c r="D88" t="s">
+        <v>23</v>
+      </c>
+      <c r="E88">
+        <v>7243660</v>
+      </c>
+      <c r="F88" t="s">
+        <v>172</v>
+      </c>
+      <c r="G88" t="s">
+        <v>23</v>
+      </c>
+      <c r="H88" t="s">
+        <v>23</v>
+      </c>
+      <c r="M88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P88" s="1">
+        <v>46167.396469907406</v>
+      </c>
+      <c r="Q88" s="4">
+        <v>46168.375</v>
+      </c>
+      <c r="R88" s="4">
+        <v>46168.522693749997</v>
+      </c>
+      <c r="S88">
+        <v>15726.000</v>
+      </c>
+      <c r="T88">
+        <v>15726.000</v>
+      </c>
+      <c r="U88">
+        <v>0</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88" s="4">
+        <v>46168.603323611111</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>19</v>
+      </c>
+      <c r="B89" t="s">
+        <v>23</v>
+      </c>
+      <c r="C89" t="s">
+        <v>23</v>
+      </c>
+      <c r="D89" t="s">
+        <v>23</v>
+      </c>
+      <c r="E89">
+        <v>7243658</v>
+      </c>
+      <c r="F89" t="s">
+        <v>174</v>
+      </c>
+      <c r="G89" t="s">
+        <v>23</v>
+      </c>
+      <c r="H89" t="s">
+        <v>23</v>
+      </c>
+      <c r="M89" t="s">
+        <v>175</v>
+      </c>
+      <c r="P89" s="1">
+        <v>46167.396019097221</v>
+      </c>
+      <c r="Q89" s="4">
+        <v>46168.479166666664</v>
+      </c>
+      <c r="R89" s="4">
+        <v>46168.596083993056</v>
+      </c>
+      <c r="S89">
+        <v>18164.000</v>
+      </c>
+      <c r="T89">
+        <v>18164.000</v>
+      </c>
+      <c r="U89">
+        <v>0</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89" s="4">
+        <v>46168.603323067131</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>19</v>
+      </c>
+      <c r="B90" t="s">
+        <v>23</v>
+      </c>
+      <c r="C90" t="s">
+        <v>23</v>
+      </c>
+      <c r="D90" t="s">
+        <v>23</v>
+      </c>
+      <c r="E90">
+        <v>7209851</v>
+      </c>
+      <c r="F90" t="s">
+        <v>176</v>
+      </c>
+      <c r="G90" t="s">
+        <v>23</v>
+      </c>
+      <c r="H90" t="s">
+        <v>23</v>
+      </c>
+      <c r="M90" t="s">
+        <v>177</v>
+      </c>
+      <c r="P90" s="1">
+        <v>46161.374809525463</v>
+      </c>
+      <c r="R90" s="4">
+        <v>46168.442082719906</v>
+      </c>
+      <c r="S90">
+        <v>10564.000</v>
+      </c>
+      <c r="T90">
+        <v>10564.000</v>
+      </c>
+      <c r="U90">
+        <v>0</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90" s="4">
+        <v>46168.603322337964</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>19</v>
+      </c>
+      <c r="B91" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91" t="s">
+        <v>23</v>
+      </c>
+      <c r="D91" t="s">
+        <v>23</v>
+      </c>
+      <c r="E91">
+        <v>7243663</v>
+      </c>
+      <c r="F91" t="s">
+        <v>178</v>
+      </c>
+      <c r="G91" t="s">
+        <v>23</v>
+      </c>
+      <c r="H91" t="s">
+        <v>23</v>
+      </c>
+      <c r="M91" t="s">
+        <v>179</v>
+      </c>
+      <c r="P91" s="1">
+        <v>46167.396879664353</v>
+      </c>
+      <c r="Q91" s="4">
+        <v>46168.3125</v>
+      </c>
+      <c r="R91" s="4">
+        <v>46168.372719247687</v>
+      </c>
+      <c r="S91">
+        <v>7178.000</v>
+      </c>
+      <c r="T91">
+        <v>7178.000</v>
+      </c>
+      <c r="U91">
+        <v>0</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91" s="4">
+        <v>46168.383504201389</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>19</v>
+      </c>
+      <c r="B92" t="s">
+        <v>23</v>
+      </c>
+      <c r="C92" t="s">
+        <v>23</v>
+      </c>
+      <c r="D92" t="s">
+        <v>23</v>
+      </c>
+      <c r="E92">
+        <v>7243656</v>
+      </c>
+      <c r="F92" t="s">
+        <v>180</v>
+      </c>
+      <c r="G92" t="s">
+        <v>23</v>
+      </c>
+      <c r="H92" t="s">
+        <v>23</v>
+      </c>
+      <c r="M92" t="s">
+        <v>181</v>
+      </c>
+      <c r="P92" s="1">
+        <v>46167.395494872682</v>
+      </c>
+      <c r="Q92" s="4">
+        <v>46168.25</v>
+      </c>
+      <c r="R92" s="4">
+        <v>46168.325715162035</v>
+      </c>
+      <c r="S92">
+        <v>8924.000</v>
+      </c>
+      <c r="T92">
+        <v>8924.000</v>
+      </c>
+      <c r="U92">
+        <v>0</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92" s="4">
+        <v>46168.383503321762</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>19</v>
+      </c>
+      <c r="B93" t="s">
+        <v>23</v>
+      </c>
+      <c r="C93" t="s">
+        <v>23</v>
+      </c>
+      <c r="D93" t="s">
+        <v>23</v>
+      </c>
+      <c r="E93">
+        <v>7234523</v>
+      </c>
+      <c r="F93" t="s">
+        <v>182</v>
+      </c>
+      <c r="G93" t="s">
+        <v>23</v>
+      </c>
+      <c r="H93" t="s">
+        <v>23</v>
+      </c>
+      <c r="M93" t="s">
+        <v>183</v>
+      </c>
+      <c r="P93" s="1">
+        <v>46164.418446909724</v>
+      </c>
+      <c r="R93" s="4">
+        <v>46164.542648229166</v>
+      </c>
+      <c r="S93">
+        <v>3573.000</v>
+      </c>
+      <c r="T93">
+        <v>3573.000</v>
+      </c>
+      <c r="U93">
+        <v>0</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93" s="4">
+        <v>46164.552599270835</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B94" t="s">
+        <v>23</v>
+      </c>
+      <c r="C94" t="s">
+        <v>23</v>
+      </c>
+      <c r="D94" t="s">
+        <v>23</v>
+      </c>
+      <c r="E94">
+        <v>7222955</v>
+      </c>
+      <c r="F94" t="s">
+        <v>184</v>
+      </c>
+      <c r="G94" t="s">
+        <v>23</v>
+      </c>
+      <c r="H94" t="s">
+        <v>23</v>
+      </c>
+      <c r="M94" t="s">
+        <v>185</v>
+      </c>
+      <c r="P94" s="1">
+        <v>46162.757414780091</v>
+      </c>
+      <c r="Q94" s="4">
+        <v>46164.260416666664</v>
+      </c>
+      <c r="R94" s="4">
+        <v>46164.550929016201</v>
+      </c>
+      <c r="S94">
+        <v>10360.000</v>
+      </c>
+      <c r="T94">
+        <v>10360.000</v>
+      </c>
+      <c r="U94">
+        <v>0</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+      <c r="W94" s="4">
+        <v>46164.552598877315</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>19</v>
+      </c>
+      <c r="B95" t="s">
+        <v>23</v>
+      </c>
+      <c r="C95" t="s">
+        <v>23</v>
+      </c>
+      <c r="D95" t="s">
+        <v>23</v>
+      </c>
+      <c r="E95">
+        <v>7222913</v>
+      </c>
+      <c r="F95" t="s">
+        <v>186</v>
+      </c>
+      <c r="G95" t="s">
+        <v>23</v>
+      </c>
+      <c r="H95" t="s">
+        <v>23</v>
+      </c>
+      <c r="M95" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="P95" s="1">
+        <v>46162.756352662036</v>
+      </c>
+      <c r="Q95" s="4">
+        <v>46164.333333333336</v>
+      </c>
+      <c r="R95" s="4">
+        <v>46164.404302395837</v>
+      </c>
+      <c r="S95">
+        <v>7657.000</v>
+      </c>
+      <c r="T95">
+        <v>7657.000</v>
+      </c>
+      <c r="U95">
+        <v>0</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95" s="4">
+        <v>46164.453907951392</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>19</v>
+      </c>
+      <c r="B96" t="s">
+        <v>23</v>
+      </c>
+      <c r="C96" t="s">
+        <v>23</v>
+      </c>
+      <c r="D96" t="s">
+        <v>23</v>
+      </c>
+      <c r="E96">
+        <v>7217995</v>
+      </c>
+      <c r="F96" t="s">
+        <v>188</v>
+      </c>
+      <c r="G96" t="s">
+        <v>23</v>
+      </c>
+      <c r="H96" t="s">
+        <v>23</v>
+      </c>
+      <c r="M96" t="s">
+        <v>189</v>
+      </c>
+      <c r="P96" s="1">
+        <v>46162.28924351852</v>
+      </c>
+      <c r="Q96" s="4">
+        <v>46163.291666666664</v>
+      </c>
+      <c r="R96" s="4">
+        <v>46163.616474340277</v>
+      </c>
+      <c r="S96">
+        <v>5708.000</v>
+      </c>
+      <c r="T96">
+        <v>5708.000</v>
+      </c>
+      <c r="U96">
+        <v>0</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96" s="4">
+        <v>46164.389474687501</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>19</v>
+      </c>
+      <c r="B97" t="s">
+        <v>23</v>
+      </c>
+      <c r="C97" t="s">
+        <v>23</v>
+      </c>
+      <c r="D97" t="s">
+        <v>23</v>
+      </c>
+      <c r="E97">
+        <v>7209848</v>
+      </c>
+      <c r="F97" t="s">
+        <v>190</v>
+      </c>
+      <c r="G97" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" t="s">
+        <v>23</v>
+      </c>
+      <c r="M97" t="s">
+        <v>191</v>
+      </c>
+      <c r="O97" s="4">
+        <v>46161.291666666664</v>
+      </c>
+      <c r="P97" s="1">
+        <v>46161.373708449071</v>
+      </c>
+      <c r="Q97" s="4">
+        <v>46161.586805555555</v>
+      </c>
+      <c r="R97" s="4">
+        <v>46163.626690358797</v>
+      </c>
+      <c r="S97">
+        <v>16674.000</v>
+      </c>
+      <c r="T97">
+        <v>16674.000</v>
+      </c>
+      <c r="U97">
+        <v>0</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97" s="4">
+        <v>46164.389386608796</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>19</v>
+      </c>
+      <c r="B98" t="s">
+        <v>23</v>
+      </c>
+      <c r="C98" t="s">
+        <v>23</v>
+      </c>
+      <c r="D98" t="s">
+        <v>23</v>
+      </c>
+      <c r="E98">
+        <v>7222907</v>
+      </c>
+      <c r="F98" t="s">
+        <v>192</v>
+      </c>
+      <c r="G98" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" t="s">
+        <v>23</v>
+      </c>
+      <c r="M98" t="s">
+        <v>193</v>
+      </c>
+      <c r="P98" s="1">
+        <v>46162.75522561343</v>
+      </c>
+      <c r="Q98" s="4">
+        <v>46163.368055555555</v>
+      </c>
+      <c r="R98" s="4">
+        <v>46163.519357025463</v>
+      </c>
+      <c r="S98">
+        <v>10357.000</v>
+      </c>
+      <c r="T98">
+        <v>10357.000</v>
+      </c>
+      <c r="U98">
+        <v>0</v>
+      </c>
+      <c r="V98">
+        <v>0</v>
+      </c>
+      <c r="W98" s="4">
+        <v>46163.541440972222</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>19</v>
+      </c>
+      <c r="B99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C99" t="s">
+        <v>23</v>
+      </c>
+      <c r="D99" t="s">
+        <v>23</v>
+      </c>
+      <c r="E99">
+        <v>7217994</v>
+      </c>
+      <c r="F99" t="s">
+        <v>194</v>
+      </c>
+      <c r="G99" t="s">
+        <v>23</v>
+      </c>
+      <c r="H99" t="s">
+        <v>23</v>
+      </c>
+      <c r="M99" t="s">
+        <v>195</v>
+      </c>
+      <c r="P99" s="1">
+        <v>46162.288815127315</v>
+      </c>
+      <c r="Q99" s="4">
+        <v>46163.291666666664</v>
+      </c>
+      <c r="R99" s="4">
+        <v>46163.35348445602</v>
+      </c>
+      <c r="S99">
+        <v>3946.000</v>
+      </c>
+      <c r="T99">
+        <v>3946.000</v>
+      </c>
+      <c r="U99">
+        <v>0</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="W99" s="4">
+        <v>46163.541440775465</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>19</v>
+      </c>
+      <c r="B100" t="s">
+        <v>23</v>
+      </c>
+      <c r="C100" t="s">
+        <v>23</v>
+      </c>
+      <c r="D100" t="s">
+        <v>23</v>
+      </c>
+      <c r="E100">
+        <v>7217993</v>
+      </c>
+      <c r="F100" t="s">
+        <v>196</v>
+      </c>
+      <c r="G100" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" t="s">
+        <v>23</v>
+      </c>
+      <c r="M100" t="s">
+        <v>197</v>
+      </c>
+      <c r="O100" s="4">
+        <v>46162.416666666664</v>
+      </c>
+      <c r="P100" s="1">
+        <v>46162.287909756946</v>
+      </c>
+      <c r="Q100" s="4">
+        <v>46162.416666666664</v>
+      </c>
+      <c r="R100" s="4">
+        <v>46163.518015046298</v>
+      </c>
+      <c r="S100">
+        <v>12356.000</v>
+      </c>
+      <c r="T100">
+        <v>12356.000</v>
+      </c>
+      <c r="U100">
+        <v>0</v>
+      </c>
+      <c r="V100">
+        <v>0</v>
+      </c>
+      <c r="W100" s="4">
+        <v>46163.541439895831</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>19</v>
+      </c>
+      <c r="B101" t="s">
+        <v>23</v>
+      </c>
+      <c r="C101" t="s">
+        <v>23</v>
+      </c>
+      <c r="D101" t="s">
+        <v>23</v>
+      </c>
+      <c r="E101">
+        <v>7217991</v>
+      </c>
+      <c r="F101" t="s">
+        <v>198</v>
+      </c>
+      <c r="G101" t="s">
+        <v>23</v>
+      </c>
+      <c r="H101" t="s">
+        <v>23</v>
+      </c>
+      <c r="M101" t="s">
+        <v>199</v>
+      </c>
+      <c r="O101" s="4">
+        <v>46162.291666666664</v>
+      </c>
+      <c r="P101" s="1">
+        <v>46162.28736678241</v>
+      </c>
+      <c r="Q101" s="4">
+        <v>46162.513220173612</v>
+      </c>
+      <c r="R101" s="4">
+        <v>46163.531940428242</v>
+      </c>
+      <c r="S101">
+        <v>12360.000</v>
+      </c>
+      <c r="T101">
+        <v>12360.000</v>
+      </c>
+      <c r="U101">
+        <v>0</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101" s="4">
+        <v>46163.541439351851</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>19</v>
+      </c>
+      <c r="B102" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102" t="s">
+        <v>23</v>
+      </c>
+      <c r="D102" t="s">
+        <v>23</v>
+      </c>
+      <c r="E102">
+        <v>7209853</v>
+      </c>
+      <c r="F102" t="s">
+        <v>200</v>
+      </c>
+      <c r="G102" t="s">
+        <v>23</v>
+      </c>
+      <c r="H102" t="s">
+        <v>23</v>
+      </c>
+      <c r="M102" t="s">
+        <v>201</v>
+      </c>
+      <c r="P102" s="1">
+        <v>46161.375624884262</v>
+      </c>
+      <c r="R102" s="4">
+        <v>46162.474544826386</v>
+      </c>
+      <c r="S102">
+        <v>10350.000</v>
+      </c>
+      <c r="T102">
+        <v>10350.000</v>
+      </c>
+      <c r="U102">
+        <v>0</v>
+      </c>
+      <c r="V102">
+        <v>0</v>
+      </c>
+      <c r="W102" s="4">
+        <v>46163.484965937503</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>19</v>
+      </c>
+      <c r="B103" t="s">
+        <v>23</v>
+      </c>
+      <c r="C103" t="s">
+        <v>23</v>
+      </c>
+      <c r="D103" t="s">
+        <v>23</v>
+      </c>
+      <c r="E103">
+        <v>7186224</v>
+      </c>
+      <c r="F103" t="s">
+        <v>202</v>
+      </c>
+      <c r="G103" t="s">
+        <v>23</v>
+      </c>
+      <c r="H103" t="s">
+        <v>23</v>
+      </c>
+      <c r="M103" t="s">
+        <v>167</v>
+      </c>
+      <c r="P103" s="1">
+        <v>46157.585680983793</v>
+      </c>
+      <c r="Q103" s="4">
+        <v>46160.493105243055</v>
+      </c>
+      <c r="R103" s="4">
+        <v>46160.607764236112</v>
+      </c>
+      <c r="S103">
+        <v>8153.000</v>
+      </c>
+      <c r="T103">
+        <v>8153.000</v>
+      </c>
+      <c r="U103">
+        <v>0</v>
+      </c>
+      <c r="V103">
+        <v>0</v>
+      </c>
+      <c r="W103" s="4">
+        <v>46161.606680011573</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>19</v>
+      </c>
+      <c r="B104" t="s">
+        <v>23</v>
+      </c>
+      <c r="C104" t="s">
+        <v>23</v>
+      </c>
+      <c r="D104" t="s">
+        <v>23</v>
+      </c>
+      <c r="E104">
+        <v>7186209</v>
+      </c>
+      <c r="F104" t="s">
+        <v>203</v>
+      </c>
+      <c r="G104" t="s">
+        <v>23</v>
+      </c>
+      <c r="H104" t="s">
+        <v>23</v>
+      </c>
+      <c r="M104" t="s">
+        <v>204</v>
+      </c>
+      <c r="P104" s="1">
+        <v>46157.580364664354</v>
+      </c>
+      <c r="Q104" s="4">
+        <v>46160.367256516205</v>
+      </c>
+      <c r="R104" s="4">
+        <v>46160.444021875002</v>
+      </c>
+      <c r="S104">
+        <v>19189.000</v>
+      </c>
+      <c r="T104">
+        <v>19189.000</v>
+      </c>
+      <c r="U104">
+        <v>0</v>
+      </c>
+      <c r="V104">
+        <v>0</v>
+      </c>
+      <c r="W104" s="4">
+        <v>46161.605472025461</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>19</v>
+      </c>
+      <c r="B105" t="s">
+        <v>23</v>
+      </c>
+      <c r="C105" t="s">
+        <v>23</v>
+      </c>
+      <c r="D105" t="s">
+        <v>23</v>
+      </c>
+      <c r="E105">
+        <v>7185903</v>
+      </c>
+      <c r="F105" t="s">
+        <v>205</v>
+      </c>
+      <c r="G105" t="s">
+        <v>23</v>
+      </c>
+      <c r="H105" t="s">
+        <v>23</v>
+      </c>
+      <c r="M105" t="s">
+        <v>206</v>
+      </c>
+      <c r="P105" s="1">
+        <v>46157.55131412037</v>
+      </c>
+      <c r="Q105" s="4">
+        <v>46160.493105243055</v>
+      </c>
+      <c r="R105" s="4">
+        <v>46160.545683645832</v>
+      </c>
+      <c r="S105">
+        <v>39356.000</v>
+      </c>
+      <c r="T105">
+        <v>39356.000</v>
+      </c>
+      <c r="U105">
+        <v>0</v>
+      </c>
+      <c r="V105">
+        <v>0</v>
+      </c>
+      <c r="W105" s="4">
+        <v>46161.604525312498</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>19</v>
+      </c>
+      <c r="B106" t="s">
+        <v>23</v>
+      </c>
+      <c r="C106" t="s">
+        <v>23</v>
+      </c>
+      <c r="D106" t="s">
+        <v>23</v>
+      </c>
+      <c r="E106">
+        <v>7177836</v>
+      </c>
+      <c r="F106" t="s">
+        <v>207</v>
+      </c>
+      <c r="G106" t="s">
+        <v>23</v>
+      </c>
+      <c r="H106" t="s">
+        <v>23</v>
+      </c>
+      <c r="M106" t="s">
+        <v>208</v>
+      </c>
+      <c r="O106" s="4">
+        <v>46157.416666666664</v>
+      </c>
+      <c r="P106" s="1">
+        <v>46155.705813773151</v>
+      </c>
+      <c r="Q106" s="4">
+        <v>46157.466666666667</v>
+      </c>
+      <c r="R106" s="4">
+        <v>46160.360912615739</v>
+      </c>
+      <c r="S106">
+        <v>17794.000</v>
+      </c>
+      <c r="T106">
+        <v>17794.000</v>
+      </c>
+      <c r="U106">
+        <v>0</v>
+      </c>
+      <c r="V106">
+        <v>0</v>
+      </c>
+      <c r="W106" s="4">
+        <v>46160.503910451385</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>19</v>
+      </c>
+      <c r="B107" t="s">
+        <v>23</v>
+      </c>
+      <c r="C107" t="s">
+        <v>23</v>
+      </c>
+      <c r="D107" t="s">
+        <v>23</v>
+      </c>
+      <c r="E107">
+        <v>7175007</v>
+      </c>
+      <c r="F107" t="s">
+        <v>209</v>
+      </c>
+      <c r="G107" t="s">
+        <v>23</v>
+      </c>
+      <c r="H107" t="s">
+        <v>23</v>
+      </c>
+      <c r="M107" t="s">
+        <v>210</v>
+      </c>
+      <c r="O107" s="4">
+        <v>46157.291666666664</v>
+      </c>
+      <c r="P107" s="1">
+        <v>46155.454049652777</v>
+      </c>
+      <c r="Q107" s="4">
+        <v>46157.35833333333</v>
+      </c>
+      <c r="R107" s="4">
+        <v>46157.601774965275</v>
+      </c>
+      <c r="S107">
+        <v>21375.000</v>
+      </c>
+      <c r="T107">
+        <v>21375.000</v>
+      </c>
+      <c r="U107">
+        <v>0</v>
+      </c>
+      <c r="V107">
+        <v>0</v>
+      </c>
+      <c r="W107" s="4">
+        <v>46157.688587037039</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>19</v>
+      </c>
+      <c r="B108" t="s">
+        <v>23</v>
+      </c>
+      <c r="C108" t="s">
+        <v>23</v>
+      </c>
+      <c r="D108" t="s">
+        <v>23</v>
+      </c>
+      <c r="E108">
         <v>7167099</v>
       </c>
-      <c r="F80" t="s">
-        <v>180</v>
-      </c>
-      <c r="G80" t="s">
-        <v>23</v>
-      </c>
-      <c r="H80" t="s">
-        <v>23</v>
-      </c>
-      <c r="M80" t="s">
-        <v>181</v>
-      </c>
-      <c r="P80" s="1">
+      <c r="F108" t="s">
+        <v>211</v>
+      </c>
+      <c r="G108" t="s">
+        <v>23</v>
+      </c>
+      <c r="H108" t="s">
+        <v>23</v>
+      </c>
+      <c r="M108" t="s">
+        <v>212</v>
+      </c>
+      <c r="P108" s="1">
         <v>46154.541764120368</v>
       </c>
-      <c r="R80" s="4">
+      <c r="R108" s="4">
         <v>46155.643980821762</v>
       </c>
-      <c r="S80">
+      <c r="S108">
         <v>11855.000</v>
       </c>
-      <c r="T80">
+      <c r="T108">
         <v>11855.000</v>
       </c>
-      <c r="U80">
-        <v>0</v>
-      </c>
-      <c r="V80">
-        <v>0</v>
-      </c>
-      <c r="W80" s="4">
+      <c r="U108">
+        <v>0</v>
+      </c>
+      <c r="V108">
+        <v>0</v>
+      </c>
+      <c r="W108" s="4">
         <v>46157.304165428242</v>
       </c>
     </row>
-    <row r="81">
-      <c r="S81" s="2">
-        <f ca="1">SUM(S2:S80)</f>
-        <v>0</v>
-      </c>
-      <c r="T81" s="2">
-        <f ca="1">SUM(T2:T80)</f>
-        <v>0</v>
-      </c>
-      <c r="U81" s="2">
-        <f ca="1">SUM(U2:U80)</f>
-        <v>0</v>
-      </c>
-      <c r="V81" s="2">
-        <f ca="1">SUM(V2:V80)</f>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>19</v>
+      </c>
+      <c r="B109" t="s">
+        <v>23</v>
+      </c>
+      <c r="C109" t="s">
+        <v>23</v>
+      </c>
+      <c r="D109" t="s">
+        <v>213</v>
+      </c>
+      <c r="E109">
+        <v>7108660</v>
+      </c>
+      <c r="F109" t="s">
+        <v>214</v>
+      </c>
+      <c r="G109" t="s">
+        <v>23</v>
+      </c>
+      <c r="H109" t="s">
+        <v>215</v>
+      </c>
+      <c r="I109" t="s">
+        <v>215</v>
+      </c>
+      <c r="J109" t="s">
+        <v>216</v>
+      </c>
+      <c r="K109" t="s">
+        <v>217</v>
+      </c>
+      <c r="M109" t="s">
+        <v>23</v>
+      </c>
+      <c r="P109" s="1">
+        <v>46142.678548877317</v>
+      </c>
+      <c r="R109" s="4">
+        <v>46142.683541168983</v>
+      </c>
+      <c r="S109">
+        <v>100.000</v>
+      </c>
+      <c r="T109">
+        <v>100.000</v>
+      </c>
+      <c r="U109">
+        <v>0</v>
+      </c>
+      <c r="V109">
+        <v>0</v>
+      </c>
+      <c r="W109" s="4">
+        <v>46142.68461369213</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="S110" s="2">
+        <f ca="1">SUM(S2:S109)</f>
+        <v>0</v>
+      </c>
+      <c r="T110" s="2">
+        <f ca="1">SUM(T2:T109)</f>
+        <v>0</v>
+      </c>
+      <c r="U110" s="2">
+        <f ca="1">SUM(U2:U109)</f>
+        <v>0</v>
+      </c>
+      <c r="V110" s="2">
+        <f ca="1">SUM(V2:V109)</f>
         <v>0</v>
       </c>
     </row>

--- a/InOrders_latest.xlsx
+++ b/InOrders_latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="245">
   <si>
     <t>Status</t>
   </si>
@@ -85,64 +85,276 @@
     <t>Updated</t>
   </si>
   <si>
+    <t>Notified</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
+    <t>520065211900100</t>
+  </si>
+  <si>
+    <t>2026-06-10 | Imteks (Origin: Georgia) | ASN-IMT-001</t>
+  </si>
+  <si>
+    <t>520065211800100</t>
+  </si>
+  <si>
+    <t>520064219500100</t>
+  </si>
+  <si>
+    <t>2026-06-08 | Imteks Giyim (TR) | ASN-ITR-001</t>
+  </si>
+  <si>
+    <t>520064217600100</t>
+  </si>
+  <si>
+    <t>2026-06-08 | Imteks Giyim (GE) | ASN-IGE-001</t>
+  </si>
+  <si>
+    <t>520064217700100</t>
+  </si>
+  <si>
+    <t>520064218000100</t>
+  </si>
+  <si>
+    <t>520064218100100</t>
+  </si>
+  <si>
+    <t>520064217800100</t>
+  </si>
+  <si>
+    <t>520064217900100</t>
+  </si>
+  <si>
+    <t>520064218200100</t>
+  </si>
+  <si>
+    <t>520064218300100</t>
+  </si>
+  <si>
+    <t>520064217100100</t>
+  </si>
+  <si>
+    <t>520064217200100</t>
+  </si>
+  <si>
+    <t>520064217300100</t>
+  </si>
+  <si>
+    <t>520064217400100</t>
+  </si>
+  <si>
+    <t>520064217500100</t>
+  </si>
+  <si>
+    <t>520063612400200</t>
+  </si>
+  <si>
+    <t>0101886222</t>
+  </si>
+  <si>
+    <t>Truck 70</t>
+  </si>
+  <si>
+    <t>0101886720</t>
+  </si>
+  <si>
+    <t>Truck 71</t>
+  </si>
+  <si>
+    <t>0101883946</t>
+  </si>
+  <si>
+    <t>Truck 69</t>
+  </si>
+  <si>
+    <t>Arrival space</t>
+  </si>
+  <si>
+    <t>0101878070</t>
+  </si>
+  <si>
+    <t>Truck 66</t>
+  </si>
+  <si>
+    <t>0101850638</t>
+  </si>
+  <si>
+    <t>Truck 54</t>
+  </si>
+  <si>
+    <t>JohannesUPSStockUP</t>
+  </si>
+  <si>
+    <t>Johannes_Prod_Test_UPS_StockUP</t>
+  </si>
+  <si>
+    <t>0101878078</t>
+  </si>
+  <si>
+    <t>Truck 67</t>
+  </si>
+  <si>
+    <t>0101878091</t>
+  </si>
+  <si>
+    <t>Truck 68</t>
+  </si>
+  <si>
+    <t>0101873444</t>
+  </si>
+  <si>
+    <t>Truck 65_2</t>
+  </si>
+  <si>
+    <t>0101873442</t>
+  </si>
+  <si>
+    <t>Truck65_1</t>
+  </si>
+  <si>
+    <t>0101867079</t>
+  </si>
+  <si>
+    <t>Truck 64</t>
+  </si>
+  <si>
+    <t>0101865832</t>
+  </si>
+  <si>
+    <t>Truck 62</t>
+  </si>
+  <si>
+    <t>0101867048</t>
+  </si>
+  <si>
+    <t>Truck 63</t>
+  </si>
+  <si>
+    <t>0101865821</t>
+  </si>
+  <si>
+    <t>Truck 61</t>
+  </si>
+  <si>
+    <t>0101861223</t>
+  </si>
+  <si>
+    <t>Truck 60</t>
+  </si>
+  <si>
+    <t>0101857514</t>
+  </si>
+  <si>
+    <t>Truck 59</t>
+  </si>
+  <si>
+    <t>0101856191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truck 57
+</t>
+  </si>
+  <si>
     <t>0101857485</t>
   </si>
   <si>
     <t>Truck 58</t>
   </si>
   <si>
+    <t>520063571300100</t>
+  </si>
+  <si>
+    <t>2026-05-22 | Gelişim Tekstil | ASN-GTK-001</t>
+  </si>
+  <si>
+    <t>520063571200100</t>
+  </si>
+  <si>
+    <t>520063571600100</t>
+  </si>
+  <si>
+    <t>520063571100100</t>
+  </si>
+  <si>
+    <t>520064225200100</t>
+  </si>
+  <si>
+    <t>520064227400100</t>
+  </si>
+  <si>
+    <t>520064225500100</t>
+  </si>
+  <si>
+    <t>520064226900100</t>
+  </si>
+  <si>
+    <t>520064227000100</t>
+  </si>
+  <si>
+    <t>520064226800100</t>
+  </si>
+  <si>
+    <t>520064226600100</t>
+  </si>
+  <si>
+    <t>520063570500100</t>
+  </si>
+  <si>
+    <t>520064225900100</t>
+  </si>
+  <si>
+    <t>520064224800100</t>
+  </si>
+  <si>
+    <t>520064225000100</t>
+  </si>
+  <si>
+    <t>520064224900100</t>
+  </si>
+  <si>
+    <t>520064227300100</t>
+  </si>
+  <si>
+    <t>520064227100100</t>
+  </si>
+  <si>
+    <t>520064226700100</t>
+  </si>
+  <si>
+    <t>520064225800100</t>
+  </si>
+  <si>
+    <t>520063571000100</t>
+  </si>
+  <si>
+    <t>520064226500100</t>
+  </si>
+  <si>
+    <t>520063570300100</t>
+  </si>
+  <si>
+    <t>520064225300100</t>
+  </si>
+  <si>
+    <t>520063570600100</t>
+  </si>
+  <si>
+    <t>520064225100100</t>
+  </si>
+  <si>
+    <t>0101856108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truck 56
+</t>
+  </si>
+  <si>
     <t>0101851677</t>
   </si>
   <si>
     <t>Truck 55</t>
-  </si>
-  <si>
-    <t>0101865821</t>
-  </si>
-  <si>
-    <t>Truck 61</t>
-  </si>
-  <si>
-    <t>Notified</t>
-  </si>
-  <si>
-    <t>0101878091</t>
-  </si>
-  <si>
-    <t>Truck 68</t>
-  </si>
-  <si>
-    <t>0101878078</t>
-  </si>
-  <si>
-    <t>Truck 67</t>
-  </si>
-  <si>
-    <t>0101878070</t>
-  </si>
-  <si>
-    <t>Truck 66</t>
-  </si>
-  <si>
-    <t>0101873444</t>
-  </si>
-  <si>
-    <t>Truck 65_2</t>
-  </si>
-  <si>
-    <t>0101873442</t>
-  </si>
-  <si>
-    <t>Truck65_1</t>
-  </si>
-  <si>
-    <t>0101867079</t>
-  </si>
-  <si>
-    <t>Truck 64</t>
   </si>
   <si>
     <t>0101847437</t>
@@ -152,147 +364,77 @@
 </t>
   </si>
   <si>
-    <t>0101861223</t>
-  </si>
-  <si>
-    <t>Truck 60</t>
-  </si>
-  <si>
-    <t>0101857514</t>
-  </si>
-  <si>
-    <t>Truck 59</t>
-  </si>
-  <si>
-    <t>0101867048</t>
-  </si>
-  <si>
-    <t>Truck 63</t>
-  </si>
-  <si>
-    <t>0101865832</t>
-  </si>
-  <si>
-    <t>Truck 62</t>
-  </si>
-  <si>
-    <t>520063571300100</t>
-  </si>
-  <si>
-    <t>2026-05-22 | Gelişim Tekstil | ASN-GTK-001</t>
-  </si>
-  <si>
-    <t>520063571200100</t>
-  </si>
-  <si>
-    <t>520063571600100</t>
-  </si>
-  <si>
-    <t>520063571100100</t>
-  </si>
-  <si>
-    <t>0101856191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truck 57
+    <t>0101843290</t>
+  </si>
+  <si>
+    <t>Truck 52</t>
+  </si>
+  <si>
+    <t>0101843289</t>
+  </si>
+  <si>
+    <t>Truck 51</t>
+  </si>
+  <si>
+    <t>0101835438</t>
+  </si>
+  <si>
+    <t>Truck 50_1</t>
+  </si>
+  <si>
+    <t>0101833617</t>
+  </si>
+  <si>
+    <t>Truck50_2</t>
+  </si>
+  <si>
+    <t>0101833616</t>
+  </si>
+  <si>
+    <t>Truck 49</t>
+  </si>
+  <si>
+    <t>0101829631</t>
+  </si>
+  <si>
+    <t>Truck 48</t>
+  </si>
+  <si>
+    <t>0101828861</t>
+  </si>
+  <si>
+    <t>Truck 47</t>
+  </si>
+  <si>
+    <t>0101822294</t>
+  </si>
+  <si>
+    <t>Truck46_1</t>
+  </si>
+  <si>
+    <t>0101822293</t>
+  </si>
+  <si>
+    <t>Truck46_2</t>
+  </si>
+  <si>
+    <t>0101814762</t>
+  </si>
+  <si>
+    <t>Truck 44</t>
+  </si>
+  <si>
+    <t>0101811564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truck 43
 </t>
   </si>
   <si>
-    <t>520064225200100</t>
-  </si>
-  <si>
-    <t>520064227400100</t>
-  </si>
-  <si>
-    <t>520064225500100</t>
-  </si>
-  <si>
-    <t>520064226900100</t>
-  </si>
-  <si>
-    <t>520064227000100</t>
-  </si>
-  <si>
-    <t>520064226800100</t>
-  </si>
-  <si>
-    <t>520064226600100</t>
-  </si>
-  <si>
-    <t>520064225900100</t>
-  </si>
-  <si>
-    <t>520064224800100</t>
-  </si>
-  <si>
-    <t>520064225000100</t>
-  </si>
-  <si>
-    <t>520064224900100</t>
-  </si>
-  <si>
-    <t>520064227300100</t>
-  </si>
-  <si>
-    <t>520064227100100</t>
-  </si>
-  <si>
-    <t>520064226700100</t>
-  </si>
-  <si>
-    <t>520064225800100</t>
-  </si>
-  <si>
-    <t>520063571000100</t>
-  </si>
-  <si>
-    <t>520064226500100</t>
-  </si>
-  <si>
-    <t>520063570300100</t>
-  </si>
-  <si>
-    <t>520064225300100</t>
-  </si>
-  <si>
-    <t>520063570600100</t>
-  </si>
-  <si>
-    <t>520064225100100</t>
-  </si>
-  <si>
-    <t>0101856108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truck 56
-</t>
-  </si>
-  <si>
-    <t>520063570500100</t>
-  </si>
-  <si>
-    <t>0101850638</t>
-  </si>
-  <si>
-    <t>Truck 54</t>
-  </si>
-  <si>
-    <t>JohannesUPSStockUP</t>
-  </si>
-  <si>
-    <t>Johannes_Prod_Test_UPS_StockUP</t>
-  </si>
-  <si>
-    <t>0101843290</t>
-  </si>
-  <si>
-    <t>Truck 52</t>
-  </si>
-  <si>
-    <t>0101843289</t>
-  </si>
-  <si>
-    <t>Truck 51</t>
+    <t>0101819592</t>
+  </si>
+  <si>
+    <t>Truck 45_1</t>
   </si>
   <si>
     <t>0101819595</t>
@@ -301,12 +443,6 @@
     <t>Truck 45_2</t>
   </si>
   <si>
-    <t>0101819592</t>
-  </si>
-  <si>
-    <t>Truck 45_1</t>
-  </si>
-  <si>
     <t>0101807477</t>
   </si>
   <si>
@@ -317,36 +453,6 @@
   </si>
   <si>
     <t>Truck 42</t>
-  </si>
-  <si>
-    <t>0101803752</t>
-  </si>
-  <si>
-    <t>Truck 38</t>
-  </si>
-  <si>
-    <t>0101835438</t>
-  </si>
-  <si>
-    <t>Truck 50_1</t>
-  </si>
-  <si>
-    <t>0101833617</t>
-  </si>
-  <si>
-    <t>Truck50_2</t>
-  </si>
-  <si>
-    <t>0101828861</t>
-  </si>
-  <si>
-    <t>Truck 47</t>
-  </si>
-  <si>
-    <t>0101833616</t>
-  </si>
-  <si>
-    <t>Truck 49</t>
   </si>
   <si>
     <t>0101803882</t>
@@ -356,53 +462,76 @@
 </t>
   </si>
   <si>
+    <t>0101803799</t>
+  </si>
+  <si>
+    <t>Truck 39</t>
+  </si>
+  <si>
+    <t>0101791647</t>
+  </si>
+  <si>
+    <t>Truck 37</t>
+  </si>
+  <si>
+    <t>0101803752</t>
+  </si>
+  <si>
+    <t>Truck 38</t>
+  </si>
+  <si>
+    <t>0101791598</t>
+  </si>
+  <si>
+    <t>Truck 36</t>
+  </si>
+  <si>
+    <t>0101788940</t>
+  </si>
+  <si>
+    <t>Truck 34</t>
+  </si>
+  <si>
+    <t>0101787699</t>
+  </si>
+  <si>
+    <t>Truck 33</t>
+  </si>
+  <si>
     <t>0101787704</t>
   </si>
   <si>
     <t>Truck 35</t>
   </si>
   <si>
+    <t>0101783934</t>
+  </si>
+  <si>
+    <t>truck32_2</t>
+  </si>
+  <si>
+    <t>0101783855</t>
+  </si>
+  <si>
+    <t>truck32_1</t>
+  </si>
+  <si>
+    <t>0101784196</t>
+  </si>
+  <si>
+    <t>truck30</t>
+  </si>
+  <si>
     <t>0101786095</t>
   </si>
   <si>
     <t>truck31</t>
   </si>
   <si>
-    <t>0101822294</t>
-  </si>
-  <si>
-    <t>Truck46_1</t>
-  </si>
-  <si>
-    <t>0101822293</t>
-  </si>
-  <si>
-    <t>Truck46_2</t>
-  </si>
-  <si>
-    <t>0101811564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truck 43
-</t>
-  </si>
-  <si>
-    <t>0101829631</t>
-  </si>
-  <si>
-    <t>Truck 48</t>
-  </si>
-  <si>
-    <t>0101814762</t>
-  </si>
-  <si>
-    <t>Truck 44</t>
-  </si>
-  <si>
-    <t>0101791647</t>
-  </si>
-  <si>
-    <t>Truck 37</t>
+    <t>0101783776</t>
+  </si>
+  <si>
+    <t>truck29_2</t>
   </si>
   <si>
     <t>0101783775</t>
@@ -411,64 +540,70 @@
     <t>truck29_1</t>
   </si>
   <si>
+    <t>Shopify Cutover Inbound</t>
+  </si>
+  <si>
+    <t>Shopify Cutover Virtual Inbound Stockupf for Cutover Outbound</t>
+  </si>
+  <si>
     <t>0101781187</t>
   </si>
   <si>
     <t>truck28</t>
   </si>
   <si>
+    <t>0101772410</t>
+  </si>
+  <si>
+    <t>truck27</t>
+  </si>
+  <si>
+    <t>0101771612</t>
+  </si>
+  <si>
+    <t>truck26</t>
+  </si>
+  <si>
+    <t>0101780370</t>
+  </si>
+  <si>
+    <t>truck25_2</t>
+  </si>
+  <si>
     <t>0101780369</t>
   </si>
   <si>
     <t>truck 25_1</t>
   </si>
   <si>
-    <t>0101803799</t>
-  </si>
-  <si>
-    <t>Truck 39</t>
-  </si>
-  <si>
-    <t>0101791598</t>
-  </si>
-  <si>
-    <t>Truck 36</t>
-  </si>
-  <si>
-    <t>0101787699</t>
-  </si>
-  <si>
-    <t>Truck 33</t>
-  </si>
-  <si>
-    <t>0101783855</t>
-  </si>
-  <si>
-    <t>truck32_1</t>
-  </si>
-  <si>
-    <t>0101783934</t>
-  </si>
-  <si>
-    <t>truck32_2</t>
-  </si>
-  <si>
-    <t>0101788940</t>
-  </si>
-  <si>
-    <t>Truck 34</t>
-  </si>
-  <si>
-    <t>0101784196</t>
-  </si>
-  <si>
-    <t>truck30</t>
-  </si>
-  <si>
-    <t>0101783776</t>
-  </si>
-  <si>
-    <t>truck29_2</t>
+    <t>0101771085</t>
+  </si>
+  <si>
+    <t>truck24</t>
+  </si>
+  <si>
+    <t>0101771004</t>
+  </si>
+  <si>
+    <t>truck23</t>
+  </si>
+  <si>
+    <t>0101768648</t>
+  </si>
+  <si>
+    <t>truck22_2</t>
+  </si>
+  <si>
+    <t>0101768624</t>
+  </si>
+  <si>
+    <t>truck22_1</t>
+  </si>
+  <si>
+    <t>0101768534</t>
+  </si>
+  <si>
+    <t>truck21</t>
   </si>
   <si>
     <t>0101768495</t>
@@ -477,64 +612,10 @@
     <t>truck20</t>
   </si>
   <si>
-    <t>Shopify Cutover Inbound</t>
-  </si>
-  <si>
-    <t>Shopify Cutover Virtual Inbound Stockupf for Cutover Outbound</t>
-  </si>
-  <si>
-    <t>0101772410</t>
-  </si>
-  <si>
-    <t>truck27</t>
-  </si>
-  <si>
-    <t>0101771612</t>
-  </si>
-  <si>
-    <t>truck26</t>
-  </si>
-  <si>
-    <t>0101780370</t>
-  </si>
-  <si>
-    <t>truck25_2</t>
-  </si>
-  <si>
-    <t>0101771085</t>
-  </si>
-  <si>
-    <t>truck24</t>
-  </si>
-  <si>
-    <t>0101771004</t>
-  </si>
-  <si>
-    <t>truck23</t>
-  </si>
-  <si>
-    <t>0101768648</t>
-  </si>
-  <si>
-    <t>truck22_2</t>
-  </si>
-  <si>
-    <t>0101737929</t>
-  </si>
-  <si>
-    <t>Truck6</t>
-  </si>
-  <si>
-    <t>0101768624</t>
-  </si>
-  <si>
-    <t>truck22_1</t>
-  </si>
-  <si>
-    <t>0101768534</t>
-  </si>
-  <si>
-    <t>truck21</t>
+    <t>0101767215</t>
+  </si>
+  <si>
+    <t>truck19</t>
   </si>
   <si>
     <t>0101765025</t>
@@ -547,18 +628,6 @@
   </si>
   <si>
     <t>truck17</t>
-  </si>
-  <si>
-    <t>0101744972</t>
-  </si>
-  <si>
-    <t>truck8</t>
-  </si>
-  <si>
-    <t>0101767215</t>
-  </si>
-  <si>
-    <t>truck19</t>
   </si>
   <si>
     <t>0101762744</t>
@@ -586,46 +655,58 @@
 </t>
   </si>
   <si>
+    <t>0101759115</t>
+  </si>
+  <si>
+    <t>truck13</t>
+  </si>
+  <si>
     <t>0101754210</t>
   </si>
   <si>
     <t>truck 12_2</t>
   </si>
   <si>
+    <t>0101754187</t>
+  </si>
+  <si>
+    <t>truck 12_1</t>
+  </si>
+  <si>
+    <t>0101737834</t>
+  </si>
+  <si>
+    <t>truck11</t>
+  </si>
+  <si>
+    <t>0101750224</t>
+  </si>
+  <si>
+    <t>truck10</t>
+  </si>
+  <si>
+    <t>0101746503</t>
+  </si>
+  <si>
+    <t>truck9</t>
+  </si>
+  <si>
+    <t>0101744972</t>
+  </si>
+  <si>
+    <t>truck8</t>
+  </si>
+  <si>
     <t>0101743044</t>
   </si>
   <si>
     <t>truck7</t>
   </si>
   <si>
-    <t>0101759115</t>
-  </si>
-  <si>
-    <t>truck13</t>
-  </si>
-  <si>
-    <t>0101754187</t>
-  </si>
-  <si>
-    <t>truck 12_1</t>
-  </si>
-  <si>
-    <t>0101737834</t>
-  </si>
-  <si>
-    <t>truck11</t>
-  </si>
-  <si>
-    <t>0101750224</t>
-  </si>
-  <si>
-    <t>truck10</t>
-  </si>
-  <si>
-    <t>0101746503</t>
-  </si>
-  <si>
-    <t>truck9</t>
+    <t>0101737929</t>
+  </si>
+  <si>
+    <t>Truck6</t>
   </si>
   <si>
     <t>0101738755</t>
@@ -1040,16 +1121,16 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W110"/>
+  <dimension ref="A1:W130"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="10.28125" customWidth="1"/>
+    <col min="1" max="1" width="13.421875" customWidth="1"/>
     <col min="2" max="2" width="16.00390625" customWidth="1"/>
     <col min="3" max="3" width="29.8515625" customWidth="1"/>
     <col min="4" max="4" width="12.28125" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" customWidth="1"/>
     <col min="6" max="6" width="24.140625" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="47.7109375" customWidth="1"/>
     <col min="8" max="8" width="22.28125" customWidth="1"/>
     <col min="9" max="9" width="12.8515625" customWidth="1"/>
     <col min="10" max="10" width="15.00390625" customWidth="1"/>
@@ -1139,1043 +1220,992 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>7355667</v>
+        <v>7382509</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P2" s="1">
-        <v>46191.4713122338</v>
-      </c>
-      <c r="R2" s="4">
-        <v>46198.319310104169</v>
+        <v>46198.737117013887</v>
       </c>
       <c r="S2">
-        <v>15383.000</v>
+        <v>1120.000</v>
       </c>
       <c r="T2">
-        <v>15383.000</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1120.000</v>
       </c>
       <c r="V2">
         <v>0</v>
       </c>
       <c r="W2" s="4">
-        <v>46198.319958796295</v>
+        <v>46198.737558761575</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>7352722</v>
+        <v>7382508</v>
       </c>
       <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
         <v>26</v>
       </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="P3" s="1">
-        <v>46190.517798842593</v>
-      </c>
-      <c r="R3" s="4">
-        <v>46198.316219409724</v>
+        <v>46198.737110150461</v>
       </c>
       <c r="S3">
-        <v>13727.000</v>
+        <v>1971.000</v>
       </c>
       <c r="T3">
-        <v>13727.000</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1971.000</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
       <c r="W3" s="4">
-        <v>46198.317383530091</v>
+        <v>46198.737558761575</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>7362235</v>
+        <v>7382456</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="P4" s="1">
-        <v>46195.402748692133</v>
-      </c>
-      <c r="R4" s="4">
-        <v>46198.313491319444</v>
+        <v>46198.735387152781</v>
       </c>
       <c r="S4">
-        <v>10614.000</v>
+        <v>1540.000</v>
       </c>
       <c r="T4">
-        <v>10614.000</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1540.000</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
       <c r="W4" s="4">
-        <v>46198.314641435187</v>
+        <v>46198.737558761575</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5">
+        <v>7382452</v>
+      </c>
+      <c r="F5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5">
-        <v>7373968</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>31</v>
       </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="P5" s="1">
-        <v>46197.485422534723</v>
+        <v>46198.732921678238</v>
       </c>
       <c r="S5">
-        <v>18575.000</v>
+        <v>787.000</v>
       </c>
       <c r="T5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>18575.000</v>
+        <v>787.000</v>
       </c>
       <c r="V5">
         <v>0</v>
       </c>
       <c r="W5" s="4">
-        <v>46197.668712349536</v>
+        <v>46198.737558564811</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>7374444</v>
+        <v>7382451</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="P6" s="1">
-        <v>46197.553791817132</v>
+        <v>46198.732911574072</v>
       </c>
       <c r="S6">
-        <v>10410.000</v>
+        <v>1850.000</v>
       </c>
       <c r="T6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>10410.000</v>
+        <v>1850.000</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6" s="4">
-        <v>46197.554211886571</v>
+        <v>46198.737558182867</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>7374441</v>
+        <v>7382450</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M7" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P7" s="1">
-        <v>46197.552075150466</v>
+        <v>46198.732898379632</v>
       </c>
       <c r="S7">
-        <v>10194.000</v>
+        <v>3021.000</v>
       </c>
       <c r="T7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>10194.000</v>
+        <v>3021.000</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7" s="4">
-        <v>46197.552593900466</v>
+        <v>46198.737557835651</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>7369152</v>
+        <v>7382449</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P8" s="1">
-        <v>46196.459848344908</v>
-      </c>
-      <c r="R8" s="4">
-        <v>46197.493816087961</v>
+        <v>46198.732894409724</v>
       </c>
       <c r="S8">
-        <v>300.000</v>
+        <v>1432.000</v>
       </c>
       <c r="T8">
-        <v>300.000</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1432.000</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8" s="4">
-        <v>46197.550397141204</v>
+        <v>46198.737557488428</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9">
-        <v>7369151</v>
+        <v>7382448</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M9" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="P9" s="1">
-        <v>46196.459830243053</v>
-      </c>
-      <c r="R9" s="4">
-        <v>46197.531721678242</v>
+        <v>46198.73288984954</v>
       </c>
       <c r="S9">
-        <v>3638.000</v>
+        <v>1038.000</v>
       </c>
       <c r="T9">
-        <v>3638.000</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1038.000</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9" s="4">
-        <v>46197.550396956016</v>
+        <v>46198.737557291664</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10">
-        <v>7368806</v>
+        <v>7382447</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M10" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="P10" s="1">
-        <v>46196.377559722219</v>
-      </c>
-      <c r="R10" s="4">
-        <v>46197.497936342595</v>
+        <v>46198.732886261576</v>
       </c>
       <c r="S10">
-        <v>5755.000</v>
+        <v>1256.000</v>
       </c>
       <c r="T10">
-        <v>5755.000</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1256.000</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10" s="4">
-        <v>46197.550396064813</v>
+        <v>46198.737556944441</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11">
-        <v>7352670</v>
+        <v>7382445</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>44</v>
+        <v>24</v>
+      </c>
+      <c r="M11" t="s">
+        <v>24</v>
       </c>
       <c r="P11" s="1">
-        <v>46190.508466550928</v>
-      </c>
-      <c r="R11" s="4">
-        <v>46197.408573148146</v>
+        <v>46198.73287994213</v>
       </c>
       <c r="S11">
-        <v>10751.000</v>
+        <v>2105.000</v>
       </c>
       <c r="T11">
-        <v>10751.000</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2105.000</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11" s="4">
-        <v>46197.438478206015</v>
+        <v>46198.737556562497</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E12">
-        <v>7358767</v>
+        <v>7382444</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M12" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="P12" s="1">
-        <v>46192.659844444446</v>
-      </c>
-      <c r="R12" s="4">
-        <v>46197.3828096875</v>
+        <v>46198.732873067129</v>
       </c>
       <c r="S12">
-        <v>10207.000</v>
+        <v>2179.000</v>
       </c>
       <c r="T12">
-        <v>10207.000</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2179.000</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12" s="4">
-        <v>46197.391247916668</v>
+        <v>46198.737556400461</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13">
-        <v>7358766</v>
+        <v>7382443</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M13" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="P13" s="1">
-        <v>46192.659814814811</v>
-      </c>
-      <c r="R13" s="4">
-        <v>46197.366926122682</v>
+        <v>46198.732865821759</v>
       </c>
       <c r="S13">
-        <v>8661.000</v>
+        <v>2953.000</v>
       </c>
       <c r="T13">
-        <v>8661.000</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2953.000</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
       <c r="W13" s="4">
-        <v>46197.391093518519</v>
+        <v>46198.737556215281</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14">
-        <v>7362236</v>
+        <v>7382442</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M14" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="P14" s="1">
-        <v>46195.402819178242</v>
-      </c>
-      <c r="R14" s="4">
-        <v>46196.601059108798</v>
+        <v>46198.732861307872</v>
       </c>
       <c r="S14">
-        <v>6305.000</v>
+        <v>1725.000</v>
       </c>
       <c r="T14">
-        <v>6305.000</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1725.000</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14" s="4">
-        <v>46197.278671446758</v>
+        <v>46198.737556215281</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15">
-        <v>7362625</v>
+        <v>7382441</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M15" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="P15" s="1">
-        <v>46195.438085185182</v>
-      </c>
-      <c r="R15" s="4">
-        <v>46196.523870486111</v>
+        <v>46198.732857673611</v>
       </c>
       <c r="S15">
-        <v>6200.000</v>
+        <v>1187.000</v>
       </c>
       <c r="T15">
-        <v>6200.000</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1187.000</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15" s="4">
-        <v>46197.278575775461</v>
+        <v>46198.737556018517</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E16">
-        <v>7353363</v>
+        <v>7382440</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G16" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M16" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="P16" s="1">
-        <v>46190.666969988422</v>
-      </c>
-      <c r="R16" s="4">
-        <v>46195.511062997684</v>
+        <v>46198.732847916668</v>
       </c>
       <c r="S16">
-        <v>472.000</v>
+        <v>3785.000</v>
       </c>
       <c r="T16">
-        <v>472.000</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3785.000</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16" s="4">
-        <v>46196.389409641204</v>
+        <v>46198.737556018517</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E17">
-        <v>7353362</v>
+        <v>7382439</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G17" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M17" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="P17" s="1">
-        <v>46190.666969444443</v>
-      </c>
-      <c r="R17" s="4">
-        <v>46195.521521527779</v>
+        <v>46198.73284394676</v>
       </c>
       <c r="S17">
-        <v>612.000</v>
+        <v>1275.000</v>
       </c>
       <c r="T17">
-        <v>612.000</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1275.000</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17" s="4">
-        <v>46196.389409641204</v>
+        <v>46198.737556018517</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E18">
-        <v>7353361</v>
+        <v>7382438</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G18" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M18" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="P18" s="1">
-        <v>46190.666967094905</v>
-      </c>
-      <c r="R18" s="4">
-        <v>46195.535836192132</v>
+        <v>46198.732842511577</v>
       </c>
       <c r="S18">
-        <v>2383.000</v>
+        <v>289.000</v>
       </c>
       <c r="T18">
-        <v>2383.000</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>289.000</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18" s="4">
-        <v>46196.389409641204</v>
+        <v>46198.73755528935</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19">
-        <v>7353360</v>
+        <v>7380191</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M19" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="P19" s="1">
-        <v>46190.666964201388</v>
-      </c>
-      <c r="R19" s="4">
-        <v>46195.523977164354</v>
+        <v>46198.481063622683</v>
       </c>
       <c r="S19">
-        <v>2262.000</v>
+        <v>8875.000</v>
       </c>
       <c r="T19">
-        <v>2262.000</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>8875.000</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19" s="4">
-        <v>46196.389409641204</v>
+        <v>46198.483989386572</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E20">
-        <v>7355924</v>
+        <v>7380190</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H20" t="s">
-        <v>23</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>59</v>
+        <v>24</v>
+      </c>
+      <c r="M20" t="s">
+        <v>48</v>
       </c>
       <c r="P20" s="1">
-        <v>46191.548452546296</v>
-      </c>
-      <c r="R20" s="4">
-        <v>46195.391070254627</v>
+        <v>46198.481004479167</v>
       </c>
       <c r="S20">
-        <v>8044.000</v>
+        <v>9916.000</v>
       </c>
       <c r="T20">
-        <v>8044.000</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>9916.000</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20" s="4">
-        <v>46196.389409641204</v>
+        <v>46198.483988460648</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E21">
-        <v>7353359</v>
+        <v>7379335</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="G21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="P21" s="1">
-        <v>46190.66696145833</v>
-      </c>
-      <c r="R21" s="4">
-        <v>46195.537172372686</v>
+        <v>46198.391359803238</v>
       </c>
       <c r="S21">
-        <v>3982.000</v>
+        <v>11465.000</v>
       </c>
       <c r="T21">
-        <v>3982.000</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>11465.000</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21" s="4">
-        <v>46196.389409456016</v>
+        <v>46198.392504664349</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22">
-        <v>7353358</v>
+        <v>7374441</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P22" s="1">
-        <v>46190.666954432869</v>
+        <v>46197.552075150466</v>
       </c>
       <c r="R22" s="4">
-        <v>46195.532108368054</v>
+        <v>46199.288609340278</v>
       </c>
       <c r="S22">
-        <v>1113.000</v>
+        <v>10194.000</v>
       </c>
       <c r="T22">
-        <v>1113.000</v>
+        <v>839.000</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>9355.000</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22" s="4">
-        <v>46196.389409456016</v>
+        <v>46199.252992164351</v>
       </c>
     </row>
     <row r="23">
@@ -2183,40 +2213,46 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23">
-        <v>7353357</v>
+        <v>7349603</v>
       </c>
       <c r="F23" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M23" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="N23" s="1">
+        <v>46190</v>
       </c>
       <c r="P23" s="1">
-        <v>46190.666949340281</v>
+        <v>46189.643392094906</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>46190.996527777781</v>
       </c>
       <c r="R23" s="4">
-        <v>46195.517305439818</v>
+        <v>46190.579668171296</v>
       </c>
       <c r="S23">
-        <v>447.000</v>
+        <v>5965.000</v>
       </c>
       <c r="T23">
-        <v>447.000</v>
+        <v>5965.000</v>
       </c>
       <c r="U23">
         <v>0</v>
@@ -2225,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="4">
-        <v>46196.389409456016</v>
+        <v>46191.313541932868</v>
       </c>
     </row>
     <row r="24">
@@ -2233,49 +2269,55 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E24">
-        <v>7353356</v>
+        <v>7166305</v>
       </c>
       <c r="F24" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M24" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="N24" s="1">
+        <v>46152</v>
       </c>
       <c r="P24" s="1">
-        <v>46190.66694664352</v>
+        <v>46154.508897418978</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>46162.29583333333</v>
       </c>
       <c r="R24" s="4">
-        <v>46195.528761724534</v>
+        <v>46154.512428125003</v>
       </c>
       <c r="S24">
-        <v>284.000</v>
+        <v>100.000</v>
       </c>
       <c r="T24">
-        <v>284.000</v>
+        <v>98.000</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.000</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24" s="4">
-        <v>46196.389409456016</v>
+        <v>46190.318931481481</v>
       </c>
     </row>
     <row r="25">
@@ -2283,40 +2325,40 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25">
-        <v>7353355</v>
+        <v>7374444</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M25" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="P25" s="1">
-        <v>46190.666944293982</v>
+        <v>46197.553791817132</v>
       </c>
       <c r="R25" s="4">
-        <v>46195.528790659722</v>
+        <v>46198.500830902776</v>
       </c>
       <c r="S25">
-        <v>304.000</v>
+        <v>10410.000</v>
       </c>
       <c r="T25">
-        <v>304.000</v>
+        <v>10410.000</v>
       </c>
       <c r="U25">
         <v>0</v>
@@ -2325,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="W25" s="4">
-        <v>46196.389409456016</v>
+        <v>46198.517632291667</v>
       </c>
     </row>
     <row r="26">
@@ -2333,40 +2375,40 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26">
-        <v>7353354</v>
+        <v>7373968</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M26" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="P26" s="1">
-        <v>46190.666940659721</v>
+        <v>46197.485422534723</v>
       </c>
       <c r="R26" s="4">
-        <v>46195.536209409722</v>
+        <v>46199.287059374998</v>
       </c>
       <c r="S26">
-        <v>1251.000</v>
+        <v>18575.000</v>
       </c>
       <c r="T26">
-        <v>1251.000</v>
+        <v>18575.000</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -2375,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="W26" s="4">
-        <v>46196.389409456016</v>
+        <v>46199.324616701386</v>
       </c>
     </row>
     <row r="27">
@@ -2383,40 +2425,40 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E27">
-        <v>7353353</v>
+        <v>7369152</v>
       </c>
       <c r="F27" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M27" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="P27" s="1">
-        <v>46190.666939583331</v>
+        <v>46196.459848344908</v>
       </c>
       <c r="R27" s="4">
-        <v>46195.537300034724</v>
+        <v>46197.493816087961</v>
       </c>
       <c r="S27">
-        <v>1257.000</v>
+        <v>300.000</v>
       </c>
       <c r="T27">
-        <v>1257.000</v>
+        <v>300.000</v>
       </c>
       <c r="U27">
         <v>0</v>
@@ -2425,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="W27" s="4">
-        <v>46196.389409456016</v>
+        <v>46197.550397141204</v>
       </c>
     </row>
     <row r="28">
@@ -2433,40 +2475,40 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E28">
-        <v>7353351</v>
+        <v>7369151</v>
       </c>
       <c r="F28" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M28" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="P28" s="1">
-        <v>46190.666933101849</v>
+        <v>46196.459830243053</v>
       </c>
       <c r="R28" s="4">
-        <v>46195.523942245367</v>
+        <v>46197.531721678242</v>
       </c>
       <c r="S28">
-        <v>1295.000</v>
+        <v>3638.000</v>
       </c>
       <c r="T28">
-        <v>1295.000</v>
+        <v>3638.000</v>
       </c>
       <c r="U28">
         <v>0</v>
@@ -2475,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="W28" s="4">
-        <v>46196.389409293981</v>
+        <v>46197.550396956016</v>
       </c>
     </row>
     <row r="29">
@@ -2483,40 +2525,40 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E29">
-        <v>7353350</v>
+        <v>7368806</v>
       </c>
       <c r="F29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M29" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="P29" s="1">
-        <v>46190.666932719905</v>
+        <v>46196.377559722219</v>
       </c>
       <c r="R29" s="4">
-        <v>46195.536177581016</v>
+        <v>46197.497936342595</v>
       </c>
       <c r="S29">
-        <v>72.000</v>
+        <v>5755.000</v>
       </c>
       <c r="T29">
-        <v>72.000</v>
+        <v>5755.000</v>
       </c>
       <c r="U29">
         <v>0</v>
@@ -2525,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="W29" s="4">
-        <v>46196.389409293981</v>
+        <v>46197.550396064813</v>
       </c>
     </row>
     <row r="30">
@@ -2533,40 +2575,40 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E30">
-        <v>7353349</v>
+        <v>7362625</v>
       </c>
       <c r="F30" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" t="s">
+        <v>24</v>
+      </c>
+      <c r="M30" t="s">
         <v>69</v>
       </c>
-      <c r="G30" t="s">
-        <v>23</v>
-      </c>
-      <c r="H30" t="s">
-        <v>23</v>
-      </c>
-      <c r="M30" t="s">
-        <v>54</v>
-      </c>
       <c r="P30" s="1">
-        <v>46190.666930555555</v>
+        <v>46195.438085185182</v>
       </c>
       <c r="R30" s="4">
-        <v>46195.536192395833</v>
+        <v>46196.523870486111</v>
       </c>
       <c r="S30">
-        <v>101.000</v>
+        <v>6200.000</v>
       </c>
       <c r="T30">
-        <v>101.000</v>
+        <v>6200.000</v>
       </c>
       <c r="U30">
         <v>0</v>
@@ -2575,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="W30" s="4">
-        <v>46196.389409293981</v>
+        <v>46197.278575775461</v>
       </c>
     </row>
     <row r="31">
@@ -2583,40 +2625,40 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E31">
-        <v>7353348</v>
+        <v>7362236</v>
       </c>
       <c r="F31" t="s">
         <v>70</v>
       </c>
       <c r="G31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M31" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="P31" s="1">
-        <v>46190.666919525465</v>
+        <v>46195.402819178242</v>
       </c>
       <c r="R31" s="4">
-        <v>46195.534000462962</v>
+        <v>46196.601059108798</v>
       </c>
       <c r="S31">
-        <v>1620.000</v>
+        <v>6305.000</v>
       </c>
       <c r="T31">
-        <v>1620.000</v>
+        <v>6305.000</v>
       </c>
       <c r="U31">
         <v>0</v>
@@ -2625,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="W31" s="4">
-        <v>46196.389409293981</v>
+        <v>46197.278671446758</v>
       </c>
     </row>
     <row r="32">
@@ -2633,40 +2675,40 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E32">
-        <v>7353347</v>
+        <v>7362235</v>
       </c>
       <c r="F32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M32" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="P32" s="1">
-        <v>46190.666916979164</v>
+        <v>46195.402748692133</v>
       </c>
       <c r="R32" s="4">
-        <v>46195.527235069443</v>
+        <v>46198.313491319444</v>
       </c>
       <c r="S32">
-        <v>600.000</v>
+        <v>10614.000</v>
       </c>
       <c r="T32">
-        <v>600.000</v>
+        <v>10614.000</v>
       </c>
       <c r="U32">
         <v>0</v>
@@ -2675,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="W32" s="4">
-        <v>46196.389409293981</v>
+        <v>46198.314641435187</v>
       </c>
     </row>
     <row r="33">
@@ -2683,40 +2725,40 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E33">
-        <v>7353346</v>
+        <v>7358767</v>
       </c>
       <c r="F33" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M33" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="P33" s="1">
-        <v>46190.66691284722</v>
+        <v>46192.659844444446</v>
       </c>
       <c r="R33" s="4">
-        <v>46195.522001273152</v>
+        <v>46197.3828096875</v>
       </c>
       <c r="S33">
-        <v>1338.000</v>
+        <v>10207.000</v>
       </c>
       <c r="T33">
-        <v>1338.000</v>
+        <v>10207.000</v>
       </c>
       <c r="U33">
         <v>0</v>
@@ -2725,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="W33" s="4">
-        <v>46196.389409293981</v>
+        <v>46197.391247916668</v>
       </c>
     </row>
     <row r="34">
@@ -2733,40 +2775,40 @@
         <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E34">
-        <v>7353345</v>
+        <v>7358766</v>
       </c>
       <c r="F34" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M34" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="P34" s="1">
-        <v>46190.666911921297</v>
+        <v>46192.659814814811</v>
       </c>
       <c r="R34" s="4">
-        <v>46195.532152511572</v>
+        <v>46197.366926122682</v>
       </c>
       <c r="S34">
-        <v>968.000</v>
+        <v>8661.000</v>
       </c>
       <c r="T34">
-        <v>968.000</v>
+        <v>8661.000</v>
       </c>
       <c r="U34">
         <v>0</v>
@@ -2775,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="W34" s="4">
-        <v>46196.389409293981</v>
+        <v>46197.391093518519</v>
       </c>
     </row>
     <row r="35">
@@ -2783,40 +2825,40 @@
         <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E35">
-        <v>7353344</v>
+        <v>7355924</v>
       </c>
       <c r="F35" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H35" t="s">
-        <v>23</v>
-      </c>
-      <c r="M35" t="s">
-        <v>54</v>
+        <v>24</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="P35" s="1">
-        <v>46190.666910844906</v>
+        <v>46191.548452546296</v>
       </c>
       <c r="R35" s="4">
-        <v>46195.537341087962</v>
+        <v>46195.391070254627</v>
       </c>
       <c r="S35">
-        <v>917.000</v>
+        <v>8044.000</v>
       </c>
       <c r="T35">
-        <v>917.000</v>
+        <v>8044.000</v>
       </c>
       <c r="U35">
         <v>0</v>
@@ -2825,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="W35" s="4">
-        <v>46196.389409293981</v>
+        <v>46196.389409641204</v>
       </c>
     </row>
     <row r="36">
@@ -2833,40 +2875,40 @@
         <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E36">
-        <v>7353343</v>
+        <v>7355667</v>
       </c>
       <c r="F36" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M36" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="P36" s="1">
-        <v>46190.666907604165</v>
+        <v>46191.4713122338</v>
       </c>
       <c r="R36" s="4">
-        <v>46195.526307291664</v>
+        <v>46198.319310104169</v>
       </c>
       <c r="S36">
-        <v>3514.000</v>
+        <v>15383.000</v>
       </c>
       <c r="T36">
-        <v>3514.000</v>
+        <v>15383.000</v>
       </c>
       <c r="U36">
         <v>0</v>
@@ -2875,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="W36" s="4">
-        <v>46196.389409108793</v>
+        <v>46198.319958796295</v>
       </c>
     </row>
     <row r="37">
@@ -2883,40 +2925,40 @@
         <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E37">
-        <v>7353342</v>
+        <v>7353363</v>
       </c>
       <c r="F37" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M37" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="P37" s="1">
-        <v>46190.666906134262</v>
+        <v>46190.666969988422</v>
       </c>
       <c r="R37" s="4">
-        <v>46195.518147222225</v>
+        <v>46195.511062997684</v>
       </c>
       <c r="S37">
-        <v>646.000</v>
+        <v>472.000</v>
       </c>
       <c r="T37">
-        <v>646.000</v>
+        <v>472.000</v>
       </c>
       <c r="U37">
         <v>0</v>
@@ -2925,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="W37" s="4">
-        <v>46196.389409108793</v>
+        <v>46196.389409641204</v>
       </c>
     </row>
     <row r="38">
@@ -2933,40 +2975,40 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E38">
-        <v>7353341</v>
+        <v>7353362</v>
       </c>
       <c r="F38" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M38" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="P38" s="1">
-        <v>46190.666903969905</v>
+        <v>46190.666969444443</v>
       </c>
       <c r="R38" s="4">
-        <v>46195.535854247682</v>
+        <v>46195.521521527779</v>
       </c>
       <c r="S38">
-        <v>2209.000</v>
+        <v>612.000</v>
       </c>
       <c r="T38">
-        <v>2209.000</v>
+        <v>612.000</v>
       </c>
       <c r="U38">
         <v>0</v>
@@ -2975,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="W38" s="4">
-        <v>46196.389409108793</v>
+        <v>46196.389409641204</v>
       </c>
     </row>
     <row r="39">
@@ -2983,40 +3025,40 @@
         <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E39">
-        <v>7353340</v>
+        <v>7353361</v>
       </c>
       <c r="F39" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M39" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="P39" s="1">
-        <v>46190.666894560185</v>
+        <v>46190.666967094905</v>
       </c>
       <c r="R39" s="4">
-        <v>46195.524072835651</v>
+        <v>46195.535836192132</v>
       </c>
       <c r="S39">
-        <v>4385.000</v>
+        <v>2383.000</v>
       </c>
       <c r="T39">
-        <v>4385.000</v>
+        <v>2383.000</v>
       </c>
       <c r="U39">
         <v>0</v>
@@ -3025,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="W39" s="4">
-        <v>46196.389409108793</v>
+        <v>46196.389409641204</v>
       </c>
     </row>
     <row r="40">
@@ -3033,40 +3075,40 @@
         <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E40">
-        <v>7353339</v>
+        <v>7353360</v>
       </c>
       <c r="F40" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M40" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="P40" s="1">
-        <v>46190.666882442129</v>
+        <v>46190.666964201388</v>
       </c>
       <c r="R40" s="4">
-        <v>46195.535098726854</v>
+        <v>46195.523977164354</v>
       </c>
       <c r="S40">
-        <v>2886.000</v>
+        <v>2262.000</v>
       </c>
       <c r="T40">
-        <v>2886.000</v>
+        <v>2262.000</v>
       </c>
       <c r="U40">
         <v>0</v>
@@ -3075,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="W40" s="4">
-        <v>46196.389408912037</v>
+        <v>46196.389409641204</v>
       </c>
     </row>
     <row r="41">
@@ -3083,40 +3125,40 @@
         <v>19</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E41">
-        <v>7353338</v>
+        <v>7353359</v>
       </c>
       <c r="F41" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M41" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="P41" s="1">
-        <v>46190.666870520836</v>
+        <v>46190.66696145833</v>
       </c>
       <c r="R41" s="4">
-        <v>46195.537258252312</v>
+        <v>46195.537172372686</v>
       </c>
       <c r="S41">
-        <v>2648.000</v>
+        <v>3982.000</v>
       </c>
       <c r="T41">
-        <v>2648.000</v>
+        <v>3982.000</v>
       </c>
       <c r="U41">
         <v>0</v>
@@ -3125,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="W41" s="4">
-        <v>46196.389408912037</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="42">
@@ -3133,40 +3175,40 @@
         <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E42">
-        <v>7353112</v>
+        <v>7353358</v>
       </c>
       <c r="F42" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H42" t="s">
-        <v>23</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>82</v>
+        <v>24</v>
+      </c>
+      <c r="M42" t="s">
+        <v>83</v>
       </c>
       <c r="P42" s="1">
-        <v>46190.633443321756</v>
+        <v>46190.666954432869</v>
       </c>
       <c r="R42" s="4">
-        <v>46195.593899918982</v>
+        <v>46195.532108368054</v>
       </c>
       <c r="S42">
-        <v>15034.000</v>
+        <v>1113.000</v>
       </c>
       <c r="T42">
-        <v>15034.000</v>
+        <v>1113.000</v>
       </c>
       <c r="U42">
         <v>0</v>
@@ -3175,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="W42" s="4">
-        <v>46196.389407835646</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="43">
@@ -3183,40 +3225,40 @@
         <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E43">
-        <v>7353352</v>
+        <v>7353357</v>
       </c>
       <c r="F43" t="s">
+        <v>89</v>
+      </c>
+      <c r="G43" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" t="s">
+        <v>24</v>
+      </c>
+      <c r="M43" t="s">
         <v>83</v>
       </c>
-      <c r="G43" t="s">
-        <v>23</v>
-      </c>
-      <c r="H43" t="s">
-        <v>23</v>
-      </c>
-      <c r="M43" t="s">
-        <v>54</v>
-      </c>
       <c r="P43" s="1">
-        <v>46190.66693417824</v>
+        <v>46190.666949340281</v>
       </c>
       <c r="R43" s="4">
-        <v>46195.537318483795</v>
+        <v>46195.517305439818</v>
       </c>
       <c r="S43">
-        <v>7113.000</v>
+        <v>447.000</v>
       </c>
       <c r="T43">
-        <v>7113.000</v>
+        <v>447.000</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -3225,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="W43" s="4">
-        <v>46196.388202118054</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="44">
@@ -3233,46 +3275,40 @@
         <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E44">
-        <v>7349603</v>
+        <v>7353356</v>
       </c>
       <c r="F44" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M44" t="s">
-        <v>85</v>
-      </c>
-      <c r="N44" s="1">
-        <v>46190</v>
+        <v>83</v>
       </c>
       <c r="P44" s="1">
-        <v>46189.643392094906</v>
-      </c>
-      <c r="Q44" s="4">
-        <v>46190.996527777781</v>
+        <v>46190.66694664352</v>
       </c>
       <c r="R44" s="4">
-        <v>46190.579668171296</v>
+        <v>46195.528761724534</v>
       </c>
       <c r="S44">
-        <v>5965.000</v>
+        <v>284.000</v>
       </c>
       <c r="T44">
-        <v>5965.000</v>
+        <v>284.000</v>
       </c>
       <c r="U44">
         <v>0</v>
@@ -3281,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="W44" s="4">
-        <v>46191.313541932868</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="45">
@@ -3289,55 +3325,49 @@
         <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E45">
-        <v>7166305</v>
+        <v>7353355</v>
       </c>
       <c r="F45" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M45" t="s">
-        <v>87</v>
-      </c>
-      <c r="N45" s="1">
-        <v>46152</v>
+        <v>83</v>
       </c>
       <c r="P45" s="1">
-        <v>46154.508897418978</v>
-      </c>
-      <c r="Q45" s="4">
-        <v>46162.29583333333</v>
+        <v>46190.666944293982</v>
       </c>
       <c r="R45" s="4">
-        <v>46154.512428125003</v>
+        <v>46195.528790659722</v>
       </c>
       <c r="S45">
-        <v>100.000</v>
+        <v>304.000</v>
       </c>
       <c r="T45">
-        <v>98.000</v>
+        <v>304.000</v>
       </c>
       <c r="U45">
-        <v>2.000</v>
+        <v>0</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45" s="4">
-        <v>46190.318931481481</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="46">
@@ -3345,40 +3375,40 @@
         <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E46">
-        <v>7344984</v>
+        <v>7353354</v>
       </c>
       <c r="F46" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M46" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="P46" s="1">
-        <v>46188.6820028125</v>
+        <v>46190.666940659721</v>
       </c>
       <c r="R46" s="4">
-        <v>46189.581174189814</v>
+        <v>46195.536209409722</v>
       </c>
       <c r="S46">
-        <v>14515.000</v>
+        <v>1251.000</v>
       </c>
       <c r="T46">
-        <v>14515.000</v>
+        <v>1251.000</v>
       </c>
       <c r="U46">
         <v>0</v>
@@ -3387,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="W46" s="4">
-        <v>46190.318753738429</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="47">
@@ -3395,43 +3425,40 @@
         <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E47">
-        <v>7343721</v>
+        <v>7353353</v>
       </c>
       <c r="F47" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M47" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="P47" s="1">
-        <v>46188.52897230324</v>
-      </c>
-      <c r="Q47" s="4">
-        <v>46189.270138888889</v>
+        <v>46190.666939583331</v>
       </c>
       <c r="R47" s="4">
-        <v>46189.525954201388</v>
+        <v>46195.537300034724</v>
       </c>
       <c r="S47">
-        <v>9210.000</v>
+        <v>1257.000</v>
       </c>
       <c r="T47">
-        <v>9210.000</v>
+        <v>1257.000</v>
       </c>
       <c r="U47">
         <v>0</v>
@@ -3440,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="W47" s="4">
-        <v>46189.538887268522</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="48">
@@ -3448,43 +3475,40 @@
         <v>19</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E48">
-        <v>7312333</v>
+        <v>7353352</v>
       </c>
       <c r="F48" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M48" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="P48" s="1">
-        <v>46181.394416122683</v>
-      </c>
-      <c r="Q48" s="4">
-        <v>46182.458333333336</v>
+        <v>46190.66693417824</v>
       </c>
       <c r="R48" s="4">
-        <v>46188.402503240737</v>
+        <v>46195.537318483795</v>
       </c>
       <c r="S48">
-        <v>8272.000</v>
+        <v>7113.000</v>
       </c>
       <c r="T48">
-        <v>8272.000</v>
+        <v>7113.000</v>
       </c>
       <c r="U48">
         <v>0</v>
@@ -3493,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="W48" s="4">
-        <v>46188.404413310185</v>
+        <v>46196.388202118054</v>
       </c>
     </row>
     <row r="49">
@@ -3501,43 +3525,40 @@
         <v>19</v>
       </c>
       <c r="B49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E49">
-        <v>7312334</v>
+        <v>7353351</v>
       </c>
       <c r="F49" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M49" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="P49" s="1">
-        <v>46181.394481597221</v>
-      </c>
-      <c r="Q49" s="4">
-        <v>46182.458333333336</v>
+        <v>46190.666933101849</v>
       </c>
       <c r="R49" s="4">
-        <v>46188.363727511576</v>
+        <v>46195.523942245367</v>
       </c>
       <c r="S49">
-        <v>5617.000</v>
+        <v>1295.000</v>
       </c>
       <c r="T49">
-        <v>5617.000</v>
+        <v>1295.000</v>
       </c>
       <c r="U49">
         <v>0</v>
@@ -3546,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="W49" s="4">
-        <v>46188.368130752315</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="50">
@@ -3554,43 +3575,40 @@
         <v>19</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E50">
-        <v>7306694</v>
+        <v>7353350</v>
       </c>
       <c r="F50" t="s">
         <v>96</v>
       </c>
       <c r="G50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M50" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="P50" s="1">
-        <v>46178.650135613425</v>
-      </c>
-      <c r="Q50" s="4">
-        <v>46181.3125</v>
+        <v>46190.666932719905</v>
       </c>
       <c r="R50" s="4">
-        <v>46188.351883217591</v>
+        <v>46195.536177581016</v>
       </c>
       <c r="S50">
-        <v>7291.000</v>
+        <v>72.000</v>
       </c>
       <c r="T50">
-        <v>7291.000</v>
+        <v>72.000</v>
       </c>
       <c r="U50">
         <v>0</v>
@@ -3599,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="W50" s="4">
-        <v>46188.368130405092</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="51">
@@ -3607,43 +3625,40 @@
         <v>19</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E51">
-        <v>7306693</v>
+        <v>7353349</v>
       </c>
       <c r="F51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M51" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="P51" s="1">
-        <v>46178.650101388892</v>
-      </c>
-      <c r="Q51" s="4">
-        <v>46181.395833333336</v>
+        <v>46190.666930555555</v>
       </c>
       <c r="R51" s="4">
-        <v>46188.361928472223</v>
+        <v>46195.536192395833</v>
       </c>
       <c r="S51">
-        <v>5272.000</v>
+        <v>101.000</v>
       </c>
       <c r="T51">
-        <v>5272.000</v>
+        <v>101.000</v>
       </c>
       <c r="U51">
         <v>0</v>
@@ -3652,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="W51" s="4">
-        <v>46188.368129826391</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="52">
@@ -3660,40 +3675,40 @@
         <v>19</v>
       </c>
       <c r="B52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E52">
-        <v>7296112</v>
+        <v>7353348</v>
       </c>
       <c r="F52" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M52" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P52" s="1">
-        <v>46176.490794872683</v>
+        <v>46190.666919525465</v>
       </c>
       <c r="R52" s="4">
-        <v>46188.357570370368</v>
+        <v>46195.534000462962</v>
       </c>
       <c r="S52">
-        <v>7146.000</v>
+        <v>1620.000</v>
       </c>
       <c r="T52">
-        <v>7146.000</v>
+        <v>1620.000</v>
       </c>
       <c r="U52">
         <v>0</v>
@@ -3702,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="W52" s="4">
-        <v>46188.368129664355</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="53">
@@ -3710,43 +3725,40 @@
         <v>19</v>
       </c>
       <c r="B53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E53">
-        <v>7331780</v>
+        <v>7353347</v>
       </c>
       <c r="F53" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M53" t="s">
-        <v>103</v>
-      </c>
-      <c r="O53" s="4">
-        <v>46185.364583333336</v>
+        <v>83</v>
       </c>
       <c r="P53" s="1">
-        <v>46184.420189351855</v>
+        <v>46190.666916979164</v>
       </c>
       <c r="R53" s="4">
-        <v>46188.330705902779</v>
+        <v>46195.527235069443</v>
       </c>
       <c r="S53">
-        <v>2185.000</v>
+        <v>600.000</v>
       </c>
       <c r="T53">
-        <v>2185.000</v>
+        <v>600.000</v>
       </c>
       <c r="U53">
         <v>0</v>
@@ -3755,7 +3767,7 @@
         <v>0</v>
       </c>
       <c r="W53" s="4">
-        <v>46188.33742491898</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="54">
@@ -3763,46 +3775,40 @@
         <v>19</v>
       </c>
       <c r="B54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E54">
-        <v>7331779</v>
+        <v>7353346</v>
       </c>
       <c r="F54" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M54" t="s">
-        <v>105</v>
-      </c>
-      <c r="O54" s="4">
-        <v>46185</v>
+        <v>83</v>
       </c>
       <c r="P54" s="1">
-        <v>46184.420142511575</v>
-      </c>
-      <c r="Q54" s="4">
-        <v>46181</v>
+        <v>46190.66691284722</v>
       </c>
       <c r="R54" s="4">
-        <v>46188.332772222224</v>
+        <v>46195.522001273152</v>
       </c>
       <c r="S54">
-        <v>16497.000</v>
+        <v>1338.000</v>
       </c>
       <c r="T54">
-        <v>16497.000</v>
+        <v>1338.000</v>
       </c>
       <c r="U54">
         <v>0</v>
@@ -3811,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="W54" s="4">
-        <v>46188.337424189813</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="55">
@@ -3819,43 +3825,40 @@
         <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E55">
-        <v>7327419</v>
+        <v>7353345</v>
       </c>
       <c r="F55" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M55" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="P55" s="1">
-        <v>46183.517797372682</v>
-      </c>
-      <c r="Q55" s="4">
-        <v>46184.3125</v>
+        <v>46190.666911921297</v>
       </c>
       <c r="R55" s="4">
-        <v>46188.329073842593</v>
+        <v>46195.532152511572</v>
       </c>
       <c r="S55">
-        <v>10574.000</v>
+        <v>968.000</v>
       </c>
       <c r="T55">
-        <v>10574.000</v>
+        <v>968.000</v>
       </c>
       <c r="U55">
         <v>0</v>
@@ -3864,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="W55" s="4">
-        <v>46188.337423263889</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="56">
@@ -3872,40 +3875,40 @@
         <v>19</v>
       </c>
       <c r="B56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E56">
-        <v>7331318</v>
+        <v>7353344</v>
       </c>
       <c r="F56" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M56" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="P56" s="1">
-        <v>46184.369259340281</v>
+        <v>46190.666910844906</v>
       </c>
       <c r="R56" s="4">
-        <v>46185.506102002313</v>
+        <v>46195.537341087962</v>
       </c>
       <c r="S56">
-        <v>10749.000</v>
+        <v>917.000</v>
       </c>
       <c r="T56">
-        <v>10749.000</v>
+        <v>917.000</v>
       </c>
       <c r="U56">
         <v>0</v>
@@ -3914,7 +3917,7 @@
         <v>0</v>
       </c>
       <c r="W56" s="4">
-        <v>46188.329308333334</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="57">
@@ -3922,43 +3925,40 @@
         <v>19</v>
       </c>
       <c r="B57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E57">
-        <v>7306692</v>
+        <v>7353343</v>
       </c>
       <c r="F57" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H57" t="s">
-        <v>23</v>
-      </c>
-      <c r="M57" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="O57" s="4">
-        <v>46181.34375</v>
+        <v>24</v>
+      </c>
+      <c r="M57" t="s">
+        <v>83</v>
       </c>
       <c r="P57" s="1">
-        <v>46178.650014085651</v>
+        <v>46190.666907604165</v>
       </c>
       <c r="R57" s="4">
-        <v>46188.321652777777</v>
+        <v>46195.526307291664</v>
       </c>
       <c r="S57">
-        <v>10749.000</v>
+        <v>3514.000</v>
       </c>
       <c r="T57">
-        <v>10749.000</v>
+        <v>3514.000</v>
       </c>
       <c r="U57">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="W57" s="4">
-        <v>46188.329306516207</v>
+        <v>46196.389409108793</v>
       </c>
     </row>
     <row r="58">
@@ -3975,43 +3975,40 @@
         <v>19</v>
       </c>
       <c r="B58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E58">
-        <v>7290512</v>
+        <v>7353342</v>
       </c>
       <c r="F58" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M58" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="P58" s="1">
-        <v>46175.705376817132</v>
-      </c>
-      <c r="Q58" s="4">
-        <v>46176.5</v>
+        <v>46190.666906134262</v>
       </c>
       <c r="R58" s="4">
-        <v>46188.325696840278</v>
+        <v>46195.518147222225</v>
       </c>
       <c r="S58">
-        <v>14234.000</v>
+        <v>646.000</v>
       </c>
       <c r="T58">
-        <v>14234.000</v>
+        <v>646.000</v>
       </c>
       <c r="U58">
         <v>0</v>
@@ -4020,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="W58" s="4">
-        <v>46188.329304166669</v>
+        <v>46196.389409108793</v>
       </c>
     </row>
     <row r="59">
@@ -4028,43 +4025,40 @@
         <v>19</v>
       </c>
       <c r="B59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E59">
-        <v>7277742</v>
+        <v>7353341</v>
       </c>
       <c r="F59" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M59" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="P59" s="1">
-        <v>46174.491930821758</v>
-      </c>
-      <c r="Q59" s="4">
-        <v>46174.416666666664</v>
+        <v>46190.666903969905</v>
       </c>
       <c r="R59" s="4">
-        <v>46188.313768368054</v>
+        <v>46195.535854247682</v>
       </c>
       <c r="S59">
-        <v>18914.000</v>
+        <v>2209.000</v>
       </c>
       <c r="T59">
-        <v>18914.000</v>
+        <v>2209.000</v>
       </c>
       <c r="U59">
         <v>0</v>
@@ -4073,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="W59" s="4">
-        <v>46188.329302546299</v>
+        <v>46196.389409108793</v>
       </c>
     </row>
     <row r="60">
@@ -4081,43 +4075,40 @@
         <v>19</v>
       </c>
       <c r="B60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E60">
-        <v>7321304</v>
+        <v>7353340</v>
       </c>
       <c r="F60" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="G60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M60" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="P60" s="1">
-        <v>46182.379826539349</v>
-      </c>
-      <c r="Q60" s="4">
-        <v>46183.458333333336</v>
+        <v>46190.666894560185</v>
       </c>
       <c r="R60" s="4">
-        <v>46184.566309837966</v>
+        <v>46195.524072835651</v>
       </c>
       <c r="S60">
-        <v>1784.000</v>
+        <v>4385.000</v>
       </c>
       <c r="T60">
-        <v>1784.000</v>
+        <v>4385.000</v>
       </c>
       <c r="U60">
         <v>0</v>
@@ -4126,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="W60" s="4">
-        <v>46188.318567708331</v>
+        <v>46196.389409108793</v>
       </c>
     </row>
     <row r="61">
@@ -4134,43 +4125,40 @@
         <v>19</v>
       </c>
       <c r="B61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E61">
-        <v>7321303</v>
+        <v>7353339</v>
       </c>
       <c r="F61" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="G61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M61" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="P61" s="1">
-        <v>46182.379728553242</v>
-      </c>
-      <c r="Q61" s="4">
-        <v>46183.458333333336</v>
+        <v>46190.666882442129</v>
       </c>
       <c r="R61" s="4">
-        <v>46185.474632175923</v>
+        <v>46195.535098726854</v>
       </c>
       <c r="S61">
-        <v>15852.000</v>
+        <v>2886.000</v>
       </c>
       <c r="T61">
-        <v>15852.000</v>
+        <v>2886.000</v>
       </c>
       <c r="U61">
         <v>0</v>
@@ -4179,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="W61" s="4">
-        <v>46188.318567164351</v>
+        <v>46196.389408912037</v>
       </c>
     </row>
     <row r="62">
@@ -4187,43 +4175,40 @@
         <v>19</v>
       </c>
       <c r="B62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E62">
-        <v>7312335</v>
+        <v>7353338</v>
       </c>
       <c r="F62" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="G62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H62" t="s">
-        <v>23</v>
-      </c>
-      <c r="M62" s="5" t="s">
-        <v>121</v>
+        <v>24</v>
+      </c>
+      <c r="M62" t="s">
+        <v>83</v>
       </c>
       <c r="P62" s="1">
-        <v>46181.394497488429</v>
-      </c>
-      <c r="Q62" s="4">
-        <v>46182.388888888891</v>
+        <v>46190.666870520836</v>
       </c>
       <c r="R62" s="4">
-        <v>46185.475467280092</v>
+        <v>46195.537258252312</v>
       </c>
       <c r="S62">
-        <v>16641.000</v>
+        <v>2648.000</v>
       </c>
       <c r="T62">
-        <v>16641.000</v>
+        <v>2648.000</v>
       </c>
       <c r="U62">
         <v>0</v>
@@ -4232,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="W62" s="4">
-        <v>46188.318566284725</v>
+        <v>46196.389408912037</v>
       </c>
     </row>
     <row r="63">
@@ -4240,40 +4225,40 @@
         <v>19</v>
       </c>
       <c r="B63" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C63" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D63" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E63">
-        <v>7329559</v>
+        <v>7353112</v>
       </c>
       <c r="F63" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="G63" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H63" t="s">
-        <v>23</v>
-      </c>
-      <c r="M63" t="s">
-        <v>123</v>
+        <v>24</v>
+      </c>
+      <c r="M63" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="P63" s="1">
-        <v>46183.835381215278</v>
+        <v>46190.633443321756</v>
       </c>
       <c r="R63" s="4">
-        <v>46185.394576122686</v>
+        <v>46195.593899918982</v>
       </c>
       <c r="S63">
-        <v>18992.000</v>
+        <v>15034.000</v>
       </c>
       <c r="T63">
-        <v>18992.000</v>
+        <v>15034.000</v>
       </c>
       <c r="U63">
         <v>0</v>
@@ -4282,7 +4267,7 @@
         <v>0</v>
       </c>
       <c r="W63" s="4">
-        <v>46188.318260497683</v>
+        <v>46196.389407835646</v>
       </c>
     </row>
     <row r="64">
@@ -4290,43 +4275,40 @@
         <v>19</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E64">
-        <v>7312336</v>
+        <v>7352722</v>
       </c>
       <c r="F64" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="G64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M64" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="P64" s="1">
-        <v>46181.394619016202</v>
-      </c>
-      <c r="Q64" s="4">
-        <v>46182.416666666664</v>
+        <v>46190.517798842593</v>
       </c>
       <c r="R64" s="4">
-        <v>46182.563263425924</v>
+        <v>46198.316219409724</v>
       </c>
       <c r="S64">
-        <v>8559.000</v>
+        <v>13727.000</v>
       </c>
       <c r="T64">
-        <v>8559.000</v>
+        <v>13727.000</v>
       </c>
       <c r="U64">
         <v>0</v>
@@ -4335,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="W64" s="4">
-        <v>46183.499163692133</v>
+        <v>46198.317383530091</v>
       </c>
     </row>
     <row r="65">
@@ -4343,46 +4325,40 @@
         <v>19</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E65">
-        <v>7297491</v>
+        <v>7352670</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="G65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H65" t="s">
-        <v>23</v>
-      </c>
-      <c r="M65" t="s">
-        <v>127</v>
-      </c>
-      <c r="O65" s="4">
-        <v>46178.416666666664</v>
+        <v>24</v>
+      </c>
+      <c r="M65" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="P65" s="1">
-        <v>46176.651283530089</v>
-      </c>
-      <c r="Q65" s="4">
-        <v>46178.260416666664</v>
+        <v>46190.508466550928</v>
       </c>
       <c r="R65" s="4">
-        <v>46182.304580173608</v>
+        <v>46197.408573148146</v>
       </c>
       <c r="S65">
-        <v>19653.000</v>
+        <v>10751.000</v>
       </c>
       <c r="T65">
-        <v>19653.000</v>
+        <v>10751.000</v>
       </c>
       <c r="U65">
         <v>0</v>
@@ -4391,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="W65" s="4">
-        <v>46182.394867361108</v>
+        <v>46197.438478206015</v>
       </c>
     </row>
     <row r="66">
@@ -4399,43 +4375,40 @@
         <v>19</v>
       </c>
       <c r="B66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E66">
-        <v>7276670</v>
+        <v>7344984</v>
       </c>
       <c r="F66" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="G66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M66" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="P66" s="1">
-        <v>46174.386795023151</v>
-      </c>
-      <c r="Q66" s="4">
-        <v>46174.3125</v>
+        <v>46188.6820028125</v>
       </c>
       <c r="R66" s="4">
-        <v>46181.602299189813</v>
+        <v>46189.581174189814</v>
       </c>
       <c r="S66">
-        <v>7766.000</v>
+        <v>14515.000</v>
       </c>
       <c r="T66">
-        <v>7766.000</v>
+        <v>14515.000</v>
       </c>
       <c r="U66">
         <v>0</v>
@@ -4444,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="W66" s="4">
-        <v>46181.607877893519</v>
+        <v>46190.318753738429</v>
       </c>
     </row>
     <row r="67">
@@ -4452,43 +4425,43 @@
         <v>19</v>
       </c>
       <c r="B67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E67">
-        <v>7256959</v>
+        <v>7343721</v>
       </c>
       <c r="F67" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="G67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M67" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="P67" s="1">
-        <v>46169.73840185185</v>
+        <v>46188.52897230324</v>
       </c>
       <c r="Q67" s="4">
-        <v>46171.520833333336</v>
+        <v>46189.270138888889</v>
       </c>
       <c r="R67" s="4">
-        <v>46181.602367395833</v>
+        <v>46189.525954201388</v>
       </c>
       <c r="S67">
-        <v>11921.000</v>
+        <v>9210.000</v>
       </c>
       <c r="T67">
-        <v>11921.000</v>
+        <v>9210.000</v>
       </c>
       <c r="U67">
         <v>0</v>
@@ -4497,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="W67" s="4">
-        <v>46181.607877002316</v>
+        <v>46189.538887268522</v>
       </c>
     </row>
     <row r="68">
@@ -4505,46 +4478,43 @@
         <v>19</v>
       </c>
       <c r="B68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E68">
-        <v>7256837</v>
+        <v>7331780</v>
       </c>
       <c r="F68" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="G68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M68" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="O68" s="4">
-        <v>46170.541666666664</v>
+        <v>46185.364583333336</v>
       </c>
       <c r="P68" s="1">
-        <v>46169.717724456015</v>
-      </c>
-      <c r="Q68" s="4">
-        <v>46171.375</v>
+        <v>46184.420189351855</v>
       </c>
       <c r="R68" s="4">
-        <v>46181.601758877317</v>
+        <v>46188.330705902779</v>
       </c>
       <c r="S68">
-        <v>10645.000</v>
+        <v>2185.000</v>
       </c>
       <c r="T68">
-        <v>10645.000</v>
+        <v>2185.000</v>
       </c>
       <c r="U68">
         <v>0</v>
@@ -4553,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="W68" s="4">
-        <v>46181.607876122682</v>
+        <v>46188.33742491898</v>
       </c>
     </row>
     <row r="69">
@@ -4561,43 +4531,46 @@
         <v>19</v>
       </c>
       <c r="B69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E69">
-        <v>7297492</v>
+        <v>7331779</v>
       </c>
       <c r="F69" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="G69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M69" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="O69" s="4">
-        <v>46178.427083333336</v>
+        <v>46185</v>
       </c>
       <c r="P69" s="1">
-        <v>46176.651338159725</v>
+        <v>46184.420142511575</v>
+      </c>
+      <c r="Q69" s="4">
+        <v>46181</v>
       </c>
       <c r="R69" s="4">
-        <v>46178.483032060183</v>
+        <v>46188.332772222224</v>
       </c>
       <c r="S69">
-        <v>6802.000</v>
+        <v>16497.000</v>
       </c>
       <c r="T69">
-        <v>6802.000</v>
+        <v>16497.000</v>
       </c>
       <c r="U69">
         <v>0</v>
@@ -4606,7 +4579,7 @@
         <v>0</v>
       </c>
       <c r="W69" s="4">
-        <v>46181.304573692127</v>
+        <v>46188.337424189813</v>
       </c>
     </row>
     <row r="70">
@@ -4614,43 +4587,40 @@
         <v>19</v>
       </c>
       <c r="B70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E70">
-        <v>7290516</v>
+        <v>7331318</v>
       </c>
       <c r="F70" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="G70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M70" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="P70" s="1">
-        <v>46175.705564502314</v>
-      </c>
-      <c r="Q70" s="4">
-        <v>46176.59375</v>
+        <v>46184.369259340281</v>
       </c>
       <c r="R70" s="4">
-        <v>46178.37381646991</v>
+        <v>46185.506102002313</v>
       </c>
       <c r="S70">
-        <v>6600.000</v>
+        <v>10749.000</v>
       </c>
       <c r="T70">
-        <v>6600.000</v>
+        <v>10749.000</v>
       </c>
       <c r="U70">
         <v>0</v>
@@ -4659,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="W70" s="4">
-        <v>46181.304297951392</v>
+        <v>46188.329308333334</v>
       </c>
     </row>
     <row r="71">
@@ -4667,43 +4637,40 @@
         <v>19</v>
       </c>
       <c r="B71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E71">
-        <v>7290513</v>
+        <v>7329559</v>
       </c>
       <c r="F71" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="G71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M71" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="P71" s="1">
-        <v>46175.705472835645</v>
-      </c>
-      <c r="Q71" s="4">
-        <v>46175.541666666664</v>
+        <v>46183.835381215278</v>
       </c>
       <c r="R71" s="4">
-        <v>46176.390187384262</v>
+        <v>46185.394576122686</v>
       </c>
       <c r="S71">
-        <v>10634.000</v>
+        <v>18992.000</v>
       </c>
       <c r="T71">
-        <v>10634.000</v>
+        <v>18992.000</v>
       </c>
       <c r="U71">
         <v>0</v>
@@ -4712,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="W71" s="4">
-        <v>46176.479922453706</v>
+        <v>46188.318260497683</v>
       </c>
     </row>
     <row r="72">
@@ -4720,43 +4687,43 @@
         <v>19</v>
       </c>
       <c r="B72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E72">
-        <v>7277745</v>
+        <v>7327419</v>
       </c>
       <c r="F72" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="G72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M72" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="P72" s="1">
-        <v>46174.492115972222</v>
+        <v>46183.517797372682</v>
       </c>
       <c r="Q72" s="4">
-        <v>46175.291666666664</v>
+        <v>46184.3125</v>
       </c>
       <c r="R72" s="4">
-        <v>46176.394080127313</v>
+        <v>46188.329073842593</v>
       </c>
       <c r="S72">
-        <v>8925.000</v>
+        <v>10574.000</v>
       </c>
       <c r="T72">
-        <v>8925.000</v>
+        <v>10574.000</v>
       </c>
       <c r="U72">
         <v>0</v>
@@ -4765,7 +4732,7 @@
         <v>0</v>
       </c>
       <c r="W72" s="4">
-        <v>46176.479621759259</v>
+        <v>46188.337423263889</v>
       </c>
     </row>
     <row r="73">
@@ -4773,43 +4740,43 @@
         <v>19</v>
       </c>
       <c r="B73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E73">
-        <v>7277755</v>
+        <v>7321304</v>
       </c>
       <c r="F73" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="G73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M73" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="P73" s="1">
-        <v>46174.492233680554</v>
+        <v>46182.379826539349</v>
       </c>
       <c r="Q73" s="4">
-        <v>46175.291666666664</v>
+        <v>46183.458333333336</v>
       </c>
       <c r="R73" s="4">
-        <v>46175.460509027776</v>
+        <v>46184.566309837966</v>
       </c>
       <c r="S73">
-        <v>1502.000</v>
+        <v>1784.000</v>
       </c>
       <c r="T73">
-        <v>1502.000</v>
+        <v>1784.000</v>
       </c>
       <c r="U73">
         <v>0</v>
@@ -4818,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="W73" s="4">
-        <v>46176.367452777777</v>
+        <v>46188.318567708331</v>
       </c>
     </row>
     <row r="74">
@@ -4826,43 +4793,43 @@
         <v>19</v>
       </c>
       <c r="B74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E74">
-        <v>7290515</v>
+        <v>7321303</v>
       </c>
       <c r="F74" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="G74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M74" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="P74" s="1">
-        <v>46175.705520370371</v>
+        <v>46182.379728553242</v>
       </c>
       <c r="Q74" s="4">
-        <v>46175.604166666664</v>
+        <v>46183.458333333336</v>
       </c>
       <c r="R74" s="4">
-        <v>46176.32743784722</v>
+        <v>46185.474632175923</v>
       </c>
       <c r="S74">
-        <v>9893.000</v>
+        <v>15852.000</v>
       </c>
       <c r="T74">
-        <v>9893.000</v>
+        <v>15852.000</v>
       </c>
       <c r="U74">
         <v>0</v>
@@ -4871,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="W74" s="4">
-        <v>46176.36704571759</v>
+        <v>46188.318567164351</v>
       </c>
     </row>
     <row r="75">
@@ -4879,43 +4846,43 @@
         <v>19</v>
       </c>
       <c r="B75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E75">
-        <v>7277744</v>
+        <v>7312336</v>
       </c>
       <c r="F75" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="G75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M75" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="P75" s="1">
-        <v>46174.49203425926</v>
+        <v>46181.394619016202</v>
       </c>
       <c r="Q75" s="4">
-        <v>46174.5</v>
+        <v>46182.416666666664</v>
       </c>
       <c r="R75" s="4">
-        <v>46175.401104085649</v>
+        <v>46182.563263425924</v>
       </c>
       <c r="S75">
-        <v>14377.000</v>
+        <v>8559.000</v>
       </c>
       <c r="T75">
-        <v>14377.000</v>
+        <v>8559.000</v>
       </c>
       <c r="U75">
         <v>0</v>
@@ -4924,7 +4891,7 @@
         <v>0</v>
       </c>
       <c r="W75" s="4">
-        <v>46175.446175925928</v>
+        <v>46183.499163692133</v>
       </c>
     </row>
     <row r="76">
@@ -4932,43 +4899,43 @@
         <v>19</v>
       </c>
       <c r="B76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E76">
-        <v>7276672</v>
+        <v>7312335</v>
       </c>
       <c r="F76" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="G76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H76" t="s">
-        <v>23</v>
-      </c>
-      <c r="M76" t="s">
-        <v>149</v>
+        <v>24</v>
+      </c>
+      <c r="M76" s="5" t="s">
+        <v>136</v>
       </c>
       <c r="P76" s="1">
-        <v>46174.386965358797</v>
+        <v>46181.394497488429</v>
       </c>
       <c r="Q76" s="4">
-        <v>46174.3125</v>
+        <v>46182.388888888891</v>
       </c>
       <c r="R76" s="4">
-        <v>46175.277797997682</v>
+        <v>46185.475467280092</v>
       </c>
       <c r="S76">
-        <v>445.000</v>
+        <v>16641.000</v>
       </c>
       <c r="T76">
-        <v>445.000</v>
+        <v>16641.000</v>
       </c>
       <c r="U76">
         <v>0</v>
@@ -4977,7 +4944,7 @@
         <v>0</v>
       </c>
       <c r="W76" s="4">
-        <v>46175.446175925928</v>
+        <v>46188.318566284725</v>
       </c>
     </row>
     <row r="77">
@@ -4985,43 +4952,43 @@
         <v>19</v>
       </c>
       <c r="B77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E77">
-        <v>7243664</v>
+        <v>7312334</v>
       </c>
       <c r="F77" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="G77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M77" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="P77" s="1">
-        <v>46167.397293715279</v>
+        <v>46181.394481597221</v>
       </c>
       <c r="Q77" s="4">
-        <v>46169.3125</v>
+        <v>46182.458333333336</v>
       </c>
       <c r="R77" s="4">
-        <v>46170.486638159724</v>
+        <v>46188.363727511576</v>
       </c>
       <c r="S77">
-        <v>5002.000</v>
+        <v>5617.000</v>
       </c>
       <c r="T77">
-        <v>5002.000</v>
+        <v>5617.000</v>
       </c>
       <c r="U77">
         <v>0</v>
@@ -5030,7 +4997,7 @@
         <v>0</v>
       </c>
       <c r="W77" s="4">
-        <v>46171.52288329861</v>
+        <v>46188.368130752315</v>
       </c>
     </row>
     <row r="78">
@@ -5038,40 +5005,43 @@
         <v>19</v>
       </c>
       <c r="B78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E78">
-        <v>7261067</v>
+        <v>7312333</v>
       </c>
       <c r="F78" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="G78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M78" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="P78" s="1">
-        <v>46171.450339317133</v>
+        <v>46181.394416122683</v>
+      </c>
+      <c r="Q78" s="4">
+        <v>46182.458333333336</v>
       </c>
       <c r="R78" s="4">
-        <v>46171.468652743053</v>
+        <v>46188.402503240737</v>
       </c>
       <c r="S78">
-        <v>13827.000</v>
+        <v>8272.000</v>
       </c>
       <c r="T78">
-        <v>13827.000</v>
+        <v>8272.000</v>
       </c>
       <c r="U78">
         <v>0</v>
@@ -5080,7 +5050,7 @@
         <v>0</v>
       </c>
       <c r="W78" s="4">
-        <v>46171.521808101854</v>
+        <v>46188.404413310185</v>
       </c>
     </row>
     <row r="79">
@@ -5088,43 +5058,43 @@
         <v>19</v>
       </c>
       <c r="B79" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C79" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D79" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E79">
-        <v>7256954</v>
+        <v>7306694</v>
       </c>
       <c r="F79" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="G79" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H79" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M79" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="P79" s="1">
-        <v>46169.737280092595</v>
+        <v>46178.650135613425</v>
       </c>
       <c r="Q79" s="4">
-        <v>46171.416666666664</v>
+        <v>46181.3125</v>
       </c>
       <c r="R79" s="4">
-        <v>46171.471500266205</v>
+        <v>46188.351883217591</v>
       </c>
       <c r="S79">
-        <v>11226.000</v>
+        <v>7291.000</v>
       </c>
       <c r="T79">
-        <v>11226.000</v>
+        <v>7291.000</v>
       </c>
       <c r="U79">
         <v>0</v>
@@ -5133,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="W79" s="4">
-        <v>46171.521807557867</v>
+        <v>46188.368130405092</v>
       </c>
     </row>
     <row r="80">
@@ -5141,43 +5111,43 @@
         <v>19</v>
       </c>
       <c r="B80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E80">
-        <v>7256935</v>
+        <v>7306693</v>
       </c>
       <c r="F80" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="G80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M80" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="P80" s="1">
-        <v>46169.735800810187</v>
+        <v>46178.650101388892</v>
       </c>
       <c r="Q80" s="4">
-        <v>46171.25</v>
+        <v>46181.395833333336</v>
       </c>
       <c r="R80" s="4">
-        <v>46171.474860069444</v>
+        <v>46188.361928472223</v>
       </c>
       <c r="S80">
-        <v>12909.000</v>
+        <v>5272.000</v>
       </c>
       <c r="T80">
-        <v>12909.000</v>
+        <v>5272.000</v>
       </c>
       <c r="U80">
         <v>0</v>
@@ -5186,7 +5156,7 @@
         <v>0</v>
       </c>
       <c r="W80" s="4">
-        <v>46171.521807025463</v>
+        <v>46188.368129826391</v>
       </c>
     </row>
     <row r="81">
@@ -5194,46 +5164,43 @@
         <v>19</v>
       </c>
       <c r="B81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E81">
-        <v>7256927</v>
+        <v>7306692</v>
       </c>
       <c r="F81" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="G81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H81" t="s">
-        <v>23</v>
-      </c>
-      <c r="M81" t="s">
-        <v>159</v>
+        <v>24</v>
+      </c>
+      <c r="M81" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="O81" s="4">
-        <v>46170.541666666664</v>
+        <v>46181.34375</v>
       </c>
       <c r="P81" s="1">
-        <v>46169.733974768518</v>
-      </c>
-      <c r="Q81" s="4">
-        <v>46171.375</v>
+        <v>46178.650014085651</v>
       </c>
       <c r="R81" s="4">
-        <v>46171.384800081018</v>
+        <v>46188.321652777777</v>
       </c>
       <c r="S81">
-        <v>470.000</v>
+        <v>10749.000</v>
       </c>
       <c r="T81">
-        <v>470.000</v>
+        <v>10749.000</v>
       </c>
       <c r="U81">
         <v>0</v>
@@ -5242,7 +5209,7 @@
         <v>0</v>
       </c>
       <c r="W81" s="4">
-        <v>46171.521806828707</v>
+        <v>46188.329306516207</v>
       </c>
     </row>
     <row r="82">
@@ -5250,46 +5217,43 @@
         <v>19</v>
       </c>
       <c r="B82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E82">
-        <v>7256698</v>
+        <v>7297492</v>
       </c>
       <c r="F82" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="G82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M82" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="O82" s="4">
-        <v>46170.416666666664</v>
+        <v>46178.427083333336</v>
       </c>
       <c r="P82" s="1">
-        <v>46169.704318553238</v>
-      </c>
-      <c r="Q82" s="4">
-        <v>46170.4375</v>
+        <v>46176.651338159725</v>
       </c>
       <c r="R82" s="4">
-        <v>46170.55747615741</v>
+        <v>46178.483032060183</v>
       </c>
       <c r="S82">
-        <v>15811.000</v>
+        <v>6802.000</v>
       </c>
       <c r="T82">
-        <v>15811.000</v>
+        <v>6802.000</v>
       </c>
       <c r="U82">
         <v>0</v>
@@ -5298,7 +5262,7 @@
         <v>0</v>
       </c>
       <c r="W82" s="4">
-        <v>46171.52180628472</v>
+        <v>46181.304573692127</v>
       </c>
     </row>
     <row r="83">
@@ -5306,46 +5270,46 @@
         <v>19</v>
       </c>
       <c r="B83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E83">
-        <v>7256674</v>
+        <v>7297491</v>
       </c>
       <c r="F83" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="G83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M83" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="O83" s="4">
-        <v>46170.291666666664</v>
+        <v>46178.416666666664</v>
       </c>
       <c r="P83" s="1">
-        <v>46169.697586805552</v>
+        <v>46176.651283530089</v>
       </c>
       <c r="Q83" s="4">
-        <v>46171.291666666664</v>
+        <v>46178.260416666664</v>
       </c>
       <c r="R83" s="4">
-        <v>46171.366929745367</v>
+        <v>46182.304580173608</v>
       </c>
       <c r="S83">
-        <v>6703.000</v>
+        <v>19653.000</v>
       </c>
       <c r="T83">
-        <v>6703.000</v>
+        <v>19653.000</v>
       </c>
       <c r="U83">
         <v>0</v>
@@ -5354,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="W83" s="4">
-        <v>46171.521805937497</v>
+        <v>46182.394867361108</v>
       </c>
     </row>
     <row r="84">
@@ -5362,43 +5326,40 @@
         <v>19</v>
       </c>
       <c r="B84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E84">
-        <v>7243671</v>
+        <v>7296112</v>
       </c>
       <c r="F84" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M84" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="P84" s="1">
-        <v>46167.398480636577</v>
-      </c>
-      <c r="Q84" s="4">
-        <v>46170.25</v>
+        <v>46176.490794872683</v>
       </c>
       <c r="R84" s="4">
-        <v>46170.38833533565</v>
+        <v>46188.357570370368</v>
       </c>
       <c r="S84">
-        <v>767.000</v>
+        <v>7146.000</v>
       </c>
       <c r="T84">
-        <v>767.000</v>
+        <v>7146.000</v>
       </c>
       <c r="U84">
         <v>0</v>
@@ -5407,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="W84" s="4">
-        <v>46171.521805752316</v>
+        <v>46188.368129664355</v>
       </c>
     </row>
     <row r="85">
@@ -5415,43 +5376,43 @@
         <v>19</v>
       </c>
       <c r="B85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E85">
-        <v>7186225</v>
+        <v>7290516</v>
       </c>
       <c r="F85" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="G85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M85" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="P85" s="1">
-        <v>46157.585703935183</v>
+        <v>46175.705564502314</v>
       </c>
       <c r="Q85" s="4">
-        <v>46160.493105243055</v>
+        <v>46176.59375</v>
       </c>
       <c r="R85" s="4">
-        <v>46170.487253356485</v>
+        <v>46178.37381646991</v>
       </c>
       <c r="S85">
-        <v>13685.000</v>
+        <v>6600.000</v>
       </c>
       <c r="T85">
-        <v>13685.000</v>
+        <v>6600.000</v>
       </c>
       <c r="U85">
         <v>0</v>
@@ -5460,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="W85" s="4">
-        <v>46171.521805011573</v>
+        <v>46181.304297951392</v>
       </c>
     </row>
     <row r="86">
@@ -5468,43 +5429,43 @@
         <v>19</v>
       </c>
       <c r="B86" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C86" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D86" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E86">
-        <v>7243667</v>
+        <v>7290515</v>
       </c>
       <c r="F86" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="G86" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H86" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M86" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="P86" s="1">
-        <v>46167.398084108798</v>
+        <v>46175.705520370371</v>
       </c>
       <c r="Q86" s="4">
-        <v>46170.25</v>
+        <v>46175.604166666664</v>
       </c>
       <c r="R86" s="4">
-        <v>46170.366140659724</v>
+        <v>46176.32743784722</v>
       </c>
       <c r="S86">
-        <v>7345.000</v>
+        <v>9893.000</v>
       </c>
       <c r="T86">
-        <v>7345.000</v>
+        <v>9893.000</v>
       </c>
       <c r="U86">
         <v>0</v>
@@ -5513,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="W86" s="4">
-        <v>46170.37235636574</v>
+        <v>46176.36704571759</v>
       </c>
     </row>
     <row r="87">
@@ -5521,43 +5482,43 @@
         <v>19</v>
       </c>
       <c r="B87" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C87" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D87" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E87">
-        <v>7243666</v>
+        <v>7290513</v>
       </c>
       <c r="F87" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="G87" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H87" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M87" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="P87" s="1">
-        <v>46167.397709988429</v>
+        <v>46175.705472835645</v>
       </c>
       <c r="Q87" s="4">
-        <v>46169.444444444445</v>
+        <v>46175.541666666664</v>
       </c>
       <c r="R87" s="4">
-        <v>46169.627317511571</v>
+        <v>46176.390187384262</v>
       </c>
       <c r="S87">
-        <v>5379.000</v>
+        <v>10634.000</v>
       </c>
       <c r="T87">
-        <v>5379.000</v>
+        <v>10634.000</v>
       </c>
       <c r="U87">
         <v>0</v>
@@ -5566,7 +5527,7 @@
         <v>0</v>
       </c>
       <c r="W87" s="4">
-        <v>46170.372355636573</v>
+        <v>46176.479922453706</v>
       </c>
     </row>
     <row r="88">
@@ -5574,43 +5535,43 @@
         <v>19</v>
       </c>
       <c r="B88" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C88" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D88" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E88">
-        <v>7243660</v>
+        <v>7290512</v>
       </c>
       <c r="F88" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="G88" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H88" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M88" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="P88" s="1">
-        <v>46167.396469907406</v>
+        <v>46175.705376817132</v>
       </c>
       <c r="Q88" s="4">
-        <v>46168.375</v>
+        <v>46176.5</v>
       </c>
       <c r="R88" s="4">
-        <v>46168.522693749997</v>
+        <v>46188.325696840278</v>
       </c>
       <c r="S88">
-        <v>15726.000</v>
+        <v>14234.000</v>
       </c>
       <c r="T88">
-        <v>15726.000</v>
+        <v>14234.000</v>
       </c>
       <c r="U88">
         <v>0</v>
@@ -5619,7 +5580,7 @@
         <v>0</v>
       </c>
       <c r="W88" s="4">
-        <v>46168.603323611111</v>
+        <v>46188.329304166669</v>
       </c>
     </row>
     <row r="89">
@@ -5627,43 +5588,43 @@
         <v>19</v>
       </c>
       <c r="B89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E89">
-        <v>7243658</v>
+        <v>7277755</v>
       </c>
       <c r="F89" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="G89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M89" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="P89" s="1">
-        <v>46167.396019097221</v>
+        <v>46174.492233680554</v>
       </c>
       <c r="Q89" s="4">
-        <v>46168.479166666664</v>
+        <v>46175.291666666664</v>
       </c>
       <c r="R89" s="4">
-        <v>46168.596083993056</v>
+        <v>46175.460509027776</v>
       </c>
       <c r="S89">
-        <v>18164.000</v>
+        <v>1502.000</v>
       </c>
       <c r="T89">
-        <v>18164.000</v>
+        <v>1502.000</v>
       </c>
       <c r="U89">
         <v>0</v>
@@ -5672,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="W89" s="4">
-        <v>46168.603323067131</v>
+        <v>46176.367452777777</v>
       </c>
     </row>
     <row r="90">
@@ -5680,40 +5641,43 @@
         <v>19</v>
       </c>
       <c r="B90" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C90" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D90" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E90">
-        <v>7209851</v>
+        <v>7277745</v>
       </c>
       <c r="F90" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="G90" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H90" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M90" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="P90" s="1">
-        <v>46161.374809525463</v>
+        <v>46174.492115972222</v>
+      </c>
+      <c r="Q90" s="4">
+        <v>46175.291666666664</v>
       </c>
       <c r="R90" s="4">
-        <v>46168.442082719906</v>
+        <v>46176.394080127313</v>
       </c>
       <c r="S90">
-        <v>10564.000</v>
+        <v>8925.000</v>
       </c>
       <c r="T90">
-        <v>10564.000</v>
+        <v>8925.000</v>
       </c>
       <c r="U90">
         <v>0</v>
@@ -5722,7 +5686,7 @@
         <v>0</v>
       </c>
       <c r="W90" s="4">
-        <v>46168.603322337964</v>
+        <v>46176.479621759259</v>
       </c>
     </row>
     <row r="91">
@@ -5730,43 +5694,43 @@
         <v>19</v>
       </c>
       <c r="B91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E91">
-        <v>7243663</v>
+        <v>7277744</v>
       </c>
       <c r="F91" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="G91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M91" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="P91" s="1">
-        <v>46167.396879664353</v>
+        <v>46174.49203425926</v>
       </c>
       <c r="Q91" s="4">
-        <v>46168.3125</v>
+        <v>46174.5</v>
       </c>
       <c r="R91" s="4">
-        <v>46168.372719247687</v>
+        <v>46175.401104085649</v>
       </c>
       <c r="S91">
-        <v>7178.000</v>
+        <v>14377.000</v>
       </c>
       <c r="T91">
-        <v>7178.000</v>
+        <v>14377.000</v>
       </c>
       <c r="U91">
         <v>0</v>
@@ -5775,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="W91" s="4">
-        <v>46168.383504201389</v>
+        <v>46175.446175925928</v>
       </c>
     </row>
     <row r="92">
@@ -5783,43 +5747,43 @@
         <v>19</v>
       </c>
       <c r="B92" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C92" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D92" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E92">
-        <v>7243656</v>
+        <v>7277742</v>
       </c>
       <c r="F92" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="G92" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H92" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M92" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="P92" s="1">
-        <v>46167.395494872682</v>
+        <v>46174.491930821758</v>
       </c>
       <c r="Q92" s="4">
-        <v>46168.25</v>
+        <v>46174.416666666664</v>
       </c>
       <c r="R92" s="4">
-        <v>46168.325715162035</v>
+        <v>46188.313768368054</v>
       </c>
       <c r="S92">
-        <v>8924.000</v>
+        <v>18914.000</v>
       </c>
       <c r="T92">
-        <v>8924.000</v>
+        <v>18914.000</v>
       </c>
       <c r="U92">
         <v>0</v>
@@ -5828,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="W92" s="4">
-        <v>46168.383503321762</v>
+        <v>46188.329302546299</v>
       </c>
     </row>
     <row r="93">
@@ -5836,40 +5800,43 @@
         <v>19</v>
       </c>
       <c r="B93" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C93" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D93" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E93">
-        <v>7234523</v>
+        <v>7276672</v>
       </c>
       <c r="F93" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="G93" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H93" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M93" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="P93" s="1">
-        <v>46164.418446909724</v>
+        <v>46174.386965358797</v>
+      </c>
+      <c r="Q93" s="4">
+        <v>46174.3125</v>
       </c>
       <c r="R93" s="4">
-        <v>46164.542648229166</v>
+        <v>46175.277797997682</v>
       </c>
       <c r="S93">
-        <v>3573.000</v>
+        <v>445.000</v>
       </c>
       <c r="T93">
-        <v>3573.000</v>
+        <v>445.000</v>
       </c>
       <c r="U93">
         <v>0</v>
@@ -5878,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="W93" s="4">
-        <v>46164.552599270835</v>
+        <v>46175.446175925928</v>
       </c>
     </row>
     <row r="94">
@@ -5886,43 +5853,43 @@
         <v>19</v>
       </c>
       <c r="B94" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C94" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D94" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E94">
-        <v>7222955</v>
+        <v>7276670</v>
       </c>
       <c r="F94" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="G94" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H94" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M94" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="P94" s="1">
-        <v>46162.757414780091</v>
+        <v>46174.386795023151</v>
       </c>
       <c r="Q94" s="4">
-        <v>46164.260416666664</v>
+        <v>46174.3125</v>
       </c>
       <c r="R94" s="4">
-        <v>46164.550929016201</v>
+        <v>46181.602299189813</v>
       </c>
       <c r="S94">
-        <v>10360.000</v>
+        <v>7766.000</v>
       </c>
       <c r="T94">
-        <v>10360.000</v>
+        <v>7766.000</v>
       </c>
       <c r="U94">
         <v>0</v>
@@ -5931,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="W94" s="4">
-        <v>46164.552598877315</v>
+        <v>46181.607877893519</v>
       </c>
     </row>
     <row r="95">
@@ -5939,43 +5906,40 @@
         <v>19</v>
       </c>
       <c r="B95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E95">
-        <v>7222913</v>
+        <v>7261067</v>
       </c>
       <c r="F95" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="G95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H95" t="s">
-        <v>23</v>
-      </c>
-      <c r="M95" s="5" t="s">
-        <v>187</v>
+        <v>24</v>
+      </c>
+      <c r="M95" t="s">
+        <v>174</v>
       </c>
       <c r="P95" s="1">
-        <v>46162.756352662036</v>
-      </c>
-      <c r="Q95" s="4">
-        <v>46164.333333333336</v>
+        <v>46171.450339317133</v>
       </c>
       <c r="R95" s="4">
-        <v>46164.404302395837</v>
+        <v>46171.468652743053</v>
       </c>
       <c r="S95">
-        <v>7657.000</v>
+        <v>13827.000</v>
       </c>
       <c r="T95">
-        <v>7657.000</v>
+        <v>13827.000</v>
       </c>
       <c r="U95">
         <v>0</v>
@@ -5984,7 +5948,7 @@
         <v>0</v>
       </c>
       <c r="W95" s="4">
-        <v>46164.453907951392</v>
+        <v>46171.521808101854</v>
       </c>
     </row>
     <row r="96">
@@ -5992,43 +5956,43 @@
         <v>19</v>
       </c>
       <c r="B96" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C96" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D96" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E96">
-        <v>7217995</v>
+        <v>7256959</v>
       </c>
       <c r="F96" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="G96" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H96" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M96" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="P96" s="1">
-        <v>46162.28924351852</v>
+        <v>46169.73840185185</v>
       </c>
       <c r="Q96" s="4">
-        <v>46163.291666666664</v>
+        <v>46171.520833333336</v>
       </c>
       <c r="R96" s="4">
-        <v>46163.616474340277</v>
+        <v>46181.602367395833</v>
       </c>
       <c r="S96">
-        <v>5708.000</v>
+        <v>11921.000</v>
       </c>
       <c r="T96">
-        <v>5708.000</v>
+        <v>11921.000</v>
       </c>
       <c r="U96">
         <v>0</v>
@@ -6037,7 +6001,7 @@
         <v>0</v>
       </c>
       <c r="W96" s="4">
-        <v>46164.389474687501</v>
+        <v>46181.607877002316</v>
       </c>
     </row>
     <row r="97">
@@ -6045,46 +6009,43 @@
         <v>19</v>
       </c>
       <c r="B97" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C97" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D97" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E97">
-        <v>7209848</v>
+        <v>7256954</v>
       </c>
       <c r="F97" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="G97" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H97" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M97" t="s">
-        <v>191</v>
-      </c>
-      <c r="O97" s="4">
-        <v>46161.291666666664</v>
+        <v>178</v>
       </c>
       <c r="P97" s="1">
-        <v>46161.373708449071</v>
+        <v>46169.737280092595</v>
       </c>
       <c r="Q97" s="4">
-        <v>46161.586805555555</v>
+        <v>46171.416666666664</v>
       </c>
       <c r="R97" s="4">
-        <v>46163.626690358797</v>
+        <v>46171.471500266205</v>
       </c>
       <c r="S97">
-        <v>16674.000</v>
+        <v>11226.000</v>
       </c>
       <c r="T97">
-        <v>16674.000</v>
+        <v>11226.000</v>
       </c>
       <c r="U97">
         <v>0</v>
@@ -6093,7 +6054,7 @@
         <v>0</v>
       </c>
       <c r="W97" s="4">
-        <v>46164.389386608796</v>
+        <v>46171.521807557867</v>
       </c>
     </row>
     <row r="98">
@@ -6101,43 +6062,43 @@
         <v>19</v>
       </c>
       <c r="B98" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C98" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D98" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E98">
-        <v>7222907</v>
+        <v>7256935</v>
       </c>
       <c r="F98" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="G98" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H98" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M98" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="P98" s="1">
-        <v>46162.75522561343</v>
+        <v>46169.735800810187</v>
       </c>
       <c r="Q98" s="4">
-        <v>46163.368055555555</v>
+        <v>46171.25</v>
       </c>
       <c r="R98" s="4">
-        <v>46163.519357025463</v>
+        <v>46171.474860069444</v>
       </c>
       <c r="S98">
-        <v>10357.000</v>
+        <v>12909.000</v>
       </c>
       <c r="T98">
-        <v>10357.000</v>
+        <v>12909.000</v>
       </c>
       <c r="U98">
         <v>0</v>
@@ -6146,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="W98" s="4">
-        <v>46163.541440972222</v>
+        <v>46171.521807025463</v>
       </c>
     </row>
     <row r="99">
@@ -6154,43 +6115,46 @@
         <v>19</v>
       </c>
       <c r="B99" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C99" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D99" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E99">
-        <v>7217994</v>
+        <v>7256927</v>
       </c>
       <c r="F99" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="G99" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H99" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M99" t="s">
-        <v>195</v>
+        <v>182</v>
+      </c>
+      <c r="O99" s="4">
+        <v>46170.541666666664</v>
       </c>
       <c r="P99" s="1">
-        <v>46162.288815127315</v>
+        <v>46169.733974768518</v>
       </c>
       <c r="Q99" s="4">
-        <v>46163.291666666664</v>
+        <v>46171.375</v>
       </c>
       <c r="R99" s="4">
-        <v>46163.35348445602</v>
+        <v>46171.384800081018</v>
       </c>
       <c r="S99">
-        <v>3946.000</v>
+        <v>470.000</v>
       </c>
       <c r="T99">
-        <v>3946.000</v>
+        <v>470.000</v>
       </c>
       <c r="U99">
         <v>0</v>
@@ -6199,7 +6163,7 @@
         <v>0</v>
       </c>
       <c r="W99" s="4">
-        <v>46163.541440775465</v>
+        <v>46171.521806828707</v>
       </c>
     </row>
     <row r="100">
@@ -6207,46 +6171,46 @@
         <v>19</v>
       </c>
       <c r="B100" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C100" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D100" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E100">
-        <v>7217993</v>
+        <v>7256837</v>
       </c>
       <c r="F100" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="G100" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H100" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M100" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="O100" s="4">
-        <v>46162.416666666664</v>
+        <v>46170.541666666664</v>
       </c>
       <c r="P100" s="1">
-        <v>46162.287909756946</v>
+        <v>46169.717724456015</v>
       </c>
       <c r="Q100" s="4">
-        <v>46162.416666666664</v>
+        <v>46171.375</v>
       </c>
       <c r="R100" s="4">
-        <v>46163.518015046298</v>
+        <v>46181.601758877317</v>
       </c>
       <c r="S100">
-        <v>12356.000</v>
+        <v>10645.000</v>
       </c>
       <c r="T100">
-        <v>12356.000</v>
+        <v>10645.000</v>
       </c>
       <c r="U100">
         <v>0</v>
@@ -6255,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="W100" s="4">
-        <v>46163.541439895831</v>
+        <v>46181.607876122682</v>
       </c>
     </row>
     <row r="101">
@@ -6263,46 +6227,46 @@
         <v>19</v>
       </c>
       <c r="B101" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C101" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D101" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E101">
-        <v>7217991</v>
+        <v>7256698</v>
       </c>
       <c r="F101" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="G101" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H101" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M101" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="O101" s="4">
-        <v>46162.291666666664</v>
+        <v>46170.416666666664</v>
       </c>
       <c r="P101" s="1">
-        <v>46162.28736678241</v>
+        <v>46169.704318553238</v>
       </c>
       <c r="Q101" s="4">
-        <v>46162.513220173612</v>
+        <v>46170.4375</v>
       </c>
       <c r="R101" s="4">
-        <v>46163.531940428242</v>
+        <v>46170.55747615741</v>
       </c>
       <c r="S101">
-        <v>12360.000</v>
+        <v>15811.000</v>
       </c>
       <c r="T101">
-        <v>12360.000</v>
+        <v>15811.000</v>
       </c>
       <c r="U101">
         <v>0</v>
@@ -6311,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="W101" s="4">
-        <v>46163.541439351851</v>
+        <v>46171.52180628472</v>
       </c>
     </row>
     <row r="102">
@@ -6319,40 +6283,46 @@
         <v>19</v>
       </c>
       <c r="B102" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C102" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D102" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E102">
-        <v>7209853</v>
+        <v>7256674</v>
       </c>
       <c r="F102" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="G102" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H102" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M102" t="s">
-        <v>201</v>
+        <v>188</v>
+      </c>
+      <c r="O102" s="4">
+        <v>46170.291666666664</v>
       </c>
       <c r="P102" s="1">
-        <v>46161.375624884262</v>
+        <v>46169.697586805552</v>
+      </c>
+      <c r="Q102" s="4">
+        <v>46171.291666666664</v>
       </c>
       <c r="R102" s="4">
-        <v>46162.474544826386</v>
+        <v>46171.366929745367</v>
       </c>
       <c r="S102">
-        <v>10350.000</v>
+        <v>6703.000</v>
       </c>
       <c r="T102">
-        <v>10350.000</v>
+        <v>6703.000</v>
       </c>
       <c r="U102">
         <v>0</v>
@@ -6361,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="W102" s="4">
-        <v>46163.484965937503</v>
+        <v>46171.521805937497</v>
       </c>
     </row>
     <row r="103">
@@ -6369,43 +6339,43 @@
         <v>19</v>
       </c>
       <c r="B103" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C103" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D103" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E103">
-        <v>7186224</v>
+        <v>7243671</v>
       </c>
       <c r="F103" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="G103" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H103" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M103" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="P103" s="1">
-        <v>46157.585680983793</v>
+        <v>46167.398480636577</v>
       </c>
       <c r="Q103" s="4">
-        <v>46160.493105243055</v>
+        <v>46170.25</v>
       </c>
       <c r="R103" s="4">
-        <v>46160.607764236112</v>
+        <v>46170.38833533565</v>
       </c>
       <c r="S103">
-        <v>8153.000</v>
+        <v>767.000</v>
       </c>
       <c r="T103">
-        <v>8153.000</v>
+        <v>767.000</v>
       </c>
       <c r="U103">
         <v>0</v>
@@ -6414,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="W103" s="4">
-        <v>46161.606680011573</v>
+        <v>46171.521805752316</v>
       </c>
     </row>
     <row r="104">
@@ -6422,43 +6392,43 @@
         <v>19</v>
       </c>
       <c r="B104" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C104" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D104" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E104">
-        <v>7186209</v>
+        <v>7243667</v>
       </c>
       <c r="F104" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="G104" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H104" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M104" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="P104" s="1">
-        <v>46157.580364664354</v>
+        <v>46167.398084108798</v>
       </c>
       <c r="Q104" s="4">
-        <v>46160.367256516205</v>
+        <v>46170.25</v>
       </c>
       <c r="R104" s="4">
-        <v>46160.444021875002</v>
+        <v>46170.366140659724</v>
       </c>
       <c r="S104">
-        <v>19189.000</v>
+        <v>7345.000</v>
       </c>
       <c r="T104">
-        <v>19189.000</v>
+        <v>7345.000</v>
       </c>
       <c r="U104">
         <v>0</v>
@@ -6467,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="W104" s="4">
-        <v>46161.605472025461</v>
+        <v>46170.37235636574</v>
       </c>
     </row>
     <row r="105">
@@ -6475,43 +6445,43 @@
         <v>19</v>
       </c>
       <c r="B105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E105">
-        <v>7185903</v>
+        <v>7243666</v>
       </c>
       <c r="F105" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="G105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M105" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="P105" s="1">
-        <v>46157.55131412037</v>
+        <v>46167.397709988429</v>
       </c>
       <c r="Q105" s="4">
-        <v>46160.493105243055</v>
+        <v>46169.444444444445</v>
       </c>
       <c r="R105" s="4">
-        <v>46160.545683645832</v>
+        <v>46169.627317511571</v>
       </c>
       <c r="S105">
-        <v>39356.000</v>
+        <v>5379.000</v>
       </c>
       <c r="T105">
-        <v>39356.000</v>
+        <v>5379.000</v>
       </c>
       <c r="U105">
         <v>0</v>
@@ -6520,7 +6490,7 @@
         <v>0</v>
       </c>
       <c r="W105" s="4">
-        <v>46161.604525312498</v>
+        <v>46170.372355636573</v>
       </c>
     </row>
     <row r="106">
@@ -6528,46 +6498,43 @@
         <v>19</v>
       </c>
       <c r="B106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E106">
-        <v>7177836</v>
+        <v>7243664</v>
       </c>
       <c r="F106" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="G106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M106" t="s">
-        <v>208</v>
-      </c>
-      <c r="O106" s="4">
-        <v>46157.416666666664</v>
+        <v>196</v>
       </c>
       <c r="P106" s="1">
-        <v>46155.705813773151</v>
+        <v>46167.397293715279</v>
       </c>
       <c r="Q106" s="4">
-        <v>46157.466666666667</v>
+        <v>46169.3125</v>
       </c>
       <c r="R106" s="4">
-        <v>46160.360912615739</v>
+        <v>46170.486638159724</v>
       </c>
       <c r="S106">
-        <v>17794.000</v>
+        <v>5002.000</v>
       </c>
       <c r="T106">
-        <v>17794.000</v>
+        <v>5002.000</v>
       </c>
       <c r="U106">
         <v>0</v>
@@ -6576,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="W106" s="4">
-        <v>46160.503910451385</v>
+        <v>46171.52288329861</v>
       </c>
     </row>
     <row r="107">
@@ -6584,46 +6551,43 @@
         <v>19</v>
       </c>
       <c r="B107" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D107" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E107">
-        <v>7175007</v>
+        <v>7243663</v>
       </c>
       <c r="F107" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="G107" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H107" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M107" t="s">
-        <v>210</v>
-      </c>
-      <c r="O107" s="4">
-        <v>46157.291666666664</v>
+        <v>198</v>
       </c>
       <c r="P107" s="1">
-        <v>46155.454049652777</v>
+        <v>46167.396879664353</v>
       </c>
       <c r="Q107" s="4">
-        <v>46157.35833333333</v>
+        <v>46168.3125</v>
       </c>
       <c r="R107" s="4">
-        <v>46157.601774965275</v>
+        <v>46168.372719247687</v>
       </c>
       <c r="S107">
-        <v>21375.000</v>
+        <v>7178.000</v>
       </c>
       <c r="T107">
-        <v>21375.000</v>
+        <v>7178.000</v>
       </c>
       <c r="U107">
         <v>0</v>
@@ -6632,7 +6596,7 @@
         <v>0</v>
       </c>
       <c r="W107" s="4">
-        <v>46157.688587037039</v>
+        <v>46168.383504201389</v>
       </c>
     </row>
     <row r="108">
@@ -6640,40 +6604,43 @@
         <v>19</v>
       </c>
       <c r="B108" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C108" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D108" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E108">
-        <v>7167099</v>
+        <v>7243660</v>
       </c>
       <c r="F108" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="G108" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H108" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M108" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="P108" s="1">
-        <v>46154.541764120368</v>
+        <v>46167.396469907406</v>
+      </c>
+      <c r="Q108" s="4">
+        <v>46168.375</v>
       </c>
       <c r="R108" s="4">
-        <v>46155.643980821762</v>
+        <v>46168.522693749997</v>
       </c>
       <c r="S108">
-        <v>11855.000</v>
+        <v>15726.000</v>
       </c>
       <c r="T108">
-        <v>11855.000</v>
+        <v>15726.000</v>
       </c>
       <c r="U108">
         <v>0</v>
@@ -6682,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="W108" s="4">
-        <v>46157.304165428242</v>
+        <v>46168.603323611111</v>
       </c>
     </row>
     <row r="109">
@@ -6690,75 +6657,1138 @@
         <v>19</v>
       </c>
       <c r="B109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D109" t="s">
+        <v>24</v>
+      </c>
+      <c r="E109">
+        <v>7243658</v>
+      </c>
+      <c r="F109" t="s">
+        <v>201</v>
+      </c>
+      <c r="G109" t="s">
+        <v>24</v>
+      </c>
+      <c r="H109" t="s">
+        <v>24</v>
+      </c>
+      <c r="M109" t="s">
+        <v>202</v>
+      </c>
+      <c r="P109" s="1">
+        <v>46167.396019097221</v>
+      </c>
+      <c r="Q109" s="4">
+        <v>46168.479166666664</v>
+      </c>
+      <c r="R109" s="4">
+        <v>46168.596083993056</v>
+      </c>
+      <c r="S109">
+        <v>18164.000</v>
+      </c>
+      <c r="T109">
+        <v>18164.000</v>
+      </c>
+      <c r="U109">
+        <v>0</v>
+      </c>
+      <c r="V109">
+        <v>0</v>
+      </c>
+      <c r="W109" s="4">
+        <v>46168.603323067131</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>19</v>
+      </c>
+      <c r="B110" t="s">
+        <v>24</v>
+      </c>
+      <c r="C110" t="s">
+        <v>24</v>
+      </c>
+      <c r="D110" t="s">
+        <v>24</v>
+      </c>
+      <c r="E110">
+        <v>7243656</v>
+      </c>
+      <c r="F110" t="s">
+        <v>203</v>
+      </c>
+      <c r="G110" t="s">
+        <v>24</v>
+      </c>
+      <c r="H110" t="s">
+        <v>24</v>
+      </c>
+      <c r="M110" t="s">
+        <v>204</v>
+      </c>
+      <c r="P110" s="1">
+        <v>46167.395494872682</v>
+      </c>
+      <c r="Q110" s="4">
+        <v>46168.25</v>
+      </c>
+      <c r="R110" s="4">
+        <v>46168.325715162035</v>
+      </c>
+      <c r="S110">
+        <v>8924.000</v>
+      </c>
+      <c r="T110">
+        <v>8924.000</v>
+      </c>
+      <c r="U110">
+        <v>0</v>
+      </c>
+      <c r="V110">
+        <v>0</v>
+      </c>
+      <c r="W110" s="4">
+        <v>46168.383503321762</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>19</v>
+      </c>
+      <c r="B111" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" t="s">
+        <v>24</v>
+      </c>
+      <c r="D111" t="s">
+        <v>24</v>
+      </c>
+      <c r="E111">
+        <v>7234523</v>
+      </c>
+      <c r="F111" t="s">
+        <v>205</v>
+      </c>
+      <c r="G111" t="s">
+        <v>24</v>
+      </c>
+      <c r="H111" t="s">
+        <v>24</v>
+      </c>
+      <c r="M111" t="s">
+        <v>206</v>
+      </c>
+      <c r="P111" s="1">
+        <v>46164.418446909724</v>
+      </c>
+      <c r="R111" s="4">
+        <v>46164.542648229166</v>
+      </c>
+      <c r="S111">
+        <v>3573.000</v>
+      </c>
+      <c r="T111">
+        <v>3573.000</v>
+      </c>
+      <c r="U111">
+        <v>0</v>
+      </c>
+      <c r="V111">
+        <v>0</v>
+      </c>
+      <c r="W111" s="4">
+        <v>46164.552599270835</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>19</v>
+      </c>
+      <c r="B112" t="s">
+        <v>24</v>
+      </c>
+      <c r="C112" t="s">
+        <v>24</v>
+      </c>
+      <c r="D112" t="s">
+        <v>24</v>
+      </c>
+      <c r="E112">
+        <v>7222955</v>
+      </c>
+      <c r="F112" t="s">
+        <v>207</v>
+      </c>
+      <c r="G112" t="s">
+        <v>24</v>
+      </c>
+      <c r="H112" t="s">
+        <v>24</v>
+      </c>
+      <c r="M112" t="s">
+        <v>208</v>
+      </c>
+      <c r="P112" s="1">
+        <v>46162.757414780091</v>
+      </c>
+      <c r="Q112" s="4">
+        <v>46164.260416666664</v>
+      </c>
+      <c r="R112" s="4">
+        <v>46164.550929016201</v>
+      </c>
+      <c r="S112">
+        <v>10360.000</v>
+      </c>
+      <c r="T112">
+        <v>10360.000</v>
+      </c>
+      <c r="U112">
+        <v>0</v>
+      </c>
+      <c r="V112">
+        <v>0</v>
+      </c>
+      <c r="W112" s="4">
+        <v>46164.552598877315</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>19</v>
+      </c>
+      <c r="B113" t="s">
+        <v>24</v>
+      </c>
+      <c r="C113" t="s">
+        <v>24</v>
+      </c>
+      <c r="D113" t="s">
+        <v>24</v>
+      </c>
+      <c r="E113">
+        <v>7222913</v>
+      </c>
+      <c r="F113" t="s">
+        <v>209</v>
+      </c>
+      <c r="G113" t="s">
+        <v>24</v>
+      </c>
+      <c r="H113" t="s">
+        <v>24</v>
+      </c>
+      <c r="M113" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="P113" s="1">
+        <v>46162.756352662036</v>
+      </c>
+      <c r="Q113" s="4">
+        <v>46164.333333333336</v>
+      </c>
+      <c r="R113" s="4">
+        <v>46164.404302395837</v>
+      </c>
+      <c r="S113">
+        <v>7657.000</v>
+      </c>
+      <c r="T113">
+        <v>7657.000</v>
+      </c>
+      <c r="U113">
+        <v>0</v>
+      </c>
+      <c r="V113">
+        <v>0</v>
+      </c>
+      <c r="W113" s="4">
+        <v>46164.453907951392</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>19</v>
+      </c>
+      <c r="B114" t="s">
+        <v>24</v>
+      </c>
+      <c r="C114" t="s">
+        <v>24</v>
+      </c>
+      <c r="D114" t="s">
+        <v>24</v>
+      </c>
+      <c r="E114">
+        <v>7222907</v>
+      </c>
+      <c r="F114" t="s">
+        <v>211</v>
+      </c>
+      <c r="G114" t="s">
+        <v>24</v>
+      </c>
+      <c r="H114" t="s">
+        <v>24</v>
+      </c>
+      <c r="M114" t="s">
+        <v>212</v>
+      </c>
+      <c r="P114" s="1">
+        <v>46162.75522561343</v>
+      </c>
+      <c r="Q114" s="4">
+        <v>46163.368055555555</v>
+      </c>
+      <c r="R114" s="4">
+        <v>46163.519357025463</v>
+      </c>
+      <c r="S114">
+        <v>10357.000</v>
+      </c>
+      <c r="T114">
+        <v>10357.000</v>
+      </c>
+      <c r="U114">
+        <v>0</v>
+      </c>
+      <c r="V114">
+        <v>0</v>
+      </c>
+      <c r="W114" s="4">
+        <v>46163.541440972222</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>19</v>
+      </c>
+      <c r="B115" t="s">
+        <v>24</v>
+      </c>
+      <c r="C115" t="s">
+        <v>24</v>
+      </c>
+      <c r="D115" t="s">
+        <v>24</v>
+      </c>
+      <c r="E115">
+        <v>7217995</v>
+      </c>
+      <c r="F115" t="s">
         <v>213</v>
       </c>
-      <c r="E109">
+      <c r="G115" t="s">
+        <v>24</v>
+      </c>
+      <c r="H115" t="s">
+        <v>24</v>
+      </c>
+      <c r="M115" t="s">
+        <v>214</v>
+      </c>
+      <c r="P115" s="1">
+        <v>46162.28924351852</v>
+      </c>
+      <c r="Q115" s="4">
+        <v>46163.291666666664</v>
+      </c>
+      <c r="R115" s="4">
+        <v>46163.616474340277</v>
+      </c>
+      <c r="S115">
+        <v>5708.000</v>
+      </c>
+      <c r="T115">
+        <v>5708.000</v>
+      </c>
+      <c r="U115">
+        <v>0</v>
+      </c>
+      <c r="V115">
+        <v>0</v>
+      </c>
+      <c r="W115" s="4">
+        <v>46164.389474687501</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>19</v>
+      </c>
+      <c r="B116" t="s">
+        <v>24</v>
+      </c>
+      <c r="C116" t="s">
+        <v>24</v>
+      </c>
+      <c r="D116" t="s">
+        <v>24</v>
+      </c>
+      <c r="E116">
+        <v>7217994</v>
+      </c>
+      <c r="F116" t="s">
+        <v>215</v>
+      </c>
+      <c r="G116" t="s">
+        <v>24</v>
+      </c>
+      <c r="H116" t="s">
+        <v>24</v>
+      </c>
+      <c r="M116" t="s">
+        <v>216</v>
+      </c>
+      <c r="P116" s="1">
+        <v>46162.288815127315</v>
+      </c>
+      <c r="Q116" s="4">
+        <v>46163.291666666664</v>
+      </c>
+      <c r="R116" s="4">
+        <v>46163.35348445602</v>
+      </c>
+      <c r="S116">
+        <v>3946.000</v>
+      </c>
+      <c r="T116">
+        <v>3946.000</v>
+      </c>
+      <c r="U116">
+        <v>0</v>
+      </c>
+      <c r="V116">
+        <v>0</v>
+      </c>
+      <c r="W116" s="4">
+        <v>46163.541440775465</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>19</v>
+      </c>
+      <c r="B117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C117" t="s">
+        <v>24</v>
+      </c>
+      <c r="D117" t="s">
+        <v>24</v>
+      </c>
+      <c r="E117">
+        <v>7217993</v>
+      </c>
+      <c r="F117" t="s">
+        <v>217</v>
+      </c>
+      <c r="G117" t="s">
+        <v>24</v>
+      </c>
+      <c r="H117" t="s">
+        <v>24</v>
+      </c>
+      <c r="M117" t="s">
+        <v>218</v>
+      </c>
+      <c r="O117" s="4">
+        <v>46162.416666666664</v>
+      </c>
+      <c r="P117" s="1">
+        <v>46162.287909756946</v>
+      </c>
+      <c r="Q117" s="4">
+        <v>46162.416666666664</v>
+      </c>
+      <c r="R117" s="4">
+        <v>46163.518015046298</v>
+      </c>
+      <c r="S117">
+        <v>12356.000</v>
+      </c>
+      <c r="T117">
+        <v>12356.000</v>
+      </c>
+      <c r="U117">
+        <v>0</v>
+      </c>
+      <c r="V117">
+        <v>0</v>
+      </c>
+      <c r="W117" s="4">
+        <v>46163.541439895831</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>19</v>
+      </c>
+      <c r="B118" t="s">
+        <v>24</v>
+      </c>
+      <c r="C118" t="s">
+        <v>24</v>
+      </c>
+      <c r="D118" t="s">
+        <v>24</v>
+      </c>
+      <c r="E118">
+        <v>7217991</v>
+      </c>
+      <c r="F118" t="s">
+        <v>219</v>
+      </c>
+      <c r="G118" t="s">
+        <v>24</v>
+      </c>
+      <c r="H118" t="s">
+        <v>24</v>
+      </c>
+      <c r="M118" t="s">
+        <v>220</v>
+      </c>
+      <c r="O118" s="4">
+        <v>46162.291666666664</v>
+      </c>
+      <c r="P118" s="1">
+        <v>46162.28736678241</v>
+      </c>
+      <c r="Q118" s="4">
+        <v>46162.513220173612</v>
+      </c>
+      <c r="R118" s="4">
+        <v>46163.531940428242</v>
+      </c>
+      <c r="S118">
+        <v>12360.000</v>
+      </c>
+      <c r="T118">
+        <v>12360.000</v>
+      </c>
+      <c r="U118">
+        <v>0</v>
+      </c>
+      <c r="V118">
+        <v>0</v>
+      </c>
+      <c r="W118" s="4">
+        <v>46163.541439351851</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>19</v>
+      </c>
+      <c r="B119" t="s">
+        <v>24</v>
+      </c>
+      <c r="C119" t="s">
+        <v>24</v>
+      </c>
+      <c r="D119" t="s">
+        <v>24</v>
+      </c>
+      <c r="E119">
+        <v>7209853</v>
+      </c>
+      <c r="F119" t="s">
+        <v>221</v>
+      </c>
+      <c r="G119" t="s">
+        <v>24</v>
+      </c>
+      <c r="H119" t="s">
+        <v>24</v>
+      </c>
+      <c r="M119" t="s">
+        <v>222</v>
+      </c>
+      <c r="P119" s="1">
+        <v>46161.375624884262</v>
+      </c>
+      <c r="R119" s="4">
+        <v>46162.474544826386</v>
+      </c>
+      <c r="S119">
+        <v>10350.000</v>
+      </c>
+      <c r="T119">
+        <v>10350.000</v>
+      </c>
+      <c r="U119">
+        <v>0</v>
+      </c>
+      <c r="V119">
+        <v>0</v>
+      </c>
+      <c r="W119" s="4">
+        <v>46163.484965937503</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>19</v>
+      </c>
+      <c r="B120" t="s">
+        <v>24</v>
+      </c>
+      <c r="C120" t="s">
+        <v>24</v>
+      </c>
+      <c r="D120" t="s">
+        <v>24</v>
+      </c>
+      <c r="E120">
+        <v>7209851</v>
+      </c>
+      <c r="F120" t="s">
+        <v>223</v>
+      </c>
+      <c r="G120" t="s">
+        <v>24</v>
+      </c>
+      <c r="H120" t="s">
+        <v>24</v>
+      </c>
+      <c r="M120" t="s">
+        <v>224</v>
+      </c>
+      <c r="P120" s="1">
+        <v>46161.374809525463</v>
+      </c>
+      <c r="R120" s="4">
+        <v>46168.442082719906</v>
+      </c>
+      <c r="S120">
+        <v>10564.000</v>
+      </c>
+      <c r="T120">
+        <v>10564.000</v>
+      </c>
+      <c r="U120">
+        <v>0</v>
+      </c>
+      <c r="V120">
+        <v>0</v>
+      </c>
+      <c r="W120" s="4">
+        <v>46168.603322337964</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>19</v>
+      </c>
+      <c r="B121" t="s">
+        <v>24</v>
+      </c>
+      <c r="C121" t="s">
+        <v>24</v>
+      </c>
+      <c r="D121" t="s">
+        <v>24</v>
+      </c>
+      <c r="E121">
+        <v>7209848</v>
+      </c>
+      <c r="F121" t="s">
+        <v>225</v>
+      </c>
+      <c r="G121" t="s">
+        <v>24</v>
+      </c>
+      <c r="H121" t="s">
+        <v>24</v>
+      </c>
+      <c r="M121" t="s">
+        <v>226</v>
+      </c>
+      <c r="O121" s="4">
+        <v>46161.291666666664</v>
+      </c>
+      <c r="P121" s="1">
+        <v>46161.373708449071</v>
+      </c>
+      <c r="Q121" s="4">
+        <v>46161.586805555555</v>
+      </c>
+      <c r="R121" s="4">
+        <v>46163.626690358797</v>
+      </c>
+      <c r="S121">
+        <v>16674.000</v>
+      </c>
+      <c r="T121">
+        <v>16674.000</v>
+      </c>
+      <c r="U121">
+        <v>0</v>
+      </c>
+      <c r="V121">
+        <v>0</v>
+      </c>
+      <c r="W121" s="4">
+        <v>46164.389386608796</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>19</v>
+      </c>
+      <c r="B122" t="s">
+        <v>24</v>
+      </c>
+      <c r="C122" t="s">
+        <v>24</v>
+      </c>
+      <c r="D122" t="s">
+        <v>24</v>
+      </c>
+      <c r="E122">
+        <v>7186225</v>
+      </c>
+      <c r="F122" t="s">
+        <v>227</v>
+      </c>
+      <c r="G122" t="s">
+        <v>24</v>
+      </c>
+      <c r="H122" t="s">
+        <v>24</v>
+      </c>
+      <c r="M122" t="s">
+        <v>228</v>
+      </c>
+      <c r="P122" s="1">
+        <v>46157.585703935183</v>
+      </c>
+      <c r="Q122" s="4">
+        <v>46160.493105243055</v>
+      </c>
+      <c r="R122" s="4">
+        <v>46170.487253356485</v>
+      </c>
+      <c r="S122">
+        <v>13685.000</v>
+      </c>
+      <c r="T122">
+        <v>13685.000</v>
+      </c>
+      <c r="U122">
+        <v>0</v>
+      </c>
+      <c r="V122">
+        <v>0</v>
+      </c>
+      <c r="W122" s="4">
+        <v>46171.521805011573</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>19</v>
+      </c>
+      <c r="B123" t="s">
+        <v>24</v>
+      </c>
+      <c r="C123" t="s">
+        <v>24</v>
+      </c>
+      <c r="D123" t="s">
+        <v>24</v>
+      </c>
+      <c r="E123">
+        <v>7186224</v>
+      </c>
+      <c r="F123" t="s">
+        <v>229</v>
+      </c>
+      <c r="G123" t="s">
+        <v>24</v>
+      </c>
+      <c r="H123" t="s">
+        <v>24</v>
+      </c>
+      <c r="M123" t="s">
+        <v>228</v>
+      </c>
+      <c r="P123" s="1">
+        <v>46157.585680983793</v>
+      </c>
+      <c r="Q123" s="4">
+        <v>46160.493105243055</v>
+      </c>
+      <c r="R123" s="4">
+        <v>46160.607764236112</v>
+      </c>
+      <c r="S123">
+        <v>8153.000</v>
+      </c>
+      <c r="T123">
+        <v>8153.000</v>
+      </c>
+      <c r="U123">
+        <v>0</v>
+      </c>
+      <c r="V123">
+        <v>0</v>
+      </c>
+      <c r="W123" s="4">
+        <v>46161.606680011573</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>19</v>
+      </c>
+      <c r="B124" t="s">
+        <v>24</v>
+      </c>
+      <c r="C124" t="s">
+        <v>24</v>
+      </c>
+      <c r="D124" t="s">
+        <v>24</v>
+      </c>
+      <c r="E124">
+        <v>7186209</v>
+      </c>
+      <c r="F124" t="s">
+        <v>230</v>
+      </c>
+      <c r="G124" t="s">
+        <v>24</v>
+      </c>
+      <c r="H124" t="s">
+        <v>24</v>
+      </c>
+      <c r="M124" t="s">
+        <v>231</v>
+      </c>
+      <c r="P124" s="1">
+        <v>46157.580364664354</v>
+      </c>
+      <c r="Q124" s="4">
+        <v>46160.367256516205</v>
+      </c>
+      <c r="R124" s="4">
+        <v>46160.444021875002</v>
+      </c>
+      <c r="S124">
+        <v>19189.000</v>
+      </c>
+      <c r="T124">
+        <v>19189.000</v>
+      </c>
+      <c r="U124">
+        <v>0</v>
+      </c>
+      <c r="V124">
+        <v>0</v>
+      </c>
+      <c r="W124" s="4">
+        <v>46161.605472025461</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>19</v>
+      </c>
+      <c r="B125" t="s">
+        <v>24</v>
+      </c>
+      <c r="C125" t="s">
+        <v>24</v>
+      </c>
+      <c r="D125" t="s">
+        <v>24</v>
+      </c>
+      <c r="E125">
+        <v>7185903</v>
+      </c>
+      <c r="F125" t="s">
+        <v>232</v>
+      </c>
+      <c r="G125" t="s">
+        <v>24</v>
+      </c>
+      <c r="H125" t="s">
+        <v>24</v>
+      </c>
+      <c r="M125" t="s">
+        <v>233</v>
+      </c>
+      <c r="P125" s="1">
+        <v>46157.55131412037</v>
+      </c>
+      <c r="Q125" s="4">
+        <v>46160.493105243055</v>
+      </c>
+      <c r="R125" s="4">
+        <v>46160.545683645832</v>
+      </c>
+      <c r="S125">
+        <v>39356.000</v>
+      </c>
+      <c r="T125">
+        <v>39356.000</v>
+      </c>
+      <c r="U125">
+        <v>0</v>
+      </c>
+      <c r="V125">
+        <v>0</v>
+      </c>
+      <c r="W125" s="4">
+        <v>46161.604525312498</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>19</v>
+      </c>
+      <c r="B126" t="s">
+        <v>24</v>
+      </c>
+      <c r="C126" t="s">
+        <v>24</v>
+      </c>
+      <c r="D126" t="s">
+        <v>24</v>
+      </c>
+      <c r="E126">
+        <v>7177836</v>
+      </c>
+      <c r="F126" t="s">
+        <v>234</v>
+      </c>
+      <c r="G126" t="s">
+        <v>24</v>
+      </c>
+      <c r="H126" t="s">
+        <v>24</v>
+      </c>
+      <c r="M126" t="s">
+        <v>235</v>
+      </c>
+      <c r="O126" s="4">
+        <v>46157.416666666664</v>
+      </c>
+      <c r="P126" s="1">
+        <v>46155.705813773151</v>
+      </c>
+      <c r="Q126" s="4">
+        <v>46157.466666666667</v>
+      </c>
+      <c r="R126" s="4">
+        <v>46160.360912615739</v>
+      </c>
+      <c r="S126">
+        <v>17794.000</v>
+      </c>
+      <c r="T126">
+        <v>17794.000</v>
+      </c>
+      <c r="U126">
+        <v>0</v>
+      </c>
+      <c r="V126">
+        <v>0</v>
+      </c>
+      <c r="W126" s="4">
+        <v>46160.503910451385</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>19</v>
+      </c>
+      <c r="B127" t="s">
+        <v>24</v>
+      </c>
+      <c r="C127" t="s">
+        <v>24</v>
+      </c>
+      <c r="D127" t="s">
+        <v>24</v>
+      </c>
+      <c r="E127">
+        <v>7175007</v>
+      </c>
+      <c r="F127" t="s">
+        <v>236</v>
+      </c>
+      <c r="G127" t="s">
+        <v>24</v>
+      </c>
+      <c r="H127" t="s">
+        <v>24</v>
+      </c>
+      <c r="M127" t="s">
+        <v>237</v>
+      </c>
+      <c r="O127" s="4">
+        <v>46157.291666666664</v>
+      </c>
+      <c r="P127" s="1">
+        <v>46155.454049652777</v>
+      </c>
+      <c r="Q127" s="4">
+        <v>46157.35833333333</v>
+      </c>
+      <c r="R127" s="4">
+        <v>46157.601774965275</v>
+      </c>
+      <c r="S127">
+        <v>21375.000</v>
+      </c>
+      <c r="T127">
+        <v>21375.000</v>
+      </c>
+      <c r="U127">
+        <v>0</v>
+      </c>
+      <c r="V127">
+        <v>0</v>
+      </c>
+      <c r="W127" s="4">
+        <v>46157.688587037039</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>19</v>
+      </c>
+      <c r="B128" t="s">
+        <v>24</v>
+      </c>
+      <c r="C128" t="s">
+        <v>24</v>
+      </c>
+      <c r="D128" t="s">
+        <v>24</v>
+      </c>
+      <c r="E128">
+        <v>7167099</v>
+      </c>
+      <c r="F128" t="s">
+        <v>238</v>
+      </c>
+      <c r="G128" t="s">
+        <v>24</v>
+      </c>
+      <c r="H128" t="s">
+        <v>24</v>
+      </c>
+      <c r="M128" t="s">
+        <v>239</v>
+      </c>
+      <c r="P128" s="1">
+        <v>46154.541764120368</v>
+      </c>
+      <c r="R128" s="4">
+        <v>46155.643980821762</v>
+      </c>
+      <c r="S128">
+        <v>11855.000</v>
+      </c>
+      <c r="T128">
+        <v>11855.000</v>
+      </c>
+      <c r="U128">
+        <v>0</v>
+      </c>
+      <c r="V128">
+        <v>0</v>
+      </c>
+      <c r="W128" s="4">
+        <v>46157.304165428242</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>19</v>
+      </c>
+      <c r="B129" t="s">
+        <v>24</v>
+      </c>
+      <c r="C129" t="s">
+        <v>24</v>
+      </c>
+      <c r="D129" t="s">
+        <v>240</v>
+      </c>
+      <c r="E129">
         <v>7108660</v>
       </c>
-      <c r="F109" t="s">
-        <v>214</v>
-      </c>
-      <c r="G109" t="s">
-        <v>23</v>
-      </c>
-      <c r="H109" t="s">
-        <v>215</v>
-      </c>
-      <c r="I109" t="s">
-        <v>215</v>
-      </c>
-      <c r="J109" t="s">
-        <v>216</v>
-      </c>
-      <c r="K109" t="s">
-        <v>217</v>
-      </c>
-      <c r="M109" t="s">
-        <v>23</v>
-      </c>
-      <c r="P109" s="1">
+      <c r="F129" t="s">
+        <v>241</v>
+      </c>
+      <c r="G129" t="s">
+        <v>24</v>
+      </c>
+      <c r="H129" t="s">
+        <v>242</v>
+      </c>
+      <c r="I129" t="s">
+        <v>242</v>
+      </c>
+      <c r="J129" t="s">
+        <v>243</v>
+      </c>
+      <c r="K129" t="s">
+        <v>244</v>
+      </c>
+      <c r="M129" t="s">
+        <v>24</v>
+      </c>
+      <c r="P129" s="1">
         <v>46142.678548877317</v>
       </c>
-      <c r="R109" s="4">
+      <c r="R129" s="4">
         <v>46142.683541168983</v>
       </c>
-      <c r="S109">
+      <c r="S129">
         <v>100.000</v>
       </c>
-      <c r="T109">
+      <c r="T129">
         <v>100.000</v>
       </c>
-      <c r="U109">
-        <v>0</v>
-      </c>
-      <c r="V109">
-        <v>0</v>
-      </c>
-      <c r="W109" s="4">
+      <c r="U129">
+        <v>0</v>
+      </c>
+      <c r="V129">
+        <v>0</v>
+      </c>
+      <c r="W129" s="4">
         <v>46142.68461369213</v>
       </c>
     </row>
-    <row r="110">
-      <c r="S110" s="2">
-        <f ca="1">SUM(S2:S109)</f>
-        <v>0</v>
-      </c>
-      <c r="T110" s="2">
-        <f ca="1">SUM(T2:T109)</f>
-        <v>0</v>
-      </c>
-      <c r="U110" s="2">
-        <f ca="1">SUM(U2:U109)</f>
-        <v>0</v>
-      </c>
-      <c r="V110" s="2">
-        <f ca="1">SUM(V2:V109)</f>
+    <row r="130">
+      <c r="S130" s="2">
+        <f ca="1">SUM(S2:S129)</f>
+        <v>0</v>
+      </c>
+      <c r="T130" s="2">
+        <f ca="1">SUM(T2:T129)</f>
+        <v>0</v>
+      </c>
+      <c r="U130" s="2">
+        <f ca="1">SUM(U2:U129)</f>
+        <v>0</v>
+      </c>
+      <c r="V130" s="2">
+        <f ca="1">SUM(V2:V129)</f>
         <v>0</v>
       </c>
     </row>

--- a/InOrders_latest.xlsx
+++ b/InOrders_latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="251">
   <si>
     <t>Status</t>
   </si>
@@ -89,6 +89,24 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>0101891040</t>
+  </si>
+  <si>
+    <t>Truck 74</t>
+  </si>
+  <si>
+    <t>0101889216</t>
+  </si>
+  <si>
+    <t>Truck 73</t>
+  </si>
+  <si>
+    <t>0101887837</t>
+  </si>
+  <si>
+    <t>Truck 72</t>
   </si>
   <si>
     <t>520065211900100</t>
@@ -1121,7 +1139,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W130"/>
+  <dimension ref="A1:W133"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="13.421875" customWidth="1"/>
@@ -1232,37 +1250,37 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>7382509</v>
+        <v>7386859</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
       </c>
       <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
       <c r="P2" s="1">
-        <v>46198.737117013887</v>
+        <v>46199.698073726853</v>
       </c>
       <c r="S2">
-        <v>1120.000</v>
+        <v>5956.000</v>
       </c>
       <c r="T2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1120.000</v>
+        <v>5956.000</v>
       </c>
       <c r="V2">
         <v>0</v>
       </c>
       <c r="W2" s="4">
-        <v>46198.737558761575</v>
+        <v>46199.698821261576</v>
       </c>
     </row>
     <row r="3">
@@ -1279,37 +1297,37 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>7382508</v>
+        <v>7386838</v>
       </c>
       <c r="F3" t="s">
         <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="P3" s="1">
-        <v>46198.737110150461</v>
+        <v>46199.694861493059</v>
       </c>
       <c r="S3">
-        <v>1971.000</v>
+        <v>8551.000</v>
       </c>
       <c r="T3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1971.000</v>
+        <v>8551.000</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
       <c r="W3" s="4">
-        <v>46198.737558761575</v>
+        <v>46199.695792789353</v>
       </c>
     </row>
     <row r="4">
@@ -1326,37 +1344,37 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>7382456</v>
+        <v>7386771</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
         <v>24</v>
       </c>
       <c r="M4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="P4" s="1">
-        <v>46198.735387152781</v>
+        <v>46199.682600925924</v>
       </c>
       <c r="S4">
-        <v>1540.000</v>
+        <v>9251.000</v>
       </c>
       <c r="T4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1540.000</v>
+        <v>9251.000</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
       <c r="W4" s="4">
-        <v>46198.737558761575</v>
+        <v>46199.68826354167</v>
       </c>
     </row>
     <row r="5">
@@ -1373,13 +1391,13 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>7382452</v>
+        <v>7382509</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
         <v>24</v>
@@ -1388,22 +1406,22 @@
         <v>24</v>
       </c>
       <c r="P5" s="1">
-        <v>46198.732921678238</v>
+        <v>46198.737117013887</v>
       </c>
       <c r="S5">
-        <v>787.000</v>
+        <v>1120.000</v>
       </c>
       <c r="T5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>787.000</v>
+        <v>1120.000</v>
       </c>
       <c r="V5">
         <v>0</v>
       </c>
       <c r="W5" s="4">
-        <v>46198.737558564811</v>
+        <v>46198.737558761575</v>
       </c>
     </row>
     <row r="6">
@@ -1420,14 +1438,14 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>7382451</v>
+        <v>7382508</v>
       </c>
       <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
         <v>32</v>
       </c>
-      <c r="G6" t="s">
-        <v>31</v>
-      </c>
       <c r="H6" t="s">
         <v>24</v>
       </c>
@@ -1435,22 +1453,22 @@
         <v>24</v>
       </c>
       <c r="P6" s="1">
-        <v>46198.732911574072</v>
+        <v>46198.737110150461</v>
       </c>
       <c r="S6">
-        <v>1850.000</v>
+        <v>1971.000</v>
       </c>
       <c r="T6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1850.000</v>
+        <v>1971.000</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6" s="4">
-        <v>46198.737558182867</v>
+        <v>46198.737558761575</v>
       </c>
     </row>
     <row r="7">
@@ -1467,13 +1485,13 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>7382450</v>
+        <v>7382456</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
         <v>24</v>
@@ -1482,22 +1500,22 @@
         <v>24</v>
       </c>
       <c r="P7" s="1">
-        <v>46198.732898379632</v>
+        <v>46198.735387152781</v>
       </c>
       <c r="S7">
-        <v>3021.000</v>
+        <v>1540.000</v>
       </c>
       <c r="T7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>3021.000</v>
+        <v>1540.000</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7" s="4">
-        <v>46198.737557835651</v>
+        <v>46198.737558761575</v>
       </c>
     </row>
     <row r="8">
@@ -1514,13 +1532,13 @@
         <v>24</v>
       </c>
       <c r="E8">
-        <v>7382449</v>
+        <v>7382452</v>
       </c>
       <c r="F8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
         <v>24</v>
@@ -1529,22 +1547,22 @@
         <v>24</v>
       </c>
       <c r="P8" s="1">
-        <v>46198.732894409724</v>
+        <v>46198.732921678238</v>
       </c>
       <c r="S8">
-        <v>1432.000</v>
+        <v>787.000</v>
       </c>
       <c r="T8">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1432.000</v>
+        <v>787.000</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8" s="4">
-        <v>46198.737557488428</v>
+        <v>46198.737558564811</v>
       </c>
     </row>
     <row r="9">
@@ -1561,13 +1579,13 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>7382448</v>
+        <v>7382451</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s">
         <v>24</v>
@@ -1576,22 +1594,22 @@
         <v>24</v>
       </c>
       <c r="P9" s="1">
-        <v>46198.73288984954</v>
+        <v>46198.732911574072</v>
       </c>
       <c r="S9">
-        <v>1038.000</v>
+        <v>1850.000</v>
       </c>
       <c r="T9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>1038.000</v>
+        <v>1850.000</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9" s="4">
-        <v>46198.737557291664</v>
+        <v>46198.737558182867</v>
       </c>
     </row>
     <row r="10">
@@ -1608,13 +1626,13 @@
         <v>24</v>
       </c>
       <c r="E10">
-        <v>7382447</v>
+        <v>7382450</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H10" t="s">
         <v>24</v>
@@ -1623,22 +1641,22 @@
         <v>24</v>
       </c>
       <c r="P10" s="1">
-        <v>46198.732886261576</v>
+        <v>46198.732898379632</v>
       </c>
       <c r="S10">
-        <v>1256.000</v>
+        <v>3021.000</v>
       </c>
       <c r="T10">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>1256.000</v>
+        <v>3021.000</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10" s="4">
-        <v>46198.737556944441</v>
+        <v>46198.737557835651</v>
       </c>
     </row>
     <row r="11">
@@ -1655,14 +1673,14 @@
         <v>24</v>
       </c>
       <c r="E11">
-        <v>7382445</v>
+        <v>7382449</v>
       </c>
       <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" t="s">
         <v>37</v>
       </c>
-      <c r="G11" t="s">
-        <v>31</v>
-      </c>
       <c r="H11" t="s">
         <v>24</v>
       </c>
@@ -1670,22 +1688,22 @@
         <v>24</v>
       </c>
       <c r="P11" s="1">
-        <v>46198.73287994213</v>
+        <v>46198.732894409724</v>
       </c>
       <c r="S11">
-        <v>2105.000</v>
+        <v>1432.000</v>
       </c>
       <c r="T11">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>2105.000</v>
+        <v>1432.000</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11" s="4">
-        <v>46198.737556562497</v>
+        <v>46198.737557488428</v>
       </c>
     </row>
     <row r="12">
@@ -1702,13 +1720,13 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>7382444</v>
+        <v>7382448</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s">
         <v>24</v>
@@ -1717,22 +1735,22 @@
         <v>24</v>
       </c>
       <c r="P12" s="1">
-        <v>46198.732873067129</v>
+        <v>46198.73288984954</v>
       </c>
       <c r="S12">
-        <v>2179.000</v>
+        <v>1038.000</v>
       </c>
       <c r="T12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>2179.000</v>
+        <v>1038.000</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12" s="4">
-        <v>46198.737556400461</v>
+        <v>46198.737557291664</v>
       </c>
     </row>
     <row r="13">
@@ -1749,13 +1767,13 @@
         <v>24</v>
       </c>
       <c r="E13">
-        <v>7382443</v>
+        <v>7382447</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G13" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H13" t="s">
         <v>24</v>
@@ -1764,22 +1782,22 @@
         <v>24</v>
       </c>
       <c r="P13" s="1">
-        <v>46198.732865821759</v>
+        <v>46198.732886261576</v>
       </c>
       <c r="S13">
-        <v>2953.000</v>
+        <v>1256.000</v>
       </c>
       <c r="T13">
         <v>0</v>
       </c>
       <c r="U13">
-        <v>2953.000</v>
+        <v>1256.000</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
       <c r="W13" s="4">
-        <v>46198.737556215281</v>
+        <v>46198.737556944441</v>
       </c>
     </row>
     <row r="14">
@@ -1796,13 +1814,13 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>7382442</v>
+        <v>7382445</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H14" t="s">
         <v>24</v>
@@ -1811,22 +1829,22 @@
         <v>24</v>
       </c>
       <c r="P14" s="1">
-        <v>46198.732861307872</v>
+        <v>46198.73287994213</v>
       </c>
       <c r="S14">
-        <v>1725.000</v>
+        <v>2105.000</v>
       </c>
       <c r="T14">
         <v>0</v>
       </c>
       <c r="U14">
-        <v>1725.000</v>
+        <v>2105.000</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14" s="4">
-        <v>46198.737556215281</v>
+        <v>46198.737556562497</v>
       </c>
     </row>
     <row r="15">
@@ -1843,13 +1861,13 @@
         <v>24</v>
       </c>
       <c r="E15">
-        <v>7382441</v>
+        <v>7382444</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G15" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H15" t="s">
         <v>24</v>
@@ -1858,22 +1876,22 @@
         <v>24</v>
       </c>
       <c r="P15" s="1">
-        <v>46198.732857673611</v>
+        <v>46198.732873067129</v>
       </c>
       <c r="S15">
-        <v>1187.000</v>
+        <v>2179.000</v>
       </c>
       <c r="T15">
         <v>0</v>
       </c>
       <c r="U15">
-        <v>1187.000</v>
+        <v>2179.000</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15" s="4">
-        <v>46198.737556018517</v>
+        <v>46198.737556400461</v>
       </c>
     </row>
     <row r="16">
@@ -1890,13 +1908,13 @@
         <v>24</v>
       </c>
       <c r="E16">
-        <v>7382440</v>
+        <v>7382443</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G16" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H16" t="s">
         <v>24</v>
@@ -1905,22 +1923,22 @@
         <v>24</v>
       </c>
       <c r="P16" s="1">
-        <v>46198.732847916668</v>
+        <v>46198.732865821759</v>
       </c>
       <c r="S16">
-        <v>3785.000</v>
+        <v>2953.000</v>
       </c>
       <c r="T16">
         <v>0</v>
       </c>
       <c r="U16">
-        <v>3785.000</v>
+        <v>2953.000</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16" s="4">
-        <v>46198.737556018517</v>
+        <v>46198.737556215281</v>
       </c>
     </row>
     <row r="17">
@@ -1937,13 +1955,13 @@
         <v>24</v>
       </c>
       <c r="E17">
-        <v>7382439</v>
+        <v>7382442</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H17" t="s">
         <v>24</v>
@@ -1952,22 +1970,22 @@
         <v>24</v>
       </c>
       <c r="P17" s="1">
-        <v>46198.73284394676</v>
+        <v>46198.732861307872</v>
       </c>
       <c r="S17">
-        <v>1275.000</v>
+        <v>1725.000</v>
       </c>
       <c r="T17">
         <v>0</v>
       </c>
       <c r="U17">
-        <v>1275.000</v>
+        <v>1725.000</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17" s="4">
-        <v>46198.737556018517</v>
+        <v>46198.737556215281</v>
       </c>
     </row>
     <row r="18">
@@ -1984,13 +2002,13 @@
         <v>24</v>
       </c>
       <c r="E18">
-        <v>7382438</v>
+        <v>7382441</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H18" t="s">
         <v>24</v>
@@ -1999,22 +2017,22 @@
         <v>24</v>
       </c>
       <c r="P18" s="1">
-        <v>46198.732842511577</v>
+        <v>46198.732857673611</v>
       </c>
       <c r="S18">
-        <v>289.000</v>
+        <v>1187.000</v>
       </c>
       <c r="T18">
         <v>0</v>
       </c>
       <c r="U18">
-        <v>289.000</v>
+        <v>1187.000</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18" s="4">
-        <v>46198.73755528935</v>
+        <v>46198.737556018517</v>
       </c>
     </row>
     <row r="19">
@@ -2031,37 +2049,37 @@
         <v>24</v>
       </c>
       <c r="E19">
-        <v>7380191</v>
+        <v>7382440</v>
       </c>
       <c r="F19" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G19" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H19" t="s">
         <v>24</v>
       </c>
       <c r="M19" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="P19" s="1">
-        <v>46198.481063622683</v>
+        <v>46198.732847916668</v>
       </c>
       <c r="S19">
-        <v>8875.000</v>
+        <v>3785.000</v>
       </c>
       <c r="T19">
         <v>0</v>
       </c>
       <c r="U19">
-        <v>8875.000</v>
+        <v>3785.000</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19" s="4">
-        <v>46198.483989386572</v>
+        <v>46198.737556018517</v>
       </c>
     </row>
     <row r="20">
@@ -2078,37 +2096,37 @@
         <v>24</v>
       </c>
       <c r="E20">
-        <v>7380190</v>
+        <v>7382439</v>
       </c>
       <c r="F20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G20" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H20" t="s">
         <v>24</v>
       </c>
       <c r="M20" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="P20" s="1">
-        <v>46198.481004479167</v>
+        <v>46198.73284394676</v>
       </c>
       <c r="S20">
-        <v>9916.000</v>
+        <v>1275.000</v>
       </c>
       <c r="T20">
         <v>0</v>
       </c>
       <c r="U20">
-        <v>9916.000</v>
+        <v>1275.000</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20" s="4">
-        <v>46198.483988460648</v>
+        <v>46198.737556018517</v>
       </c>
     </row>
     <row r="21">
@@ -2125,92 +2143,89 @@
         <v>24</v>
       </c>
       <c r="E21">
-        <v>7379335</v>
+        <v>7382438</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G21" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H21" t="s">
         <v>24</v>
       </c>
       <c r="M21" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="P21" s="1">
-        <v>46198.391359803238</v>
+        <v>46198.732842511577</v>
       </c>
       <c r="S21">
-        <v>11465.000</v>
+        <v>289.000</v>
       </c>
       <c r="T21">
         <v>0</v>
       </c>
       <c r="U21">
-        <v>11465.000</v>
+        <v>289.000</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21" s="4">
-        <v>46198.392504664349</v>
+        <v>46198.73755528935</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22">
+        <v>7380191</v>
+      </c>
+      <c r="F22" t="s">
         <v>51</v>
       </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22">
-        <v>7374441</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="M22" t="s">
         <v>52</v>
       </c>
-      <c r="G22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" t="s">
-        <v>24</v>
-      </c>
-      <c r="M22" t="s">
-        <v>53</v>
-      </c>
       <c r="P22" s="1">
-        <v>46197.552075150466</v>
-      </c>
-      <c r="R22" s="4">
-        <v>46199.288609340278</v>
+        <v>46198.481063622683</v>
       </c>
       <c r="S22">
-        <v>10194.000</v>
+        <v>8875.000</v>
       </c>
       <c r="T22">
-        <v>839.000</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>9355.000</v>
+        <v>8875.000</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22" s="4">
-        <v>46199.252992164351</v>
+        <v>46198.483989386572</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -2222,51 +2237,42 @@
         <v>24</v>
       </c>
       <c r="E23">
-        <v>7349603</v>
+        <v>7380190</v>
       </c>
       <c r="F23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" t="s">
         <v>54</v>
       </c>
-      <c r="G23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" t="s">
-        <v>55</v>
-      </c>
-      <c r="N23" s="1">
-        <v>46190</v>
-      </c>
       <c r="P23" s="1">
-        <v>46189.643392094906</v>
-      </c>
-      <c r="Q23" s="4">
-        <v>46190.996527777781</v>
-      </c>
-      <c r="R23" s="4">
-        <v>46190.579668171296</v>
+        <v>46198.481004479167</v>
       </c>
       <c r="S23">
-        <v>5965.000</v>
+        <v>9916.000</v>
       </c>
       <c r="T23">
-        <v>5965.000</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>9916.000</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23" s="4">
-        <v>46191.313541932868</v>
+        <v>46198.483988460648</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -2278,51 +2284,42 @@
         <v>24</v>
       </c>
       <c r="E24">
-        <v>7166305</v>
+        <v>7379335</v>
       </c>
       <c r="F24" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" t="s">
         <v>56</v>
       </c>
-      <c r="G24" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M24" t="s">
-        <v>57</v>
-      </c>
-      <c r="N24" s="1">
-        <v>46152</v>
-      </c>
       <c r="P24" s="1">
-        <v>46154.508897418978</v>
-      </c>
-      <c r="Q24" s="4">
-        <v>46162.29583333333</v>
-      </c>
-      <c r="R24" s="4">
-        <v>46154.512428125003</v>
+        <v>46198.391359803238</v>
       </c>
       <c r="S24">
-        <v>100.000</v>
+        <v>11465.000</v>
       </c>
       <c r="T24">
-        <v>98.000</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>2.000</v>
+        <v>11465.000</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24" s="4">
-        <v>46190.318931481481</v>
+        <v>46198.392504664349</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -2334,7 +2331,7 @@
         <v>24</v>
       </c>
       <c r="E25">
-        <v>7374444</v>
+        <v>7374441</v>
       </c>
       <c r="F25" t="s">
         <v>58</v>
@@ -2349,25 +2346,25 @@
         <v>59</v>
       </c>
       <c r="P25" s="1">
-        <v>46197.553791817132</v>
+        <v>46197.552075150466</v>
       </c>
       <c r="R25" s="4">
-        <v>46198.500830902776</v>
+        <v>46202.31123402778</v>
       </c>
       <c r="S25">
-        <v>10410.000</v>
+        <v>10194.000</v>
       </c>
       <c r="T25">
-        <v>10410.000</v>
+        <v>9994.000</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>200.000</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25" s="4">
-        <v>46198.517632291667</v>
+        <v>46199.252992164351</v>
       </c>
     </row>
     <row r="26">
@@ -2384,7 +2381,7 @@
         <v>24</v>
       </c>
       <c r="E26">
-        <v>7373968</v>
+        <v>7349603</v>
       </c>
       <c r="F26" t="s">
         <v>60</v>
@@ -2398,17 +2395,23 @@
       <c r="M26" t="s">
         <v>61</v>
       </c>
+      <c r="N26" s="1">
+        <v>46190</v>
+      </c>
       <c r="P26" s="1">
-        <v>46197.485422534723</v>
+        <v>46189.643392094906</v>
+      </c>
+      <c r="Q26" s="4">
+        <v>46190.996527777781</v>
       </c>
       <c r="R26" s="4">
-        <v>46199.287059374998</v>
+        <v>46190.579668171296</v>
       </c>
       <c r="S26">
-        <v>18575.000</v>
+        <v>5965.000</v>
       </c>
       <c r="T26">
-        <v>18575.000</v>
+        <v>5965.000</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -2417,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="W26" s="4">
-        <v>46199.324616701386</v>
+        <v>46191.313541932868</v>
       </c>
     </row>
     <row r="27">
@@ -2434,7 +2437,7 @@
         <v>24</v>
       </c>
       <c r="E27">
-        <v>7369152</v>
+        <v>7166305</v>
       </c>
       <c r="F27" t="s">
         <v>62</v>
@@ -2448,26 +2451,32 @@
       <c r="M27" t="s">
         <v>63</v>
       </c>
+      <c r="N27" s="1">
+        <v>46152</v>
+      </c>
       <c r="P27" s="1">
-        <v>46196.459848344908</v>
+        <v>46154.508897418978</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>46162.29583333333</v>
       </c>
       <c r="R27" s="4">
-        <v>46197.493816087961</v>
+        <v>46154.512428125003</v>
       </c>
       <c r="S27">
-        <v>300.000</v>
+        <v>100.000</v>
       </c>
       <c r="T27">
-        <v>300.000</v>
+        <v>98.000</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.000</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27" s="4">
-        <v>46197.550397141204</v>
+        <v>46190.318931481481</v>
       </c>
     </row>
     <row r="28">
@@ -2484,7 +2493,7 @@
         <v>24</v>
       </c>
       <c r="E28">
-        <v>7369151</v>
+        <v>7374444</v>
       </c>
       <c r="F28" t="s">
         <v>64</v>
@@ -2499,16 +2508,16 @@
         <v>65</v>
       </c>
       <c r="P28" s="1">
-        <v>46196.459830243053</v>
+        <v>46197.553791817132</v>
       </c>
       <c r="R28" s="4">
-        <v>46197.531721678242</v>
+        <v>46198.500830902776</v>
       </c>
       <c r="S28">
-        <v>3638.000</v>
+        <v>10410.000</v>
       </c>
       <c r="T28">
-        <v>3638.000</v>
+        <v>10410.000</v>
       </c>
       <c r="U28">
         <v>0</v>
@@ -2517,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="W28" s="4">
-        <v>46197.550396956016</v>
+        <v>46198.517632291667</v>
       </c>
     </row>
     <row r="29">
@@ -2534,7 +2543,7 @@
         <v>24</v>
       </c>
       <c r="E29">
-        <v>7368806</v>
+        <v>7373968</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -2549,16 +2558,16 @@
         <v>67</v>
       </c>
       <c r="P29" s="1">
-        <v>46196.377559722219</v>
+        <v>46197.485422534723</v>
       </c>
       <c r="R29" s="4">
-        <v>46197.497936342595</v>
+        <v>46199.287059374998</v>
       </c>
       <c r="S29">
-        <v>5755.000</v>
+        <v>18575.000</v>
       </c>
       <c r="T29">
-        <v>5755.000</v>
+        <v>18575.000</v>
       </c>
       <c r="U29">
         <v>0</v>
@@ -2567,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="W29" s="4">
-        <v>46197.550396064813</v>
+        <v>46199.324616701386</v>
       </c>
     </row>
     <row r="30">
@@ -2584,7 +2593,7 @@
         <v>24</v>
       </c>
       <c r="E30">
-        <v>7362625</v>
+        <v>7369152</v>
       </c>
       <c r="F30" t="s">
         <v>68</v>
@@ -2599,16 +2608,16 @@
         <v>69</v>
       </c>
       <c r="P30" s="1">
-        <v>46195.438085185182</v>
+        <v>46196.459848344908</v>
       </c>
       <c r="R30" s="4">
-        <v>46196.523870486111</v>
+        <v>46197.493816087961</v>
       </c>
       <c r="S30">
-        <v>6200.000</v>
+        <v>300.000</v>
       </c>
       <c r="T30">
-        <v>6200.000</v>
+        <v>300.000</v>
       </c>
       <c r="U30">
         <v>0</v>
@@ -2617,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="W30" s="4">
-        <v>46197.278575775461</v>
+        <v>46197.550397141204</v>
       </c>
     </row>
     <row r="31">
@@ -2634,7 +2643,7 @@
         <v>24</v>
       </c>
       <c r="E31">
-        <v>7362236</v>
+        <v>7369151</v>
       </c>
       <c r="F31" t="s">
         <v>70</v>
@@ -2649,16 +2658,16 @@
         <v>71</v>
       </c>
       <c r="P31" s="1">
-        <v>46195.402819178242</v>
+        <v>46196.459830243053</v>
       </c>
       <c r="R31" s="4">
-        <v>46196.601059108798</v>
+        <v>46197.531721678242</v>
       </c>
       <c r="S31">
-        <v>6305.000</v>
+        <v>3638.000</v>
       </c>
       <c r="T31">
-        <v>6305.000</v>
+        <v>3638.000</v>
       </c>
       <c r="U31">
         <v>0</v>
@@ -2667,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="W31" s="4">
-        <v>46197.278671446758</v>
+        <v>46197.550396956016</v>
       </c>
     </row>
     <row r="32">
@@ -2684,7 +2693,7 @@
         <v>24</v>
       </c>
       <c r="E32">
-        <v>7362235</v>
+        <v>7368806</v>
       </c>
       <c r="F32" t="s">
         <v>72</v>
@@ -2699,16 +2708,16 @@
         <v>73</v>
       </c>
       <c r="P32" s="1">
-        <v>46195.402748692133</v>
+        <v>46196.377559722219</v>
       </c>
       <c r="R32" s="4">
-        <v>46198.313491319444</v>
+        <v>46197.497936342595</v>
       </c>
       <c r="S32">
-        <v>10614.000</v>
+        <v>5755.000</v>
       </c>
       <c r="T32">
-        <v>10614.000</v>
+        <v>5755.000</v>
       </c>
       <c r="U32">
         <v>0</v>
@@ -2717,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="W32" s="4">
-        <v>46198.314641435187</v>
+        <v>46197.550396064813</v>
       </c>
     </row>
     <row r="33">
@@ -2734,7 +2743,7 @@
         <v>24</v>
       </c>
       <c r="E33">
-        <v>7358767</v>
+        <v>7362625</v>
       </c>
       <c r="F33" t="s">
         <v>74</v>
@@ -2749,16 +2758,16 @@
         <v>75</v>
       </c>
       <c r="P33" s="1">
-        <v>46192.659844444446</v>
+        <v>46195.438085185182</v>
       </c>
       <c r="R33" s="4">
-        <v>46197.3828096875</v>
+        <v>46196.523870486111</v>
       </c>
       <c r="S33">
-        <v>10207.000</v>
+        <v>6200.000</v>
       </c>
       <c r="T33">
-        <v>10207.000</v>
+        <v>6200.000</v>
       </c>
       <c r="U33">
         <v>0</v>
@@ -2767,7 +2776,7 @@
         <v>0</v>
       </c>
       <c r="W33" s="4">
-        <v>46197.391247916668</v>
+        <v>46197.278575775461</v>
       </c>
     </row>
     <row r="34">
@@ -2784,7 +2793,7 @@
         <v>24</v>
       </c>
       <c r="E34">
-        <v>7358766</v>
+        <v>7362236</v>
       </c>
       <c r="F34" t="s">
         <v>76</v>
@@ -2799,16 +2808,16 @@
         <v>77</v>
       </c>
       <c r="P34" s="1">
-        <v>46192.659814814811</v>
+        <v>46195.402819178242</v>
       </c>
       <c r="R34" s="4">
-        <v>46197.366926122682</v>
+        <v>46196.601059108798</v>
       </c>
       <c r="S34">
-        <v>8661.000</v>
+        <v>6305.000</v>
       </c>
       <c r="T34">
-        <v>8661.000</v>
+        <v>6305.000</v>
       </c>
       <c r="U34">
         <v>0</v>
@@ -2817,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="W34" s="4">
-        <v>46197.391093518519</v>
+        <v>46197.278671446758</v>
       </c>
     </row>
     <row r="35">
@@ -2834,7 +2843,7 @@
         <v>24</v>
       </c>
       <c r="E35">
-        <v>7355924</v>
+        <v>7362235</v>
       </c>
       <c r="F35" t="s">
         <v>78</v>
@@ -2845,20 +2854,20 @@
       <c r="H35" t="s">
         <v>24</v>
       </c>
-      <c r="M35" s="5" t="s">
+      <c r="M35" t="s">
         <v>79</v>
       </c>
       <c r="P35" s="1">
-        <v>46191.548452546296</v>
+        <v>46195.402748692133</v>
       </c>
       <c r="R35" s="4">
-        <v>46195.391070254627</v>
+        <v>46198.313491319444</v>
       </c>
       <c r="S35">
-        <v>8044.000</v>
+        <v>10614.000</v>
       </c>
       <c r="T35">
-        <v>8044.000</v>
+        <v>10614.000</v>
       </c>
       <c r="U35">
         <v>0</v>
@@ -2867,7 +2876,7 @@
         <v>0</v>
       </c>
       <c r="W35" s="4">
-        <v>46196.389409641204</v>
+        <v>46198.314641435187</v>
       </c>
     </row>
     <row r="36">
@@ -2884,7 +2893,7 @@
         <v>24</v>
       </c>
       <c r="E36">
-        <v>7355667</v>
+        <v>7358767</v>
       </c>
       <c r="F36" t="s">
         <v>80</v>
@@ -2899,16 +2908,16 @@
         <v>81</v>
       </c>
       <c r="P36" s="1">
-        <v>46191.4713122338</v>
+        <v>46192.659844444446</v>
       </c>
       <c r="R36" s="4">
-        <v>46198.319310104169</v>
+        <v>46197.3828096875</v>
       </c>
       <c r="S36">
-        <v>15383.000</v>
+        <v>10207.000</v>
       </c>
       <c r="T36">
-        <v>15383.000</v>
+        <v>10207.000</v>
       </c>
       <c r="U36">
         <v>0</v>
@@ -2917,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="W36" s="4">
-        <v>46198.319958796295</v>
+        <v>46197.391247916668</v>
       </c>
     </row>
     <row r="37">
@@ -2934,7 +2943,7 @@
         <v>24</v>
       </c>
       <c r="E37">
-        <v>7353363</v>
+        <v>7358766</v>
       </c>
       <c r="F37" t="s">
         <v>82</v>
@@ -2949,16 +2958,16 @@
         <v>83</v>
       </c>
       <c r="P37" s="1">
-        <v>46190.666969988422</v>
+        <v>46192.659814814811</v>
       </c>
       <c r="R37" s="4">
-        <v>46195.511062997684</v>
+        <v>46197.366926122682</v>
       </c>
       <c r="S37">
-        <v>472.000</v>
+        <v>8661.000</v>
       </c>
       <c r="T37">
-        <v>472.000</v>
+        <v>8661.000</v>
       </c>
       <c r="U37">
         <v>0</v>
@@ -2967,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="W37" s="4">
-        <v>46196.389409641204</v>
+        <v>46197.391093518519</v>
       </c>
     </row>
     <row r="38">
@@ -2984,7 +2993,7 @@
         <v>24</v>
       </c>
       <c r="E38">
-        <v>7353362</v>
+        <v>7355924</v>
       </c>
       <c r="F38" t="s">
         <v>84</v>
@@ -2995,20 +3004,20 @@
       <c r="H38" t="s">
         <v>24</v>
       </c>
-      <c r="M38" t="s">
-        <v>83</v>
+      <c r="M38" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="P38" s="1">
-        <v>46190.666969444443</v>
+        <v>46191.548452546296</v>
       </c>
       <c r="R38" s="4">
-        <v>46195.521521527779</v>
+        <v>46195.391070254627</v>
       </c>
       <c r="S38">
-        <v>612.000</v>
+        <v>8044.000</v>
       </c>
       <c r="T38">
-        <v>612.000</v>
+        <v>8044.000</v>
       </c>
       <c r="U38">
         <v>0</v>
@@ -3034,10 +3043,10 @@
         <v>24</v>
       </c>
       <c r="E39">
-        <v>7353361</v>
+        <v>7355667</v>
       </c>
       <c r="F39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G39" t="s">
         <v>24</v>
@@ -3046,19 +3055,19 @@
         <v>24</v>
       </c>
       <c r="M39" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="P39" s="1">
-        <v>46190.666967094905</v>
+        <v>46191.4713122338</v>
       </c>
       <c r="R39" s="4">
-        <v>46195.535836192132</v>
+        <v>46198.319310104169</v>
       </c>
       <c r="S39">
-        <v>2383.000</v>
+        <v>15383.000</v>
       </c>
       <c r="T39">
-        <v>2383.000</v>
+        <v>15383.000</v>
       </c>
       <c r="U39">
         <v>0</v>
@@ -3067,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="W39" s="4">
-        <v>46196.389409641204</v>
+        <v>46198.319958796295</v>
       </c>
     </row>
     <row r="40">
@@ -3084,10 +3093,10 @@
         <v>24</v>
       </c>
       <c r="E40">
-        <v>7353360</v>
+        <v>7353363</v>
       </c>
       <c r="F40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s">
         <v>24</v>
@@ -3096,19 +3105,19 @@
         <v>24</v>
       </c>
       <c r="M40" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P40" s="1">
-        <v>46190.666964201388</v>
+        <v>46190.666969988422</v>
       </c>
       <c r="R40" s="4">
-        <v>46195.523977164354</v>
+        <v>46195.511062997684</v>
       </c>
       <c r="S40">
-        <v>2262.000</v>
+        <v>472.000</v>
       </c>
       <c r="T40">
-        <v>2262.000</v>
+        <v>472.000</v>
       </c>
       <c r="U40">
         <v>0</v>
@@ -3134,10 +3143,10 @@
         <v>24</v>
       </c>
       <c r="E41">
-        <v>7353359</v>
+        <v>7353362</v>
       </c>
       <c r="F41" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s">
         <v>24</v>
@@ -3146,19 +3155,19 @@
         <v>24</v>
       </c>
       <c r="M41" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P41" s="1">
-        <v>46190.66696145833</v>
+        <v>46190.666969444443</v>
       </c>
       <c r="R41" s="4">
-        <v>46195.537172372686</v>
+        <v>46195.521521527779</v>
       </c>
       <c r="S41">
-        <v>3982.000</v>
+        <v>612.000</v>
       </c>
       <c r="T41">
-        <v>3982.000</v>
+        <v>612.000</v>
       </c>
       <c r="U41">
         <v>0</v>
@@ -3167,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="W41" s="4">
-        <v>46196.389409456016</v>
+        <v>46196.389409641204</v>
       </c>
     </row>
     <row r="42">
@@ -3184,10 +3193,10 @@
         <v>24</v>
       </c>
       <c r="E42">
-        <v>7353358</v>
+        <v>7353361</v>
       </c>
       <c r="F42" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G42" t="s">
         <v>24</v>
@@ -3196,19 +3205,19 @@
         <v>24</v>
       </c>
       <c r="M42" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P42" s="1">
-        <v>46190.666954432869</v>
+        <v>46190.666967094905</v>
       </c>
       <c r="R42" s="4">
-        <v>46195.532108368054</v>
+        <v>46195.535836192132</v>
       </c>
       <c r="S42">
-        <v>1113.000</v>
+        <v>2383.000</v>
       </c>
       <c r="T42">
-        <v>1113.000</v>
+        <v>2383.000</v>
       </c>
       <c r="U42">
         <v>0</v>
@@ -3217,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="W42" s="4">
-        <v>46196.389409456016</v>
+        <v>46196.389409641204</v>
       </c>
     </row>
     <row r="43">
@@ -3234,31 +3243,31 @@
         <v>24</v>
       </c>
       <c r="E43">
-        <v>7353357</v>
+        <v>7353360</v>
       </c>
       <c r="F43" t="s">
+        <v>92</v>
+      </c>
+      <c r="G43" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" t="s">
+        <v>24</v>
+      </c>
+      <c r="M43" t="s">
         <v>89</v>
       </c>
-      <c r="G43" t="s">
-        <v>24</v>
-      </c>
-      <c r="H43" t="s">
-        <v>24</v>
-      </c>
-      <c r="M43" t="s">
-        <v>83</v>
-      </c>
       <c r="P43" s="1">
-        <v>46190.666949340281</v>
+        <v>46190.666964201388</v>
       </c>
       <c r="R43" s="4">
-        <v>46195.517305439818</v>
+        <v>46195.523977164354</v>
       </c>
       <c r="S43">
-        <v>447.000</v>
+        <v>2262.000</v>
       </c>
       <c r="T43">
-        <v>447.000</v>
+        <v>2262.000</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -3267,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="W43" s="4">
-        <v>46196.389409456016</v>
+        <v>46196.389409641204</v>
       </c>
     </row>
     <row r="44">
@@ -3284,10 +3293,10 @@
         <v>24</v>
       </c>
       <c r="E44">
-        <v>7353356</v>
+        <v>7353359</v>
       </c>
       <c r="F44" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s">
         <v>24</v>
@@ -3296,19 +3305,19 @@
         <v>24</v>
       </c>
       <c r="M44" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P44" s="1">
-        <v>46190.66694664352</v>
+        <v>46190.66696145833</v>
       </c>
       <c r="R44" s="4">
-        <v>46195.528761724534</v>
+        <v>46195.537172372686</v>
       </c>
       <c r="S44">
-        <v>284.000</v>
+        <v>3982.000</v>
       </c>
       <c r="T44">
-        <v>284.000</v>
+        <v>3982.000</v>
       </c>
       <c r="U44">
         <v>0</v>
@@ -3334,10 +3343,10 @@
         <v>24</v>
       </c>
       <c r="E45">
-        <v>7353355</v>
+        <v>7353358</v>
       </c>
       <c r="F45" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G45" t="s">
         <v>24</v>
@@ -3346,19 +3355,19 @@
         <v>24</v>
       </c>
       <c r="M45" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P45" s="1">
-        <v>46190.666944293982</v>
+        <v>46190.666954432869</v>
       </c>
       <c r="R45" s="4">
-        <v>46195.528790659722</v>
+        <v>46195.532108368054</v>
       </c>
       <c r="S45">
-        <v>304.000</v>
+        <v>1113.000</v>
       </c>
       <c r="T45">
-        <v>304.000</v>
+        <v>1113.000</v>
       </c>
       <c r="U45">
         <v>0</v>
@@ -3384,10 +3393,10 @@
         <v>24</v>
       </c>
       <c r="E46">
-        <v>7353354</v>
+        <v>7353357</v>
       </c>
       <c r="F46" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G46" t="s">
         <v>24</v>
@@ -3396,19 +3405,19 @@
         <v>24</v>
       </c>
       <c r="M46" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P46" s="1">
-        <v>46190.666940659721</v>
+        <v>46190.666949340281</v>
       </c>
       <c r="R46" s="4">
-        <v>46195.536209409722</v>
+        <v>46195.517305439818</v>
       </c>
       <c r="S46">
-        <v>1251.000</v>
+        <v>447.000</v>
       </c>
       <c r="T46">
-        <v>1251.000</v>
+        <v>447.000</v>
       </c>
       <c r="U46">
         <v>0</v>
@@ -3434,10 +3443,10 @@
         <v>24</v>
       </c>
       <c r="E47">
-        <v>7353353</v>
+        <v>7353356</v>
       </c>
       <c r="F47" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G47" t="s">
         <v>24</v>
@@ -3446,19 +3455,19 @@
         <v>24</v>
       </c>
       <c r="M47" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P47" s="1">
-        <v>46190.666939583331</v>
+        <v>46190.66694664352</v>
       </c>
       <c r="R47" s="4">
-        <v>46195.537300034724</v>
+        <v>46195.528761724534</v>
       </c>
       <c r="S47">
-        <v>1257.000</v>
+        <v>284.000</v>
       </c>
       <c r="T47">
-        <v>1257.000</v>
+        <v>284.000</v>
       </c>
       <c r="U47">
         <v>0</v>
@@ -3484,10 +3493,10 @@
         <v>24</v>
       </c>
       <c r="E48">
-        <v>7353352</v>
+        <v>7353355</v>
       </c>
       <c r="F48" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -3496,19 +3505,19 @@
         <v>24</v>
       </c>
       <c r="M48" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P48" s="1">
-        <v>46190.66693417824</v>
+        <v>46190.666944293982</v>
       </c>
       <c r="R48" s="4">
-        <v>46195.537318483795</v>
+        <v>46195.528790659722</v>
       </c>
       <c r="S48">
-        <v>7113.000</v>
+        <v>304.000</v>
       </c>
       <c r="T48">
-        <v>7113.000</v>
+        <v>304.000</v>
       </c>
       <c r="U48">
         <v>0</v>
@@ -3517,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="W48" s="4">
-        <v>46196.388202118054</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="49">
@@ -3534,10 +3543,10 @@
         <v>24</v>
       </c>
       <c r="E49">
-        <v>7353351</v>
+        <v>7353354</v>
       </c>
       <c r="F49" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -3546,19 +3555,19 @@
         <v>24</v>
       </c>
       <c r="M49" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P49" s="1">
-        <v>46190.666933101849</v>
+        <v>46190.666940659721</v>
       </c>
       <c r="R49" s="4">
-        <v>46195.523942245367</v>
+        <v>46195.536209409722</v>
       </c>
       <c r="S49">
-        <v>1295.000</v>
+        <v>1251.000</v>
       </c>
       <c r="T49">
-        <v>1295.000</v>
+        <v>1251.000</v>
       </c>
       <c r="U49">
         <v>0</v>
@@ -3567,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="W49" s="4">
-        <v>46196.389409293981</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="50">
@@ -3584,10 +3593,10 @@
         <v>24</v>
       </c>
       <c r="E50">
-        <v>7353350</v>
+        <v>7353353</v>
       </c>
       <c r="F50" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G50" t="s">
         <v>24</v>
@@ -3596,19 +3605,19 @@
         <v>24</v>
       </c>
       <c r="M50" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P50" s="1">
-        <v>46190.666932719905</v>
+        <v>46190.666939583331</v>
       </c>
       <c r="R50" s="4">
-        <v>46195.536177581016</v>
+        <v>46195.537300034724</v>
       </c>
       <c r="S50">
-        <v>72.000</v>
+        <v>1257.000</v>
       </c>
       <c r="T50">
-        <v>72.000</v>
+        <v>1257.000</v>
       </c>
       <c r="U50">
         <v>0</v>
@@ -3617,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="W50" s="4">
-        <v>46196.389409293981</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="51">
@@ -3634,10 +3643,10 @@
         <v>24</v>
       </c>
       <c r="E51">
-        <v>7353349</v>
+        <v>7353352</v>
       </c>
       <c r="F51" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G51" t="s">
         <v>24</v>
@@ -3646,19 +3655,19 @@
         <v>24</v>
       </c>
       <c r="M51" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P51" s="1">
-        <v>46190.666930555555</v>
+        <v>46190.66693417824</v>
       </c>
       <c r="R51" s="4">
-        <v>46195.536192395833</v>
+        <v>46195.537318483795</v>
       </c>
       <c r="S51">
-        <v>101.000</v>
+        <v>7113.000</v>
       </c>
       <c r="T51">
-        <v>101.000</v>
+        <v>7113.000</v>
       </c>
       <c r="U51">
         <v>0</v>
@@ -3667,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="W51" s="4">
-        <v>46196.389409293981</v>
+        <v>46196.388202118054</v>
       </c>
     </row>
     <row r="52">
@@ -3684,10 +3693,10 @@
         <v>24</v>
       </c>
       <c r="E52">
-        <v>7353348</v>
+        <v>7353351</v>
       </c>
       <c r="F52" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G52" t="s">
         <v>24</v>
@@ -3696,19 +3705,19 @@
         <v>24</v>
       </c>
       <c r="M52" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P52" s="1">
-        <v>46190.666919525465</v>
+        <v>46190.666933101849</v>
       </c>
       <c r="R52" s="4">
-        <v>46195.534000462962</v>
+        <v>46195.523942245367</v>
       </c>
       <c r="S52">
-        <v>1620.000</v>
+        <v>1295.000</v>
       </c>
       <c r="T52">
-        <v>1620.000</v>
+        <v>1295.000</v>
       </c>
       <c r="U52">
         <v>0</v>
@@ -3734,10 +3743,10 @@
         <v>24</v>
       </c>
       <c r="E53">
-        <v>7353347</v>
+        <v>7353350</v>
       </c>
       <c r="F53" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G53" t="s">
         <v>24</v>
@@ -3746,19 +3755,19 @@
         <v>24</v>
       </c>
       <c r="M53" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P53" s="1">
-        <v>46190.666916979164</v>
+        <v>46190.666932719905</v>
       </c>
       <c r="R53" s="4">
-        <v>46195.527235069443</v>
+        <v>46195.536177581016</v>
       </c>
       <c r="S53">
-        <v>600.000</v>
+        <v>72.000</v>
       </c>
       <c r="T53">
-        <v>600.000</v>
+        <v>72.000</v>
       </c>
       <c r="U53">
         <v>0</v>
@@ -3784,10 +3793,10 @@
         <v>24</v>
       </c>
       <c r="E54">
-        <v>7353346</v>
+        <v>7353349</v>
       </c>
       <c r="F54" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G54" t="s">
         <v>24</v>
@@ -3796,19 +3805,19 @@
         <v>24</v>
       </c>
       <c r="M54" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P54" s="1">
-        <v>46190.66691284722</v>
+        <v>46190.666930555555</v>
       </c>
       <c r="R54" s="4">
-        <v>46195.522001273152</v>
+        <v>46195.536192395833</v>
       </c>
       <c r="S54">
-        <v>1338.000</v>
+        <v>101.000</v>
       </c>
       <c r="T54">
-        <v>1338.000</v>
+        <v>101.000</v>
       </c>
       <c r="U54">
         <v>0</v>
@@ -3834,10 +3843,10 @@
         <v>24</v>
       </c>
       <c r="E55">
-        <v>7353345</v>
+        <v>7353348</v>
       </c>
       <c r="F55" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G55" t="s">
         <v>24</v>
@@ -3846,19 +3855,19 @@
         <v>24</v>
       </c>
       <c r="M55" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P55" s="1">
-        <v>46190.666911921297</v>
+        <v>46190.666919525465</v>
       </c>
       <c r="R55" s="4">
-        <v>46195.532152511572</v>
+        <v>46195.534000462962</v>
       </c>
       <c r="S55">
-        <v>968.000</v>
+        <v>1620.000</v>
       </c>
       <c r="T55">
-        <v>968.000</v>
+        <v>1620.000</v>
       </c>
       <c r="U55">
         <v>0</v>
@@ -3884,10 +3893,10 @@
         <v>24</v>
       </c>
       <c r="E56">
-        <v>7353344</v>
+        <v>7353347</v>
       </c>
       <c r="F56" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G56" t="s">
         <v>24</v>
@@ -3896,19 +3905,19 @@
         <v>24</v>
       </c>
       <c r="M56" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P56" s="1">
-        <v>46190.666910844906</v>
+        <v>46190.666916979164</v>
       </c>
       <c r="R56" s="4">
-        <v>46195.537341087962</v>
+        <v>46195.527235069443</v>
       </c>
       <c r="S56">
-        <v>917.000</v>
+        <v>600.000</v>
       </c>
       <c r="T56">
-        <v>917.000</v>
+        <v>600.000</v>
       </c>
       <c r="U56">
         <v>0</v>
@@ -3934,10 +3943,10 @@
         <v>24</v>
       </c>
       <c r="E57">
-        <v>7353343</v>
+        <v>7353346</v>
       </c>
       <c r="F57" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -3946,19 +3955,19 @@
         <v>24</v>
       </c>
       <c r="M57" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P57" s="1">
-        <v>46190.666907604165</v>
+        <v>46190.66691284722</v>
       </c>
       <c r="R57" s="4">
-        <v>46195.526307291664</v>
+        <v>46195.522001273152</v>
       </c>
       <c r="S57">
-        <v>3514.000</v>
+        <v>1338.000</v>
       </c>
       <c r="T57">
-        <v>3514.000</v>
+        <v>1338.000</v>
       </c>
       <c r="U57">
         <v>0</v>
@@ -3967,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="W57" s="4">
-        <v>46196.389409108793</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="58">
@@ -3984,10 +3993,10 @@
         <v>24</v>
       </c>
       <c r="E58">
-        <v>7353342</v>
+        <v>7353345</v>
       </c>
       <c r="F58" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G58" t="s">
         <v>24</v>
@@ -3996,19 +4005,19 @@
         <v>24</v>
       </c>
       <c r="M58" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P58" s="1">
-        <v>46190.666906134262</v>
+        <v>46190.666911921297</v>
       </c>
       <c r="R58" s="4">
-        <v>46195.518147222225</v>
+        <v>46195.532152511572</v>
       </c>
       <c r="S58">
-        <v>646.000</v>
+        <v>968.000</v>
       </c>
       <c r="T58">
-        <v>646.000</v>
+        <v>968.000</v>
       </c>
       <c r="U58">
         <v>0</v>
@@ -4017,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="W58" s="4">
-        <v>46196.389409108793</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="59">
@@ -4034,10 +4043,10 @@
         <v>24</v>
       </c>
       <c r="E59">
-        <v>7353341</v>
+        <v>7353344</v>
       </c>
       <c r="F59" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G59" t="s">
         <v>24</v>
@@ -4046,19 +4055,19 @@
         <v>24</v>
       </c>
       <c r="M59" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P59" s="1">
-        <v>46190.666903969905</v>
+        <v>46190.666910844906</v>
       </c>
       <c r="R59" s="4">
-        <v>46195.535854247682</v>
+        <v>46195.537341087962</v>
       </c>
       <c r="S59">
-        <v>2209.000</v>
+        <v>917.000</v>
       </c>
       <c r="T59">
-        <v>2209.000</v>
+        <v>917.000</v>
       </c>
       <c r="U59">
         <v>0</v>
@@ -4067,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="W59" s="4">
-        <v>46196.389409108793</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="60">
@@ -4084,10 +4093,10 @@
         <v>24</v>
       </c>
       <c r="E60">
-        <v>7353340</v>
+        <v>7353343</v>
       </c>
       <c r="F60" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G60" t="s">
         <v>24</v>
@@ -4096,19 +4105,19 @@
         <v>24</v>
       </c>
       <c r="M60" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P60" s="1">
-        <v>46190.666894560185</v>
+        <v>46190.666907604165</v>
       </c>
       <c r="R60" s="4">
-        <v>46195.524072835651</v>
+        <v>46195.526307291664</v>
       </c>
       <c r="S60">
-        <v>4385.000</v>
+        <v>3514.000</v>
       </c>
       <c r="T60">
-        <v>4385.000</v>
+        <v>3514.000</v>
       </c>
       <c r="U60">
         <v>0</v>
@@ -4134,10 +4143,10 @@
         <v>24</v>
       </c>
       <c r="E61">
-        <v>7353339</v>
+        <v>7353342</v>
       </c>
       <c r="F61" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -4146,19 +4155,19 @@
         <v>24</v>
       </c>
       <c r="M61" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P61" s="1">
-        <v>46190.666882442129</v>
+        <v>46190.666906134262</v>
       </c>
       <c r="R61" s="4">
-        <v>46195.535098726854</v>
+        <v>46195.518147222225</v>
       </c>
       <c r="S61">
-        <v>2886.000</v>
+        <v>646.000</v>
       </c>
       <c r="T61">
-        <v>2886.000</v>
+        <v>646.000</v>
       </c>
       <c r="U61">
         <v>0</v>
@@ -4167,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="W61" s="4">
-        <v>46196.389408912037</v>
+        <v>46196.389409108793</v>
       </c>
     </row>
     <row r="62">
@@ -4184,10 +4193,10 @@
         <v>24</v>
       </c>
       <c r="E62">
-        <v>7353338</v>
+        <v>7353341</v>
       </c>
       <c r="F62" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -4196,19 +4205,19 @@
         <v>24</v>
       </c>
       <c r="M62" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P62" s="1">
-        <v>46190.666870520836</v>
+        <v>46190.666903969905</v>
       </c>
       <c r="R62" s="4">
-        <v>46195.537258252312</v>
+        <v>46195.535854247682</v>
       </c>
       <c r="S62">
-        <v>2648.000</v>
+        <v>2209.000</v>
       </c>
       <c r="T62">
-        <v>2648.000</v>
+        <v>2209.000</v>
       </c>
       <c r="U62">
         <v>0</v>
@@ -4217,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="W62" s="4">
-        <v>46196.389408912037</v>
+        <v>46196.389409108793</v>
       </c>
     </row>
     <row r="63">
@@ -4234,10 +4243,10 @@
         <v>24</v>
       </c>
       <c r="E63">
-        <v>7353112</v>
+        <v>7353340</v>
       </c>
       <c r="F63" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G63" t="s">
         <v>24</v>
@@ -4245,20 +4254,20 @@
       <c r="H63" t="s">
         <v>24</v>
       </c>
-      <c r="M63" s="5" t="s">
-        <v>110</v>
+      <c r="M63" t="s">
+        <v>89</v>
       </c>
       <c r="P63" s="1">
-        <v>46190.633443321756</v>
+        <v>46190.666894560185</v>
       </c>
       <c r="R63" s="4">
-        <v>46195.593899918982</v>
+        <v>46195.524072835651</v>
       </c>
       <c r="S63">
-        <v>15034.000</v>
+        <v>4385.000</v>
       </c>
       <c r="T63">
-        <v>15034.000</v>
+        <v>4385.000</v>
       </c>
       <c r="U63">
         <v>0</v>
@@ -4267,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="W63" s="4">
-        <v>46196.389407835646</v>
+        <v>46196.389409108793</v>
       </c>
     </row>
     <row r="64">
@@ -4284,10 +4293,10 @@
         <v>24</v>
       </c>
       <c r="E64">
-        <v>7352722</v>
+        <v>7353339</v>
       </c>
       <c r="F64" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -4296,19 +4305,19 @@
         <v>24</v>
       </c>
       <c r="M64" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="P64" s="1">
-        <v>46190.517798842593</v>
+        <v>46190.666882442129</v>
       </c>
       <c r="R64" s="4">
-        <v>46198.316219409724</v>
+        <v>46195.535098726854</v>
       </c>
       <c r="S64">
-        <v>13727.000</v>
+        <v>2886.000</v>
       </c>
       <c r="T64">
-        <v>13727.000</v>
+        <v>2886.000</v>
       </c>
       <c r="U64">
         <v>0</v>
@@ -4317,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="W64" s="4">
-        <v>46198.317383530091</v>
+        <v>46196.389408912037</v>
       </c>
     </row>
     <row r="65">
@@ -4334,10 +4343,10 @@
         <v>24</v>
       </c>
       <c r="E65">
-        <v>7352670</v>
+        <v>7353338</v>
       </c>
       <c r="F65" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G65" t="s">
         <v>24</v>
@@ -4345,20 +4354,20 @@
       <c r="H65" t="s">
         <v>24</v>
       </c>
-      <c r="M65" s="5" t="s">
-        <v>114</v>
+      <c r="M65" t="s">
+        <v>89</v>
       </c>
       <c r="P65" s="1">
-        <v>46190.508466550928</v>
+        <v>46190.666870520836</v>
       </c>
       <c r="R65" s="4">
-        <v>46197.408573148146</v>
+        <v>46195.537258252312</v>
       </c>
       <c r="S65">
-        <v>10751.000</v>
+        <v>2648.000</v>
       </c>
       <c r="T65">
-        <v>10751.000</v>
+        <v>2648.000</v>
       </c>
       <c r="U65">
         <v>0</v>
@@ -4367,7 +4376,7 @@
         <v>0</v>
       </c>
       <c r="W65" s="4">
-        <v>46197.438478206015</v>
+        <v>46196.389408912037</v>
       </c>
     </row>
     <row r="66">
@@ -4384,7 +4393,7 @@
         <v>24</v>
       </c>
       <c r="E66">
-        <v>7344984</v>
+        <v>7353112</v>
       </c>
       <c r="F66" t="s">
         <v>115</v>
@@ -4395,20 +4404,20 @@
       <c r="H66" t="s">
         <v>24</v>
       </c>
-      <c r="M66" t="s">
+      <c r="M66" s="5" t="s">
         <v>116</v>
       </c>
       <c r="P66" s="1">
-        <v>46188.6820028125</v>
+        <v>46190.633443321756</v>
       </c>
       <c r="R66" s="4">
-        <v>46189.581174189814</v>
+        <v>46195.593899918982</v>
       </c>
       <c r="S66">
-        <v>14515.000</v>
+        <v>15034.000</v>
       </c>
       <c r="T66">
-        <v>14515.000</v>
+        <v>15034.000</v>
       </c>
       <c r="U66">
         <v>0</v>
@@ -4417,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="W66" s="4">
-        <v>46190.318753738429</v>
+        <v>46196.389407835646</v>
       </c>
     </row>
     <row r="67">
@@ -4434,7 +4443,7 @@
         <v>24</v>
       </c>
       <c r="E67">
-        <v>7343721</v>
+        <v>7352722</v>
       </c>
       <c r="F67" t="s">
         <v>117</v>
@@ -4449,19 +4458,16 @@
         <v>118</v>
       </c>
       <c r="P67" s="1">
-        <v>46188.52897230324</v>
-      </c>
-      <c r="Q67" s="4">
-        <v>46189.270138888889</v>
+        <v>46190.517798842593</v>
       </c>
       <c r="R67" s="4">
-        <v>46189.525954201388</v>
+        <v>46198.316219409724</v>
       </c>
       <c r="S67">
-        <v>9210.000</v>
+        <v>13727.000</v>
       </c>
       <c r="T67">
-        <v>9210.000</v>
+        <v>13727.000</v>
       </c>
       <c r="U67">
         <v>0</v>
@@ -4470,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="W67" s="4">
-        <v>46189.538887268522</v>
+        <v>46198.317383530091</v>
       </c>
     </row>
     <row r="68">
@@ -4487,7 +4493,7 @@
         <v>24</v>
       </c>
       <c r="E68">
-        <v>7331780</v>
+        <v>7352670</v>
       </c>
       <c r="F68" t="s">
         <v>119</v>
@@ -4498,23 +4504,20 @@
       <c r="H68" t="s">
         <v>24</v>
       </c>
-      <c r="M68" t="s">
+      <c r="M68" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="O68" s="4">
-        <v>46185.364583333336</v>
-      </c>
       <c r="P68" s="1">
-        <v>46184.420189351855</v>
+        <v>46190.508466550928</v>
       </c>
       <c r="R68" s="4">
-        <v>46188.330705902779</v>
+        <v>46197.408573148146</v>
       </c>
       <c r="S68">
-        <v>2185.000</v>
+        <v>10751.000</v>
       </c>
       <c r="T68">
-        <v>2185.000</v>
+        <v>10751.000</v>
       </c>
       <c r="U68">
         <v>0</v>
@@ -4523,7 +4526,7 @@
         <v>0</v>
       </c>
       <c r="W68" s="4">
-        <v>46188.33742491898</v>
+        <v>46197.438478206015</v>
       </c>
     </row>
     <row r="69">
@@ -4540,7 +4543,7 @@
         <v>24</v>
       </c>
       <c r="E69">
-        <v>7331779</v>
+        <v>7344984</v>
       </c>
       <c r="F69" t="s">
         <v>121</v>
@@ -4554,23 +4557,17 @@
       <c r="M69" t="s">
         <v>122</v>
       </c>
-      <c r="O69" s="4">
-        <v>46185</v>
-      </c>
       <c r="P69" s="1">
-        <v>46184.420142511575</v>
-      </c>
-      <c r="Q69" s="4">
-        <v>46181</v>
+        <v>46188.6820028125</v>
       </c>
       <c r="R69" s="4">
-        <v>46188.332772222224</v>
+        <v>46189.581174189814</v>
       </c>
       <c r="S69">
-        <v>16497.000</v>
+        <v>14515.000</v>
       </c>
       <c r="T69">
-        <v>16497.000</v>
+        <v>14515.000</v>
       </c>
       <c r="U69">
         <v>0</v>
@@ -4579,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="W69" s="4">
-        <v>46188.337424189813</v>
+        <v>46190.318753738429</v>
       </c>
     </row>
     <row r="70">
@@ -4596,7 +4593,7 @@
         <v>24</v>
       </c>
       <c r="E70">
-        <v>7331318</v>
+        <v>7343721</v>
       </c>
       <c r="F70" t="s">
         <v>123</v>
@@ -4611,16 +4608,19 @@
         <v>124</v>
       </c>
       <c r="P70" s="1">
-        <v>46184.369259340281</v>
+        <v>46188.52897230324</v>
+      </c>
+      <c r="Q70" s="4">
+        <v>46189.270138888889</v>
       </c>
       <c r="R70" s="4">
-        <v>46185.506102002313</v>
+        <v>46189.525954201388</v>
       </c>
       <c r="S70">
-        <v>10749.000</v>
+        <v>9210.000</v>
       </c>
       <c r="T70">
-        <v>10749.000</v>
+        <v>9210.000</v>
       </c>
       <c r="U70">
         <v>0</v>
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="W70" s="4">
-        <v>46188.329308333334</v>
+        <v>46189.538887268522</v>
       </c>
     </row>
     <row r="71">
@@ -4646,7 +4646,7 @@
         <v>24</v>
       </c>
       <c r="E71">
-        <v>7329559</v>
+        <v>7331780</v>
       </c>
       <c r="F71" t="s">
         <v>125</v>
@@ -4660,17 +4660,20 @@
       <c r="M71" t="s">
         <v>126</v>
       </c>
+      <c r="O71" s="4">
+        <v>46185.364583333336</v>
+      </c>
       <c r="P71" s="1">
-        <v>46183.835381215278</v>
+        <v>46184.420189351855</v>
       </c>
       <c r="R71" s="4">
-        <v>46185.394576122686</v>
+        <v>46188.330705902779</v>
       </c>
       <c r="S71">
-        <v>18992.000</v>
+        <v>2185.000</v>
       </c>
       <c r="T71">
-        <v>18992.000</v>
+        <v>2185.000</v>
       </c>
       <c r="U71">
         <v>0</v>
@@ -4679,7 +4682,7 @@
         <v>0</v>
       </c>
       <c r="W71" s="4">
-        <v>46188.318260497683</v>
+        <v>46188.33742491898</v>
       </c>
     </row>
     <row r="72">
@@ -4696,7 +4699,7 @@
         <v>24</v>
       </c>
       <c r="E72">
-        <v>7327419</v>
+        <v>7331779</v>
       </c>
       <c r="F72" t="s">
         <v>127</v>
@@ -4710,20 +4713,23 @@
       <c r="M72" t="s">
         <v>128</v>
       </c>
+      <c r="O72" s="4">
+        <v>46185</v>
+      </c>
       <c r="P72" s="1">
-        <v>46183.517797372682</v>
+        <v>46184.420142511575</v>
       </c>
       <c r="Q72" s="4">
-        <v>46184.3125</v>
+        <v>46181</v>
       </c>
       <c r="R72" s="4">
-        <v>46188.329073842593</v>
+        <v>46188.332772222224</v>
       </c>
       <c r="S72">
-        <v>10574.000</v>
+        <v>16497.000</v>
       </c>
       <c r="T72">
-        <v>10574.000</v>
+        <v>16497.000</v>
       </c>
       <c r="U72">
         <v>0</v>
@@ -4732,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="W72" s="4">
-        <v>46188.337423263889</v>
+        <v>46188.337424189813</v>
       </c>
     </row>
     <row r="73">
@@ -4749,7 +4755,7 @@
         <v>24</v>
       </c>
       <c r="E73">
-        <v>7321304</v>
+        <v>7331318</v>
       </c>
       <c r="F73" t="s">
         <v>129</v>
@@ -4764,19 +4770,16 @@
         <v>130</v>
       </c>
       <c r="P73" s="1">
-        <v>46182.379826539349</v>
-      </c>
-      <c r="Q73" s="4">
-        <v>46183.458333333336</v>
+        <v>46184.369259340281</v>
       </c>
       <c r="R73" s="4">
-        <v>46184.566309837966</v>
+        <v>46185.506102002313</v>
       </c>
       <c r="S73">
-        <v>1784.000</v>
+        <v>10749.000</v>
       </c>
       <c r="T73">
-        <v>1784.000</v>
+        <v>10749.000</v>
       </c>
       <c r="U73">
         <v>0</v>
@@ -4785,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="W73" s="4">
-        <v>46188.318567708331</v>
+        <v>46188.329308333334</v>
       </c>
     </row>
     <row r="74">
@@ -4802,7 +4805,7 @@
         <v>24</v>
       </c>
       <c r="E74">
-        <v>7321303</v>
+        <v>7329559</v>
       </c>
       <c r="F74" t="s">
         <v>131</v>
@@ -4817,19 +4820,16 @@
         <v>132</v>
       </c>
       <c r="P74" s="1">
-        <v>46182.379728553242</v>
-      </c>
-      <c r="Q74" s="4">
-        <v>46183.458333333336</v>
+        <v>46183.835381215278</v>
       </c>
       <c r="R74" s="4">
-        <v>46185.474632175923</v>
+        <v>46185.394576122686</v>
       </c>
       <c r="S74">
-        <v>15852.000</v>
+        <v>18992.000</v>
       </c>
       <c r="T74">
-        <v>15852.000</v>
+        <v>18992.000</v>
       </c>
       <c r="U74">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="W74" s="4">
-        <v>46188.318567164351</v>
+        <v>46188.318260497683</v>
       </c>
     </row>
     <row r="75">
@@ -4855,7 +4855,7 @@
         <v>24</v>
       </c>
       <c r="E75">
-        <v>7312336</v>
+        <v>7327419</v>
       </c>
       <c r="F75" t="s">
         <v>133</v>
@@ -4870,19 +4870,19 @@
         <v>134</v>
       </c>
       <c r="P75" s="1">
-        <v>46181.394619016202</v>
+        <v>46183.517797372682</v>
       </c>
       <c r="Q75" s="4">
-        <v>46182.416666666664</v>
+        <v>46184.3125</v>
       </c>
       <c r="R75" s="4">
-        <v>46182.563263425924</v>
+        <v>46188.329073842593</v>
       </c>
       <c r="S75">
-        <v>8559.000</v>
+        <v>10574.000</v>
       </c>
       <c r="T75">
-        <v>8559.000</v>
+        <v>10574.000</v>
       </c>
       <c r="U75">
         <v>0</v>
@@ -4891,7 +4891,7 @@
         <v>0</v>
       </c>
       <c r="W75" s="4">
-        <v>46183.499163692133</v>
+        <v>46188.337423263889</v>
       </c>
     </row>
     <row r="76">
@@ -4908,7 +4908,7 @@
         <v>24</v>
       </c>
       <c r="E76">
-        <v>7312335</v>
+        <v>7321304</v>
       </c>
       <c r="F76" t="s">
         <v>135</v>
@@ -4919,23 +4919,23 @@
       <c r="H76" t="s">
         <v>24</v>
       </c>
-      <c r="M76" s="5" t="s">
+      <c r="M76" t="s">
         <v>136</v>
       </c>
       <c r="P76" s="1">
-        <v>46181.394497488429</v>
+        <v>46182.379826539349</v>
       </c>
       <c r="Q76" s="4">
-        <v>46182.388888888891</v>
+        <v>46183.458333333336</v>
       </c>
       <c r="R76" s="4">
-        <v>46185.475467280092</v>
+        <v>46184.566309837966</v>
       </c>
       <c r="S76">
-        <v>16641.000</v>
+        <v>1784.000</v>
       </c>
       <c r="T76">
-        <v>16641.000</v>
+        <v>1784.000</v>
       </c>
       <c r="U76">
         <v>0</v>
@@ -4944,7 +4944,7 @@
         <v>0</v>
       </c>
       <c r="W76" s="4">
-        <v>46188.318566284725</v>
+        <v>46188.318567708331</v>
       </c>
     </row>
     <row r="77">
@@ -4961,7 +4961,7 @@
         <v>24</v>
       </c>
       <c r="E77">
-        <v>7312334</v>
+        <v>7321303</v>
       </c>
       <c r="F77" t="s">
         <v>137</v>
@@ -4976,19 +4976,19 @@
         <v>138</v>
       </c>
       <c r="P77" s="1">
-        <v>46181.394481597221</v>
+        <v>46182.379728553242</v>
       </c>
       <c r="Q77" s="4">
-        <v>46182.458333333336</v>
+        <v>46183.458333333336</v>
       </c>
       <c r="R77" s="4">
-        <v>46188.363727511576</v>
+        <v>46185.474632175923</v>
       </c>
       <c r="S77">
-        <v>5617.000</v>
+        <v>15852.000</v>
       </c>
       <c r="T77">
-        <v>5617.000</v>
+        <v>15852.000</v>
       </c>
       <c r="U77">
         <v>0</v>
@@ -4997,7 +4997,7 @@
         <v>0</v>
       </c>
       <c r="W77" s="4">
-        <v>46188.368130752315</v>
+        <v>46188.318567164351</v>
       </c>
     </row>
     <row r="78">
@@ -5014,7 +5014,7 @@
         <v>24</v>
       </c>
       <c r="E78">
-        <v>7312333</v>
+        <v>7312336</v>
       </c>
       <c r="F78" t="s">
         <v>139</v>
@@ -5029,19 +5029,19 @@
         <v>140</v>
       </c>
       <c r="P78" s="1">
-        <v>46181.394416122683</v>
+        <v>46181.394619016202</v>
       </c>
       <c r="Q78" s="4">
-        <v>46182.458333333336</v>
+        <v>46182.416666666664</v>
       </c>
       <c r="R78" s="4">
-        <v>46188.402503240737</v>
+        <v>46182.563263425924</v>
       </c>
       <c r="S78">
-        <v>8272.000</v>
+        <v>8559.000</v>
       </c>
       <c r="T78">
-        <v>8272.000</v>
+        <v>8559.000</v>
       </c>
       <c r="U78">
         <v>0</v>
@@ -5050,7 +5050,7 @@
         <v>0</v>
       </c>
       <c r="W78" s="4">
-        <v>46188.404413310185</v>
+        <v>46183.499163692133</v>
       </c>
     </row>
     <row r="79">
@@ -5067,7 +5067,7 @@
         <v>24</v>
       </c>
       <c r="E79">
-        <v>7306694</v>
+        <v>7312335</v>
       </c>
       <c r="F79" t="s">
         <v>141</v>
@@ -5078,23 +5078,23 @@
       <c r="H79" t="s">
         <v>24</v>
       </c>
-      <c r="M79" t="s">
+      <c r="M79" s="5" t="s">
         <v>142</v>
       </c>
       <c r="P79" s="1">
-        <v>46178.650135613425</v>
+        <v>46181.394497488429</v>
       </c>
       <c r="Q79" s="4">
-        <v>46181.3125</v>
+        <v>46182.388888888891</v>
       </c>
       <c r="R79" s="4">
-        <v>46188.351883217591</v>
+        <v>46185.475467280092</v>
       </c>
       <c r="S79">
-        <v>7291.000</v>
+        <v>16641.000</v>
       </c>
       <c r="T79">
-        <v>7291.000</v>
+        <v>16641.000</v>
       </c>
       <c r="U79">
         <v>0</v>
@@ -5103,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="W79" s="4">
-        <v>46188.368130405092</v>
+        <v>46188.318566284725</v>
       </c>
     </row>
     <row r="80">
@@ -5120,7 +5120,7 @@
         <v>24</v>
       </c>
       <c r="E80">
-        <v>7306693</v>
+        <v>7312334</v>
       </c>
       <c r="F80" t="s">
         <v>143</v>
@@ -5135,19 +5135,19 @@
         <v>144</v>
       </c>
       <c r="P80" s="1">
-        <v>46178.650101388892</v>
+        <v>46181.394481597221</v>
       </c>
       <c r="Q80" s="4">
-        <v>46181.395833333336</v>
+        <v>46182.458333333336</v>
       </c>
       <c r="R80" s="4">
-        <v>46188.361928472223</v>
+        <v>46188.363727511576</v>
       </c>
       <c r="S80">
-        <v>5272.000</v>
+        <v>5617.000</v>
       </c>
       <c r="T80">
-        <v>5272.000</v>
+        <v>5617.000</v>
       </c>
       <c r="U80">
         <v>0</v>
@@ -5156,7 +5156,7 @@
         <v>0</v>
       </c>
       <c r="W80" s="4">
-        <v>46188.368129826391</v>
+        <v>46188.368130752315</v>
       </c>
     </row>
     <row r="81">
@@ -5173,7 +5173,7 @@
         <v>24</v>
       </c>
       <c r="E81">
-        <v>7306692</v>
+        <v>7312333</v>
       </c>
       <c r="F81" t="s">
         <v>145</v>
@@ -5184,23 +5184,23 @@
       <c r="H81" t="s">
         <v>24</v>
       </c>
-      <c r="M81" s="5" t="s">
+      <c r="M81" t="s">
         <v>146</v>
       </c>
-      <c r="O81" s="4">
-        <v>46181.34375</v>
-      </c>
       <c r="P81" s="1">
-        <v>46178.650014085651</v>
+        <v>46181.394416122683</v>
+      </c>
+      <c r="Q81" s="4">
+        <v>46182.458333333336</v>
       </c>
       <c r="R81" s="4">
-        <v>46188.321652777777</v>
+        <v>46188.402503240737</v>
       </c>
       <c r="S81">
-        <v>10749.000</v>
+        <v>8272.000</v>
       </c>
       <c r="T81">
-        <v>10749.000</v>
+        <v>8272.000</v>
       </c>
       <c r="U81">
         <v>0</v>
@@ -5209,7 +5209,7 @@
         <v>0</v>
       </c>
       <c r="W81" s="4">
-        <v>46188.329306516207</v>
+        <v>46188.404413310185</v>
       </c>
     </row>
     <row r="82">
@@ -5226,7 +5226,7 @@
         <v>24</v>
       </c>
       <c r="E82">
-        <v>7297492</v>
+        <v>7306694</v>
       </c>
       <c r="F82" t="s">
         <v>147</v>
@@ -5240,20 +5240,20 @@
       <c r="M82" t="s">
         <v>148</v>
       </c>
-      <c r="O82" s="4">
-        <v>46178.427083333336</v>
-      </c>
       <c r="P82" s="1">
-        <v>46176.651338159725</v>
+        <v>46178.650135613425</v>
+      </c>
+      <c r="Q82" s="4">
+        <v>46181.3125</v>
       </c>
       <c r="R82" s="4">
-        <v>46178.483032060183</v>
+        <v>46188.351883217591</v>
       </c>
       <c r="S82">
-        <v>6802.000</v>
+        <v>7291.000</v>
       </c>
       <c r="T82">
-        <v>6802.000</v>
+        <v>7291.000</v>
       </c>
       <c r="U82">
         <v>0</v>
@@ -5262,7 +5262,7 @@
         <v>0</v>
       </c>
       <c r="W82" s="4">
-        <v>46181.304573692127</v>
+        <v>46188.368130405092</v>
       </c>
     </row>
     <row r="83">
@@ -5279,7 +5279,7 @@
         <v>24</v>
       </c>
       <c r="E83">
-        <v>7297491</v>
+        <v>7306693</v>
       </c>
       <c r="F83" t="s">
         <v>149</v>
@@ -5293,23 +5293,20 @@
       <c r="M83" t="s">
         <v>150</v>
       </c>
-      <c r="O83" s="4">
-        <v>46178.416666666664</v>
-      </c>
       <c r="P83" s="1">
-        <v>46176.651283530089</v>
+        <v>46178.650101388892</v>
       </c>
       <c r="Q83" s="4">
-        <v>46178.260416666664</v>
+        <v>46181.395833333336</v>
       </c>
       <c r="R83" s="4">
-        <v>46182.304580173608</v>
+        <v>46188.361928472223</v>
       </c>
       <c r="S83">
-        <v>19653.000</v>
+        <v>5272.000</v>
       </c>
       <c r="T83">
-        <v>19653.000</v>
+        <v>5272.000</v>
       </c>
       <c r="U83">
         <v>0</v>
@@ -5318,7 +5315,7 @@
         <v>0</v>
       </c>
       <c r="W83" s="4">
-        <v>46182.394867361108</v>
+        <v>46188.368129826391</v>
       </c>
     </row>
     <row r="84">
@@ -5335,7 +5332,7 @@
         <v>24</v>
       </c>
       <c r="E84">
-        <v>7296112</v>
+        <v>7306692</v>
       </c>
       <c r="F84" t="s">
         <v>151</v>
@@ -5346,20 +5343,23 @@
       <c r="H84" t="s">
         <v>24</v>
       </c>
-      <c r="M84" t="s">
+      <c r="M84" s="5" t="s">
         <v>152</v>
       </c>
+      <c r="O84" s="4">
+        <v>46181.34375</v>
+      </c>
       <c r="P84" s="1">
-        <v>46176.490794872683</v>
+        <v>46178.650014085651</v>
       </c>
       <c r="R84" s="4">
-        <v>46188.357570370368</v>
+        <v>46188.321652777777</v>
       </c>
       <c r="S84">
-        <v>7146.000</v>
+        <v>10749.000</v>
       </c>
       <c r="T84">
-        <v>7146.000</v>
+        <v>10749.000</v>
       </c>
       <c r="U84">
         <v>0</v>
@@ -5368,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="W84" s="4">
-        <v>46188.368129664355</v>
+        <v>46188.329306516207</v>
       </c>
     </row>
     <row r="85">
@@ -5385,7 +5385,7 @@
         <v>24</v>
       </c>
       <c r="E85">
-        <v>7290516</v>
+        <v>7297492</v>
       </c>
       <c r="F85" t="s">
         <v>153</v>
@@ -5399,20 +5399,20 @@
       <c r="M85" t="s">
         <v>154</v>
       </c>
+      <c r="O85" s="4">
+        <v>46178.427083333336</v>
+      </c>
       <c r="P85" s="1">
-        <v>46175.705564502314</v>
-      </c>
-      <c r="Q85" s="4">
-        <v>46176.59375</v>
+        <v>46176.651338159725</v>
       </c>
       <c r="R85" s="4">
-        <v>46178.37381646991</v>
+        <v>46178.483032060183</v>
       </c>
       <c r="S85">
-        <v>6600.000</v>
+        <v>6802.000</v>
       </c>
       <c r="T85">
-        <v>6600.000</v>
+        <v>6802.000</v>
       </c>
       <c r="U85">
         <v>0</v>
@@ -5421,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="W85" s="4">
-        <v>46181.304297951392</v>
+        <v>46181.304573692127</v>
       </c>
     </row>
     <row r="86">
@@ -5438,7 +5438,7 @@
         <v>24</v>
       </c>
       <c r="E86">
-        <v>7290515</v>
+        <v>7297491</v>
       </c>
       <c r="F86" t="s">
         <v>155</v>
@@ -5452,20 +5452,23 @@
       <c r="M86" t="s">
         <v>156</v>
       </c>
+      <c r="O86" s="4">
+        <v>46178.416666666664</v>
+      </c>
       <c r="P86" s="1">
-        <v>46175.705520370371</v>
+        <v>46176.651283530089</v>
       </c>
       <c r="Q86" s="4">
-        <v>46175.604166666664</v>
+        <v>46178.260416666664</v>
       </c>
       <c r="R86" s="4">
-        <v>46176.32743784722</v>
+        <v>46182.304580173608</v>
       </c>
       <c r="S86">
-        <v>9893.000</v>
+        <v>19653.000</v>
       </c>
       <c r="T86">
-        <v>9893.000</v>
+        <v>19653.000</v>
       </c>
       <c r="U86">
         <v>0</v>
@@ -5474,7 +5477,7 @@
         <v>0</v>
       </c>
       <c r="W86" s="4">
-        <v>46176.36704571759</v>
+        <v>46182.394867361108</v>
       </c>
     </row>
     <row r="87">
@@ -5491,7 +5494,7 @@
         <v>24</v>
       </c>
       <c r="E87">
-        <v>7290513</v>
+        <v>7296112</v>
       </c>
       <c r="F87" t="s">
         <v>157</v>
@@ -5506,19 +5509,16 @@
         <v>158</v>
       </c>
       <c r="P87" s="1">
-        <v>46175.705472835645</v>
-      </c>
-      <c r="Q87" s="4">
-        <v>46175.541666666664</v>
+        <v>46176.490794872683</v>
       </c>
       <c r="R87" s="4">
-        <v>46176.390187384262</v>
+        <v>46188.357570370368</v>
       </c>
       <c r="S87">
-        <v>10634.000</v>
+        <v>7146.000</v>
       </c>
       <c r="T87">
-        <v>10634.000</v>
+        <v>7146.000</v>
       </c>
       <c r="U87">
         <v>0</v>
@@ -5527,7 +5527,7 @@
         <v>0</v>
       </c>
       <c r="W87" s="4">
-        <v>46176.479922453706</v>
+        <v>46188.368129664355</v>
       </c>
     </row>
     <row r="88">
@@ -5544,7 +5544,7 @@
         <v>24</v>
       </c>
       <c r="E88">
-        <v>7290512</v>
+        <v>7290516</v>
       </c>
       <c r="F88" t="s">
         <v>159</v>
@@ -5559,19 +5559,19 @@
         <v>160</v>
       </c>
       <c r="P88" s="1">
-        <v>46175.705376817132</v>
+        <v>46175.705564502314</v>
       </c>
       <c r="Q88" s="4">
-        <v>46176.5</v>
+        <v>46176.59375</v>
       </c>
       <c r="R88" s="4">
-        <v>46188.325696840278</v>
+        <v>46178.37381646991</v>
       </c>
       <c r="S88">
-        <v>14234.000</v>
+        <v>6600.000</v>
       </c>
       <c r="T88">
-        <v>14234.000</v>
+        <v>6600.000</v>
       </c>
       <c r="U88">
         <v>0</v>
@@ -5580,7 +5580,7 @@
         <v>0</v>
       </c>
       <c r="W88" s="4">
-        <v>46188.329304166669</v>
+        <v>46181.304297951392</v>
       </c>
     </row>
     <row r="89">
@@ -5597,7 +5597,7 @@
         <v>24</v>
       </c>
       <c r="E89">
-        <v>7277755</v>
+        <v>7290515</v>
       </c>
       <c r="F89" t="s">
         <v>161</v>
@@ -5612,19 +5612,19 @@
         <v>162</v>
       </c>
       <c r="P89" s="1">
-        <v>46174.492233680554</v>
+        <v>46175.705520370371</v>
       </c>
       <c r="Q89" s="4">
-        <v>46175.291666666664</v>
+        <v>46175.604166666664</v>
       </c>
       <c r="R89" s="4">
-        <v>46175.460509027776</v>
+        <v>46176.32743784722</v>
       </c>
       <c r="S89">
-        <v>1502.000</v>
+        <v>9893.000</v>
       </c>
       <c r="T89">
-        <v>1502.000</v>
+        <v>9893.000</v>
       </c>
       <c r="U89">
         <v>0</v>
@@ -5633,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="W89" s="4">
-        <v>46176.367452777777</v>
+        <v>46176.36704571759</v>
       </c>
     </row>
     <row r="90">
@@ -5650,7 +5650,7 @@
         <v>24</v>
       </c>
       <c r="E90">
-        <v>7277745</v>
+        <v>7290513</v>
       </c>
       <c r="F90" t="s">
         <v>163</v>
@@ -5665,19 +5665,19 @@
         <v>164</v>
       </c>
       <c r="P90" s="1">
-        <v>46174.492115972222</v>
+        <v>46175.705472835645</v>
       </c>
       <c r="Q90" s="4">
-        <v>46175.291666666664</v>
+        <v>46175.541666666664</v>
       </c>
       <c r="R90" s="4">
-        <v>46176.394080127313</v>
+        <v>46176.390187384262</v>
       </c>
       <c r="S90">
-        <v>8925.000</v>
+        <v>10634.000</v>
       </c>
       <c r="T90">
-        <v>8925.000</v>
+        <v>10634.000</v>
       </c>
       <c r="U90">
         <v>0</v>
@@ -5686,7 +5686,7 @@
         <v>0</v>
       </c>
       <c r="W90" s="4">
-        <v>46176.479621759259</v>
+        <v>46176.479922453706</v>
       </c>
     </row>
     <row r="91">
@@ -5703,7 +5703,7 @@
         <v>24</v>
       </c>
       <c r="E91">
-        <v>7277744</v>
+        <v>7290512</v>
       </c>
       <c r="F91" t="s">
         <v>165</v>
@@ -5718,19 +5718,19 @@
         <v>166</v>
       </c>
       <c r="P91" s="1">
-        <v>46174.49203425926</v>
+        <v>46175.705376817132</v>
       </c>
       <c r="Q91" s="4">
-        <v>46174.5</v>
+        <v>46176.5</v>
       </c>
       <c r="R91" s="4">
-        <v>46175.401104085649</v>
+        <v>46188.325696840278</v>
       </c>
       <c r="S91">
-        <v>14377.000</v>
+        <v>14234.000</v>
       </c>
       <c r="T91">
-        <v>14377.000</v>
+        <v>14234.000</v>
       </c>
       <c r="U91">
         <v>0</v>
@@ -5739,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="W91" s="4">
-        <v>46175.446175925928</v>
+        <v>46188.329304166669</v>
       </c>
     </row>
     <row r="92">
@@ -5756,7 +5756,7 @@
         <v>24</v>
       </c>
       <c r="E92">
-        <v>7277742</v>
+        <v>7277755</v>
       </c>
       <c r="F92" t="s">
         <v>167</v>
@@ -5771,19 +5771,19 @@
         <v>168</v>
       </c>
       <c r="P92" s="1">
-        <v>46174.491930821758</v>
+        <v>46174.492233680554</v>
       </c>
       <c r="Q92" s="4">
-        <v>46174.416666666664</v>
+        <v>46175.291666666664</v>
       </c>
       <c r="R92" s="4">
-        <v>46188.313768368054</v>
+        <v>46175.460509027776</v>
       </c>
       <c r="S92">
-        <v>18914.000</v>
+        <v>1502.000</v>
       </c>
       <c r="T92">
-        <v>18914.000</v>
+        <v>1502.000</v>
       </c>
       <c r="U92">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="W92" s="4">
-        <v>46188.329302546299</v>
+        <v>46176.367452777777</v>
       </c>
     </row>
     <row r="93">
@@ -5809,7 +5809,7 @@
         <v>24</v>
       </c>
       <c r="E93">
-        <v>7276672</v>
+        <v>7277745</v>
       </c>
       <c r="F93" t="s">
         <v>169</v>
@@ -5824,19 +5824,19 @@
         <v>170</v>
       </c>
       <c r="P93" s="1">
-        <v>46174.386965358797</v>
+        <v>46174.492115972222</v>
       </c>
       <c r="Q93" s="4">
-        <v>46174.3125</v>
+        <v>46175.291666666664</v>
       </c>
       <c r="R93" s="4">
-        <v>46175.277797997682</v>
+        <v>46176.394080127313</v>
       </c>
       <c r="S93">
-        <v>445.000</v>
+        <v>8925.000</v>
       </c>
       <c r="T93">
-        <v>445.000</v>
+        <v>8925.000</v>
       </c>
       <c r="U93">
         <v>0</v>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="W93" s="4">
-        <v>46175.446175925928</v>
+        <v>46176.479621759259</v>
       </c>
     </row>
     <row r="94">
@@ -5862,7 +5862,7 @@
         <v>24</v>
       </c>
       <c r="E94">
-        <v>7276670</v>
+        <v>7277744</v>
       </c>
       <c r="F94" t="s">
         <v>171</v>
@@ -5877,19 +5877,19 @@
         <v>172</v>
       </c>
       <c r="P94" s="1">
-        <v>46174.386795023151</v>
+        <v>46174.49203425926</v>
       </c>
       <c r="Q94" s="4">
-        <v>46174.3125</v>
+        <v>46174.5</v>
       </c>
       <c r="R94" s="4">
-        <v>46181.602299189813</v>
+        <v>46175.401104085649</v>
       </c>
       <c r="S94">
-        <v>7766.000</v>
+        <v>14377.000</v>
       </c>
       <c r="T94">
-        <v>7766.000</v>
+        <v>14377.000</v>
       </c>
       <c r="U94">
         <v>0</v>
@@ -5898,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="W94" s="4">
-        <v>46181.607877893519</v>
+        <v>46175.446175925928</v>
       </c>
     </row>
     <row r="95">
@@ -5915,7 +5915,7 @@
         <v>24</v>
       </c>
       <c r="E95">
-        <v>7261067</v>
+        <v>7277742</v>
       </c>
       <c r="F95" t="s">
         <v>173</v>
@@ -5930,16 +5930,19 @@
         <v>174</v>
       </c>
       <c r="P95" s="1">
-        <v>46171.450339317133</v>
+        <v>46174.491930821758</v>
+      </c>
+      <c r="Q95" s="4">
+        <v>46174.416666666664</v>
       </c>
       <c r="R95" s="4">
-        <v>46171.468652743053</v>
+        <v>46188.313768368054</v>
       </c>
       <c r="S95">
-        <v>13827.000</v>
+        <v>18914.000</v>
       </c>
       <c r="T95">
-        <v>13827.000</v>
+        <v>18914.000</v>
       </c>
       <c r="U95">
         <v>0</v>
@@ -5948,7 +5951,7 @@
         <v>0</v>
       </c>
       <c r="W95" s="4">
-        <v>46171.521808101854</v>
+        <v>46188.329302546299</v>
       </c>
     </row>
     <row r="96">
@@ -5965,7 +5968,7 @@
         <v>24</v>
       </c>
       <c r="E96">
-        <v>7256959</v>
+        <v>7276672</v>
       </c>
       <c r="F96" t="s">
         <v>175</v>
@@ -5980,19 +5983,19 @@
         <v>176</v>
       </c>
       <c r="P96" s="1">
-        <v>46169.73840185185</v>
+        <v>46174.386965358797</v>
       </c>
       <c r="Q96" s="4">
-        <v>46171.520833333336</v>
+        <v>46174.3125</v>
       </c>
       <c r="R96" s="4">
-        <v>46181.602367395833</v>
+        <v>46175.277797997682</v>
       </c>
       <c r="S96">
-        <v>11921.000</v>
+        <v>445.000</v>
       </c>
       <c r="T96">
-        <v>11921.000</v>
+        <v>445.000</v>
       </c>
       <c r="U96">
         <v>0</v>
@@ -6001,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="W96" s="4">
-        <v>46181.607877002316</v>
+        <v>46175.446175925928</v>
       </c>
     </row>
     <row r="97">
@@ -6018,7 +6021,7 @@
         <v>24</v>
       </c>
       <c r="E97">
-        <v>7256954</v>
+        <v>7276670</v>
       </c>
       <c r="F97" t="s">
         <v>177</v>
@@ -6033,19 +6036,19 @@
         <v>178</v>
       </c>
       <c r="P97" s="1">
-        <v>46169.737280092595</v>
+        <v>46174.386795023151</v>
       </c>
       <c r="Q97" s="4">
-        <v>46171.416666666664</v>
+        <v>46174.3125</v>
       </c>
       <c r="R97" s="4">
-        <v>46171.471500266205</v>
+        <v>46181.602299189813</v>
       </c>
       <c r="S97">
-        <v>11226.000</v>
+        <v>7766.000</v>
       </c>
       <c r="T97">
-        <v>11226.000</v>
+        <v>7766.000</v>
       </c>
       <c r="U97">
         <v>0</v>
@@ -6054,7 +6057,7 @@
         <v>0</v>
       </c>
       <c r="W97" s="4">
-        <v>46171.521807557867</v>
+        <v>46181.607877893519</v>
       </c>
     </row>
     <row r="98">
@@ -6071,7 +6074,7 @@
         <v>24</v>
       </c>
       <c r="E98">
-        <v>7256935</v>
+        <v>7261067</v>
       </c>
       <c r="F98" t="s">
         <v>179</v>
@@ -6086,19 +6089,16 @@
         <v>180</v>
       </c>
       <c r="P98" s="1">
-        <v>46169.735800810187</v>
-      </c>
-      <c r="Q98" s="4">
-        <v>46171.25</v>
+        <v>46171.450339317133</v>
       </c>
       <c r="R98" s="4">
-        <v>46171.474860069444</v>
+        <v>46171.468652743053</v>
       </c>
       <c r="S98">
-        <v>12909.000</v>
+        <v>13827.000</v>
       </c>
       <c r="T98">
-        <v>12909.000</v>
+        <v>13827.000</v>
       </c>
       <c r="U98">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="W98" s="4">
-        <v>46171.521807025463</v>
+        <v>46171.521808101854</v>
       </c>
     </row>
     <row r="99">
@@ -6124,7 +6124,7 @@
         <v>24</v>
       </c>
       <c r="E99">
-        <v>7256927</v>
+        <v>7256959</v>
       </c>
       <c r="F99" t="s">
         <v>181</v>
@@ -6138,23 +6138,20 @@
       <c r="M99" t="s">
         <v>182</v>
       </c>
-      <c r="O99" s="4">
-        <v>46170.541666666664</v>
-      </c>
       <c r="P99" s="1">
-        <v>46169.733974768518</v>
+        <v>46169.73840185185</v>
       </c>
       <c r="Q99" s="4">
-        <v>46171.375</v>
+        <v>46171.520833333336</v>
       </c>
       <c r="R99" s="4">
-        <v>46171.384800081018</v>
+        <v>46181.602367395833</v>
       </c>
       <c r="S99">
-        <v>470.000</v>
+        <v>11921.000</v>
       </c>
       <c r="T99">
-        <v>470.000</v>
+        <v>11921.000</v>
       </c>
       <c r="U99">
         <v>0</v>
@@ -6163,7 +6160,7 @@
         <v>0</v>
       </c>
       <c r="W99" s="4">
-        <v>46171.521806828707</v>
+        <v>46181.607877002316</v>
       </c>
     </row>
     <row r="100">
@@ -6180,7 +6177,7 @@
         <v>24</v>
       </c>
       <c r="E100">
-        <v>7256837</v>
+        <v>7256954</v>
       </c>
       <c r="F100" t="s">
         <v>183</v>
@@ -6194,23 +6191,20 @@
       <c r="M100" t="s">
         <v>184</v>
       </c>
-      <c r="O100" s="4">
-        <v>46170.541666666664</v>
-      </c>
       <c r="P100" s="1">
-        <v>46169.717724456015</v>
+        <v>46169.737280092595</v>
       </c>
       <c r="Q100" s="4">
-        <v>46171.375</v>
+        <v>46171.416666666664</v>
       </c>
       <c r="R100" s="4">
-        <v>46181.601758877317</v>
+        <v>46171.471500266205</v>
       </c>
       <c r="S100">
-        <v>10645.000</v>
+        <v>11226.000</v>
       </c>
       <c r="T100">
-        <v>10645.000</v>
+        <v>11226.000</v>
       </c>
       <c r="U100">
         <v>0</v>
@@ -6219,7 +6213,7 @@
         <v>0</v>
       </c>
       <c r="W100" s="4">
-        <v>46181.607876122682</v>
+        <v>46171.521807557867</v>
       </c>
     </row>
     <row r="101">
@@ -6236,7 +6230,7 @@
         <v>24</v>
       </c>
       <c r="E101">
-        <v>7256698</v>
+        <v>7256935</v>
       </c>
       <c r="F101" t="s">
         <v>185</v>
@@ -6250,23 +6244,20 @@
       <c r="M101" t="s">
         <v>186</v>
       </c>
-      <c r="O101" s="4">
-        <v>46170.416666666664</v>
-      </c>
       <c r="P101" s="1">
-        <v>46169.704318553238</v>
+        <v>46169.735800810187</v>
       </c>
       <c r="Q101" s="4">
-        <v>46170.4375</v>
+        <v>46171.25</v>
       </c>
       <c r="R101" s="4">
-        <v>46170.55747615741</v>
+        <v>46171.474860069444</v>
       </c>
       <c r="S101">
-        <v>15811.000</v>
+        <v>12909.000</v>
       </c>
       <c r="T101">
-        <v>15811.000</v>
+        <v>12909.000</v>
       </c>
       <c r="U101">
         <v>0</v>
@@ -6275,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="W101" s="4">
-        <v>46171.52180628472</v>
+        <v>46171.521807025463</v>
       </c>
     </row>
     <row r="102">
@@ -6292,7 +6283,7 @@
         <v>24</v>
       </c>
       <c r="E102">
-        <v>7256674</v>
+        <v>7256927</v>
       </c>
       <c r="F102" t="s">
         <v>187</v>
@@ -6307,22 +6298,22 @@
         <v>188</v>
       </c>
       <c r="O102" s="4">
-        <v>46170.291666666664</v>
+        <v>46170.541666666664</v>
       </c>
       <c r="P102" s="1">
-        <v>46169.697586805552</v>
+        <v>46169.733974768518</v>
       </c>
       <c r="Q102" s="4">
-        <v>46171.291666666664</v>
+        <v>46171.375</v>
       </c>
       <c r="R102" s="4">
-        <v>46171.366929745367</v>
+        <v>46171.384800081018</v>
       </c>
       <c r="S102">
-        <v>6703.000</v>
+        <v>470.000</v>
       </c>
       <c r="T102">
-        <v>6703.000</v>
+        <v>470.000</v>
       </c>
       <c r="U102">
         <v>0</v>
@@ -6331,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="W102" s="4">
-        <v>46171.521805937497</v>
+        <v>46171.521806828707</v>
       </c>
     </row>
     <row r="103">
@@ -6348,7 +6339,7 @@
         <v>24</v>
       </c>
       <c r="E103">
-        <v>7243671</v>
+        <v>7256837</v>
       </c>
       <c r="F103" t="s">
         <v>189</v>
@@ -6362,20 +6353,23 @@
       <c r="M103" t="s">
         <v>190</v>
       </c>
+      <c r="O103" s="4">
+        <v>46170.541666666664</v>
+      </c>
       <c r="P103" s="1">
-        <v>46167.398480636577</v>
+        <v>46169.717724456015</v>
       </c>
       <c r="Q103" s="4">
-        <v>46170.25</v>
+        <v>46171.375</v>
       </c>
       <c r="R103" s="4">
-        <v>46170.38833533565</v>
+        <v>46181.601758877317</v>
       </c>
       <c r="S103">
-        <v>767.000</v>
+        <v>10645.000</v>
       </c>
       <c r="T103">
-        <v>767.000</v>
+        <v>10645.000</v>
       </c>
       <c r="U103">
         <v>0</v>
@@ -6384,7 +6378,7 @@
         <v>0</v>
       </c>
       <c r="W103" s="4">
-        <v>46171.521805752316</v>
+        <v>46181.607876122682</v>
       </c>
     </row>
     <row r="104">
@@ -6401,7 +6395,7 @@
         <v>24</v>
       </c>
       <c r="E104">
-        <v>7243667</v>
+        <v>7256698</v>
       </c>
       <c r="F104" t="s">
         <v>191</v>
@@ -6415,20 +6409,23 @@
       <c r="M104" t="s">
         <v>192</v>
       </c>
+      <c r="O104" s="4">
+        <v>46170.416666666664</v>
+      </c>
       <c r="P104" s="1">
-        <v>46167.398084108798</v>
+        <v>46169.704318553238</v>
       </c>
       <c r="Q104" s="4">
-        <v>46170.25</v>
+        <v>46170.4375</v>
       </c>
       <c r="R104" s="4">
-        <v>46170.366140659724</v>
+        <v>46170.55747615741</v>
       </c>
       <c r="S104">
-        <v>7345.000</v>
+        <v>15811.000</v>
       </c>
       <c r="T104">
-        <v>7345.000</v>
+        <v>15811.000</v>
       </c>
       <c r="U104">
         <v>0</v>
@@ -6437,7 +6434,7 @@
         <v>0</v>
       </c>
       <c r="W104" s="4">
-        <v>46170.37235636574</v>
+        <v>46171.52180628472</v>
       </c>
     </row>
     <row r="105">
@@ -6454,7 +6451,7 @@
         <v>24</v>
       </c>
       <c r="E105">
-        <v>7243666</v>
+        <v>7256674</v>
       </c>
       <c r="F105" t="s">
         <v>193</v>
@@ -6468,20 +6465,23 @@
       <c r="M105" t="s">
         <v>194</v>
       </c>
+      <c r="O105" s="4">
+        <v>46170.291666666664</v>
+      </c>
       <c r="P105" s="1">
-        <v>46167.397709988429</v>
+        <v>46169.697586805552</v>
       </c>
       <c r="Q105" s="4">
-        <v>46169.444444444445</v>
+        <v>46171.291666666664</v>
       </c>
       <c r="R105" s="4">
-        <v>46169.627317511571</v>
+        <v>46171.366929745367</v>
       </c>
       <c r="S105">
-        <v>5379.000</v>
+        <v>6703.000</v>
       </c>
       <c r="T105">
-        <v>5379.000</v>
+        <v>6703.000</v>
       </c>
       <c r="U105">
         <v>0</v>
@@ -6490,7 +6490,7 @@
         <v>0</v>
       </c>
       <c r="W105" s="4">
-        <v>46170.372355636573</v>
+        <v>46171.521805937497</v>
       </c>
     </row>
     <row r="106">
@@ -6507,7 +6507,7 @@
         <v>24</v>
       </c>
       <c r="E106">
-        <v>7243664</v>
+        <v>7243671</v>
       </c>
       <c r="F106" t="s">
         <v>195</v>
@@ -6522,19 +6522,19 @@
         <v>196</v>
       </c>
       <c r="P106" s="1">
-        <v>46167.397293715279</v>
+        <v>46167.398480636577</v>
       </c>
       <c r="Q106" s="4">
-        <v>46169.3125</v>
+        <v>46170.25</v>
       </c>
       <c r="R106" s="4">
-        <v>46170.486638159724</v>
+        <v>46170.38833533565</v>
       </c>
       <c r="S106">
-        <v>5002.000</v>
+        <v>767.000</v>
       </c>
       <c r="T106">
-        <v>5002.000</v>
+        <v>767.000</v>
       </c>
       <c r="U106">
         <v>0</v>
@@ -6543,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="W106" s="4">
-        <v>46171.52288329861</v>
+        <v>46171.521805752316</v>
       </c>
     </row>
     <row r="107">
@@ -6560,7 +6560,7 @@
         <v>24</v>
       </c>
       <c r="E107">
-        <v>7243663</v>
+        <v>7243667</v>
       </c>
       <c r="F107" t="s">
         <v>197</v>
@@ -6575,19 +6575,19 @@
         <v>198</v>
       </c>
       <c r="P107" s="1">
-        <v>46167.396879664353</v>
+        <v>46167.398084108798</v>
       </c>
       <c r="Q107" s="4">
-        <v>46168.3125</v>
+        <v>46170.25</v>
       </c>
       <c r="R107" s="4">
-        <v>46168.372719247687</v>
+        <v>46170.366140659724</v>
       </c>
       <c r="S107">
-        <v>7178.000</v>
+        <v>7345.000</v>
       </c>
       <c r="T107">
-        <v>7178.000</v>
+        <v>7345.000</v>
       </c>
       <c r="U107">
         <v>0</v>
@@ -6596,7 +6596,7 @@
         <v>0</v>
       </c>
       <c r="W107" s="4">
-        <v>46168.383504201389</v>
+        <v>46170.37235636574</v>
       </c>
     </row>
     <row r="108">
@@ -6613,7 +6613,7 @@
         <v>24</v>
       </c>
       <c r="E108">
-        <v>7243660</v>
+        <v>7243666</v>
       </c>
       <c r="F108" t="s">
         <v>199</v>
@@ -6628,19 +6628,19 @@
         <v>200</v>
       </c>
       <c r="P108" s="1">
-        <v>46167.396469907406</v>
+        <v>46167.397709988429</v>
       </c>
       <c r="Q108" s="4">
-        <v>46168.375</v>
+        <v>46169.444444444445</v>
       </c>
       <c r="R108" s="4">
-        <v>46168.522693749997</v>
+        <v>46169.627317511571</v>
       </c>
       <c r="S108">
-        <v>15726.000</v>
+        <v>5379.000</v>
       </c>
       <c r="T108">
-        <v>15726.000</v>
+        <v>5379.000</v>
       </c>
       <c r="U108">
         <v>0</v>
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="W108" s="4">
-        <v>46168.603323611111</v>
+        <v>46170.372355636573</v>
       </c>
     </row>
     <row r="109">
@@ -6666,7 +6666,7 @@
         <v>24</v>
       </c>
       <c r="E109">
-        <v>7243658</v>
+        <v>7243664</v>
       </c>
       <c r="F109" t="s">
         <v>201</v>
@@ -6681,19 +6681,19 @@
         <v>202</v>
       </c>
       <c r="P109" s="1">
-        <v>46167.396019097221</v>
+        <v>46167.397293715279</v>
       </c>
       <c r="Q109" s="4">
-        <v>46168.479166666664</v>
+        <v>46169.3125</v>
       </c>
       <c r="R109" s="4">
-        <v>46168.596083993056</v>
+        <v>46170.486638159724</v>
       </c>
       <c r="S109">
-        <v>18164.000</v>
+        <v>5002.000</v>
       </c>
       <c r="T109">
-        <v>18164.000</v>
+        <v>5002.000</v>
       </c>
       <c r="U109">
         <v>0</v>
@@ -6702,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="W109" s="4">
-        <v>46168.603323067131</v>
+        <v>46171.52288329861</v>
       </c>
     </row>
     <row r="110">
@@ -6719,7 +6719,7 @@
         <v>24</v>
       </c>
       <c r="E110">
-        <v>7243656</v>
+        <v>7243663</v>
       </c>
       <c r="F110" t="s">
         <v>203</v>
@@ -6734,19 +6734,19 @@
         <v>204</v>
       </c>
       <c r="P110" s="1">
-        <v>46167.395494872682</v>
+        <v>46167.396879664353</v>
       </c>
       <c r="Q110" s="4">
-        <v>46168.25</v>
+        <v>46168.3125</v>
       </c>
       <c r="R110" s="4">
-        <v>46168.325715162035</v>
+        <v>46168.372719247687</v>
       </c>
       <c r="S110">
-        <v>8924.000</v>
+        <v>7178.000</v>
       </c>
       <c r="T110">
-        <v>8924.000</v>
+        <v>7178.000</v>
       </c>
       <c r="U110">
         <v>0</v>
@@ -6755,7 +6755,7 @@
         <v>0</v>
       </c>
       <c r="W110" s="4">
-        <v>46168.383503321762</v>
+        <v>46168.383504201389</v>
       </c>
     </row>
     <row r="111">
@@ -6772,7 +6772,7 @@
         <v>24</v>
       </c>
       <c r="E111">
-        <v>7234523</v>
+        <v>7243660</v>
       </c>
       <c r="F111" t="s">
         <v>205</v>
@@ -6787,16 +6787,19 @@
         <v>206</v>
       </c>
       <c r="P111" s="1">
-        <v>46164.418446909724</v>
+        <v>46167.396469907406</v>
+      </c>
+      <c r="Q111" s="4">
+        <v>46168.375</v>
       </c>
       <c r="R111" s="4">
-        <v>46164.542648229166</v>
+        <v>46168.522693749997</v>
       </c>
       <c r="S111">
-        <v>3573.000</v>
+        <v>15726.000</v>
       </c>
       <c r="T111">
-        <v>3573.000</v>
+        <v>15726.000</v>
       </c>
       <c r="U111">
         <v>0</v>
@@ -6805,7 +6808,7 @@
         <v>0</v>
       </c>
       <c r="W111" s="4">
-        <v>46164.552599270835</v>
+        <v>46168.603323611111</v>
       </c>
     </row>
     <row r="112">
@@ -6822,7 +6825,7 @@
         <v>24</v>
       </c>
       <c r="E112">
-        <v>7222955</v>
+        <v>7243658</v>
       </c>
       <c r="F112" t="s">
         <v>207</v>
@@ -6837,19 +6840,19 @@
         <v>208</v>
       </c>
       <c r="P112" s="1">
-        <v>46162.757414780091</v>
+        <v>46167.396019097221</v>
       </c>
       <c r="Q112" s="4">
-        <v>46164.260416666664</v>
+        <v>46168.479166666664</v>
       </c>
       <c r="R112" s="4">
-        <v>46164.550929016201</v>
+        <v>46168.596083993056</v>
       </c>
       <c r="S112">
-        <v>10360.000</v>
+        <v>18164.000</v>
       </c>
       <c r="T112">
-        <v>10360.000</v>
+        <v>18164.000</v>
       </c>
       <c r="U112">
         <v>0</v>
@@ -6858,7 +6861,7 @@
         <v>0</v>
       </c>
       <c r="W112" s="4">
-        <v>46164.552598877315</v>
+        <v>46168.603323067131</v>
       </c>
     </row>
     <row r="113">
@@ -6875,7 +6878,7 @@
         <v>24</v>
       </c>
       <c r="E113">
-        <v>7222913</v>
+        <v>7243656</v>
       </c>
       <c r="F113" t="s">
         <v>209</v>
@@ -6886,23 +6889,23 @@
       <c r="H113" t="s">
         <v>24</v>
       </c>
-      <c r="M113" s="5" t="s">
+      <c r="M113" t="s">
         <v>210</v>
       </c>
       <c r="P113" s="1">
-        <v>46162.756352662036</v>
+        <v>46167.395494872682</v>
       </c>
       <c r="Q113" s="4">
-        <v>46164.333333333336</v>
+        <v>46168.25</v>
       </c>
       <c r="R113" s="4">
-        <v>46164.404302395837</v>
+        <v>46168.325715162035</v>
       </c>
       <c r="S113">
-        <v>7657.000</v>
+        <v>8924.000</v>
       </c>
       <c r="T113">
-        <v>7657.000</v>
+        <v>8924.000</v>
       </c>
       <c r="U113">
         <v>0</v>
@@ -6911,7 +6914,7 @@
         <v>0</v>
       </c>
       <c r="W113" s="4">
-        <v>46164.453907951392</v>
+        <v>46168.383503321762</v>
       </c>
     </row>
     <row r="114">
@@ -6928,7 +6931,7 @@
         <v>24</v>
       </c>
       <c r="E114">
-        <v>7222907</v>
+        <v>7234523</v>
       </c>
       <c r="F114" t="s">
         <v>211</v>
@@ -6943,19 +6946,16 @@
         <v>212</v>
       </c>
       <c r="P114" s="1">
-        <v>46162.75522561343</v>
-      </c>
-      <c r="Q114" s="4">
-        <v>46163.368055555555</v>
+        <v>46164.418446909724</v>
       </c>
       <c r="R114" s="4">
-        <v>46163.519357025463</v>
+        <v>46164.542648229166</v>
       </c>
       <c r="S114">
-        <v>10357.000</v>
+        <v>3573.000</v>
       </c>
       <c r="T114">
-        <v>10357.000</v>
+        <v>3573.000</v>
       </c>
       <c r="U114">
         <v>0</v>
@@ -6964,7 +6964,7 @@
         <v>0</v>
       </c>
       <c r="W114" s="4">
-        <v>46163.541440972222</v>
+        <v>46164.552599270835</v>
       </c>
     </row>
     <row r="115">
@@ -6981,7 +6981,7 @@
         <v>24</v>
       </c>
       <c r="E115">
-        <v>7217995</v>
+        <v>7222955</v>
       </c>
       <c r="F115" t="s">
         <v>213</v>
@@ -6996,19 +6996,19 @@
         <v>214</v>
       </c>
       <c r="P115" s="1">
-        <v>46162.28924351852</v>
+        <v>46162.757414780091</v>
       </c>
       <c r="Q115" s="4">
-        <v>46163.291666666664</v>
+        <v>46164.260416666664</v>
       </c>
       <c r="R115" s="4">
-        <v>46163.616474340277</v>
+        <v>46164.550929016201</v>
       </c>
       <c r="S115">
-        <v>5708.000</v>
+        <v>10360.000</v>
       </c>
       <c r="T115">
-        <v>5708.000</v>
+        <v>10360.000</v>
       </c>
       <c r="U115">
         <v>0</v>
@@ -7017,7 +7017,7 @@
         <v>0</v>
       </c>
       <c r="W115" s="4">
-        <v>46164.389474687501</v>
+        <v>46164.552598877315</v>
       </c>
     </row>
     <row r="116">
@@ -7034,7 +7034,7 @@
         <v>24</v>
       </c>
       <c r="E116">
-        <v>7217994</v>
+        <v>7222913</v>
       </c>
       <c r="F116" t="s">
         <v>215</v>
@@ -7045,23 +7045,23 @@
       <c r="H116" t="s">
         <v>24</v>
       </c>
-      <c r="M116" t="s">
+      <c r="M116" s="5" t="s">
         <v>216</v>
       </c>
       <c r="P116" s="1">
-        <v>46162.288815127315</v>
+        <v>46162.756352662036</v>
       </c>
       <c r="Q116" s="4">
-        <v>46163.291666666664</v>
+        <v>46164.333333333336</v>
       </c>
       <c r="R116" s="4">
-        <v>46163.35348445602</v>
+        <v>46164.404302395837</v>
       </c>
       <c r="S116">
-        <v>3946.000</v>
+        <v>7657.000</v>
       </c>
       <c r="T116">
-        <v>3946.000</v>
+        <v>7657.000</v>
       </c>
       <c r="U116">
         <v>0</v>
@@ -7070,7 +7070,7 @@
         <v>0</v>
       </c>
       <c r="W116" s="4">
-        <v>46163.541440775465</v>
+        <v>46164.453907951392</v>
       </c>
     </row>
     <row r="117">
@@ -7087,7 +7087,7 @@
         <v>24</v>
       </c>
       <c r="E117">
-        <v>7217993</v>
+        <v>7222907</v>
       </c>
       <c r="F117" t="s">
         <v>217</v>
@@ -7101,23 +7101,20 @@
       <c r="M117" t="s">
         <v>218</v>
       </c>
-      <c r="O117" s="4">
-        <v>46162.416666666664</v>
-      </c>
       <c r="P117" s="1">
-        <v>46162.287909756946</v>
+        <v>46162.75522561343</v>
       </c>
       <c r="Q117" s="4">
-        <v>46162.416666666664</v>
+        <v>46163.368055555555</v>
       </c>
       <c r="R117" s="4">
-        <v>46163.518015046298</v>
+        <v>46163.519357025463</v>
       </c>
       <c r="S117">
-        <v>12356.000</v>
+        <v>10357.000</v>
       </c>
       <c r="T117">
-        <v>12356.000</v>
+        <v>10357.000</v>
       </c>
       <c r="U117">
         <v>0</v>
@@ -7126,7 +7123,7 @@
         <v>0</v>
       </c>
       <c r="W117" s="4">
-        <v>46163.541439895831</v>
+        <v>46163.541440972222</v>
       </c>
     </row>
     <row r="118">
@@ -7143,7 +7140,7 @@
         <v>24</v>
       </c>
       <c r="E118">
-        <v>7217991</v>
+        <v>7217995</v>
       </c>
       <c r="F118" t="s">
         <v>219</v>
@@ -7157,23 +7154,20 @@
       <c r="M118" t="s">
         <v>220</v>
       </c>
-      <c r="O118" s="4">
-        <v>46162.291666666664</v>
-      </c>
       <c r="P118" s="1">
-        <v>46162.28736678241</v>
+        <v>46162.28924351852</v>
       </c>
       <c r="Q118" s="4">
-        <v>46162.513220173612</v>
+        <v>46163.291666666664</v>
       </c>
       <c r="R118" s="4">
-        <v>46163.531940428242</v>
+        <v>46163.616474340277</v>
       </c>
       <c r="S118">
-        <v>12360.000</v>
+        <v>5708.000</v>
       </c>
       <c r="T118">
-        <v>12360.000</v>
+        <v>5708.000</v>
       </c>
       <c r="U118">
         <v>0</v>
@@ -7182,7 +7176,7 @@
         <v>0</v>
       </c>
       <c r="W118" s="4">
-        <v>46163.541439351851</v>
+        <v>46164.389474687501</v>
       </c>
     </row>
     <row r="119">
@@ -7199,7 +7193,7 @@
         <v>24</v>
       </c>
       <c r="E119">
-        <v>7209853</v>
+        <v>7217994</v>
       </c>
       <c r="F119" t="s">
         <v>221</v>
@@ -7214,16 +7208,19 @@
         <v>222</v>
       </c>
       <c r="P119" s="1">
-        <v>46161.375624884262</v>
+        <v>46162.288815127315</v>
+      </c>
+      <c r="Q119" s="4">
+        <v>46163.291666666664</v>
       </c>
       <c r="R119" s="4">
-        <v>46162.474544826386</v>
+        <v>46163.35348445602</v>
       </c>
       <c r="S119">
-        <v>10350.000</v>
+        <v>3946.000</v>
       </c>
       <c r="T119">
-        <v>10350.000</v>
+        <v>3946.000</v>
       </c>
       <c r="U119">
         <v>0</v>
@@ -7232,7 +7229,7 @@
         <v>0</v>
       </c>
       <c r="W119" s="4">
-        <v>46163.484965937503</v>
+        <v>46163.541440775465</v>
       </c>
     </row>
     <row r="120">
@@ -7249,7 +7246,7 @@
         <v>24</v>
       </c>
       <c r="E120">
-        <v>7209851</v>
+        <v>7217993</v>
       </c>
       <c r="F120" t="s">
         <v>223</v>
@@ -7263,17 +7260,23 @@
       <c r="M120" t="s">
         <v>224</v>
       </c>
+      <c r="O120" s="4">
+        <v>46162.416666666664</v>
+      </c>
       <c r="P120" s="1">
-        <v>46161.374809525463</v>
+        <v>46162.287909756946</v>
+      </c>
+      <c r="Q120" s="4">
+        <v>46162.416666666664</v>
       </c>
       <c r="R120" s="4">
-        <v>46168.442082719906</v>
+        <v>46163.518015046298</v>
       </c>
       <c r="S120">
-        <v>10564.000</v>
+        <v>12356.000</v>
       </c>
       <c r="T120">
-        <v>10564.000</v>
+        <v>12356.000</v>
       </c>
       <c r="U120">
         <v>0</v>
@@ -7282,7 +7285,7 @@
         <v>0</v>
       </c>
       <c r="W120" s="4">
-        <v>46168.603322337964</v>
+        <v>46163.541439895831</v>
       </c>
     </row>
     <row r="121">
@@ -7299,7 +7302,7 @@
         <v>24</v>
       </c>
       <c r="E121">
-        <v>7209848</v>
+        <v>7217991</v>
       </c>
       <c r="F121" t="s">
         <v>225</v>
@@ -7314,22 +7317,22 @@
         <v>226</v>
       </c>
       <c r="O121" s="4">
-        <v>46161.291666666664</v>
+        <v>46162.291666666664</v>
       </c>
       <c r="P121" s="1">
-        <v>46161.373708449071</v>
+        <v>46162.28736678241</v>
       </c>
       <c r="Q121" s="4">
-        <v>46161.586805555555</v>
+        <v>46162.513220173612</v>
       </c>
       <c r="R121" s="4">
-        <v>46163.626690358797</v>
+        <v>46163.531940428242</v>
       </c>
       <c r="S121">
-        <v>16674.000</v>
+        <v>12360.000</v>
       </c>
       <c r="T121">
-        <v>16674.000</v>
+        <v>12360.000</v>
       </c>
       <c r="U121">
         <v>0</v>
@@ -7338,7 +7341,7 @@
         <v>0</v>
       </c>
       <c r="W121" s="4">
-        <v>46164.389386608796</v>
+        <v>46163.541439351851</v>
       </c>
     </row>
     <row r="122">
@@ -7355,7 +7358,7 @@
         <v>24</v>
       </c>
       <c r="E122">
-        <v>7186225</v>
+        <v>7209853</v>
       </c>
       <c r="F122" t="s">
         <v>227</v>
@@ -7370,19 +7373,16 @@
         <v>228</v>
       </c>
       <c r="P122" s="1">
-        <v>46157.585703935183</v>
-      </c>
-      <c r="Q122" s="4">
-        <v>46160.493105243055</v>
+        <v>46161.375624884262</v>
       </c>
       <c r="R122" s="4">
-        <v>46170.487253356485</v>
+        <v>46162.474544826386</v>
       </c>
       <c r="S122">
-        <v>13685.000</v>
+        <v>10350.000</v>
       </c>
       <c r="T122">
-        <v>13685.000</v>
+        <v>10350.000</v>
       </c>
       <c r="U122">
         <v>0</v>
@@ -7391,7 +7391,7 @@
         <v>0</v>
       </c>
       <c r="W122" s="4">
-        <v>46171.521805011573</v>
+        <v>46163.484965937503</v>
       </c>
     </row>
     <row r="123">
@@ -7408,7 +7408,7 @@
         <v>24</v>
       </c>
       <c r="E123">
-        <v>7186224</v>
+        <v>7209851</v>
       </c>
       <c r="F123" t="s">
         <v>229</v>
@@ -7420,22 +7420,19 @@
         <v>24</v>
       </c>
       <c r="M123" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P123" s="1">
-        <v>46157.585680983793</v>
-      </c>
-      <c r="Q123" s="4">
-        <v>46160.493105243055</v>
+        <v>46161.374809525463</v>
       </c>
       <c r="R123" s="4">
-        <v>46160.607764236112</v>
+        <v>46168.442082719906</v>
       </c>
       <c r="S123">
-        <v>8153.000</v>
+        <v>10564.000</v>
       </c>
       <c r="T123">
-        <v>8153.000</v>
+        <v>10564.000</v>
       </c>
       <c r="U123">
         <v>0</v>
@@ -7444,7 +7441,7 @@
         <v>0</v>
       </c>
       <c r="W123" s="4">
-        <v>46161.606680011573</v>
+        <v>46168.603322337964</v>
       </c>
     </row>
     <row r="124">
@@ -7461,10 +7458,10 @@
         <v>24</v>
       </c>
       <c r="E124">
-        <v>7186209</v>
+        <v>7209848</v>
       </c>
       <c r="F124" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G124" t="s">
         <v>24</v>
@@ -7473,22 +7470,25 @@
         <v>24</v>
       </c>
       <c r="M124" t="s">
-        <v>231</v>
+        <v>232</v>
+      </c>
+      <c r="O124" s="4">
+        <v>46161.291666666664</v>
       </c>
       <c r="P124" s="1">
-        <v>46157.580364664354</v>
+        <v>46161.373708449071</v>
       </c>
       <c r="Q124" s="4">
-        <v>46160.367256516205</v>
+        <v>46161.586805555555</v>
       </c>
       <c r="R124" s="4">
-        <v>46160.444021875002</v>
+        <v>46163.626690358797</v>
       </c>
       <c r="S124">
-        <v>19189.000</v>
+        <v>16674.000</v>
       </c>
       <c r="T124">
-        <v>19189.000</v>
+        <v>16674.000</v>
       </c>
       <c r="U124">
         <v>0</v>
@@ -7497,7 +7497,7 @@
         <v>0</v>
       </c>
       <c r="W124" s="4">
-        <v>46161.605472025461</v>
+        <v>46164.389386608796</v>
       </c>
     </row>
     <row r="125">
@@ -7514,10 +7514,10 @@
         <v>24</v>
       </c>
       <c r="E125">
-        <v>7185903</v>
+        <v>7186225</v>
       </c>
       <c r="F125" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G125" t="s">
         <v>24</v>
@@ -7526,22 +7526,22 @@
         <v>24</v>
       </c>
       <c r="M125" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P125" s="1">
-        <v>46157.55131412037</v>
+        <v>46157.585703935183</v>
       </c>
       <c r="Q125" s="4">
         <v>46160.493105243055</v>
       </c>
       <c r="R125" s="4">
-        <v>46160.545683645832</v>
+        <v>46170.487253356485</v>
       </c>
       <c r="S125">
-        <v>39356.000</v>
+        <v>13685.000</v>
       </c>
       <c r="T125">
-        <v>39356.000</v>
+        <v>13685.000</v>
       </c>
       <c r="U125">
         <v>0</v>
@@ -7550,7 +7550,7 @@
         <v>0</v>
       </c>
       <c r="W125" s="4">
-        <v>46161.604525312498</v>
+        <v>46171.521805011573</v>
       </c>
     </row>
     <row r="126">
@@ -7567,37 +7567,34 @@
         <v>24</v>
       </c>
       <c r="E126">
-        <v>7177836</v>
+        <v>7186224</v>
       </c>
       <c r="F126" t="s">
+        <v>235</v>
+      </c>
+      <c r="G126" t="s">
+        <v>24</v>
+      </c>
+      <c r="H126" t="s">
+        <v>24</v>
+      </c>
+      <c r="M126" t="s">
         <v>234</v>
       </c>
-      <c r="G126" t="s">
-        <v>24</v>
-      </c>
-      <c r="H126" t="s">
-        <v>24</v>
-      </c>
-      <c r="M126" t="s">
-        <v>235</v>
-      </c>
-      <c r="O126" s="4">
-        <v>46157.416666666664</v>
-      </c>
       <c r="P126" s="1">
-        <v>46155.705813773151</v>
+        <v>46157.585680983793</v>
       </c>
       <c r="Q126" s="4">
-        <v>46157.466666666667</v>
+        <v>46160.493105243055</v>
       </c>
       <c r="R126" s="4">
-        <v>46160.360912615739</v>
+        <v>46160.607764236112</v>
       </c>
       <c r="S126">
-        <v>17794.000</v>
+        <v>8153.000</v>
       </c>
       <c r="T126">
-        <v>17794.000</v>
+        <v>8153.000</v>
       </c>
       <c r="U126">
         <v>0</v>
@@ -7606,7 +7603,7 @@
         <v>0</v>
       </c>
       <c r="W126" s="4">
-        <v>46160.503910451385</v>
+        <v>46161.606680011573</v>
       </c>
     </row>
     <row r="127">
@@ -7623,7 +7620,7 @@
         <v>24</v>
       </c>
       <c r="E127">
-        <v>7175007</v>
+        <v>7186209</v>
       </c>
       <c r="F127" t="s">
         <v>236</v>
@@ -7637,23 +7634,20 @@
       <c r="M127" t="s">
         <v>237</v>
       </c>
-      <c r="O127" s="4">
-        <v>46157.291666666664</v>
-      </c>
       <c r="P127" s="1">
-        <v>46155.454049652777</v>
+        <v>46157.580364664354</v>
       </c>
       <c r="Q127" s="4">
-        <v>46157.35833333333</v>
+        <v>46160.367256516205</v>
       </c>
       <c r="R127" s="4">
-        <v>46157.601774965275</v>
+        <v>46160.444021875002</v>
       </c>
       <c r="S127">
-        <v>21375.000</v>
+        <v>19189.000</v>
       </c>
       <c r="T127">
-        <v>21375.000</v>
+        <v>19189.000</v>
       </c>
       <c r="U127">
         <v>0</v>
@@ -7662,7 +7656,7 @@
         <v>0</v>
       </c>
       <c r="W127" s="4">
-        <v>46157.688587037039</v>
+        <v>46161.605472025461</v>
       </c>
     </row>
     <row r="128">
@@ -7679,7 +7673,7 @@
         <v>24</v>
       </c>
       <c r="E128">
-        <v>7167099</v>
+        <v>7185903</v>
       </c>
       <c r="F128" t="s">
         <v>238</v>
@@ -7694,16 +7688,19 @@
         <v>239</v>
       </c>
       <c r="P128" s="1">
-        <v>46154.541764120368</v>
+        <v>46157.55131412037</v>
+      </c>
+      <c r="Q128" s="4">
+        <v>46160.493105243055</v>
       </c>
       <c r="R128" s="4">
-        <v>46155.643980821762</v>
+        <v>46160.545683645832</v>
       </c>
       <c r="S128">
-        <v>11855.000</v>
+        <v>39356.000</v>
       </c>
       <c r="T128">
-        <v>11855.000</v>
+        <v>39356.000</v>
       </c>
       <c r="U128">
         <v>0</v>
@@ -7712,7 +7709,7 @@
         <v>0</v>
       </c>
       <c r="W128" s="4">
-        <v>46157.304165428242</v>
+        <v>46161.604525312498</v>
       </c>
     </row>
     <row r="129">
@@ -7726,69 +7723,231 @@
         <v>24</v>
       </c>
       <c r="D129" t="s">
+        <v>24</v>
+      </c>
+      <c r="E129">
+        <v>7177836</v>
+      </c>
+      <c r="F129" t="s">
         <v>240</v>
       </c>
-      <c r="E129">
+      <c r="G129" t="s">
+        <v>24</v>
+      </c>
+      <c r="H129" t="s">
+        <v>24</v>
+      </c>
+      <c r="M129" t="s">
+        <v>241</v>
+      </c>
+      <c r="O129" s="4">
+        <v>46157.416666666664</v>
+      </c>
+      <c r="P129" s="1">
+        <v>46155.705813773151</v>
+      </c>
+      <c r="Q129" s="4">
+        <v>46157.466666666667</v>
+      </c>
+      <c r="R129" s="4">
+        <v>46160.360912615739</v>
+      </c>
+      <c r="S129">
+        <v>17794.000</v>
+      </c>
+      <c r="T129">
+        <v>17794.000</v>
+      </c>
+      <c r="U129">
+        <v>0</v>
+      </c>
+      <c r="V129">
+        <v>0</v>
+      </c>
+      <c r="W129" s="4">
+        <v>46160.503910451385</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>19</v>
+      </c>
+      <c r="B130" t="s">
+        <v>24</v>
+      </c>
+      <c r="C130" t="s">
+        <v>24</v>
+      </c>
+      <c r="D130" t="s">
+        <v>24</v>
+      </c>
+      <c r="E130">
+        <v>7175007</v>
+      </c>
+      <c r="F130" t="s">
+        <v>242</v>
+      </c>
+      <c r="G130" t="s">
+        <v>24</v>
+      </c>
+      <c r="H130" t="s">
+        <v>24</v>
+      </c>
+      <c r="M130" t="s">
+        <v>243</v>
+      </c>
+      <c r="O130" s="4">
+        <v>46157.291666666664</v>
+      </c>
+      <c r="P130" s="1">
+        <v>46155.454049652777</v>
+      </c>
+      <c r="Q130" s="4">
+        <v>46157.35833333333</v>
+      </c>
+      <c r="R130" s="4">
+        <v>46157.601774965275</v>
+      </c>
+      <c r="S130">
+        <v>21375.000</v>
+      </c>
+      <c r="T130">
+        <v>21375.000</v>
+      </c>
+      <c r="U130">
+        <v>0</v>
+      </c>
+      <c r="V130">
+        <v>0</v>
+      </c>
+      <c r="W130" s="4">
+        <v>46157.688587037039</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>19</v>
+      </c>
+      <c r="B131" t="s">
+        <v>24</v>
+      </c>
+      <c r="C131" t="s">
+        <v>24</v>
+      </c>
+      <c r="D131" t="s">
+        <v>24</v>
+      </c>
+      <c r="E131">
+        <v>7167099</v>
+      </c>
+      <c r="F131" t="s">
+        <v>244</v>
+      </c>
+      <c r="G131" t="s">
+        <v>24</v>
+      </c>
+      <c r="H131" t="s">
+        <v>24</v>
+      </c>
+      <c r="M131" t="s">
+        <v>245</v>
+      </c>
+      <c r="P131" s="1">
+        <v>46154.541764120368</v>
+      </c>
+      <c r="R131" s="4">
+        <v>46155.643980821762</v>
+      </c>
+      <c r="S131">
+        <v>11855.000</v>
+      </c>
+      <c r="T131">
+        <v>11855.000</v>
+      </c>
+      <c r="U131">
+        <v>0</v>
+      </c>
+      <c r="V131">
+        <v>0</v>
+      </c>
+      <c r="W131" s="4">
+        <v>46157.304165428242</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>19</v>
+      </c>
+      <c r="B132" t="s">
+        <v>24</v>
+      </c>
+      <c r="C132" t="s">
+        <v>24</v>
+      </c>
+      <c r="D132" t="s">
+        <v>246</v>
+      </c>
+      <c r="E132">
         <v>7108660</v>
       </c>
-      <c r="F129" t="s">
-        <v>241</v>
-      </c>
-      <c r="G129" t="s">
-        <v>24</v>
-      </c>
-      <c r="H129" t="s">
-        <v>242</v>
-      </c>
-      <c r="I129" t="s">
-        <v>242</v>
-      </c>
-      <c r="J129" t="s">
-        <v>243</v>
-      </c>
-      <c r="K129" t="s">
-        <v>244</v>
-      </c>
-      <c r="M129" t="s">
-        <v>24</v>
-      </c>
-      <c r="P129" s="1">
+      <c r="F132" t="s">
+        <v>247</v>
+      </c>
+      <c r="G132" t="s">
+        <v>24</v>
+      </c>
+      <c r="H132" t="s">
+        <v>248</v>
+      </c>
+      <c r="I132" t="s">
+        <v>248</v>
+      </c>
+      <c r="J132" t="s">
+        <v>249</v>
+      </c>
+      <c r="K132" t="s">
+        <v>250</v>
+      </c>
+      <c r="M132" t="s">
+        <v>24</v>
+      </c>
+      <c r="P132" s="1">
         <v>46142.678548877317</v>
       </c>
-      <c r="R129" s="4">
+      <c r="R132" s="4">
         <v>46142.683541168983</v>
       </c>
-      <c r="S129">
+      <c r="S132">
         <v>100.000</v>
       </c>
-      <c r="T129">
+      <c r="T132">
         <v>100.000</v>
       </c>
-      <c r="U129">
-        <v>0</v>
-      </c>
-      <c r="V129">
-        <v>0</v>
-      </c>
-      <c r="W129" s="4">
+      <c r="U132">
+        <v>0</v>
+      </c>
+      <c r="V132">
+        <v>0</v>
+      </c>
+      <c r="W132" s="4">
         <v>46142.68461369213</v>
       </c>
     </row>
-    <row r="130">
-      <c r="S130" s="2">
-        <f ca="1">SUM(S2:S129)</f>
-        <v>0</v>
-      </c>
-      <c r="T130" s="2">
-        <f ca="1">SUM(T2:T129)</f>
-        <v>0</v>
-      </c>
-      <c r="U130" s="2">
-        <f ca="1">SUM(U2:U129)</f>
-        <v>0</v>
-      </c>
-      <c r="V130" s="2">
-        <f ca="1">SUM(V2:V129)</f>
+    <row r="133">
+      <c r="S133" s="2">
+        <f ca="1">SUM(S2:S132)</f>
+        <v>0</v>
+      </c>
+      <c r="T133" s="2">
+        <f ca="1">SUM(T2:T132)</f>
+        <v>0</v>
+      </c>
+      <c r="U133" s="2">
+        <f ca="1">SUM(U2:U132)</f>
+        <v>0</v>
+      </c>
+      <c r="V133" s="2">
+        <f ca="1">SUM(V2:V132)</f>
         <v>0</v>
       </c>
     </row>

--- a/InOrders_latest.xlsx
+++ b/InOrders_latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
   <si>
     <t>Status</t>
   </si>
@@ -91,6 +91,12 @@
     <t/>
   </si>
   <si>
+    <t>0101893003</t>
+  </si>
+  <si>
+    <t>Truck 75</t>
+  </si>
+  <si>
     <t>0101891040</t>
   </si>
   <si>
@@ -103,72 +109,75 @@
     <t>Truck 73</t>
   </si>
   <si>
+    <t>520065211900100</t>
+  </si>
+  <si>
+    <t>2026-06-10 | Imteks (Origin: Georgia) | ASN-IMT-001</t>
+  </si>
+  <si>
+    <t>520065211800100</t>
+  </si>
+  <si>
+    <t>520064219500100</t>
+  </si>
+  <si>
+    <t>2026-06-08 | Imteks Giyim (TR) | ASN-ITR-001</t>
+  </si>
+  <si>
+    <t>520064217600100</t>
+  </si>
+  <si>
+    <t>2026-06-08 | Imteks Giyim (GE) | ASN-IGE-001</t>
+  </si>
+  <si>
+    <t>520064217700100</t>
+  </si>
+  <si>
+    <t>520064218000100</t>
+  </si>
+  <si>
+    <t>520064218100100</t>
+  </si>
+  <si>
+    <t>520064217800100</t>
+  </si>
+  <si>
+    <t>520064217900100</t>
+  </si>
+  <si>
+    <t>520064218200100</t>
+  </si>
+  <si>
+    <t>520064218300100</t>
+  </si>
+  <si>
+    <t>520064217100100</t>
+  </si>
+  <si>
+    <t>520064217200100</t>
+  </si>
+  <si>
+    <t>520064217300100</t>
+  </si>
+  <si>
+    <t>520064217400100</t>
+  </si>
+  <si>
+    <t>520064217500100</t>
+  </si>
+  <si>
+    <t>520063612400200</t>
+  </si>
+  <si>
+    <t>Arrival space</t>
+  </si>
+  <si>
     <t>0101887837</t>
   </si>
   <si>
     <t>Truck 72</t>
   </si>
   <si>
-    <t>520065211900100</t>
-  </si>
-  <si>
-    <t>2026-06-10 | Imteks (Origin: Georgia) | ASN-IMT-001</t>
-  </si>
-  <si>
-    <t>520065211800100</t>
-  </si>
-  <si>
-    <t>520064219500100</t>
-  </si>
-  <si>
-    <t>2026-06-08 | Imteks Giyim (TR) | ASN-ITR-001</t>
-  </si>
-  <si>
-    <t>520064217600100</t>
-  </si>
-  <si>
-    <t>2026-06-08 | Imteks Giyim (GE) | ASN-IGE-001</t>
-  </si>
-  <si>
-    <t>520064217700100</t>
-  </si>
-  <si>
-    <t>520064218000100</t>
-  </si>
-  <si>
-    <t>520064218100100</t>
-  </si>
-  <si>
-    <t>520064217800100</t>
-  </si>
-  <si>
-    <t>520064217900100</t>
-  </si>
-  <si>
-    <t>520064218200100</t>
-  </si>
-  <si>
-    <t>520064218300100</t>
-  </si>
-  <si>
-    <t>520064217100100</t>
-  </si>
-  <si>
-    <t>520064217200100</t>
-  </si>
-  <si>
-    <t>520064217300100</t>
-  </si>
-  <si>
-    <t>520064217400100</t>
-  </si>
-  <si>
-    <t>520064217500100</t>
-  </si>
-  <si>
-    <t>520063612400200</t>
-  </si>
-  <si>
     <t>0101886222</t>
   </si>
   <si>
@@ -185,9 +194,6 @@
   </si>
   <si>
     <t>Truck 69</t>
-  </si>
-  <si>
-    <t>Arrival space</t>
   </si>
   <si>
     <t>0101878070</t>
@@ -1139,7 +1145,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W133"/>
+  <dimension ref="A1:W134"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="13.421875" customWidth="1"/>
@@ -1250,7 +1256,7 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>7386859</v>
+        <v>7396634</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
@@ -1265,22 +1271,22 @@
         <v>26</v>
       </c>
       <c r="P2" s="1">
-        <v>46199.698073726853</v>
+        <v>46202.563591863429</v>
       </c>
       <c r="S2">
-        <v>5956.000</v>
+        <v>6843.000</v>
       </c>
       <c r="T2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5956.000</v>
+        <v>6843.000</v>
       </c>
       <c r="V2">
         <v>0</v>
       </c>
       <c r="W2" s="4">
-        <v>46199.698821261576</v>
+        <v>46202.564356793984</v>
       </c>
     </row>
     <row r="3">
@@ -1297,7 +1303,7 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>7386838</v>
+        <v>7386859</v>
       </c>
       <c r="F3" t="s">
         <v>27</v>
@@ -1312,22 +1318,22 @@
         <v>28</v>
       </c>
       <c r="P3" s="1">
-        <v>46199.694861493059</v>
+        <v>46199.698073726853</v>
       </c>
       <c r="S3">
-        <v>8551.000</v>
+        <v>5956.000</v>
       </c>
       <c r="T3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>8551.000</v>
+        <v>5956.000</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
       <c r="W3" s="4">
-        <v>46199.695792789353</v>
+        <v>46199.698821261576</v>
       </c>
     </row>
     <row r="4">
@@ -1344,7 +1350,7 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>7386771</v>
+        <v>7386838</v>
       </c>
       <c r="F4" t="s">
         <v>29</v>
@@ -1359,22 +1365,22 @@
         <v>30</v>
       </c>
       <c r="P4" s="1">
-        <v>46199.682600925924</v>
+        <v>46199.694861493059</v>
       </c>
       <c r="S4">
-        <v>9251.000</v>
+        <v>8551.000</v>
       </c>
       <c r="T4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>9251.000</v>
+        <v>8551.000</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
       <c r="W4" s="4">
-        <v>46199.68826354167</v>
+        <v>46199.695792789353</v>
       </c>
     </row>
     <row r="5">
@@ -2178,7 +2184,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
@@ -2190,10 +2196,10 @@
         <v>24</v>
       </c>
       <c r="E22">
-        <v>7380191</v>
+        <v>7386771</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G22" t="s">
         <v>24</v>
@@ -2202,30 +2208,30 @@
         <v>24</v>
       </c>
       <c r="M22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P22" s="1">
-        <v>46198.481063622683</v>
+        <v>46199.682600925924</v>
       </c>
       <c r="S22">
-        <v>8875.000</v>
+        <v>9251.000</v>
       </c>
       <c r="T22">
         <v>0</v>
       </c>
       <c r="U22">
-        <v>8875.000</v>
+        <v>9251.000</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22" s="4">
-        <v>46198.483989386572</v>
+        <v>46202.354833993057</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -2237,10 +2243,10 @@
         <v>24</v>
       </c>
       <c r="E23">
-        <v>7380190</v>
+        <v>7380191</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G23" t="s">
         <v>24</v>
@@ -2249,30 +2255,33 @@
         <v>24</v>
       </c>
       <c r="M23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P23" s="1">
-        <v>46198.481004479167</v>
+        <v>46198.481063622683</v>
+      </c>
+      <c r="R23" s="4">
+        <v>46202.582847453705</v>
       </c>
       <c r="S23">
-        <v>9916.000</v>
+        <v>8875.000</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>8839.000</v>
       </c>
       <c r="U23">
-        <v>9916.000</v>
+        <v>36.000</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23" s="4">
-        <v>46198.483988460648</v>
+        <v>46202.446861608798</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -2284,10 +2293,10 @@
         <v>24</v>
       </c>
       <c r="E24">
-        <v>7379335</v>
+        <v>7380190</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G24" t="s">
         <v>24</v>
@@ -2296,30 +2305,33 @@
         <v>24</v>
       </c>
       <c r="M24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P24" s="1">
-        <v>46198.391359803238</v>
+        <v>46198.481004479167</v>
+      </c>
+      <c r="R24" s="4">
+        <v>46203.329736886575</v>
       </c>
       <c r="S24">
-        <v>11465.000</v>
+        <v>9916.000</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>9916.000</v>
       </c>
       <c r="U24">
-        <v>11465.000</v>
+        <v>0</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24" s="4">
-        <v>46198.392504664349</v>
+        <v>46202.447466701386</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -2331,7 +2343,7 @@
         <v>24</v>
       </c>
       <c r="E25">
-        <v>7374441</v>
+        <v>7379335</v>
       </c>
       <c r="F25" t="s">
         <v>58</v>
@@ -2346,30 +2358,27 @@
         <v>59</v>
       </c>
       <c r="P25" s="1">
-        <v>46197.552075150466</v>
-      </c>
-      <c r="R25" s="4">
-        <v>46202.31123402778</v>
+        <v>46198.391359803238</v>
       </c>
       <c r="S25">
-        <v>10194.000</v>
+        <v>11465.000</v>
       </c>
       <c r="T25">
-        <v>9994.000</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>200.000</v>
+        <v>11465.000</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25" s="4">
-        <v>46199.252992164351</v>
+        <v>46202.445604826389</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -2381,7 +2390,7 @@
         <v>24</v>
       </c>
       <c r="E26">
-        <v>7349603</v>
+        <v>7374441</v>
       </c>
       <c r="F26" t="s">
         <v>60</v>
@@ -2395,32 +2404,26 @@
       <c r="M26" t="s">
         <v>61</v>
       </c>
-      <c r="N26" s="1">
-        <v>46190</v>
-      </c>
       <c r="P26" s="1">
-        <v>46189.643392094906</v>
-      </c>
-      <c r="Q26" s="4">
-        <v>46190.996527777781</v>
+        <v>46197.552075150466</v>
       </c>
       <c r="R26" s="4">
-        <v>46190.579668171296</v>
+        <v>46202.31123402778</v>
       </c>
       <c r="S26">
-        <v>5965.000</v>
+        <v>10194.000</v>
       </c>
       <c r="T26">
-        <v>5965.000</v>
+        <v>9994.000</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>200.000</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26" s="4">
-        <v>46191.313541932868</v>
+        <v>46199.252992164351</v>
       </c>
     </row>
     <row r="27">
@@ -2437,7 +2440,7 @@
         <v>24</v>
       </c>
       <c r="E27">
-        <v>7166305</v>
+        <v>7349603</v>
       </c>
       <c r="F27" t="s">
         <v>62</v>
@@ -2452,31 +2455,31 @@
         <v>63</v>
       </c>
       <c r="N27" s="1">
-        <v>46152</v>
+        <v>46190</v>
       </c>
       <c r="P27" s="1">
-        <v>46154.508897418978</v>
+        <v>46189.643392094906</v>
       </c>
       <c r="Q27" s="4">
-        <v>46162.29583333333</v>
+        <v>46190.996527777781</v>
       </c>
       <c r="R27" s="4">
-        <v>46154.512428125003</v>
+        <v>46190.579668171296</v>
       </c>
       <c r="S27">
-        <v>100.000</v>
+        <v>5965.000</v>
       </c>
       <c r="T27">
-        <v>98.000</v>
+        <v>5965.000</v>
       </c>
       <c r="U27">
-        <v>2.000</v>
+        <v>0</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27" s="4">
-        <v>46190.318931481481</v>
+        <v>46191.313541932868</v>
       </c>
     </row>
     <row r="28">
@@ -2493,7 +2496,7 @@
         <v>24</v>
       </c>
       <c r="E28">
-        <v>7374444</v>
+        <v>7166305</v>
       </c>
       <c r="F28" t="s">
         <v>64</v>
@@ -2507,26 +2510,32 @@
       <c r="M28" t="s">
         <v>65</v>
       </c>
+      <c r="N28" s="1">
+        <v>46152</v>
+      </c>
       <c r="P28" s="1">
-        <v>46197.553791817132</v>
+        <v>46154.508897418978</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>46162.29583333333</v>
       </c>
       <c r="R28" s="4">
-        <v>46198.500830902776</v>
+        <v>46154.512428125003</v>
       </c>
       <c r="S28">
-        <v>10410.000</v>
+        <v>100.000</v>
       </c>
       <c r="T28">
-        <v>10410.000</v>
+        <v>98.000</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.000</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28" s="4">
-        <v>46198.517632291667</v>
+        <v>46190.318931481481</v>
       </c>
     </row>
     <row r="29">
@@ -2543,7 +2552,7 @@
         <v>24</v>
       </c>
       <c r="E29">
-        <v>7373968</v>
+        <v>7374444</v>
       </c>
       <c r="F29" t="s">
         <v>66</v>
@@ -2558,16 +2567,16 @@
         <v>67</v>
       </c>
       <c r="P29" s="1">
-        <v>46197.485422534723</v>
+        <v>46197.553791817132</v>
       </c>
       <c r="R29" s="4">
-        <v>46199.287059374998</v>
+        <v>46198.500830902776</v>
       </c>
       <c r="S29">
-        <v>18575.000</v>
+        <v>10410.000</v>
       </c>
       <c r="T29">
-        <v>18575.000</v>
+        <v>10410.000</v>
       </c>
       <c r="U29">
         <v>0</v>
@@ -2576,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="W29" s="4">
-        <v>46199.324616701386</v>
+        <v>46198.517632291667</v>
       </c>
     </row>
     <row r="30">
@@ -2593,7 +2602,7 @@
         <v>24</v>
       </c>
       <c r="E30">
-        <v>7369152</v>
+        <v>7373968</v>
       </c>
       <c r="F30" t="s">
         <v>68</v>
@@ -2608,16 +2617,16 @@
         <v>69</v>
       </c>
       <c r="P30" s="1">
-        <v>46196.459848344908</v>
+        <v>46197.485422534723</v>
       </c>
       <c r="R30" s="4">
-        <v>46197.493816087961</v>
+        <v>46199.287059374998</v>
       </c>
       <c r="S30">
-        <v>300.000</v>
+        <v>18575.000</v>
       </c>
       <c r="T30">
-        <v>300.000</v>
+        <v>18575.000</v>
       </c>
       <c r="U30">
         <v>0</v>
@@ -2626,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="W30" s="4">
-        <v>46197.550397141204</v>
+        <v>46199.324616701386</v>
       </c>
     </row>
     <row r="31">
@@ -2643,7 +2652,7 @@
         <v>24</v>
       </c>
       <c r="E31">
-        <v>7369151</v>
+        <v>7369152</v>
       </c>
       <c r="F31" t="s">
         <v>70</v>
@@ -2658,16 +2667,16 @@
         <v>71</v>
       </c>
       <c r="P31" s="1">
-        <v>46196.459830243053</v>
+        <v>46196.459848344908</v>
       </c>
       <c r="R31" s="4">
-        <v>46197.531721678242</v>
+        <v>46197.493816087961</v>
       </c>
       <c r="S31">
-        <v>3638.000</v>
+        <v>300.000</v>
       </c>
       <c r="T31">
-        <v>3638.000</v>
+        <v>300.000</v>
       </c>
       <c r="U31">
         <v>0</v>
@@ -2676,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="W31" s="4">
-        <v>46197.550396956016</v>
+        <v>46197.550397141204</v>
       </c>
     </row>
     <row r="32">
@@ -2693,7 +2702,7 @@
         <v>24</v>
       </c>
       <c r="E32">
-        <v>7368806</v>
+        <v>7369151</v>
       </c>
       <c r="F32" t="s">
         <v>72</v>
@@ -2708,16 +2717,16 @@
         <v>73</v>
       </c>
       <c r="P32" s="1">
-        <v>46196.377559722219</v>
+        <v>46196.459830243053</v>
       </c>
       <c r="R32" s="4">
-        <v>46197.497936342595</v>
+        <v>46197.531721678242</v>
       </c>
       <c r="S32">
-        <v>5755.000</v>
+        <v>3638.000</v>
       </c>
       <c r="T32">
-        <v>5755.000</v>
+        <v>3638.000</v>
       </c>
       <c r="U32">
         <v>0</v>
@@ -2726,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="W32" s="4">
-        <v>46197.550396064813</v>
+        <v>46197.550396956016</v>
       </c>
     </row>
     <row r="33">
@@ -2743,7 +2752,7 @@
         <v>24</v>
       </c>
       <c r="E33">
-        <v>7362625</v>
+        <v>7368806</v>
       </c>
       <c r="F33" t="s">
         <v>74</v>
@@ -2758,16 +2767,16 @@
         <v>75</v>
       </c>
       <c r="P33" s="1">
-        <v>46195.438085185182</v>
+        <v>46196.377559722219</v>
       </c>
       <c r="R33" s="4">
-        <v>46196.523870486111</v>
+        <v>46197.497936342595</v>
       </c>
       <c r="S33">
-        <v>6200.000</v>
+        <v>5755.000</v>
       </c>
       <c r="T33">
-        <v>6200.000</v>
+        <v>5755.000</v>
       </c>
       <c r="U33">
         <v>0</v>
@@ -2776,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="W33" s="4">
-        <v>46197.278575775461</v>
+        <v>46197.550396064813</v>
       </c>
     </row>
     <row r="34">
@@ -2793,7 +2802,7 @@
         <v>24</v>
       </c>
       <c r="E34">
-        <v>7362236</v>
+        <v>7362625</v>
       </c>
       <c r="F34" t="s">
         <v>76</v>
@@ -2808,16 +2817,16 @@
         <v>77</v>
       </c>
       <c r="P34" s="1">
-        <v>46195.402819178242</v>
+        <v>46195.438085185182</v>
       </c>
       <c r="R34" s="4">
-        <v>46196.601059108798</v>
+        <v>46196.523870486111</v>
       </c>
       <c r="S34">
-        <v>6305.000</v>
+        <v>6200.000</v>
       </c>
       <c r="T34">
-        <v>6305.000</v>
+        <v>6200.000</v>
       </c>
       <c r="U34">
         <v>0</v>
@@ -2826,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="W34" s="4">
-        <v>46197.278671446758</v>
+        <v>46197.278575775461</v>
       </c>
     </row>
     <row r="35">
@@ -2843,7 +2852,7 @@
         <v>24</v>
       </c>
       <c r="E35">
-        <v>7362235</v>
+        <v>7362236</v>
       </c>
       <c r="F35" t="s">
         <v>78</v>
@@ -2858,16 +2867,16 @@
         <v>79</v>
       </c>
       <c r="P35" s="1">
-        <v>46195.402748692133</v>
+        <v>46195.402819178242</v>
       </c>
       <c r="R35" s="4">
-        <v>46198.313491319444</v>
+        <v>46196.601059108798</v>
       </c>
       <c r="S35">
-        <v>10614.000</v>
+        <v>6305.000</v>
       </c>
       <c r="T35">
-        <v>10614.000</v>
+        <v>6305.000</v>
       </c>
       <c r="U35">
         <v>0</v>
@@ -2876,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="W35" s="4">
-        <v>46198.314641435187</v>
+        <v>46197.278671446758</v>
       </c>
     </row>
     <row r="36">
@@ -2893,7 +2902,7 @@
         <v>24</v>
       </c>
       <c r="E36">
-        <v>7358767</v>
+        <v>7362235</v>
       </c>
       <c r="F36" t="s">
         <v>80</v>
@@ -2908,16 +2917,16 @@
         <v>81</v>
       </c>
       <c r="P36" s="1">
-        <v>46192.659844444446</v>
+        <v>46195.402748692133</v>
       </c>
       <c r="R36" s="4">
-        <v>46197.3828096875</v>
+        <v>46198.313491319444</v>
       </c>
       <c r="S36">
-        <v>10207.000</v>
+        <v>10614.000</v>
       </c>
       <c r="T36">
-        <v>10207.000</v>
+        <v>10614.000</v>
       </c>
       <c r="U36">
         <v>0</v>
@@ -2926,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="W36" s="4">
-        <v>46197.391247916668</v>
+        <v>46198.314641435187</v>
       </c>
     </row>
     <row r="37">
@@ -2943,7 +2952,7 @@
         <v>24</v>
       </c>
       <c r="E37">
-        <v>7358766</v>
+        <v>7358767</v>
       </c>
       <c r="F37" t="s">
         <v>82</v>
@@ -2958,16 +2967,16 @@
         <v>83</v>
       </c>
       <c r="P37" s="1">
-        <v>46192.659814814811</v>
+        <v>46192.659844444446</v>
       </c>
       <c r="R37" s="4">
-        <v>46197.366926122682</v>
+        <v>46197.3828096875</v>
       </c>
       <c r="S37">
-        <v>8661.000</v>
+        <v>10207.000</v>
       </c>
       <c r="T37">
-        <v>8661.000</v>
+        <v>10207.000</v>
       </c>
       <c r="U37">
         <v>0</v>
@@ -2976,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="W37" s="4">
-        <v>46197.391093518519</v>
+        <v>46197.391247916668</v>
       </c>
     </row>
     <row r="38">
@@ -2993,7 +3002,7 @@
         <v>24</v>
       </c>
       <c r="E38">
-        <v>7355924</v>
+        <v>7358766</v>
       </c>
       <c r="F38" t="s">
         <v>84</v>
@@ -3004,20 +3013,20 @@
       <c r="H38" t="s">
         <v>24</v>
       </c>
-      <c r="M38" s="5" t="s">
+      <c r="M38" t="s">
         <v>85</v>
       </c>
       <c r="P38" s="1">
-        <v>46191.548452546296</v>
+        <v>46192.659814814811</v>
       </c>
       <c r="R38" s="4">
-        <v>46195.391070254627</v>
+        <v>46197.366926122682</v>
       </c>
       <c r="S38">
-        <v>8044.000</v>
+        <v>8661.000</v>
       </c>
       <c r="T38">
-        <v>8044.000</v>
+        <v>8661.000</v>
       </c>
       <c r="U38">
         <v>0</v>
@@ -3026,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="W38" s="4">
-        <v>46196.389409641204</v>
+        <v>46197.391093518519</v>
       </c>
     </row>
     <row r="39">
@@ -3043,7 +3052,7 @@
         <v>24</v>
       </c>
       <c r="E39">
-        <v>7355667</v>
+        <v>7355924</v>
       </c>
       <c r="F39" t="s">
         <v>86</v>
@@ -3054,20 +3063,20 @@
       <c r="H39" t="s">
         <v>24</v>
       </c>
-      <c r="M39" t="s">
+      <c r="M39" s="5" t="s">
         <v>87</v>
       </c>
       <c r="P39" s="1">
-        <v>46191.4713122338</v>
+        <v>46191.548452546296</v>
       </c>
       <c r="R39" s="4">
-        <v>46198.319310104169</v>
+        <v>46195.391070254627</v>
       </c>
       <c r="S39">
-        <v>15383.000</v>
+        <v>8044.000</v>
       </c>
       <c r="T39">
-        <v>15383.000</v>
+        <v>8044.000</v>
       </c>
       <c r="U39">
         <v>0</v>
@@ -3076,7 +3085,7 @@
         <v>0</v>
       </c>
       <c r="W39" s="4">
-        <v>46198.319958796295</v>
+        <v>46196.389409641204</v>
       </c>
     </row>
     <row r="40">
@@ -3093,7 +3102,7 @@
         <v>24</v>
       </c>
       <c r="E40">
-        <v>7353363</v>
+        <v>7355667</v>
       </c>
       <c r="F40" t="s">
         <v>88</v>
@@ -3108,16 +3117,16 @@
         <v>89</v>
       </c>
       <c r="P40" s="1">
-        <v>46190.666969988422</v>
+        <v>46191.4713122338</v>
       </c>
       <c r="R40" s="4">
-        <v>46195.511062997684</v>
+        <v>46198.319310104169</v>
       </c>
       <c r="S40">
-        <v>472.000</v>
+        <v>15383.000</v>
       </c>
       <c r="T40">
-        <v>472.000</v>
+        <v>15383.000</v>
       </c>
       <c r="U40">
         <v>0</v>
@@ -3126,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="W40" s="4">
-        <v>46196.389409641204</v>
+        <v>46198.319958796295</v>
       </c>
     </row>
     <row r="41">
@@ -3143,7 +3152,7 @@
         <v>24</v>
       </c>
       <c r="E41">
-        <v>7353362</v>
+        <v>7353363</v>
       </c>
       <c r="F41" t="s">
         <v>90</v>
@@ -3155,19 +3164,19 @@
         <v>24</v>
       </c>
       <c r="M41" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P41" s="1">
-        <v>46190.666969444443</v>
+        <v>46190.666969988422</v>
       </c>
       <c r="R41" s="4">
-        <v>46195.521521527779</v>
+        <v>46195.511062997684</v>
       </c>
       <c r="S41">
-        <v>612.000</v>
+        <v>472.000</v>
       </c>
       <c r="T41">
-        <v>612.000</v>
+        <v>472.000</v>
       </c>
       <c r="U41">
         <v>0</v>
@@ -3193,31 +3202,31 @@
         <v>24</v>
       </c>
       <c r="E42">
-        <v>7353361</v>
+        <v>7353362</v>
       </c>
       <c r="F42" t="s">
+        <v>92</v>
+      </c>
+      <c r="G42" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" t="s">
+        <v>24</v>
+      </c>
+      <c r="M42" t="s">
         <v>91</v>
       </c>
-      <c r="G42" t="s">
-        <v>24</v>
-      </c>
-      <c r="H42" t="s">
-        <v>24</v>
-      </c>
-      <c r="M42" t="s">
-        <v>89</v>
-      </c>
       <c r="P42" s="1">
-        <v>46190.666967094905</v>
+        <v>46190.666969444443</v>
       </c>
       <c r="R42" s="4">
-        <v>46195.535836192132</v>
+        <v>46195.521521527779</v>
       </c>
       <c r="S42">
-        <v>2383.000</v>
+        <v>612.000</v>
       </c>
       <c r="T42">
-        <v>2383.000</v>
+        <v>612.000</v>
       </c>
       <c r="U42">
         <v>0</v>
@@ -3243,10 +3252,10 @@
         <v>24</v>
       </c>
       <c r="E43">
-        <v>7353360</v>
+        <v>7353361</v>
       </c>
       <c r="F43" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s">
         <v>24</v>
@@ -3255,19 +3264,19 @@
         <v>24</v>
       </c>
       <c r="M43" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P43" s="1">
-        <v>46190.666964201388</v>
+        <v>46190.666967094905</v>
       </c>
       <c r="R43" s="4">
-        <v>46195.523977164354</v>
+        <v>46195.535836192132</v>
       </c>
       <c r="S43">
-        <v>2262.000</v>
+        <v>2383.000</v>
       </c>
       <c r="T43">
-        <v>2262.000</v>
+        <v>2383.000</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -3293,10 +3302,10 @@
         <v>24</v>
       </c>
       <c r="E44">
-        <v>7353359</v>
+        <v>7353360</v>
       </c>
       <c r="F44" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G44" t="s">
         <v>24</v>
@@ -3305,19 +3314,19 @@
         <v>24</v>
       </c>
       <c r="M44" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P44" s="1">
-        <v>46190.66696145833</v>
+        <v>46190.666964201388</v>
       </c>
       <c r="R44" s="4">
-        <v>46195.537172372686</v>
+        <v>46195.523977164354</v>
       </c>
       <c r="S44">
-        <v>3982.000</v>
+        <v>2262.000</v>
       </c>
       <c r="T44">
-        <v>3982.000</v>
+        <v>2262.000</v>
       </c>
       <c r="U44">
         <v>0</v>
@@ -3326,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="W44" s="4">
-        <v>46196.389409456016</v>
+        <v>46196.389409641204</v>
       </c>
     </row>
     <row r="45">
@@ -3343,10 +3352,10 @@
         <v>24</v>
       </c>
       <c r="E45">
-        <v>7353358</v>
+        <v>7353359</v>
       </c>
       <c r="F45" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G45" t="s">
         <v>24</v>
@@ -3355,19 +3364,19 @@
         <v>24</v>
       </c>
       <c r="M45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P45" s="1">
-        <v>46190.666954432869</v>
+        <v>46190.66696145833</v>
       </c>
       <c r="R45" s="4">
-        <v>46195.532108368054</v>
+        <v>46195.537172372686</v>
       </c>
       <c r="S45">
-        <v>1113.000</v>
+        <v>3982.000</v>
       </c>
       <c r="T45">
-        <v>1113.000</v>
+        <v>3982.000</v>
       </c>
       <c r="U45">
         <v>0</v>
@@ -3393,10 +3402,10 @@
         <v>24</v>
       </c>
       <c r="E46">
-        <v>7353357</v>
+        <v>7353358</v>
       </c>
       <c r="F46" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G46" t="s">
         <v>24</v>
@@ -3405,19 +3414,19 @@
         <v>24</v>
       </c>
       <c r="M46" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P46" s="1">
-        <v>46190.666949340281</v>
+        <v>46190.666954432869</v>
       </c>
       <c r="R46" s="4">
-        <v>46195.517305439818</v>
+        <v>46195.532108368054</v>
       </c>
       <c r="S46">
-        <v>447.000</v>
+        <v>1113.000</v>
       </c>
       <c r="T46">
-        <v>447.000</v>
+        <v>1113.000</v>
       </c>
       <c r="U46">
         <v>0</v>
@@ -3443,10 +3452,10 @@
         <v>24</v>
       </c>
       <c r="E47">
-        <v>7353356</v>
+        <v>7353357</v>
       </c>
       <c r="F47" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G47" t="s">
         <v>24</v>
@@ -3455,19 +3464,19 @@
         <v>24</v>
       </c>
       <c r="M47" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P47" s="1">
-        <v>46190.66694664352</v>
+        <v>46190.666949340281</v>
       </c>
       <c r="R47" s="4">
-        <v>46195.528761724534</v>
+        <v>46195.517305439818</v>
       </c>
       <c r="S47">
-        <v>284.000</v>
+        <v>447.000</v>
       </c>
       <c r="T47">
-        <v>284.000</v>
+        <v>447.000</v>
       </c>
       <c r="U47">
         <v>0</v>
@@ -3493,10 +3502,10 @@
         <v>24</v>
       </c>
       <c r="E48">
-        <v>7353355</v>
+        <v>7353356</v>
       </c>
       <c r="F48" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -3505,19 +3514,19 @@
         <v>24</v>
       </c>
       <c r="M48" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P48" s="1">
-        <v>46190.666944293982</v>
+        <v>46190.66694664352</v>
       </c>
       <c r="R48" s="4">
-        <v>46195.528790659722</v>
+        <v>46195.528761724534</v>
       </c>
       <c r="S48">
-        <v>304.000</v>
+        <v>284.000</v>
       </c>
       <c r="T48">
-        <v>304.000</v>
+        <v>284.000</v>
       </c>
       <c r="U48">
         <v>0</v>
@@ -3543,10 +3552,10 @@
         <v>24</v>
       </c>
       <c r="E49">
-        <v>7353354</v>
+        <v>7353355</v>
       </c>
       <c r="F49" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -3555,19 +3564,19 @@
         <v>24</v>
       </c>
       <c r="M49" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P49" s="1">
-        <v>46190.666940659721</v>
+        <v>46190.666944293982</v>
       </c>
       <c r="R49" s="4">
-        <v>46195.536209409722</v>
+        <v>46195.528790659722</v>
       </c>
       <c r="S49">
-        <v>1251.000</v>
+        <v>304.000</v>
       </c>
       <c r="T49">
-        <v>1251.000</v>
+        <v>304.000</v>
       </c>
       <c r="U49">
         <v>0</v>
@@ -3593,10 +3602,10 @@
         <v>24</v>
       </c>
       <c r="E50">
-        <v>7353353</v>
+        <v>7353354</v>
       </c>
       <c r="F50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G50" t="s">
         <v>24</v>
@@ -3605,19 +3614,19 @@
         <v>24</v>
       </c>
       <c r="M50" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P50" s="1">
-        <v>46190.666939583331</v>
+        <v>46190.666940659721</v>
       </c>
       <c r="R50" s="4">
-        <v>46195.537300034724</v>
+        <v>46195.536209409722</v>
       </c>
       <c r="S50">
-        <v>1257.000</v>
+        <v>1251.000</v>
       </c>
       <c r="T50">
-        <v>1257.000</v>
+        <v>1251.000</v>
       </c>
       <c r="U50">
         <v>0</v>
@@ -3643,10 +3652,10 @@
         <v>24</v>
       </c>
       <c r="E51">
-        <v>7353352</v>
+        <v>7353353</v>
       </c>
       <c r="F51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G51" t="s">
         <v>24</v>
@@ -3655,19 +3664,19 @@
         <v>24</v>
       </c>
       <c r="M51" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P51" s="1">
-        <v>46190.66693417824</v>
+        <v>46190.666939583331</v>
       </c>
       <c r="R51" s="4">
-        <v>46195.537318483795</v>
+        <v>46195.537300034724</v>
       </c>
       <c r="S51">
-        <v>7113.000</v>
+        <v>1257.000</v>
       </c>
       <c r="T51">
-        <v>7113.000</v>
+        <v>1257.000</v>
       </c>
       <c r="U51">
         <v>0</v>
@@ -3676,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="W51" s="4">
-        <v>46196.388202118054</v>
+        <v>46196.389409456016</v>
       </c>
     </row>
     <row r="52">
@@ -3693,10 +3702,10 @@
         <v>24</v>
       </c>
       <c r="E52">
-        <v>7353351</v>
+        <v>7353352</v>
       </c>
       <c r="F52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G52" t="s">
         <v>24</v>
@@ -3705,19 +3714,19 @@
         <v>24</v>
       </c>
       <c r="M52" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P52" s="1">
-        <v>46190.666933101849</v>
+        <v>46190.66693417824</v>
       </c>
       <c r="R52" s="4">
-        <v>46195.523942245367</v>
+        <v>46195.537318483795</v>
       </c>
       <c r="S52">
-        <v>1295.000</v>
+        <v>7113.000</v>
       </c>
       <c r="T52">
-        <v>1295.000</v>
+        <v>7113.000</v>
       </c>
       <c r="U52">
         <v>0</v>
@@ -3726,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="W52" s="4">
-        <v>46196.389409293981</v>
+        <v>46196.388202118054</v>
       </c>
     </row>
     <row r="53">
@@ -3743,10 +3752,10 @@
         <v>24</v>
       </c>
       <c r="E53">
-        <v>7353350</v>
+        <v>7353351</v>
       </c>
       <c r="F53" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G53" t="s">
         <v>24</v>
@@ -3755,19 +3764,19 @@
         <v>24</v>
       </c>
       <c r="M53" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P53" s="1">
-        <v>46190.666932719905</v>
+        <v>46190.666933101849</v>
       </c>
       <c r="R53" s="4">
-        <v>46195.536177581016</v>
+        <v>46195.523942245367</v>
       </c>
       <c r="S53">
-        <v>72.000</v>
+        <v>1295.000</v>
       </c>
       <c r="T53">
-        <v>72.000</v>
+        <v>1295.000</v>
       </c>
       <c r="U53">
         <v>0</v>
@@ -3793,10 +3802,10 @@
         <v>24</v>
       </c>
       <c r="E54">
-        <v>7353349</v>
+        <v>7353350</v>
       </c>
       <c r="F54" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G54" t="s">
         <v>24</v>
@@ -3805,19 +3814,19 @@
         <v>24</v>
       </c>
       <c r="M54" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P54" s="1">
-        <v>46190.666930555555</v>
+        <v>46190.666932719905</v>
       </c>
       <c r="R54" s="4">
-        <v>46195.536192395833</v>
+        <v>46195.536177581016</v>
       </c>
       <c r="S54">
-        <v>101.000</v>
+        <v>72.000</v>
       </c>
       <c r="T54">
-        <v>101.000</v>
+        <v>72.000</v>
       </c>
       <c r="U54">
         <v>0</v>
@@ -3843,10 +3852,10 @@
         <v>24</v>
       </c>
       <c r="E55">
-        <v>7353348</v>
+        <v>7353349</v>
       </c>
       <c r="F55" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G55" t="s">
         <v>24</v>
@@ -3855,19 +3864,19 @@
         <v>24</v>
       </c>
       <c r="M55" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P55" s="1">
-        <v>46190.666919525465</v>
+        <v>46190.666930555555</v>
       </c>
       <c r="R55" s="4">
-        <v>46195.534000462962</v>
+        <v>46195.536192395833</v>
       </c>
       <c r="S55">
-        <v>1620.000</v>
+        <v>101.000</v>
       </c>
       <c r="T55">
-        <v>1620.000</v>
+        <v>101.000</v>
       </c>
       <c r="U55">
         <v>0</v>
@@ -3893,10 +3902,10 @@
         <v>24</v>
       </c>
       <c r="E56">
-        <v>7353347</v>
+        <v>7353348</v>
       </c>
       <c r="F56" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G56" t="s">
         <v>24</v>
@@ -3905,19 +3914,19 @@
         <v>24</v>
       </c>
       <c r="M56" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P56" s="1">
-        <v>46190.666916979164</v>
+        <v>46190.666919525465</v>
       </c>
       <c r="R56" s="4">
-        <v>46195.527235069443</v>
+        <v>46195.534000462962</v>
       </c>
       <c r="S56">
-        <v>600.000</v>
+        <v>1620.000</v>
       </c>
       <c r="T56">
-        <v>600.000</v>
+        <v>1620.000</v>
       </c>
       <c r="U56">
         <v>0</v>
@@ -3943,10 +3952,10 @@
         <v>24</v>
       </c>
       <c r="E57">
-        <v>7353346</v>
+        <v>7353347</v>
       </c>
       <c r="F57" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G57" t="s">
         <v>24</v>
@@ -3955,19 +3964,19 @@
         <v>24</v>
       </c>
       <c r="M57" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P57" s="1">
-        <v>46190.66691284722</v>
+        <v>46190.666916979164</v>
       </c>
       <c r="R57" s="4">
-        <v>46195.522001273152</v>
+        <v>46195.527235069443</v>
       </c>
       <c r="S57">
-        <v>1338.000</v>
+        <v>600.000</v>
       </c>
       <c r="T57">
-        <v>1338.000</v>
+        <v>600.000</v>
       </c>
       <c r="U57">
         <v>0</v>
@@ -3993,10 +4002,10 @@
         <v>24</v>
       </c>
       <c r="E58">
-        <v>7353345</v>
+        <v>7353346</v>
       </c>
       <c r="F58" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G58" t="s">
         <v>24</v>
@@ -4005,19 +4014,19 @@
         <v>24</v>
       </c>
       <c r="M58" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P58" s="1">
-        <v>46190.666911921297</v>
+        <v>46190.66691284722</v>
       </c>
       <c r="R58" s="4">
-        <v>46195.532152511572</v>
+        <v>46195.522001273152</v>
       </c>
       <c r="S58">
-        <v>968.000</v>
+        <v>1338.000</v>
       </c>
       <c r="T58">
-        <v>968.000</v>
+        <v>1338.000</v>
       </c>
       <c r="U58">
         <v>0</v>
@@ -4043,10 +4052,10 @@
         <v>24</v>
       </c>
       <c r="E59">
-        <v>7353344</v>
+        <v>7353345</v>
       </c>
       <c r="F59" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G59" t="s">
         <v>24</v>
@@ -4055,19 +4064,19 @@
         <v>24</v>
       </c>
       <c r="M59" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P59" s="1">
-        <v>46190.666910844906</v>
+        <v>46190.666911921297</v>
       </c>
       <c r="R59" s="4">
-        <v>46195.537341087962</v>
+        <v>46195.532152511572</v>
       </c>
       <c r="S59">
-        <v>917.000</v>
+        <v>968.000</v>
       </c>
       <c r="T59">
-        <v>917.000</v>
+        <v>968.000</v>
       </c>
       <c r="U59">
         <v>0</v>
@@ -4093,10 +4102,10 @@
         <v>24</v>
       </c>
       <c r="E60">
-        <v>7353343</v>
+        <v>7353344</v>
       </c>
       <c r="F60" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G60" t="s">
         <v>24</v>
@@ -4105,19 +4114,19 @@
         <v>24</v>
       </c>
       <c r="M60" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P60" s="1">
-        <v>46190.666907604165</v>
+        <v>46190.666910844906</v>
       </c>
       <c r="R60" s="4">
-        <v>46195.526307291664</v>
+        <v>46195.537341087962</v>
       </c>
       <c r="S60">
-        <v>3514.000</v>
+        <v>917.000</v>
       </c>
       <c r="T60">
-        <v>3514.000</v>
+        <v>917.000</v>
       </c>
       <c r="U60">
         <v>0</v>
@@ -4126,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="W60" s="4">
-        <v>46196.389409108793</v>
+        <v>46196.389409293981</v>
       </c>
     </row>
     <row r="61">
@@ -4143,10 +4152,10 @@
         <v>24</v>
       </c>
       <c r="E61">
-        <v>7353342</v>
+        <v>7353343</v>
       </c>
       <c r="F61" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -4155,19 +4164,19 @@
         <v>24</v>
       </c>
       <c r="M61" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P61" s="1">
-        <v>46190.666906134262</v>
+        <v>46190.666907604165</v>
       </c>
       <c r="R61" s="4">
-        <v>46195.518147222225</v>
+        <v>46195.526307291664</v>
       </c>
       <c r="S61">
-        <v>646.000</v>
+        <v>3514.000</v>
       </c>
       <c r="T61">
-        <v>646.000</v>
+        <v>3514.000</v>
       </c>
       <c r="U61">
         <v>0</v>
@@ -4193,10 +4202,10 @@
         <v>24</v>
       </c>
       <c r="E62">
-        <v>7353341</v>
+        <v>7353342</v>
       </c>
       <c r="F62" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
@@ -4205,19 +4214,19 @@
         <v>24</v>
       </c>
       <c r="M62" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P62" s="1">
-        <v>46190.666903969905</v>
+        <v>46190.666906134262</v>
       </c>
       <c r="R62" s="4">
-        <v>46195.535854247682</v>
+        <v>46195.518147222225</v>
       </c>
       <c r="S62">
-        <v>2209.000</v>
+        <v>646.000</v>
       </c>
       <c r="T62">
-        <v>2209.000</v>
+        <v>646.000</v>
       </c>
       <c r="U62">
         <v>0</v>
@@ -4243,10 +4252,10 @@
         <v>24</v>
       </c>
       <c r="E63">
-        <v>7353340</v>
+        <v>7353341</v>
       </c>
       <c r="F63" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G63" t="s">
         <v>24</v>
@@ -4255,19 +4264,19 @@
         <v>24</v>
       </c>
       <c r="M63" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P63" s="1">
-        <v>46190.666894560185</v>
+        <v>46190.666903969905</v>
       </c>
       <c r="R63" s="4">
-        <v>46195.524072835651</v>
+        <v>46195.535854247682</v>
       </c>
       <c r="S63">
-        <v>4385.000</v>
+        <v>2209.000</v>
       </c>
       <c r="T63">
-        <v>4385.000</v>
+        <v>2209.000</v>
       </c>
       <c r="U63">
         <v>0</v>
@@ -4293,10 +4302,10 @@
         <v>24</v>
       </c>
       <c r="E64">
-        <v>7353339</v>
+        <v>7353340</v>
       </c>
       <c r="F64" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G64" t="s">
         <v>24</v>
@@ -4305,19 +4314,19 @@
         <v>24</v>
       </c>
       <c r="M64" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P64" s="1">
-        <v>46190.666882442129</v>
+        <v>46190.666894560185</v>
       </c>
       <c r="R64" s="4">
-        <v>46195.535098726854</v>
+        <v>46195.524072835651</v>
       </c>
       <c r="S64">
-        <v>2886.000</v>
+        <v>4385.000</v>
       </c>
       <c r="T64">
-        <v>2886.000</v>
+        <v>4385.000</v>
       </c>
       <c r="U64">
         <v>0</v>
@@ -4326,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="W64" s="4">
-        <v>46196.389408912037</v>
+        <v>46196.389409108793</v>
       </c>
     </row>
     <row r="65">
@@ -4343,10 +4352,10 @@
         <v>24</v>
       </c>
       <c r="E65">
-        <v>7353338</v>
+        <v>7353339</v>
       </c>
       <c r="F65" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G65" t="s">
         <v>24</v>
@@ -4355,19 +4364,19 @@
         <v>24</v>
       </c>
       <c r="M65" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P65" s="1">
-        <v>46190.666870520836</v>
+        <v>46190.666882442129</v>
       </c>
       <c r="R65" s="4">
-        <v>46195.537258252312</v>
+        <v>46195.535098726854</v>
       </c>
       <c r="S65">
-        <v>2648.000</v>
+        <v>2886.000</v>
       </c>
       <c r="T65">
-        <v>2648.000</v>
+        <v>2886.000</v>
       </c>
       <c r="U65">
         <v>0</v>
@@ -4393,10 +4402,10 @@
         <v>24</v>
       </c>
       <c r="E66">
-        <v>7353112</v>
+        <v>7353338</v>
       </c>
       <c r="F66" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G66" t="s">
         <v>24</v>
@@ -4404,20 +4413,20 @@
       <c r="H66" t="s">
         <v>24</v>
       </c>
-      <c r="M66" s="5" t="s">
-        <v>116</v>
+      <c r="M66" t="s">
+        <v>91</v>
       </c>
       <c r="P66" s="1">
-        <v>46190.633443321756</v>
+        <v>46190.666870520836</v>
       </c>
       <c r="R66" s="4">
-        <v>46195.593899918982</v>
+        <v>46195.537258252312</v>
       </c>
       <c r="S66">
-        <v>15034.000</v>
+        <v>2648.000</v>
       </c>
       <c r="T66">
-        <v>15034.000</v>
+        <v>2648.000</v>
       </c>
       <c r="U66">
         <v>0</v>
@@ -4426,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="W66" s="4">
-        <v>46196.389407835646</v>
+        <v>46196.389408912037</v>
       </c>
     </row>
     <row r="67">
@@ -4443,7 +4452,7 @@
         <v>24</v>
       </c>
       <c r="E67">
-        <v>7352722</v>
+        <v>7353112</v>
       </c>
       <c r="F67" t="s">
         <v>117</v>
@@ -4454,20 +4463,20 @@
       <c r="H67" t="s">
         <v>24</v>
       </c>
-      <c r="M67" t="s">
+      <c r="M67" s="5" t="s">
         <v>118</v>
       </c>
       <c r="P67" s="1">
-        <v>46190.517798842593</v>
+        <v>46190.633443321756</v>
       </c>
       <c r="R67" s="4">
-        <v>46198.316219409724</v>
+        <v>46195.593899918982</v>
       </c>
       <c r="S67">
-        <v>13727.000</v>
+        <v>15034.000</v>
       </c>
       <c r="T67">
-        <v>13727.000</v>
+        <v>15034.000</v>
       </c>
       <c r="U67">
         <v>0</v>
@@ -4476,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="W67" s="4">
-        <v>46198.317383530091</v>
+        <v>46196.389407835646</v>
       </c>
     </row>
     <row r="68">
@@ -4493,7 +4502,7 @@
         <v>24</v>
       </c>
       <c r="E68">
-        <v>7352670</v>
+        <v>7352722</v>
       </c>
       <c r="F68" t="s">
         <v>119</v>
@@ -4504,20 +4513,20 @@
       <c r="H68" t="s">
         <v>24</v>
       </c>
-      <c r="M68" s="5" t="s">
+      <c r="M68" t="s">
         <v>120</v>
       </c>
       <c r="P68" s="1">
-        <v>46190.508466550928</v>
+        <v>46190.517798842593</v>
       </c>
       <c r="R68" s="4">
-        <v>46197.408573148146</v>
+        <v>46198.316219409724</v>
       </c>
       <c r="S68">
-        <v>10751.000</v>
+        <v>13727.000</v>
       </c>
       <c r="T68">
-        <v>10751.000</v>
+        <v>13727.000</v>
       </c>
       <c r="U68">
         <v>0</v>
@@ -4526,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="W68" s="4">
-        <v>46197.438478206015</v>
+        <v>46198.317383530091</v>
       </c>
     </row>
     <row r="69">
@@ -4543,7 +4552,7 @@
         <v>24</v>
       </c>
       <c r="E69">
-        <v>7344984</v>
+        <v>7352670</v>
       </c>
       <c r="F69" t="s">
         <v>121</v>
@@ -4554,20 +4563,20 @@
       <c r="H69" t="s">
         <v>24</v>
       </c>
-      <c r="M69" t="s">
+      <c r="M69" s="5" t="s">
         <v>122</v>
       </c>
       <c r="P69" s="1">
-        <v>46188.6820028125</v>
+        <v>46190.508466550928</v>
       </c>
       <c r="R69" s="4">
-        <v>46189.581174189814</v>
+        <v>46197.408573148146</v>
       </c>
       <c r="S69">
-        <v>14515.000</v>
+        <v>10751.000</v>
       </c>
       <c r="T69">
-        <v>14515.000</v>
+        <v>10751.000</v>
       </c>
       <c r="U69">
         <v>0</v>
@@ -4576,7 +4585,7 @@
         <v>0</v>
       </c>
       <c r="W69" s="4">
-        <v>46190.318753738429</v>
+        <v>46197.438478206015</v>
       </c>
     </row>
     <row r="70">
@@ -4593,7 +4602,7 @@
         <v>24</v>
       </c>
       <c r="E70">
-        <v>7343721</v>
+        <v>7344984</v>
       </c>
       <c r="F70" t="s">
         <v>123</v>
@@ -4608,19 +4617,16 @@
         <v>124</v>
       </c>
       <c r="P70" s="1">
-        <v>46188.52897230324</v>
-      </c>
-      <c r="Q70" s="4">
-        <v>46189.270138888889</v>
+        <v>46188.6820028125</v>
       </c>
       <c r="R70" s="4">
-        <v>46189.525954201388</v>
+        <v>46189.581174189814</v>
       </c>
       <c r="S70">
-        <v>9210.000</v>
+        <v>14515.000</v>
       </c>
       <c r="T70">
-        <v>9210.000</v>
+        <v>14515.000</v>
       </c>
       <c r="U70">
         <v>0</v>
@@ -4629,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="W70" s="4">
-        <v>46189.538887268522</v>
+        <v>46190.318753738429</v>
       </c>
     </row>
     <row r="71">
@@ -4646,7 +4652,7 @@
         <v>24</v>
       </c>
       <c r="E71">
-        <v>7331780</v>
+        <v>7343721</v>
       </c>
       <c r="F71" t="s">
         <v>125</v>
@@ -4660,20 +4666,20 @@
       <c r="M71" t="s">
         <v>126</v>
       </c>
-      <c r="O71" s="4">
-        <v>46185.364583333336</v>
-      </c>
       <c r="P71" s="1">
-        <v>46184.420189351855</v>
+        <v>46188.52897230324</v>
+      </c>
+      <c r="Q71" s="4">
+        <v>46189.270138888889</v>
       </c>
       <c r="R71" s="4">
-        <v>46188.330705902779</v>
+        <v>46189.525954201388</v>
       </c>
       <c r="S71">
-        <v>2185.000</v>
+        <v>9210.000</v>
       </c>
       <c r="T71">
-        <v>2185.000</v>
+        <v>9210.000</v>
       </c>
       <c r="U71">
         <v>0</v>
@@ -4682,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="W71" s="4">
-        <v>46188.33742491898</v>
+        <v>46189.538887268522</v>
       </c>
     </row>
     <row r="72">
@@ -4699,7 +4705,7 @@
         <v>24</v>
       </c>
       <c r="E72">
-        <v>7331779</v>
+        <v>7331780</v>
       </c>
       <c r="F72" t="s">
         <v>127</v>
@@ -4714,22 +4720,19 @@
         <v>128</v>
       </c>
       <c r="O72" s="4">
-        <v>46185</v>
+        <v>46185.364583333336</v>
       </c>
       <c r="P72" s="1">
-        <v>46184.420142511575</v>
-      </c>
-      <c r="Q72" s="4">
-        <v>46181</v>
+        <v>46184.420189351855</v>
       </c>
       <c r="R72" s="4">
-        <v>46188.332772222224</v>
+        <v>46188.330705902779</v>
       </c>
       <c r="S72">
-        <v>16497.000</v>
+        <v>2185.000</v>
       </c>
       <c r="T72">
-        <v>16497.000</v>
+        <v>2185.000</v>
       </c>
       <c r="U72">
         <v>0</v>
@@ -4738,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="W72" s="4">
-        <v>46188.337424189813</v>
+        <v>46188.33742491898</v>
       </c>
     </row>
     <row r="73">
@@ -4755,7 +4758,7 @@
         <v>24</v>
       </c>
       <c r="E73">
-        <v>7331318</v>
+        <v>7331779</v>
       </c>
       <c r="F73" t="s">
         <v>129</v>
@@ -4769,17 +4772,23 @@
       <c r="M73" t="s">
         <v>130</v>
       </c>
+      <c r="O73" s="4">
+        <v>46185</v>
+      </c>
       <c r="P73" s="1">
-        <v>46184.369259340281</v>
+        <v>46184.420142511575</v>
+      </c>
+      <c r="Q73" s="4">
+        <v>46181</v>
       </c>
       <c r="R73" s="4">
-        <v>46185.506102002313</v>
+        <v>46188.332772222224</v>
       </c>
       <c r="S73">
-        <v>10749.000</v>
+        <v>16497.000</v>
       </c>
       <c r="T73">
-        <v>10749.000</v>
+        <v>16497.000</v>
       </c>
       <c r="U73">
         <v>0</v>
@@ -4788,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="W73" s="4">
-        <v>46188.329308333334</v>
+        <v>46188.337424189813</v>
       </c>
     </row>
     <row r="74">
@@ -4805,7 +4814,7 @@
         <v>24</v>
       </c>
       <c r="E74">
-        <v>7329559</v>
+        <v>7331318</v>
       </c>
       <c r="F74" t="s">
         <v>131</v>
@@ -4820,16 +4829,16 @@
         <v>132</v>
       </c>
       <c r="P74" s="1">
-        <v>46183.835381215278</v>
+        <v>46184.369259340281</v>
       </c>
       <c r="R74" s="4">
-        <v>46185.394576122686</v>
+        <v>46185.506102002313</v>
       </c>
       <c r="S74">
-        <v>18992.000</v>
+        <v>10749.000</v>
       </c>
       <c r="T74">
-        <v>18992.000</v>
+        <v>10749.000</v>
       </c>
       <c r="U74">
         <v>0</v>
@@ -4838,7 +4847,7 @@
         <v>0</v>
       </c>
       <c r="W74" s="4">
-        <v>46188.318260497683</v>
+        <v>46188.329308333334</v>
       </c>
     </row>
     <row r="75">
@@ -4855,7 +4864,7 @@
         <v>24</v>
       </c>
       <c r="E75">
-        <v>7327419</v>
+        <v>7329559</v>
       </c>
       <c r="F75" t="s">
         <v>133</v>
@@ -4870,19 +4879,16 @@
         <v>134</v>
       </c>
       <c r="P75" s="1">
-        <v>46183.517797372682</v>
-      </c>
-      <c r="Q75" s="4">
-        <v>46184.3125</v>
+        <v>46183.835381215278</v>
       </c>
       <c r="R75" s="4">
-        <v>46188.329073842593</v>
+        <v>46185.394576122686</v>
       </c>
       <c r="S75">
-        <v>10574.000</v>
+        <v>18992.000</v>
       </c>
       <c r="T75">
-        <v>10574.000</v>
+        <v>18992.000</v>
       </c>
       <c r="U75">
         <v>0</v>
@@ -4891,7 +4897,7 @@
         <v>0</v>
       </c>
       <c r="W75" s="4">
-        <v>46188.337423263889</v>
+        <v>46188.318260497683</v>
       </c>
     </row>
     <row r="76">
@@ -4908,7 +4914,7 @@
         <v>24</v>
       </c>
       <c r="E76">
-        <v>7321304</v>
+        <v>7327419</v>
       </c>
       <c r="F76" t="s">
         <v>135</v>
@@ -4923,19 +4929,19 @@
         <v>136</v>
       </c>
       <c r="P76" s="1">
-        <v>46182.379826539349</v>
+        <v>46183.517797372682</v>
       </c>
       <c r="Q76" s="4">
-        <v>46183.458333333336</v>
+        <v>46184.3125</v>
       </c>
       <c r="R76" s="4">
-        <v>46184.566309837966</v>
+        <v>46188.329073842593</v>
       </c>
       <c r="S76">
-        <v>1784.000</v>
+        <v>10574.000</v>
       </c>
       <c r="T76">
-        <v>1784.000</v>
+        <v>10574.000</v>
       </c>
       <c r="U76">
         <v>0</v>
@@ -4944,7 +4950,7 @@
         <v>0</v>
       </c>
       <c r="W76" s="4">
-        <v>46188.318567708331</v>
+        <v>46188.337423263889</v>
       </c>
     </row>
     <row r="77">
@@ -4961,7 +4967,7 @@
         <v>24</v>
       </c>
       <c r="E77">
-        <v>7321303</v>
+        <v>7321304</v>
       </c>
       <c r="F77" t="s">
         <v>137</v>
@@ -4976,19 +4982,19 @@
         <v>138</v>
       </c>
       <c r="P77" s="1">
-        <v>46182.379728553242</v>
+        <v>46182.379826539349</v>
       </c>
       <c r="Q77" s="4">
         <v>46183.458333333336</v>
       </c>
       <c r="R77" s="4">
-        <v>46185.474632175923</v>
+        <v>46184.566309837966</v>
       </c>
       <c r="S77">
-        <v>15852.000</v>
+        <v>1784.000</v>
       </c>
       <c r="T77">
-        <v>15852.000</v>
+        <v>1784.000</v>
       </c>
       <c r="U77">
         <v>0</v>
@@ -4997,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="W77" s="4">
-        <v>46188.318567164351</v>
+        <v>46188.318567708331</v>
       </c>
     </row>
     <row r="78">
@@ -5014,7 +5020,7 @@
         <v>24</v>
       </c>
       <c r="E78">
-        <v>7312336</v>
+        <v>7321303</v>
       </c>
       <c r="F78" t="s">
         <v>139</v>
@@ -5029,19 +5035,19 @@
         <v>140</v>
       </c>
       <c r="P78" s="1">
-        <v>46181.394619016202</v>
+        <v>46182.379728553242</v>
       </c>
       <c r="Q78" s="4">
-        <v>46182.416666666664</v>
+        <v>46183.458333333336</v>
       </c>
       <c r="R78" s="4">
-        <v>46182.563263425924</v>
+        <v>46185.474632175923</v>
       </c>
       <c r="S78">
-        <v>8559.000</v>
+        <v>15852.000</v>
       </c>
       <c r="T78">
-        <v>8559.000</v>
+        <v>15852.000</v>
       </c>
       <c r="U78">
         <v>0</v>
@@ -5050,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="W78" s="4">
-        <v>46183.499163692133</v>
+        <v>46188.318567164351</v>
       </c>
     </row>
     <row r="79">
@@ -5067,7 +5073,7 @@
         <v>24</v>
       </c>
       <c r="E79">
-        <v>7312335</v>
+        <v>7312336</v>
       </c>
       <c r="F79" t="s">
         <v>141</v>
@@ -5078,23 +5084,23 @@
       <c r="H79" t="s">
         <v>24</v>
       </c>
-      <c r="M79" s="5" t="s">
+      <c r="M79" t="s">
         <v>142</v>
       </c>
       <c r="P79" s="1">
-        <v>46181.394497488429</v>
+        <v>46181.394619016202</v>
       </c>
       <c r="Q79" s="4">
-        <v>46182.388888888891</v>
+        <v>46182.416666666664</v>
       </c>
       <c r="R79" s="4">
-        <v>46185.475467280092</v>
+        <v>46182.563263425924</v>
       </c>
       <c r="S79">
-        <v>16641.000</v>
+        <v>8559.000</v>
       </c>
       <c r="T79">
-        <v>16641.000</v>
+        <v>8559.000</v>
       </c>
       <c r="U79">
         <v>0</v>
@@ -5103,7 +5109,7 @@
         <v>0</v>
       </c>
       <c r="W79" s="4">
-        <v>46188.318566284725</v>
+        <v>46183.499163692133</v>
       </c>
     </row>
     <row r="80">
@@ -5120,7 +5126,7 @@
         <v>24</v>
       </c>
       <c r="E80">
-        <v>7312334</v>
+        <v>7312335</v>
       </c>
       <c r="F80" t="s">
         <v>143</v>
@@ -5131,23 +5137,23 @@
       <c r="H80" t="s">
         <v>24</v>
       </c>
-      <c r="M80" t="s">
+      <c r="M80" s="5" t="s">
         <v>144</v>
       </c>
       <c r="P80" s="1">
-        <v>46181.394481597221</v>
+        <v>46181.394497488429</v>
       </c>
       <c r="Q80" s="4">
-        <v>46182.458333333336</v>
+        <v>46182.388888888891</v>
       </c>
       <c r="R80" s="4">
-        <v>46188.363727511576</v>
+        <v>46185.475467280092</v>
       </c>
       <c r="S80">
-        <v>5617.000</v>
+        <v>16641.000</v>
       </c>
       <c r="T80">
-        <v>5617.000</v>
+        <v>16641.000</v>
       </c>
       <c r="U80">
         <v>0</v>
@@ -5156,7 +5162,7 @@
         <v>0</v>
       </c>
       <c r="W80" s="4">
-        <v>46188.368130752315</v>
+        <v>46188.318566284725</v>
       </c>
     </row>
     <row r="81">
@@ -5173,7 +5179,7 @@
         <v>24</v>
       </c>
       <c r="E81">
-        <v>7312333</v>
+        <v>7312334</v>
       </c>
       <c r="F81" t="s">
         <v>145</v>
@@ -5188,19 +5194,19 @@
         <v>146</v>
       </c>
       <c r="P81" s="1">
-        <v>46181.394416122683</v>
+        <v>46181.394481597221</v>
       </c>
       <c r="Q81" s="4">
         <v>46182.458333333336</v>
       </c>
       <c r="R81" s="4">
-        <v>46188.402503240737</v>
+        <v>46188.363727511576</v>
       </c>
       <c r="S81">
-        <v>8272.000</v>
+        <v>5617.000</v>
       </c>
       <c r="T81">
-        <v>8272.000</v>
+        <v>5617.000</v>
       </c>
       <c r="U81">
         <v>0</v>
@@ -5209,7 +5215,7 @@
         <v>0</v>
       </c>
       <c r="W81" s="4">
-        <v>46188.404413310185</v>
+        <v>46188.368130752315</v>
       </c>
     </row>
     <row r="82">
@@ -5226,7 +5232,7 @@
         <v>24</v>
       </c>
       <c r="E82">
-        <v>7306694</v>
+        <v>7312333</v>
       </c>
       <c r="F82" t="s">
         <v>147</v>
@@ -5241,19 +5247,19 @@
         <v>148</v>
       </c>
       <c r="P82" s="1">
-        <v>46178.650135613425</v>
+        <v>46181.394416122683</v>
       </c>
       <c r="Q82" s="4">
-        <v>46181.3125</v>
+        <v>46182.458333333336</v>
       </c>
       <c r="R82" s="4">
-        <v>46188.351883217591</v>
+        <v>46188.402503240737</v>
       </c>
       <c r="S82">
-        <v>7291.000</v>
+        <v>8272.000</v>
       </c>
       <c r="T82">
-        <v>7291.000</v>
+        <v>8272.000</v>
       </c>
       <c r="U82">
         <v>0</v>
@@ -5262,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="W82" s="4">
-        <v>46188.368130405092</v>
+        <v>46188.404413310185</v>
       </c>
     </row>
     <row r="83">
@@ -5279,7 +5285,7 @@
         <v>24</v>
       </c>
       <c r="E83">
-        <v>7306693</v>
+        <v>7306694</v>
       </c>
       <c r="F83" t="s">
         <v>149</v>
@@ -5294,19 +5300,19 @@
         <v>150</v>
       </c>
       <c r="P83" s="1">
-        <v>46178.650101388892</v>
+        <v>46178.650135613425</v>
       </c>
       <c r="Q83" s="4">
-        <v>46181.395833333336</v>
+        <v>46181.3125</v>
       </c>
       <c r="R83" s="4">
-        <v>46188.361928472223</v>
+        <v>46188.351883217591</v>
       </c>
       <c r="S83">
-        <v>5272.000</v>
+        <v>7291.000</v>
       </c>
       <c r="T83">
-        <v>5272.000</v>
+        <v>7291.000</v>
       </c>
       <c r="U83">
         <v>0</v>
@@ -5315,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="W83" s="4">
-        <v>46188.368129826391</v>
+        <v>46188.368130405092</v>
       </c>
     </row>
     <row r="84">
@@ -5332,7 +5338,7 @@
         <v>24</v>
       </c>
       <c r="E84">
-        <v>7306692</v>
+        <v>7306693</v>
       </c>
       <c r="F84" t="s">
         <v>151</v>
@@ -5343,23 +5349,23 @@
       <c r="H84" t="s">
         <v>24</v>
       </c>
-      <c r="M84" s="5" t="s">
+      <c r="M84" t="s">
         <v>152</v>
       </c>
-      <c r="O84" s="4">
-        <v>46181.34375</v>
-      </c>
       <c r="P84" s="1">
-        <v>46178.650014085651</v>
+        <v>46178.650101388892</v>
+      </c>
+      <c r="Q84" s="4">
+        <v>46181.395833333336</v>
       </c>
       <c r="R84" s="4">
-        <v>46188.321652777777</v>
+        <v>46188.361928472223</v>
       </c>
       <c r="S84">
-        <v>10749.000</v>
+        <v>5272.000</v>
       </c>
       <c r="T84">
-        <v>10749.000</v>
+        <v>5272.000</v>
       </c>
       <c r="U84">
         <v>0</v>
@@ -5368,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="W84" s="4">
-        <v>46188.329306516207</v>
+        <v>46188.368129826391</v>
       </c>
     </row>
     <row r="85">
@@ -5385,7 +5391,7 @@
         <v>24</v>
       </c>
       <c r="E85">
-        <v>7297492</v>
+        <v>7306692</v>
       </c>
       <c r="F85" t="s">
         <v>153</v>
@@ -5396,23 +5402,23 @@
       <c r="H85" t="s">
         <v>24</v>
       </c>
-      <c r="M85" t="s">
+      <c r="M85" s="5" t="s">
         <v>154</v>
       </c>
       <c r="O85" s="4">
-        <v>46178.427083333336</v>
+        <v>46181.34375</v>
       </c>
       <c r="P85" s="1">
-        <v>46176.651338159725</v>
+        <v>46178.650014085651</v>
       </c>
       <c r="R85" s="4">
-        <v>46178.483032060183</v>
+        <v>46188.321652777777</v>
       </c>
       <c r="S85">
-        <v>6802.000</v>
+        <v>10749.000</v>
       </c>
       <c r="T85">
-        <v>6802.000</v>
+        <v>10749.000</v>
       </c>
       <c r="U85">
         <v>0</v>
@@ -5421,7 +5427,7 @@
         <v>0</v>
       </c>
       <c r="W85" s="4">
-        <v>46181.304573692127</v>
+        <v>46188.329306516207</v>
       </c>
     </row>
     <row r="86">
@@ -5438,7 +5444,7 @@
         <v>24</v>
       </c>
       <c r="E86">
-        <v>7297491</v>
+        <v>7297492</v>
       </c>
       <c r="F86" t="s">
         <v>155</v>
@@ -5453,22 +5459,19 @@
         <v>156</v>
       </c>
       <c r="O86" s="4">
-        <v>46178.416666666664</v>
+        <v>46178.427083333336</v>
       </c>
       <c r="P86" s="1">
-        <v>46176.651283530089</v>
-      </c>
-      <c r="Q86" s="4">
-        <v>46178.260416666664</v>
+        <v>46176.651338159725</v>
       </c>
       <c r="R86" s="4">
-        <v>46182.304580173608</v>
+        <v>46178.483032060183</v>
       </c>
       <c r="S86">
-        <v>19653.000</v>
+        <v>6802.000</v>
       </c>
       <c r="T86">
-        <v>19653.000</v>
+        <v>6802.000</v>
       </c>
       <c r="U86">
         <v>0</v>
@@ -5477,7 +5480,7 @@
         <v>0</v>
       </c>
       <c r="W86" s="4">
-        <v>46182.394867361108</v>
+        <v>46181.304573692127</v>
       </c>
     </row>
     <row r="87">
@@ -5494,7 +5497,7 @@
         <v>24</v>
       </c>
       <c r="E87">
-        <v>7296112</v>
+        <v>7297491</v>
       </c>
       <c r="F87" t="s">
         <v>157</v>
@@ -5508,17 +5511,23 @@
       <c r="M87" t="s">
         <v>158</v>
       </c>
+      <c r="O87" s="4">
+        <v>46178.416666666664</v>
+      </c>
       <c r="P87" s="1">
-        <v>46176.490794872683</v>
+        <v>46176.651283530089</v>
+      </c>
+      <c r="Q87" s="4">
+        <v>46178.260416666664</v>
       </c>
       <c r="R87" s="4">
-        <v>46188.357570370368</v>
+        <v>46182.304580173608</v>
       </c>
       <c r="S87">
-        <v>7146.000</v>
+        <v>19653.000</v>
       </c>
       <c r="T87">
-        <v>7146.000</v>
+        <v>19653.000</v>
       </c>
       <c r="U87">
         <v>0</v>
@@ -5527,7 +5536,7 @@
         <v>0</v>
       </c>
       <c r="W87" s="4">
-        <v>46188.368129664355</v>
+        <v>46182.394867361108</v>
       </c>
     </row>
     <row r="88">
@@ -5544,7 +5553,7 @@
         <v>24</v>
       </c>
       <c r="E88">
-        <v>7290516</v>
+        <v>7296112</v>
       </c>
       <c r="F88" t="s">
         <v>159</v>
@@ -5559,19 +5568,16 @@
         <v>160</v>
       </c>
       <c r="P88" s="1">
-        <v>46175.705564502314</v>
-      </c>
-      <c r="Q88" s="4">
-        <v>46176.59375</v>
+        <v>46176.490794872683</v>
       </c>
       <c r="R88" s="4">
-        <v>46178.37381646991</v>
+        <v>46188.357570370368</v>
       </c>
       <c r="S88">
-        <v>6600.000</v>
+        <v>7146.000</v>
       </c>
       <c r="T88">
-        <v>6600.000</v>
+        <v>7146.000</v>
       </c>
       <c r="U88">
         <v>0</v>
@@ -5580,7 +5586,7 @@
         <v>0</v>
       </c>
       <c r="W88" s="4">
-        <v>46181.304297951392</v>
+        <v>46188.368129664355</v>
       </c>
     </row>
     <row r="89">
@@ -5597,7 +5603,7 @@
         <v>24</v>
       </c>
       <c r="E89">
-        <v>7290515</v>
+        <v>7290516</v>
       </c>
       <c r="F89" t="s">
         <v>161</v>
@@ -5612,19 +5618,19 @@
         <v>162</v>
       </c>
       <c r="P89" s="1">
-        <v>46175.705520370371</v>
+        <v>46175.705564502314</v>
       </c>
       <c r="Q89" s="4">
-        <v>46175.604166666664</v>
+        <v>46176.59375</v>
       </c>
       <c r="R89" s="4">
-        <v>46176.32743784722</v>
+        <v>46178.37381646991</v>
       </c>
       <c r="S89">
-        <v>9893.000</v>
+        <v>6600.000</v>
       </c>
       <c r="T89">
-        <v>9893.000</v>
+        <v>6600.000</v>
       </c>
       <c r="U89">
         <v>0</v>
@@ -5633,7 +5639,7 @@
         <v>0</v>
       </c>
       <c r="W89" s="4">
-        <v>46176.36704571759</v>
+        <v>46181.304297951392</v>
       </c>
     </row>
     <row r="90">
@@ -5650,7 +5656,7 @@
         <v>24</v>
       </c>
       <c r="E90">
-        <v>7290513</v>
+        <v>7290515</v>
       </c>
       <c r="F90" t="s">
         <v>163</v>
@@ -5665,19 +5671,19 @@
         <v>164</v>
       </c>
       <c r="P90" s="1">
-        <v>46175.705472835645</v>
+        <v>46175.705520370371</v>
       </c>
       <c r="Q90" s="4">
-        <v>46175.541666666664</v>
+        <v>46175.604166666664</v>
       </c>
       <c r="R90" s="4">
-        <v>46176.390187384262</v>
+        <v>46176.32743784722</v>
       </c>
       <c r="S90">
-        <v>10634.000</v>
+        <v>9893.000</v>
       </c>
       <c r="T90">
-        <v>10634.000</v>
+        <v>9893.000</v>
       </c>
       <c r="U90">
         <v>0</v>
@@ -5686,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="W90" s="4">
-        <v>46176.479922453706</v>
+        <v>46176.36704571759</v>
       </c>
     </row>
     <row r="91">
@@ -5703,7 +5709,7 @@
         <v>24</v>
       </c>
       <c r="E91">
-        <v>7290512</v>
+        <v>7290513</v>
       </c>
       <c r="F91" t="s">
         <v>165</v>
@@ -5718,19 +5724,19 @@
         <v>166</v>
       </c>
       <c r="P91" s="1">
-        <v>46175.705376817132</v>
+        <v>46175.705472835645</v>
       </c>
       <c r="Q91" s="4">
-        <v>46176.5</v>
+        <v>46175.541666666664</v>
       </c>
       <c r="R91" s="4">
-        <v>46188.325696840278</v>
+        <v>46176.390187384262</v>
       </c>
       <c r="S91">
-        <v>14234.000</v>
+        <v>10634.000</v>
       </c>
       <c r="T91">
-        <v>14234.000</v>
+        <v>10634.000</v>
       </c>
       <c r="U91">
         <v>0</v>
@@ -5739,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="W91" s="4">
-        <v>46188.329304166669</v>
+        <v>46176.479922453706</v>
       </c>
     </row>
     <row r="92">
@@ -5756,7 +5762,7 @@
         <v>24</v>
       </c>
       <c r="E92">
-        <v>7277755</v>
+        <v>7290512</v>
       </c>
       <c r="F92" t="s">
         <v>167</v>
@@ -5771,19 +5777,19 @@
         <v>168</v>
       </c>
       <c r="P92" s="1">
-        <v>46174.492233680554</v>
+        <v>46175.705376817132</v>
       </c>
       <c r="Q92" s="4">
-        <v>46175.291666666664</v>
+        <v>46176.5</v>
       </c>
       <c r="R92" s="4">
-        <v>46175.460509027776</v>
+        <v>46188.325696840278</v>
       </c>
       <c r="S92">
-        <v>1502.000</v>
+        <v>14234.000</v>
       </c>
       <c r="T92">
-        <v>1502.000</v>
+        <v>14234.000</v>
       </c>
       <c r="U92">
         <v>0</v>
@@ -5792,7 +5798,7 @@
         <v>0</v>
       </c>
       <c r="W92" s="4">
-        <v>46176.367452777777</v>
+        <v>46188.329304166669</v>
       </c>
     </row>
     <row r="93">
@@ -5809,7 +5815,7 @@
         <v>24</v>
       </c>
       <c r="E93">
-        <v>7277745</v>
+        <v>7277755</v>
       </c>
       <c r="F93" t="s">
         <v>169</v>
@@ -5824,19 +5830,19 @@
         <v>170</v>
       </c>
       <c r="P93" s="1">
-        <v>46174.492115972222</v>
+        <v>46174.492233680554</v>
       </c>
       <c r="Q93" s="4">
         <v>46175.291666666664</v>
       </c>
       <c r="R93" s="4">
-        <v>46176.394080127313</v>
+        <v>46175.460509027776</v>
       </c>
       <c r="S93">
-        <v>8925.000</v>
+        <v>1502.000</v>
       </c>
       <c r="T93">
-        <v>8925.000</v>
+        <v>1502.000</v>
       </c>
       <c r="U93">
         <v>0</v>
@@ -5845,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="W93" s="4">
-        <v>46176.479621759259</v>
+        <v>46176.367452777777</v>
       </c>
     </row>
     <row r="94">
@@ -5862,7 +5868,7 @@
         <v>24</v>
       </c>
       <c r="E94">
-        <v>7277744</v>
+        <v>7277745</v>
       </c>
       <c r="F94" t="s">
         <v>171</v>
@@ -5877,19 +5883,19 @@
         <v>172</v>
       </c>
       <c r="P94" s="1">
-        <v>46174.49203425926</v>
+        <v>46174.492115972222</v>
       </c>
       <c r="Q94" s="4">
-        <v>46174.5</v>
+        <v>46175.291666666664</v>
       </c>
       <c r="R94" s="4">
-        <v>46175.401104085649</v>
+        <v>46176.394080127313</v>
       </c>
       <c r="S94">
-        <v>14377.000</v>
+        <v>8925.000</v>
       </c>
       <c r="T94">
-        <v>14377.000</v>
+        <v>8925.000</v>
       </c>
       <c r="U94">
         <v>0</v>
@@ -5898,7 +5904,7 @@
         <v>0</v>
       </c>
       <c r="W94" s="4">
-        <v>46175.446175925928</v>
+        <v>46176.479621759259</v>
       </c>
     </row>
     <row r="95">
@@ -5915,7 +5921,7 @@
         <v>24</v>
       </c>
       <c r="E95">
-        <v>7277742</v>
+        <v>7277744</v>
       </c>
       <c r="F95" t="s">
         <v>173</v>
@@ -5930,19 +5936,19 @@
         <v>174</v>
       </c>
       <c r="P95" s="1">
-        <v>46174.491930821758</v>
+        <v>46174.49203425926</v>
       </c>
       <c r="Q95" s="4">
-        <v>46174.416666666664</v>
+        <v>46174.5</v>
       </c>
       <c r="R95" s="4">
-        <v>46188.313768368054</v>
+        <v>46175.401104085649</v>
       </c>
       <c r="S95">
-        <v>18914.000</v>
+        <v>14377.000</v>
       </c>
       <c r="T95">
-        <v>18914.000</v>
+        <v>14377.000</v>
       </c>
       <c r="U95">
         <v>0</v>
@@ -5951,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="W95" s="4">
-        <v>46188.329302546299</v>
+        <v>46175.446175925928</v>
       </c>
     </row>
     <row r="96">
@@ -5968,7 +5974,7 @@
         <v>24</v>
       </c>
       <c r="E96">
-        <v>7276672</v>
+        <v>7277742</v>
       </c>
       <c r="F96" t="s">
         <v>175</v>
@@ -5983,19 +5989,19 @@
         <v>176</v>
       </c>
       <c r="P96" s="1">
-        <v>46174.386965358797</v>
+        <v>46174.491930821758</v>
       </c>
       <c r="Q96" s="4">
-        <v>46174.3125</v>
+        <v>46174.416666666664</v>
       </c>
       <c r="R96" s="4">
-        <v>46175.277797997682</v>
+        <v>46188.313768368054</v>
       </c>
       <c r="S96">
-        <v>445.000</v>
+        <v>18914.000</v>
       </c>
       <c r="T96">
-        <v>445.000</v>
+        <v>18914.000</v>
       </c>
       <c r="U96">
         <v>0</v>
@@ -6004,7 +6010,7 @@
         <v>0</v>
       </c>
       <c r="W96" s="4">
-        <v>46175.446175925928</v>
+        <v>46188.329302546299</v>
       </c>
     </row>
     <row r="97">
@@ -6021,7 +6027,7 @@
         <v>24</v>
       </c>
       <c r="E97">
-        <v>7276670</v>
+        <v>7276672</v>
       </c>
       <c r="F97" t="s">
         <v>177</v>
@@ -6036,19 +6042,19 @@
         <v>178</v>
       </c>
       <c r="P97" s="1">
-        <v>46174.386795023151</v>
+        <v>46174.386965358797</v>
       </c>
       <c r="Q97" s="4">
         <v>46174.3125</v>
       </c>
       <c r="R97" s="4">
-        <v>46181.602299189813</v>
+        <v>46175.277797997682</v>
       </c>
       <c r="S97">
-        <v>7766.000</v>
+        <v>445.000</v>
       </c>
       <c r="T97">
-        <v>7766.000</v>
+        <v>445.000</v>
       </c>
       <c r="U97">
         <v>0</v>
@@ -6057,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="W97" s="4">
-        <v>46181.607877893519</v>
+        <v>46175.446175925928</v>
       </c>
     </row>
     <row r="98">
@@ -6074,7 +6080,7 @@
         <v>24</v>
       </c>
       <c r="E98">
-        <v>7261067</v>
+        <v>7276670</v>
       </c>
       <c r="F98" t="s">
         <v>179</v>
@@ -6089,16 +6095,19 @@
         <v>180</v>
       </c>
       <c r="P98" s="1">
-        <v>46171.450339317133</v>
+        <v>46174.386795023151</v>
+      </c>
+      <c r="Q98" s="4">
+        <v>46174.3125</v>
       </c>
       <c r="R98" s="4">
-        <v>46171.468652743053</v>
+        <v>46181.602299189813</v>
       </c>
       <c r="S98">
-        <v>13827.000</v>
+        <v>7766.000</v>
       </c>
       <c r="T98">
-        <v>13827.000</v>
+        <v>7766.000</v>
       </c>
       <c r="U98">
         <v>0</v>
@@ -6107,7 +6116,7 @@
         <v>0</v>
       </c>
       <c r="W98" s="4">
-        <v>46171.521808101854</v>
+        <v>46181.607877893519</v>
       </c>
     </row>
     <row r="99">
@@ -6124,7 +6133,7 @@
         <v>24</v>
       </c>
       <c r="E99">
-        <v>7256959</v>
+        <v>7261067</v>
       </c>
       <c r="F99" t="s">
         <v>181</v>
@@ -6139,19 +6148,16 @@
         <v>182</v>
       </c>
       <c r="P99" s="1">
-        <v>46169.73840185185</v>
-      </c>
-      <c r="Q99" s="4">
-        <v>46171.520833333336</v>
+        <v>46171.450339317133</v>
       </c>
       <c r="R99" s="4">
-        <v>46181.602367395833</v>
+        <v>46171.468652743053</v>
       </c>
       <c r="S99">
-        <v>11921.000</v>
+        <v>13827.000</v>
       </c>
       <c r="T99">
-        <v>11921.000</v>
+        <v>13827.000</v>
       </c>
       <c r="U99">
         <v>0</v>
@@ -6160,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="W99" s="4">
-        <v>46181.607877002316</v>
+        <v>46171.521808101854</v>
       </c>
     </row>
     <row r="100">
@@ -6177,7 +6183,7 @@
         <v>24</v>
       </c>
       <c r="E100">
-        <v>7256954</v>
+        <v>7256959</v>
       </c>
       <c r="F100" t="s">
         <v>183</v>
@@ -6192,19 +6198,19 @@
         <v>184</v>
       </c>
       <c r="P100" s="1">
-        <v>46169.737280092595</v>
+        <v>46169.73840185185</v>
       </c>
       <c r="Q100" s="4">
-        <v>46171.416666666664</v>
+        <v>46171.520833333336</v>
       </c>
       <c r="R100" s="4">
-        <v>46171.471500266205</v>
+        <v>46181.602367395833</v>
       </c>
       <c r="S100">
-        <v>11226.000</v>
+        <v>11921.000</v>
       </c>
       <c r="T100">
-        <v>11226.000</v>
+        <v>11921.000</v>
       </c>
       <c r="U100">
         <v>0</v>
@@ -6213,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="W100" s="4">
-        <v>46171.521807557867</v>
+        <v>46181.607877002316</v>
       </c>
     </row>
     <row r="101">
@@ -6230,7 +6236,7 @@
         <v>24</v>
       </c>
       <c r="E101">
-        <v>7256935</v>
+        <v>7256954</v>
       </c>
       <c r="F101" t="s">
         <v>185</v>
@@ -6245,19 +6251,19 @@
         <v>186</v>
       </c>
       <c r="P101" s="1">
-        <v>46169.735800810187</v>
+        <v>46169.737280092595</v>
       </c>
       <c r="Q101" s="4">
-        <v>46171.25</v>
+        <v>46171.416666666664</v>
       </c>
       <c r="R101" s="4">
-        <v>46171.474860069444</v>
+        <v>46171.471500266205</v>
       </c>
       <c r="S101">
-        <v>12909.000</v>
+        <v>11226.000</v>
       </c>
       <c r="T101">
-        <v>12909.000</v>
+        <v>11226.000</v>
       </c>
       <c r="U101">
         <v>0</v>
@@ -6266,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="W101" s="4">
-        <v>46171.521807025463</v>
+        <v>46171.521807557867</v>
       </c>
     </row>
     <row r="102">
@@ -6283,7 +6289,7 @@
         <v>24</v>
       </c>
       <c r="E102">
-        <v>7256927</v>
+        <v>7256935</v>
       </c>
       <c r="F102" t="s">
         <v>187</v>
@@ -6297,23 +6303,20 @@
       <c r="M102" t="s">
         <v>188</v>
       </c>
-      <c r="O102" s="4">
-        <v>46170.541666666664</v>
-      </c>
       <c r="P102" s="1">
-        <v>46169.733974768518</v>
+        <v>46169.735800810187</v>
       </c>
       <c r="Q102" s="4">
-        <v>46171.375</v>
+        <v>46171.25</v>
       </c>
       <c r="R102" s="4">
-        <v>46171.384800081018</v>
+        <v>46171.474860069444</v>
       </c>
       <c r="S102">
-        <v>470.000</v>
+        <v>12909.000</v>
       </c>
       <c r="T102">
-        <v>470.000</v>
+        <v>12909.000</v>
       </c>
       <c r="U102">
         <v>0</v>
@@ -6322,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="W102" s="4">
-        <v>46171.521806828707</v>
+        <v>46171.521807025463</v>
       </c>
     </row>
     <row r="103">
@@ -6339,7 +6342,7 @@
         <v>24</v>
       </c>
       <c r="E103">
-        <v>7256837</v>
+        <v>7256927</v>
       </c>
       <c r="F103" t="s">
         <v>189</v>
@@ -6357,19 +6360,19 @@
         <v>46170.541666666664</v>
       </c>
       <c r="P103" s="1">
-        <v>46169.717724456015</v>
+        <v>46169.733974768518</v>
       </c>
       <c r="Q103" s="4">
         <v>46171.375</v>
       </c>
       <c r="R103" s="4">
-        <v>46181.601758877317</v>
+        <v>46171.384800081018</v>
       </c>
       <c r="S103">
-        <v>10645.000</v>
+        <v>470.000</v>
       </c>
       <c r="T103">
-        <v>10645.000</v>
+        <v>470.000</v>
       </c>
       <c r="U103">
         <v>0</v>
@@ -6378,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="W103" s="4">
-        <v>46181.607876122682</v>
+        <v>46171.521806828707</v>
       </c>
     </row>
     <row r="104">
@@ -6395,7 +6398,7 @@
         <v>24</v>
       </c>
       <c r="E104">
-        <v>7256698</v>
+        <v>7256837</v>
       </c>
       <c r="F104" t="s">
         <v>191</v>
@@ -6410,22 +6413,22 @@
         <v>192</v>
       </c>
       <c r="O104" s="4">
-        <v>46170.416666666664</v>
+        <v>46170.541666666664</v>
       </c>
       <c r="P104" s="1">
-        <v>46169.704318553238</v>
+        <v>46169.717724456015</v>
       </c>
       <c r="Q104" s="4">
-        <v>46170.4375</v>
+        <v>46171.375</v>
       </c>
       <c r="R104" s="4">
-        <v>46170.55747615741</v>
+        <v>46181.601758877317</v>
       </c>
       <c r="S104">
-        <v>15811.000</v>
+        <v>10645.000</v>
       </c>
       <c r="T104">
-        <v>15811.000</v>
+        <v>10645.000</v>
       </c>
       <c r="U104">
         <v>0</v>
@@ -6434,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="W104" s="4">
-        <v>46171.52180628472</v>
+        <v>46181.607876122682</v>
       </c>
     </row>
     <row r="105">
@@ -6451,7 +6454,7 @@
         <v>24</v>
       </c>
       <c r="E105">
-        <v>7256674</v>
+        <v>7256698</v>
       </c>
       <c r="F105" t="s">
         <v>193</v>
@@ -6466,22 +6469,22 @@
         <v>194</v>
       </c>
       <c r="O105" s="4">
-        <v>46170.291666666664</v>
+        <v>46170.416666666664</v>
       </c>
       <c r="P105" s="1">
-        <v>46169.697586805552</v>
+        <v>46169.704318553238</v>
       </c>
       <c r="Q105" s="4">
-        <v>46171.291666666664</v>
+        <v>46170.4375</v>
       </c>
       <c r="R105" s="4">
-        <v>46171.366929745367</v>
+        <v>46170.55747615741</v>
       </c>
       <c r="S105">
-        <v>6703.000</v>
+        <v>15811.000</v>
       </c>
       <c r="T105">
-        <v>6703.000</v>
+        <v>15811.000</v>
       </c>
       <c r="U105">
         <v>0</v>
@@ -6490,7 +6493,7 @@
         <v>0</v>
       </c>
       <c r="W105" s="4">
-        <v>46171.521805937497</v>
+        <v>46171.52180628472</v>
       </c>
     </row>
     <row r="106">
@@ -6507,7 +6510,7 @@
         <v>24</v>
       </c>
       <c r="E106">
-        <v>7243671</v>
+        <v>7256674</v>
       </c>
       <c r="F106" t="s">
         <v>195</v>
@@ -6521,20 +6524,23 @@
       <c r="M106" t="s">
         <v>196</v>
       </c>
+      <c r="O106" s="4">
+        <v>46170.291666666664</v>
+      </c>
       <c r="P106" s="1">
-        <v>46167.398480636577</v>
+        <v>46169.697586805552</v>
       </c>
       <c r="Q106" s="4">
-        <v>46170.25</v>
+        <v>46171.291666666664</v>
       </c>
       <c r="R106" s="4">
-        <v>46170.38833533565</v>
+        <v>46171.366929745367</v>
       </c>
       <c r="S106">
-        <v>767.000</v>
+        <v>6703.000</v>
       </c>
       <c r="T106">
-        <v>767.000</v>
+        <v>6703.000</v>
       </c>
       <c r="U106">
         <v>0</v>
@@ -6543,7 +6549,7 @@
         <v>0</v>
       </c>
       <c r="W106" s="4">
-        <v>46171.521805752316</v>
+        <v>46171.521805937497</v>
       </c>
     </row>
     <row r="107">
@@ -6560,7 +6566,7 @@
         <v>24</v>
       </c>
       <c r="E107">
-        <v>7243667</v>
+        <v>7243671</v>
       </c>
       <c r="F107" t="s">
         <v>197</v>
@@ -6575,19 +6581,19 @@
         <v>198</v>
       </c>
       <c r="P107" s="1">
-        <v>46167.398084108798</v>
+        <v>46167.398480636577</v>
       </c>
       <c r="Q107" s="4">
         <v>46170.25</v>
       </c>
       <c r="R107" s="4">
-        <v>46170.366140659724</v>
+        <v>46170.38833533565</v>
       </c>
       <c r="S107">
-        <v>7345.000</v>
+        <v>767.000</v>
       </c>
       <c r="T107">
-        <v>7345.000</v>
+        <v>767.000</v>
       </c>
       <c r="U107">
         <v>0</v>
@@ -6596,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="W107" s="4">
-        <v>46170.37235636574</v>
+        <v>46171.521805752316</v>
       </c>
     </row>
     <row r="108">
@@ -6613,7 +6619,7 @@
         <v>24</v>
       </c>
       <c r="E108">
-        <v>7243666</v>
+        <v>7243667</v>
       </c>
       <c r="F108" t="s">
         <v>199</v>
@@ -6628,19 +6634,19 @@
         <v>200</v>
       </c>
       <c r="P108" s="1">
-        <v>46167.397709988429</v>
+        <v>46167.398084108798</v>
       </c>
       <c r="Q108" s="4">
-        <v>46169.444444444445</v>
+        <v>46170.25</v>
       </c>
       <c r="R108" s="4">
-        <v>46169.627317511571</v>
+        <v>46170.366140659724</v>
       </c>
       <c r="S108">
-        <v>5379.000</v>
+        <v>7345.000</v>
       </c>
       <c r="T108">
-        <v>5379.000</v>
+        <v>7345.000</v>
       </c>
       <c r="U108">
         <v>0</v>
@@ -6649,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="W108" s="4">
-        <v>46170.372355636573</v>
+        <v>46170.37235636574</v>
       </c>
     </row>
     <row r="109">
@@ -6666,7 +6672,7 @@
         <v>24</v>
       </c>
       <c r="E109">
-        <v>7243664</v>
+        <v>7243666</v>
       </c>
       <c r="F109" t="s">
         <v>201</v>
@@ -6681,19 +6687,19 @@
         <v>202</v>
       </c>
       <c r="P109" s="1">
-        <v>46167.397293715279</v>
+        <v>46167.397709988429</v>
       </c>
       <c r="Q109" s="4">
-        <v>46169.3125</v>
+        <v>46169.444444444445</v>
       </c>
       <c r="R109" s="4">
-        <v>46170.486638159724</v>
+        <v>46169.627317511571</v>
       </c>
       <c r="S109">
-        <v>5002.000</v>
+        <v>5379.000</v>
       </c>
       <c r="T109">
-        <v>5002.000</v>
+        <v>5379.000</v>
       </c>
       <c r="U109">
         <v>0</v>
@@ -6702,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="W109" s="4">
-        <v>46171.52288329861</v>
+        <v>46170.372355636573</v>
       </c>
     </row>
     <row r="110">
@@ -6719,7 +6725,7 @@
         <v>24</v>
       </c>
       <c r="E110">
-        <v>7243663</v>
+        <v>7243664</v>
       </c>
       <c r="F110" t="s">
         <v>203</v>
@@ -6734,19 +6740,19 @@
         <v>204</v>
       </c>
       <c r="P110" s="1">
-        <v>46167.396879664353</v>
+        <v>46167.397293715279</v>
       </c>
       <c r="Q110" s="4">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="R110" s="4">
-        <v>46168.372719247687</v>
+        <v>46170.486638159724</v>
       </c>
       <c r="S110">
-        <v>7178.000</v>
+        <v>5002.000</v>
       </c>
       <c r="T110">
-        <v>7178.000</v>
+        <v>5002.000</v>
       </c>
       <c r="U110">
         <v>0</v>
@@ -6755,7 +6761,7 @@
         <v>0</v>
       </c>
       <c r="W110" s="4">
-        <v>46168.383504201389</v>
+        <v>46171.52288329861</v>
       </c>
     </row>
     <row r="111">
@@ -6772,7 +6778,7 @@
         <v>24</v>
       </c>
       <c r="E111">
-        <v>7243660</v>
+        <v>7243663</v>
       </c>
       <c r="F111" t="s">
         <v>205</v>
@@ -6787,19 +6793,19 @@
         <v>206</v>
       </c>
       <c r="P111" s="1">
-        <v>46167.396469907406</v>
+        <v>46167.396879664353</v>
       </c>
       <c r="Q111" s="4">
-        <v>46168.375</v>
+        <v>46168.3125</v>
       </c>
       <c r="R111" s="4">
-        <v>46168.522693749997</v>
+        <v>46168.372719247687</v>
       </c>
       <c r="S111">
-        <v>15726.000</v>
+        <v>7178.000</v>
       </c>
       <c r="T111">
-        <v>15726.000</v>
+        <v>7178.000</v>
       </c>
       <c r="U111">
         <v>0</v>
@@ -6808,7 +6814,7 @@
         <v>0</v>
       </c>
       <c r="W111" s="4">
-        <v>46168.603323611111</v>
+        <v>46168.383504201389</v>
       </c>
     </row>
     <row r="112">
@@ -6825,7 +6831,7 @@
         <v>24</v>
       </c>
       <c r="E112">
-        <v>7243658</v>
+        <v>7243660</v>
       </c>
       <c r="F112" t="s">
         <v>207</v>
@@ -6840,19 +6846,19 @@
         <v>208</v>
       </c>
       <c r="P112" s="1">
-        <v>46167.396019097221</v>
+        <v>46167.396469907406</v>
       </c>
       <c r="Q112" s="4">
-        <v>46168.479166666664</v>
+        <v>46168.375</v>
       </c>
       <c r="R112" s="4">
-        <v>46168.596083993056</v>
+        <v>46168.522693749997</v>
       </c>
       <c r="S112">
-        <v>18164.000</v>
+        <v>15726.000</v>
       </c>
       <c r="T112">
-        <v>18164.000</v>
+        <v>15726.000</v>
       </c>
       <c r="U112">
         <v>0</v>
@@ -6861,7 +6867,7 @@
         <v>0</v>
       </c>
       <c r="W112" s="4">
-        <v>46168.603323067131</v>
+        <v>46168.603323611111</v>
       </c>
     </row>
     <row r="113">
@@ -6878,7 +6884,7 @@
         <v>24</v>
       </c>
       <c r="E113">
-        <v>7243656</v>
+        <v>7243658</v>
       </c>
       <c r="F113" t="s">
         <v>209</v>
@@ -6893,19 +6899,19 @@
         <v>210</v>
       </c>
       <c r="P113" s="1">
-        <v>46167.395494872682</v>
+        <v>46167.396019097221</v>
       </c>
       <c r="Q113" s="4">
-        <v>46168.25</v>
+        <v>46168.479166666664</v>
       </c>
       <c r="R113" s="4">
-        <v>46168.325715162035</v>
+        <v>46168.596083993056</v>
       </c>
       <c r="S113">
-        <v>8924.000</v>
+        <v>18164.000</v>
       </c>
       <c r="T113">
-        <v>8924.000</v>
+        <v>18164.000</v>
       </c>
       <c r="U113">
         <v>0</v>
@@ -6914,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="W113" s="4">
-        <v>46168.383503321762</v>
+        <v>46168.603323067131</v>
       </c>
     </row>
     <row r="114">
@@ -6931,7 +6937,7 @@
         <v>24</v>
       </c>
       <c r="E114">
-        <v>7234523</v>
+        <v>7243656</v>
       </c>
       <c r="F114" t="s">
         <v>211</v>
@@ -6946,16 +6952,19 @@
         <v>212</v>
       </c>
       <c r="P114" s="1">
-        <v>46164.418446909724</v>
+        <v>46167.395494872682</v>
+      </c>
+      <c r="Q114" s="4">
+        <v>46168.25</v>
       </c>
       <c r="R114" s="4">
-        <v>46164.542648229166</v>
+        <v>46168.325715162035</v>
       </c>
       <c r="S114">
-        <v>3573.000</v>
+        <v>8924.000</v>
       </c>
       <c r="T114">
-        <v>3573.000</v>
+        <v>8924.000</v>
       </c>
       <c r="U114">
         <v>0</v>
@@ -6964,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="W114" s="4">
-        <v>46164.552599270835</v>
+        <v>46168.383503321762</v>
       </c>
     </row>
     <row r="115">
@@ -6981,7 +6990,7 @@
         <v>24</v>
       </c>
       <c r="E115">
-        <v>7222955</v>
+        <v>7234523</v>
       </c>
       <c r="F115" t="s">
         <v>213</v>
@@ -6996,19 +7005,16 @@
         <v>214</v>
       </c>
       <c r="P115" s="1">
-        <v>46162.757414780091</v>
-      </c>
-      <c r="Q115" s="4">
-        <v>46164.260416666664</v>
+        <v>46164.418446909724</v>
       </c>
       <c r="R115" s="4">
-        <v>46164.550929016201</v>
+        <v>46164.542648229166</v>
       </c>
       <c r="S115">
-        <v>10360.000</v>
+        <v>3573.000</v>
       </c>
       <c r="T115">
-        <v>10360.000</v>
+        <v>3573.000</v>
       </c>
       <c r="U115">
         <v>0</v>
@@ -7017,7 +7023,7 @@
         <v>0</v>
       </c>
       <c r="W115" s="4">
-        <v>46164.552598877315</v>
+        <v>46164.552599270835</v>
       </c>
     </row>
     <row r="116">
@@ -7034,7 +7040,7 @@
         <v>24</v>
       </c>
       <c r="E116">
-        <v>7222913</v>
+        <v>7222955</v>
       </c>
       <c r="F116" t="s">
         <v>215</v>
@@ -7045,23 +7051,23 @@
       <c r="H116" t="s">
         <v>24</v>
       </c>
-      <c r="M116" s="5" t="s">
+      <c r="M116" t="s">
         <v>216</v>
       </c>
       <c r="P116" s="1">
-        <v>46162.756352662036</v>
+        <v>46162.757414780091</v>
       </c>
       <c r="Q116" s="4">
-        <v>46164.333333333336</v>
+        <v>46164.260416666664</v>
       </c>
       <c r="R116" s="4">
-        <v>46164.404302395837</v>
+        <v>46164.550929016201</v>
       </c>
       <c r="S116">
-        <v>7657.000</v>
+        <v>10360.000</v>
       </c>
       <c r="T116">
-        <v>7657.000</v>
+        <v>10360.000</v>
       </c>
       <c r="U116">
         <v>0</v>
@@ -7070,7 +7076,7 @@
         <v>0</v>
       </c>
       <c r="W116" s="4">
-        <v>46164.453907951392</v>
+        <v>46164.552598877315</v>
       </c>
     </row>
     <row r="117">
@@ -7087,7 +7093,7 @@
         <v>24</v>
       </c>
       <c r="E117">
-        <v>7222907</v>
+        <v>7222913</v>
       </c>
       <c r="F117" t="s">
         <v>217</v>
@@ -7098,23 +7104,23 @@
       <c r="H117" t="s">
         <v>24</v>
       </c>
-      <c r="M117" t="s">
+      <c r="M117" s="5" t="s">
         <v>218</v>
       </c>
       <c r="P117" s="1">
-        <v>46162.75522561343</v>
+        <v>46162.756352662036</v>
       </c>
       <c r="Q117" s="4">
-        <v>46163.368055555555</v>
+        <v>46164.333333333336</v>
       </c>
       <c r="R117" s="4">
-        <v>46163.519357025463</v>
+        <v>46164.404302395837</v>
       </c>
       <c r="S117">
-        <v>10357.000</v>
+        <v>7657.000</v>
       </c>
       <c r="T117">
-        <v>10357.000</v>
+        <v>7657.000</v>
       </c>
       <c r="U117">
         <v>0</v>
@@ -7123,7 +7129,7 @@
         <v>0</v>
       </c>
       <c r="W117" s="4">
-        <v>46163.541440972222</v>
+        <v>46164.453907951392</v>
       </c>
     </row>
     <row r="118">
@@ -7140,7 +7146,7 @@
         <v>24</v>
       </c>
       <c r="E118">
-        <v>7217995</v>
+        <v>7222907</v>
       </c>
       <c r="F118" t="s">
         <v>219</v>
@@ -7155,19 +7161,19 @@
         <v>220</v>
       </c>
       <c r="P118" s="1">
-        <v>46162.28924351852</v>
+        <v>46162.75522561343</v>
       </c>
       <c r="Q118" s="4">
-        <v>46163.291666666664</v>
+        <v>46163.368055555555</v>
       </c>
       <c r="R118" s="4">
-        <v>46163.616474340277</v>
+        <v>46163.519357025463</v>
       </c>
       <c r="S118">
-        <v>5708.000</v>
+        <v>10357.000</v>
       </c>
       <c r="T118">
-        <v>5708.000</v>
+        <v>10357.000</v>
       </c>
       <c r="U118">
         <v>0</v>
@@ -7176,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="W118" s="4">
-        <v>46164.389474687501</v>
+        <v>46163.541440972222</v>
       </c>
     </row>
     <row r="119">
@@ -7193,7 +7199,7 @@
         <v>24</v>
       </c>
       <c r="E119">
-        <v>7217994</v>
+        <v>7217995</v>
       </c>
       <c r="F119" t="s">
         <v>221</v>
@@ -7208,19 +7214,19 @@
         <v>222</v>
       </c>
       <c r="P119" s="1">
-        <v>46162.288815127315</v>
+        <v>46162.28924351852</v>
       </c>
       <c r="Q119" s="4">
         <v>46163.291666666664</v>
       </c>
       <c r="R119" s="4">
-        <v>46163.35348445602</v>
+        <v>46163.616474340277</v>
       </c>
       <c r="S119">
-        <v>3946.000</v>
+        <v>5708.000</v>
       </c>
       <c r="T119">
-        <v>3946.000</v>
+        <v>5708.000</v>
       </c>
       <c r="U119">
         <v>0</v>
@@ -7229,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="W119" s="4">
-        <v>46163.541440775465</v>
+        <v>46164.389474687501</v>
       </c>
     </row>
     <row r="120">
@@ -7246,7 +7252,7 @@
         <v>24</v>
       </c>
       <c r="E120">
-        <v>7217993</v>
+        <v>7217994</v>
       </c>
       <c r="F120" t="s">
         <v>223</v>
@@ -7260,23 +7266,20 @@
       <c r="M120" t="s">
         <v>224</v>
       </c>
-      <c r="O120" s="4">
-        <v>46162.416666666664</v>
-      </c>
       <c r="P120" s="1">
-        <v>46162.287909756946</v>
+        <v>46162.288815127315</v>
       </c>
       <c r="Q120" s="4">
-        <v>46162.416666666664</v>
+        <v>46163.291666666664</v>
       </c>
       <c r="R120" s="4">
-        <v>46163.518015046298</v>
+        <v>46163.35348445602</v>
       </c>
       <c r="S120">
-        <v>12356.000</v>
+        <v>3946.000</v>
       </c>
       <c r="T120">
-        <v>12356.000</v>
+        <v>3946.000</v>
       </c>
       <c r="U120">
         <v>0</v>
@@ -7285,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="W120" s="4">
-        <v>46163.541439895831</v>
+        <v>46163.541440775465</v>
       </c>
     </row>
     <row r="121">
@@ -7302,7 +7305,7 @@
         <v>24</v>
       </c>
       <c r="E121">
-        <v>7217991</v>
+        <v>7217993</v>
       </c>
       <c r="F121" t="s">
         <v>225</v>
@@ -7317,22 +7320,22 @@
         <v>226</v>
       </c>
       <c r="O121" s="4">
-        <v>46162.291666666664</v>
+        <v>46162.416666666664</v>
       </c>
       <c r="P121" s="1">
-        <v>46162.28736678241</v>
+        <v>46162.287909756946</v>
       </c>
       <c r="Q121" s="4">
-        <v>46162.513220173612</v>
+        <v>46162.416666666664</v>
       </c>
       <c r="R121" s="4">
-        <v>46163.531940428242</v>
+        <v>46163.518015046298</v>
       </c>
       <c r="S121">
-        <v>12360.000</v>
+        <v>12356.000</v>
       </c>
       <c r="T121">
-        <v>12360.000</v>
+        <v>12356.000</v>
       </c>
       <c r="U121">
         <v>0</v>
@@ -7341,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="W121" s="4">
-        <v>46163.541439351851</v>
+        <v>46163.541439895831</v>
       </c>
     </row>
     <row r="122">
@@ -7358,7 +7361,7 @@
         <v>24</v>
       </c>
       <c r="E122">
-        <v>7209853</v>
+        <v>7217991</v>
       </c>
       <c r="F122" t="s">
         <v>227</v>
@@ -7372,17 +7375,23 @@
       <c r="M122" t="s">
         <v>228</v>
       </c>
+      <c r="O122" s="4">
+        <v>46162.291666666664</v>
+      </c>
       <c r="P122" s="1">
-        <v>46161.375624884262</v>
+        <v>46162.28736678241</v>
+      </c>
+      <c r="Q122" s="4">
+        <v>46162.513220173612</v>
       </c>
       <c r="R122" s="4">
-        <v>46162.474544826386</v>
+        <v>46163.531940428242</v>
       </c>
       <c r="S122">
-        <v>10350.000</v>
+        <v>12360.000</v>
       </c>
       <c r="T122">
-        <v>10350.000</v>
+        <v>12360.000</v>
       </c>
       <c r="U122">
         <v>0</v>
@@ -7391,7 +7400,7 @@
         <v>0</v>
       </c>
       <c r="W122" s="4">
-        <v>46163.484965937503</v>
+        <v>46163.541439351851</v>
       </c>
     </row>
     <row r="123">
@@ -7408,7 +7417,7 @@
         <v>24</v>
       </c>
       <c r="E123">
-        <v>7209851</v>
+        <v>7209853</v>
       </c>
       <c r="F123" t="s">
         <v>229</v>
@@ -7423,16 +7432,16 @@
         <v>230</v>
       </c>
       <c r="P123" s="1">
-        <v>46161.374809525463</v>
+        <v>46161.375624884262</v>
       </c>
       <c r="R123" s="4">
-        <v>46168.442082719906</v>
+        <v>46162.474544826386</v>
       </c>
       <c r="S123">
-        <v>10564.000</v>
+        <v>10350.000</v>
       </c>
       <c r="T123">
-        <v>10564.000</v>
+        <v>10350.000</v>
       </c>
       <c r="U123">
         <v>0</v>
@@ -7441,7 +7450,7 @@
         <v>0</v>
       </c>
       <c r="W123" s="4">
-        <v>46168.603322337964</v>
+        <v>46163.484965937503</v>
       </c>
     </row>
     <row r="124">
@@ -7458,7 +7467,7 @@
         <v>24</v>
       </c>
       <c r="E124">
-        <v>7209848</v>
+        <v>7209851</v>
       </c>
       <c r="F124" t="s">
         <v>231</v>
@@ -7472,23 +7481,17 @@
       <c r="M124" t="s">
         <v>232</v>
       </c>
-      <c r="O124" s="4">
-        <v>46161.291666666664</v>
-      </c>
       <c r="P124" s="1">
-        <v>46161.373708449071</v>
-      </c>
-      <c r="Q124" s="4">
-        <v>46161.586805555555</v>
+        <v>46161.374809525463</v>
       </c>
       <c r="R124" s="4">
-        <v>46163.626690358797</v>
+        <v>46168.442082719906</v>
       </c>
       <c r="S124">
-        <v>16674.000</v>
+        <v>10564.000</v>
       </c>
       <c r="T124">
-        <v>16674.000</v>
+        <v>10564.000</v>
       </c>
       <c r="U124">
         <v>0</v>
@@ -7497,7 +7500,7 @@
         <v>0</v>
       </c>
       <c r="W124" s="4">
-        <v>46164.389386608796</v>
+        <v>46168.603322337964</v>
       </c>
     </row>
     <row r="125">
@@ -7514,7 +7517,7 @@
         <v>24</v>
       </c>
       <c r="E125">
-        <v>7186225</v>
+        <v>7209848</v>
       </c>
       <c r="F125" t="s">
         <v>233</v>
@@ -7528,20 +7531,23 @@
       <c r="M125" t="s">
         <v>234</v>
       </c>
+      <c r="O125" s="4">
+        <v>46161.291666666664</v>
+      </c>
       <c r="P125" s="1">
-        <v>46157.585703935183</v>
+        <v>46161.373708449071</v>
       </c>
       <c r="Q125" s="4">
-        <v>46160.493105243055</v>
+        <v>46161.586805555555</v>
       </c>
       <c r="R125" s="4">
-        <v>46170.487253356485</v>
+        <v>46163.626690358797</v>
       </c>
       <c r="S125">
-        <v>13685.000</v>
+        <v>16674.000</v>
       </c>
       <c r="T125">
-        <v>13685.000</v>
+        <v>16674.000</v>
       </c>
       <c r="U125">
         <v>0</v>
@@ -7550,7 +7556,7 @@
         <v>0</v>
       </c>
       <c r="W125" s="4">
-        <v>46171.521805011573</v>
+        <v>46164.389386608796</v>
       </c>
     </row>
     <row r="126">
@@ -7567,7 +7573,7 @@
         <v>24</v>
       </c>
       <c r="E126">
-        <v>7186224</v>
+        <v>7186225</v>
       </c>
       <c r="F126" t="s">
         <v>235</v>
@@ -7579,22 +7585,22 @@
         <v>24</v>
       </c>
       <c r="M126" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P126" s="1">
-        <v>46157.585680983793</v>
+        <v>46157.585703935183</v>
       </c>
       <c r="Q126" s="4">
         <v>46160.493105243055</v>
       </c>
       <c r="R126" s="4">
-        <v>46160.607764236112</v>
+        <v>46170.487253356485</v>
       </c>
       <c r="S126">
-        <v>8153.000</v>
+        <v>13685.000</v>
       </c>
       <c r="T126">
-        <v>8153.000</v>
+        <v>13685.000</v>
       </c>
       <c r="U126">
         <v>0</v>
@@ -7603,7 +7609,7 @@
         <v>0</v>
       </c>
       <c r="W126" s="4">
-        <v>46161.606680011573</v>
+        <v>46171.521805011573</v>
       </c>
     </row>
     <row r="127">
@@ -7620,34 +7626,34 @@
         <v>24</v>
       </c>
       <c r="E127">
-        <v>7186209</v>
+        <v>7186224</v>
       </c>
       <c r="F127" t="s">
+        <v>237</v>
+      </c>
+      <c r="G127" t="s">
+        <v>24</v>
+      </c>
+      <c r="H127" t="s">
+        <v>24</v>
+      </c>
+      <c r="M127" t="s">
         <v>236</v>
       </c>
-      <c r="G127" t="s">
-        <v>24</v>
-      </c>
-      <c r="H127" t="s">
-        <v>24</v>
-      </c>
-      <c r="M127" t="s">
-        <v>237</v>
-      </c>
       <c r="P127" s="1">
-        <v>46157.580364664354</v>
+        <v>46157.585680983793</v>
       </c>
       <c r="Q127" s="4">
-        <v>46160.367256516205</v>
+        <v>46160.493105243055</v>
       </c>
       <c r="R127" s="4">
-        <v>46160.444021875002</v>
+        <v>46160.607764236112</v>
       </c>
       <c r="S127">
-        <v>19189.000</v>
+        <v>8153.000</v>
       </c>
       <c r="T127">
-        <v>19189.000</v>
+        <v>8153.000</v>
       </c>
       <c r="U127">
         <v>0</v>
@@ -7656,7 +7662,7 @@
         <v>0</v>
       </c>
       <c r="W127" s="4">
-        <v>46161.605472025461</v>
+        <v>46161.606680011573</v>
       </c>
     </row>
     <row r="128">
@@ -7673,7 +7679,7 @@
         <v>24</v>
       </c>
       <c r="E128">
-        <v>7185903</v>
+        <v>7186209</v>
       </c>
       <c r="F128" t="s">
         <v>238</v>
@@ -7688,19 +7694,19 @@
         <v>239</v>
       </c>
       <c r="P128" s="1">
-        <v>46157.55131412037</v>
+        <v>46157.580364664354</v>
       </c>
       <c r="Q128" s="4">
-        <v>46160.493105243055</v>
+        <v>46160.367256516205</v>
       </c>
       <c r="R128" s="4">
-        <v>46160.545683645832</v>
+        <v>46160.444021875002</v>
       </c>
       <c r="S128">
-        <v>39356.000</v>
+        <v>19189.000</v>
       </c>
       <c r="T128">
-        <v>39356.000</v>
+        <v>19189.000</v>
       </c>
       <c r="U128">
         <v>0</v>
@@ -7709,7 +7715,7 @@
         <v>0</v>
       </c>
       <c r="W128" s="4">
-        <v>46161.604525312498</v>
+        <v>46161.605472025461</v>
       </c>
     </row>
     <row r="129">
@@ -7726,7 +7732,7 @@
         <v>24</v>
       </c>
       <c r="E129">
-        <v>7177836</v>
+        <v>7185903</v>
       </c>
       <c r="F129" t="s">
         <v>240</v>
@@ -7740,23 +7746,20 @@
       <c r="M129" t="s">
         <v>241</v>
       </c>
-      <c r="O129" s="4">
-        <v>46157.416666666664</v>
-      </c>
       <c r="P129" s="1">
-        <v>46155.705813773151</v>
+        <v>46157.55131412037</v>
       </c>
       <c r="Q129" s="4">
-        <v>46157.466666666667</v>
+        <v>46160.493105243055</v>
       </c>
       <c r="R129" s="4">
-        <v>46160.360912615739</v>
+        <v>46160.545683645832</v>
       </c>
       <c r="S129">
-        <v>17794.000</v>
+        <v>39356.000</v>
       </c>
       <c r="T129">
-        <v>17794.000</v>
+        <v>39356.000</v>
       </c>
       <c r="U129">
         <v>0</v>
@@ -7765,7 +7768,7 @@
         <v>0</v>
       </c>
       <c r="W129" s="4">
-        <v>46160.503910451385</v>
+        <v>46161.604525312498</v>
       </c>
     </row>
     <row r="130">
@@ -7782,7 +7785,7 @@
         <v>24</v>
       </c>
       <c r="E130">
-        <v>7175007</v>
+        <v>7177836</v>
       </c>
       <c r="F130" t="s">
         <v>242</v>
@@ -7797,22 +7800,22 @@
         <v>243</v>
       </c>
       <c r="O130" s="4">
-        <v>46157.291666666664</v>
+        <v>46157.416666666664</v>
       </c>
       <c r="P130" s="1">
-        <v>46155.454049652777</v>
+        <v>46155.705813773151</v>
       </c>
       <c r="Q130" s="4">
-        <v>46157.35833333333</v>
+        <v>46157.466666666667</v>
       </c>
       <c r="R130" s="4">
-        <v>46157.601774965275</v>
+        <v>46160.360912615739</v>
       </c>
       <c r="S130">
-        <v>21375.000</v>
+        <v>17794.000</v>
       </c>
       <c r="T130">
-        <v>21375.000</v>
+        <v>17794.000</v>
       </c>
       <c r="U130">
         <v>0</v>
@@ -7821,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="W130" s="4">
-        <v>46157.688587037039</v>
+        <v>46160.503910451385</v>
       </c>
     </row>
     <row r="131">
@@ -7838,7 +7841,7 @@
         <v>24</v>
       </c>
       <c r="E131">
-        <v>7167099</v>
+        <v>7175007</v>
       </c>
       <c r="F131" t="s">
         <v>244</v>
@@ -7852,17 +7855,23 @@
       <c r="M131" t="s">
         <v>245</v>
       </c>
+      <c r="O131" s="4">
+        <v>46157.291666666664</v>
+      </c>
       <c r="P131" s="1">
-        <v>46154.541764120368</v>
+        <v>46155.454049652777</v>
+      </c>
+      <c r="Q131" s="4">
+        <v>46157.35833333333</v>
       </c>
       <c r="R131" s="4">
-        <v>46155.643980821762</v>
+        <v>46157.601774965275</v>
       </c>
       <c r="S131">
-        <v>11855.000</v>
+        <v>21375.000</v>
       </c>
       <c r="T131">
-        <v>11855.000</v>
+        <v>21375.000</v>
       </c>
       <c r="U131">
         <v>0</v>
@@ -7871,7 +7880,7 @@
         <v>0</v>
       </c>
       <c r="W131" s="4">
-        <v>46157.304165428242</v>
+        <v>46157.688587037039</v>
       </c>
     </row>
     <row r="132">
@@ -7885,69 +7894,119 @@
         <v>24</v>
       </c>
       <c r="D132" t="s">
+        <v>24</v>
+      </c>
+      <c r="E132">
+        <v>7167099</v>
+      </c>
+      <c r="F132" t="s">
         <v>246</v>
       </c>
-      <c r="E132">
+      <c r="G132" t="s">
+        <v>24</v>
+      </c>
+      <c r="H132" t="s">
+        <v>24</v>
+      </c>
+      <c r="M132" t="s">
+        <v>247</v>
+      </c>
+      <c r="P132" s="1">
+        <v>46154.541764120368</v>
+      </c>
+      <c r="R132" s="4">
+        <v>46155.643980821762</v>
+      </c>
+      <c r="S132">
+        <v>11855.000</v>
+      </c>
+      <c r="T132">
+        <v>11855.000</v>
+      </c>
+      <c r="U132">
+        <v>0</v>
+      </c>
+      <c r="V132">
+        <v>0</v>
+      </c>
+      <c r="W132" s="4">
+        <v>46157.304165428242</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>19</v>
+      </c>
+      <c r="B133" t="s">
+        <v>24</v>
+      </c>
+      <c r="C133" t="s">
+        <v>24</v>
+      </c>
+      <c r="D133" t="s">
+        <v>248</v>
+      </c>
+      <c r="E133">
         <v>7108660</v>
       </c>
-      <c r="F132" t="s">
-        <v>247</v>
-      </c>
-      <c r="G132" t="s">
-        <v>24</v>
-      </c>
-      <c r="H132" t="s">
-        <v>248</v>
-      </c>
-      <c r="I132" t="s">
-        <v>248</v>
-      </c>
-      <c r="J132" t="s">
+      <c r="F133" t="s">
         <v>249</v>
       </c>
-      <c r="K132" t="s">
+      <c r="G133" t="s">
+        <v>24</v>
+      </c>
+      <c r="H133" t="s">
         <v>250</v>
       </c>
-      <c r="M132" t="s">
-        <v>24</v>
-      </c>
-      <c r="P132" s="1">
+      <c r="I133" t="s">
+        <v>250</v>
+      </c>
+      <c r="J133" t="s">
+        <v>251</v>
+      </c>
+      <c r="K133" t="s">
+        <v>252</v>
+      </c>
+      <c r="M133" t="s">
+        <v>24</v>
+      </c>
+      <c r="P133" s="1">
         <v>46142.678548877317</v>
       </c>
-      <c r="R132" s="4">
+      <c r="R133" s="4">
         <v>46142.683541168983</v>
       </c>
-      <c r="S132">
+      <c r="S133">
         <v>100.000</v>
       </c>
-      <c r="T132">
+      <c r="T133">
         <v>100.000</v>
       </c>
-      <c r="U132">
-        <v>0</v>
-      </c>
-      <c r="V132">
-        <v>0</v>
-      </c>
-      <c r="W132" s="4">
+      <c r="U133">
+        <v>0</v>
+      </c>
+      <c r="V133">
+        <v>0</v>
+      </c>
+      <c r="W133" s="4">
         <v>46142.68461369213</v>
       </c>
     </row>
-    <row r="133">
-      <c r="S133" s="2">
-        <f ca="1">SUM(S2:S132)</f>
-        <v>0</v>
-      </c>
-      <c r="T133" s="2">
-        <f ca="1">SUM(T2:T132)</f>
-        <v>0</v>
-      </c>
-      <c r="U133" s="2">
-        <f ca="1">SUM(U2:U132)</f>
-        <v>0</v>
-      </c>
-      <c r="V133" s="2">
-        <f ca="1">SUM(V2:V132)</f>
+    <row r="134">
+      <c r="S134" s="2">
+        <f ca="1">SUM(S2:S133)</f>
+        <v>0</v>
+      </c>
+      <c r="T134" s="2">
+        <f ca="1">SUM(T2:T133)</f>
+        <v>0</v>
+      </c>
+      <c r="U134" s="2">
+        <f ca="1">SUM(U2:U133)</f>
+        <v>0</v>
+      </c>
+      <c r="V134" s="2">
+        <f ca="1">SUM(V2:V133)</f>
         <v>0</v>
       </c>
     </row>

--- a/InOrders_latest.xlsx
+++ b/InOrders_latest.xlsx
@@ -184,34 +184,34 @@
     <t>Truck 70</t>
   </si>
   <si>
+    <t>0101883946</t>
+  </si>
+  <si>
+    <t>Truck 69</t>
+  </si>
+  <si>
+    <t>0101878070</t>
+  </si>
+  <si>
+    <t>Truck 66</t>
+  </si>
+  <si>
+    <t>0101850638</t>
+  </si>
+  <si>
+    <t>Truck 54</t>
+  </si>
+  <si>
+    <t>JohannesUPSStockUP</t>
+  </si>
+  <si>
+    <t>Johannes_Prod_Test_UPS_StockUP</t>
+  </si>
+  <si>
     <t>0101886720</t>
   </si>
   <si>
     <t>Truck 71</t>
-  </si>
-  <si>
-    <t>0101883946</t>
-  </si>
-  <si>
-    <t>Truck 69</t>
-  </si>
-  <si>
-    <t>0101878070</t>
-  </si>
-  <si>
-    <t>Truck 66</t>
-  </si>
-  <si>
-    <t>0101850638</t>
-  </si>
-  <si>
-    <t>Truck 54</t>
-  </si>
-  <si>
-    <t>JohannesUPSStockUP</t>
-  </si>
-  <si>
-    <t>Johannes_Prod_Test_UPS_StockUP</t>
   </si>
   <si>
     <t>0101878078</t>
@@ -2293,7 +2293,7 @@
         <v>24</v>
       </c>
       <c r="E24">
-        <v>7380190</v>
+        <v>7379335</v>
       </c>
       <c r="F24" t="s">
         <v>56</v>
@@ -2308,25 +2308,25 @@
         <v>57</v>
       </c>
       <c r="P24" s="1">
-        <v>46198.481004479167</v>
+        <v>46198.391359803238</v>
       </c>
       <c r="R24" s="4">
-        <v>46203.329736886575</v>
+        <v>46204.329143784722</v>
       </c>
       <c r="S24">
-        <v>9916.000</v>
+        <v>11465.000</v>
       </c>
       <c r="T24">
-        <v>9916.000</v>
+        <v>11425.000</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>40.000</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24" s="4">
-        <v>46202.447466701386</v>
+        <v>46202.445604826389</v>
       </c>
     </row>
     <row r="25">
@@ -2343,7 +2343,7 @@
         <v>24</v>
       </c>
       <c r="E25">
-        <v>7379335</v>
+        <v>7374441</v>
       </c>
       <c r="F25" t="s">
         <v>58</v>
@@ -2358,27 +2358,30 @@
         <v>59</v>
       </c>
       <c r="P25" s="1">
-        <v>46198.391359803238</v>
+        <v>46197.552075150466</v>
+      </c>
+      <c r="R25" s="4">
+        <v>46202.31123402778</v>
       </c>
       <c r="S25">
-        <v>11465.000</v>
+        <v>10194.000</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>9994.000</v>
       </c>
       <c r="U25">
-        <v>11465.000</v>
+        <v>200.000</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25" s="4">
-        <v>46202.445604826389</v>
+        <v>46199.252992164351</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -2390,7 +2393,7 @@
         <v>24</v>
       </c>
       <c r="E26">
-        <v>7374441</v>
+        <v>7349603</v>
       </c>
       <c r="F26" t="s">
         <v>60</v>
@@ -2404,26 +2407,32 @@
       <c r="M26" t="s">
         <v>61</v>
       </c>
+      <c r="N26" s="1">
+        <v>46190</v>
+      </c>
       <c r="P26" s="1">
-        <v>46197.552075150466</v>
+        <v>46189.643392094906</v>
+      </c>
+      <c r="Q26" s="4">
+        <v>46190.996527777781</v>
       </c>
       <c r="R26" s="4">
-        <v>46202.31123402778</v>
+        <v>46190.579668171296</v>
       </c>
       <c r="S26">
-        <v>10194.000</v>
+        <v>5965.000</v>
       </c>
       <c r="T26">
-        <v>9994.000</v>
+        <v>5965.000</v>
       </c>
       <c r="U26">
-        <v>200.000</v>
+        <v>0</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26" s="4">
-        <v>46199.252992164351</v>
+        <v>46191.313541932868</v>
       </c>
     </row>
     <row r="27">
@@ -2440,7 +2449,7 @@
         <v>24</v>
       </c>
       <c r="E27">
-        <v>7349603</v>
+        <v>7166305</v>
       </c>
       <c r="F27" t="s">
         <v>62</v>
@@ -2455,31 +2464,31 @@
         <v>63</v>
       </c>
       <c r="N27" s="1">
-        <v>46190</v>
+        <v>46152</v>
       </c>
       <c r="P27" s="1">
-        <v>46189.643392094906</v>
+        <v>46154.508897418978</v>
       </c>
       <c r="Q27" s="4">
-        <v>46190.996527777781</v>
+        <v>46162.29583333333</v>
       </c>
       <c r="R27" s="4">
-        <v>46190.579668171296</v>
+        <v>46154.512428125003</v>
       </c>
       <c r="S27">
-        <v>5965.000</v>
+        <v>100.000</v>
       </c>
       <c r="T27">
-        <v>5965.000</v>
+        <v>98.000</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.000</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27" s="4">
-        <v>46191.313541932868</v>
+        <v>46190.318931481481</v>
       </c>
     </row>
     <row r="28">
@@ -2496,7 +2505,7 @@
         <v>24</v>
       </c>
       <c r="E28">
-        <v>7166305</v>
+        <v>7380190</v>
       </c>
       <c r="F28" t="s">
         <v>64</v>
@@ -2510,32 +2519,26 @@
       <c r="M28" t="s">
         <v>65</v>
       </c>
-      <c r="N28" s="1">
-        <v>46152</v>
-      </c>
       <c r="P28" s="1">
-        <v>46154.508897418978</v>
-      </c>
-      <c r="Q28" s="4">
-        <v>46162.29583333333</v>
+        <v>46198.481004479167</v>
       </c>
       <c r="R28" s="4">
-        <v>46154.512428125003</v>
+        <v>46203.329736886575</v>
       </c>
       <c r="S28">
-        <v>100.000</v>
+        <v>9916.000</v>
       </c>
       <c r="T28">
-        <v>98.000</v>
+        <v>9916.000</v>
       </c>
       <c r="U28">
-        <v>2.000</v>
+        <v>0</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28" s="4">
-        <v>46190.318931481481</v>
+        <v>46203.509567858797</v>
       </c>
     </row>
     <row r="29">
